--- a/data/derived/todaysdeal-analysis.xlsx
+++ b/data/derived/todaysdeal-analysis.xlsx
@@ -57,12 +57,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:E126"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -86,6 +87,11 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -102,6 +108,9 @@
       <c r="D2" s="2">
         <v>0</v>
       </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -118,6 +127,9 @@
       <c r="D3" s="2">
         <v>1</v>
       </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -134,6 +146,9 @@
       <c r="D4" s="2">
         <v>0</v>
       </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -150,27 +165,33 @@
       <c r="D5" s="2">
         <v>0</v>
       </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>100208089</t>
+          <t>100187146</t>
         </is>
       </c>
       <c r="B6" s="2">
         <v>0</v>
       </c>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>100262120</t>
+          <t>100208089</t>
         </is>
       </c>
       <c r="B7" s="2">
@@ -180,13 +201,16 @@
         <v>1</v>
       </c>
       <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>100265766</t>
+          <t>100262120</t>
         </is>
       </c>
       <c r="B8" s="2">
@@ -196,13 +220,16 @@
         <v>1</v>
       </c>
       <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>100274539</t>
+          <t>100265766</t>
         </is>
       </c>
       <c r="B9" s="2">
@@ -212,45 +239,54 @@
         <v>1</v>
       </c>
       <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>100292269</t>
+          <t>100274539</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>100292757</t>
+          <t>100292269</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>100305602</t>
+          <t>100292757</t>
         </is>
       </c>
       <c r="B12" s="2">
@@ -260,13 +296,16 @@
         <v>1</v>
       </c>
       <c r="D12" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>100326348</t>
+          <t>100305602</t>
         </is>
       </c>
       <c r="B13" s="2">
@@ -276,93 +315,111 @@
         <v>1</v>
       </c>
       <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>100327929</t>
+          <t>100326348</t>
         </is>
       </c>
       <c r="B14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>100340418</t>
+          <t>100327929</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="2">
         <v>0</v>
       </c>
       <c r="D15" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>100387111</t>
+          <t>100336563</t>
         </is>
       </c>
       <c r="B16" s="2">
         <v>0</v>
       </c>
       <c r="C16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>100458264</t>
+          <t>100340418</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" s="2">
         <v>0</v>
       </c>
       <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>100474685</t>
+          <t>100387111</t>
         </is>
       </c>
       <c r="B18" s="2">
         <v>0</v>
       </c>
       <c r="C18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>100492521</t>
+          <t>100419781</t>
         </is>
       </c>
       <c r="B19" s="2">
@@ -372,13 +429,16 @@
         <v>0</v>
       </c>
       <c r="D19" s="2">
+        <v>0</v>
+      </c>
+      <c r="E19" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>100542499</t>
+          <t>100449422</t>
         </is>
       </c>
       <c r="B20" s="2">
@@ -388,77 +448,92 @@
         <v>0</v>
       </c>
       <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>100587614</t>
+          <t>100458264</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" s="2">
         <v>0</v>
       </c>
       <c r="D21" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>100596797</t>
+          <t>100474685</t>
         </is>
       </c>
       <c r="B22" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C22" s="2">
         <v>0</v>
       </c>
       <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>100627146</t>
+          <t>100492521</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" s="2">
         <v>0</v>
       </c>
       <c r="D23" s="2">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>100650054</t>
+          <t>100503327</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" s="2">
         <v>0</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>100752133</t>
+          <t>100542499</t>
         </is>
       </c>
       <c r="B25" s="2">
@@ -469,28 +544,34 @@
       </c>
       <c r="D25" s="2">
         <v>1</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>100770404</t>
+          <t>100586493</t>
         </is>
       </c>
       <c r="B26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" s="2">
         <v>0</v>
       </c>
       <c r="D26" s="2">
         <v>0</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>100774355</t>
+          <t>100587614</t>
         </is>
       </c>
       <c r="B27" s="2">
@@ -501,108 +582,129 @@
       </c>
       <c r="D27" s="2">
         <v>1</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>100791832</t>
+          <t>100596797</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C28" s="2">
         <v>0</v>
       </c>
       <c r="D28" s="2">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>100823000</t>
+          <t>100627146</t>
         </is>
       </c>
       <c r="B29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" s="2">
         <v>0</v>
       </c>
       <c r="D29" s="2">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>100827249</t>
+          <t>100650054</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" s="2">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>100864321</t>
+          <t>100730113</t>
         </is>
       </c>
       <c r="B31" s="2">
         <v>0</v>
       </c>
       <c r="C31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>100888704</t>
+          <t>100752133</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
       </c>
       <c r="D32" s="2">
+        <v>1</v>
+      </c>
+      <c r="E32" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>100955968</t>
+          <t>100770404</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>100972973</t>
+          <t>100774355</t>
         </is>
       </c>
       <c r="B34" s="2">
@@ -613,28 +715,34 @@
       </c>
       <c r="D34" s="2">
         <v>1</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>101037405</t>
+          <t>100791832</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
       </c>
       <c r="D35" s="2">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="E35" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>101111804</t>
+          <t>100823000</t>
         </is>
       </c>
       <c r="B36" s="2">
@@ -644,93 +752,111 @@
         <v>0</v>
       </c>
       <c r="D36" s="2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>101161925</t>
+          <t>100827249</t>
         </is>
       </c>
       <c r="B37" s="2">
         <v>0</v>
       </c>
       <c r="C37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>101195987</t>
+          <t>100862614</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
       </c>
       <c r="D38" s="2">
         <v>0</v>
+      </c>
+      <c r="E38" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>101232925</t>
+          <t>100864321</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39" s="2">
+        <v>0</v>
+      </c>
+      <c r="E39" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>101295037</t>
+          <t>100888704</t>
         </is>
       </c>
       <c r="B40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" s="2">
+        <v>0</v>
+      </c>
+      <c r="E40" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>101372175</t>
+          <t>100955968</t>
         </is>
       </c>
       <c r="B41" s="2">
         <v>0</v>
       </c>
       <c r="C41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>101396394</t>
+          <t>100972973</t>
         </is>
       </c>
       <c r="B42" s="2">
@@ -741,220 +867,262 @@
       </c>
       <c r="D42" s="2">
         <v>1</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>101434241</t>
+          <t>101034585</t>
         </is>
       </c>
       <c r="B43" s="2">
         <v>0</v>
       </c>
       <c r="C43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>101437685</t>
+          <t>101037405</t>
         </is>
       </c>
       <c r="B44" s="2">
         <v>1</v>
       </c>
       <c r="C44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="2">
+        <v>0</v>
+      </c>
+      <c r="E44" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>101467964</t>
+          <t>101102225</t>
         </is>
       </c>
       <c r="B45" s="2">
         <v>0</v>
       </c>
       <c r="C45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" s="2">
         <v>0</v>
+      </c>
+      <c r="E45" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>101481537</t>
+          <t>101111804</t>
         </is>
       </c>
       <c r="B46" s="2">
         <v>0</v>
       </c>
       <c r="C46" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" s="2">
+        <v>1</v>
+      </c>
+      <c r="E46" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>101509593</t>
+          <t>101161925</t>
         </is>
       </c>
       <c r="B47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47" s="2">
         <v>0</v>
       </c>
       <c r="D47" s="2">
+        <v>1</v>
+      </c>
+      <c r="E47" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>101573499</t>
+          <t>101174078</t>
         </is>
       </c>
       <c r="B48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
       </c>
       <c r="D48" s="2">
         <v>0</v>
+      </c>
+      <c r="E48" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>101836491</t>
+          <t>101195987</t>
         </is>
       </c>
       <c r="B49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" s="2">
+        <v>0</v>
+      </c>
+      <c r="E49" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>101863433</t>
+          <t>101232925</t>
         </is>
       </c>
       <c r="B50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50" s="2">
+        <v>0</v>
+      </c>
+      <c r="E50" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>101885140</t>
+          <t>101295037</t>
         </is>
       </c>
       <c r="B51" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" s="2">
+        <v>0</v>
+      </c>
+      <c r="E51" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>101888773</t>
+          <t>101336693</t>
         </is>
       </c>
       <c r="B52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52" s="2">
         <v>0</v>
+      </c>
+      <c r="E52" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>102006080</t>
+          <t>101372175</t>
         </is>
       </c>
       <c r="B53" s="2">
         <v>0</v>
       </c>
       <c r="C53" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" s="2">
         <v>1</v>
+      </c>
+      <c r="E53" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>102006845</t>
+          <t>101396394</t>
         </is>
       </c>
       <c r="B54" s="2">
         <v>0</v>
       </c>
       <c r="C54" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54" s="2">
+        <v>1</v>
+      </c>
+      <c r="E54" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>102227253</t>
+          <t>101407817</t>
         </is>
       </c>
       <c r="B55" s="2">
         <v>0</v>
       </c>
       <c r="C55" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55" s="2">
         <v>0</v>
+      </c>
+      <c r="E55" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>102299090</t>
+          <t>101434241</t>
         </is>
       </c>
       <c r="B56" s="2">
@@ -964,29 +1132,35 @@
         <v>1</v>
       </c>
       <c r="D56" s="2">
+        <v>0</v>
+      </c>
+      <c r="E56" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>102307203</t>
+          <t>101437685</t>
         </is>
       </c>
       <c r="B57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E57" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>102375097</t>
+          <t>101467964</t>
         </is>
       </c>
       <c r="B58" s="2">
@@ -996,29 +1170,35 @@
         <v>1</v>
       </c>
       <c r="D58" s="2">
+        <v>0</v>
+      </c>
+      <c r="E58" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>102454744</t>
+          <t>101481537</t>
         </is>
       </c>
       <c r="B59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59" s="2">
+        <v>0</v>
+      </c>
+      <c r="E59" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>102497144</t>
+          <t>101509593</t>
         </is>
       </c>
       <c r="B60" s="2">
@@ -1028,13 +1208,16 @@
         <v>0</v>
       </c>
       <c r="D60" s="2">
+        <v>0</v>
+      </c>
+      <c r="E60" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>102600124</t>
+          <t>101573499</t>
         </is>
       </c>
       <c r="B61" s="2">
@@ -1044,45 +1227,54 @@
         <v>0</v>
       </c>
       <c r="D61" s="2">
+        <v>0</v>
+      </c>
+      <c r="E61" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>102655931</t>
+          <t>101836491</t>
         </is>
       </c>
       <c r="B62" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C62" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" s="2">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="E62" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>102673781</t>
+          <t>101863433</t>
         </is>
       </c>
       <c r="B63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C63" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E63" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>102690829</t>
+          <t>101875176</t>
         </is>
       </c>
       <c r="B64" s="2">
@@ -1092,13 +1284,16 @@
         <v>0</v>
       </c>
       <c r="D64" s="2">
+        <v>0</v>
+      </c>
+      <c r="E64" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>102698382</t>
+          <t>101885140</t>
         </is>
       </c>
       <c r="B65" s="2">
@@ -1108,29 +1303,35 @@
         <v>0</v>
       </c>
       <c r="D65" s="2">
+        <v>0</v>
+      </c>
+      <c r="E65" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>102705657</t>
+          <t>101888773</t>
         </is>
       </c>
       <c r="B66" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E66" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>102748593</t>
+          <t>102006080</t>
         </is>
       </c>
       <c r="B67" s="2">
@@ -1140,45 +1341,54 @@
         <v>1</v>
       </c>
       <c r="D67" s="2">
+        <v>1</v>
+      </c>
+      <c r="E67" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1100079588</t>
+          <t>102006845</t>
         </is>
       </c>
       <c r="B68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68" s="2">
+        <v>0</v>
+      </c>
+      <c r="E68" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>500000823</t>
+          <t>102050130</t>
         </is>
       </c>
       <c r="B69" s="2">
         <v>0</v>
       </c>
       <c r="C69" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69" s="2">
         <v>0</v>
+      </c>
+      <c r="E69" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>500000921</t>
+          <t>102109244</t>
         </is>
       </c>
       <c r="B70" s="2">
@@ -1188,29 +1398,35 @@
         <v>0</v>
       </c>
       <c r="D70" s="2">
+        <v>0</v>
+      </c>
+      <c r="E70" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>500003288</t>
+          <t>102203438</t>
         </is>
       </c>
       <c r="B71" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C71" s="2">
         <v>0</v>
       </c>
       <c r="D71" s="2">
         <v>0</v>
+      </c>
+      <c r="E71" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>500003682</t>
+          <t>102227253</t>
         </is>
       </c>
       <c r="B72" s="2">
@@ -1220,109 +1436,130 @@
         <v>1</v>
       </c>
       <c r="D72" s="2">
+        <v>0</v>
+      </c>
+      <c r="E72" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>500009413</t>
+          <t>102282059</t>
         </is>
       </c>
       <c r="B73" s="2">
         <v>0</v>
       </c>
       <c r="C73" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73" s="2">
         <v>0</v>
+      </c>
+      <c r="E73" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>500016197</t>
+          <t>102299090</t>
         </is>
       </c>
       <c r="B74" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C74" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74" s="2">
+        <v>0</v>
+      </c>
+      <c r="E74" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>500023997</t>
+          <t>102307203</t>
         </is>
       </c>
       <c r="B75" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" s="2">
         <v>0</v>
       </c>
       <c r="D75" s="2">
+        <v>1</v>
+      </c>
+      <c r="E75" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>500024124</t>
+          <t>102375097</t>
         </is>
       </c>
       <c r="B76" s="2">
         <v>0</v>
       </c>
       <c r="C76" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D76" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E76" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>500028485</t>
+          <t>102454744</t>
         </is>
       </c>
       <c r="B77" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C77" s="2">
         <v>0</v>
       </c>
       <c r="D77" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E77" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>500031276</t>
+          <t>102497144</t>
         </is>
       </c>
       <c r="B78" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78" s="2">
+        <v>0</v>
+      </c>
+      <c r="E78" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>500032408</t>
+          <t>102600124</t>
         </is>
       </c>
       <c r="B79" s="2">
@@ -1332,29 +1569,35 @@
         <v>0</v>
       </c>
       <c r="D79" s="2">
+        <v>0</v>
+      </c>
+      <c r="E79" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>500035796</t>
+          <t>102655931</t>
         </is>
       </c>
       <c r="B80" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C80" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D80" s="2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E80" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>500036672</t>
+          <t>102673781</t>
         </is>
       </c>
       <c r="B81" s="2">
@@ -1364,77 +1607,92 @@
         <v>0</v>
       </c>
       <c r="D81" s="2">
+        <v>1</v>
+      </c>
+      <c r="E81" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>500052051</t>
+          <t>102690829</t>
         </is>
       </c>
       <c r="B82" s="2">
         <v>0</v>
       </c>
       <c r="C82" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D82" s="2">
+        <v>1</v>
+      </c>
+      <c r="E82" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>500057619</t>
+          <t>102698382</t>
         </is>
       </c>
       <c r="B83" s="2">
         <v>1</v>
       </c>
       <c r="C83" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83" s="2">
+        <v>0</v>
+      </c>
+      <c r="E83" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>500060661</t>
+          <t>102705657</t>
         </is>
       </c>
       <c r="B84" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C84" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D84" s="2">
+        <v>1</v>
+      </c>
+      <c r="E84" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>500061708</t>
+          <t>102748593</t>
         </is>
       </c>
       <c r="B85" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C85" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E85" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>500094507</t>
+          <t>102793147</t>
         </is>
       </c>
       <c r="B86" s="2">
@@ -1444,45 +1702,54 @@
         <v>0</v>
       </c>
       <c r="D86" s="2">
+        <v>0</v>
+      </c>
+      <c r="E86" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>500111404</t>
+          <t>1100079588</t>
         </is>
       </c>
       <c r="B87" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C87" s="2">
         <v>0</v>
       </c>
       <c r="D87" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E87" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>500115640</t>
+          <t>500000823</t>
         </is>
       </c>
       <c r="B88" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C88" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88" s="2">
+        <v>0</v>
+      </c>
+      <c r="E88" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>500117284</t>
+          <t>500000921</t>
         </is>
       </c>
       <c r="B89" s="2">
@@ -1493,44 +1760,53 @@
       </c>
       <c r="D89" s="2">
         <v>1</v>
+      </c>
+      <c r="E89" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>500120216</t>
+          <t>500002685</t>
         </is>
       </c>
       <c r="B90" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C90" s="2">
         <v>0</v>
       </c>
       <c r="D90" s="2">
+        <v>0</v>
+      </c>
+      <c r="E90" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>500126621</t>
+          <t>500003288</t>
         </is>
       </c>
       <c r="B91" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C91" s="2">
         <v>0</v>
       </c>
       <c r="D91" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E91" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>500143502</t>
+          <t>500003682</t>
         </is>
       </c>
       <c r="B92" s="2">
@@ -1541,28 +1817,34 @@
       </c>
       <c r="D92" s="2">
         <v>0</v>
+      </c>
+      <c r="E92" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>500143882</t>
+          <t>500009413</t>
         </is>
       </c>
       <c r="B93" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93" s="2">
         <v>0</v>
+      </c>
+      <c r="E93" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>500146800</t>
+          <t>500016197</t>
         </is>
       </c>
       <c r="B94" s="2">
@@ -1572,77 +1854,92 @@
         <v>0</v>
       </c>
       <c r="D94" s="2">
+        <v>0</v>
+      </c>
+      <c r="E94" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>500185891</t>
+          <t>500020789</t>
         </is>
       </c>
       <c r="B95" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C95" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D95" s="2">
         <v>0</v>
+      </c>
+      <c r="E95" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>500187931</t>
+          <t>500023997</t>
         </is>
       </c>
       <c r="B96" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C96" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96" s="2">
+        <v>0</v>
+      </c>
+      <c r="E96" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>500211718</t>
+          <t>500024124</t>
         </is>
       </c>
       <c r="B97" s="2">
         <v>0</v>
       </c>
       <c r="C97" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97" s="2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E97" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>500217683</t>
+          <t>500028485</t>
         </is>
       </c>
       <c r="B98" s="2">
         <v>0</v>
       </c>
       <c r="C98" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98" s="2">
         <v>1</v>
+      </c>
+      <c r="E98" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>500236829</t>
+          <t>500031276</t>
         </is>
       </c>
       <c r="B99" s="2">
@@ -1652,13 +1949,16 @@
         <v>1</v>
       </c>
       <c r="D99" s="2">
+        <v>0</v>
+      </c>
+      <c r="E99" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>500240447</t>
+          <t>500032408</t>
         </is>
       </c>
       <c r="B100" s="2">
@@ -1668,49 +1968,514 @@
         <v>0</v>
       </c>
       <c r="D100" s="2">
+        <v>0</v>
+      </c>
+      <c r="E100" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>500241388</t>
+          <t>500035796</t>
         </is>
       </c>
       <c r="B101" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C101" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D101" s="2">
+        <v>1</v>
+      </c>
+      <c r="E101" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>500036672</t>
+        </is>
+      </c>
+      <c r="B102" s="2">
+        <v>1</v>
+      </c>
+      <c r="C102" s="2">
+        <v>0</v>
+      </c>
+      <c r="D102" s="2">
+        <v>0</v>
+      </c>
+      <c r="E102" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>500037006</t>
+        </is>
+      </c>
+      <c r="B103" s="2">
+        <v>0</v>
+      </c>
+      <c r="C103" s="2">
+        <v>0</v>
+      </c>
+      <c r="D103" s="2">
+        <v>0</v>
+      </c>
+      <c r="E103" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>500052051</t>
+        </is>
+      </c>
+      <c r="B104" s="2">
+        <v>0</v>
+      </c>
+      <c r="C104" s="2">
+        <v>1</v>
+      </c>
+      <c r="D104" s="2">
+        <v>0</v>
+      </c>
+      <c r="E104" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>500057619</t>
+        </is>
+      </c>
+      <c r="B105" s="2">
+        <v>1</v>
+      </c>
+      <c r="C105" s="2">
+        <v>1</v>
+      </c>
+      <c r="D105" s="2">
+        <v>0</v>
+      </c>
+      <c r="E105" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>500060661</t>
+        </is>
+      </c>
+      <c r="B106" s="2">
+        <v>1</v>
+      </c>
+      <c r="C106" s="2">
+        <v>1</v>
+      </c>
+      <c r="D106" s="2">
+        <v>0</v>
+      </c>
+      <c r="E106" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>500061708</t>
+        </is>
+      </c>
+      <c r="B107" s="2">
+        <v>1</v>
+      </c>
+      <c r="C107" s="2">
+        <v>0</v>
+      </c>
+      <c r="D107" s="2">
+        <v>1</v>
+      </c>
+      <c r="E107" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>500094507</t>
+        </is>
+      </c>
+      <c r="B108" s="2">
+        <v>0</v>
+      </c>
+      <c r="C108" s="2">
+        <v>0</v>
+      </c>
+      <c r="D108" s="2">
+        <v>1</v>
+      </c>
+      <c r="E108" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>500111404</t>
+        </is>
+      </c>
+      <c r="B109" s="2">
+        <v>0</v>
+      </c>
+      <c r="C109" s="2">
+        <v>0</v>
+      </c>
+      <c r="D109" s="2">
+        <v>1</v>
+      </c>
+      <c r="E109" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>500115640</t>
+        </is>
+      </c>
+      <c r="B110" s="2">
+        <v>1</v>
+      </c>
+      <c r="C110" s="2">
+        <v>0</v>
+      </c>
+      <c r="D110" s="2">
+        <v>0</v>
+      </c>
+      <c r="E110" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>500117284</t>
+        </is>
+      </c>
+      <c r="B111" s="2">
+        <v>0</v>
+      </c>
+      <c r="C111" s="2">
+        <v>0</v>
+      </c>
+      <c r="D111" s="2">
+        <v>1</v>
+      </c>
+      <c r="E111" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>500120216</t>
+        </is>
+      </c>
+      <c r="B112" s="2">
+        <v>1</v>
+      </c>
+      <c r="C112" s="2">
+        <v>0</v>
+      </c>
+      <c r="D112" s="2">
+        <v>1</v>
+      </c>
+      <c r="E112" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>500126621</t>
+        </is>
+      </c>
+      <c r="B113" s="2">
+        <v>0</v>
+      </c>
+      <c r="C113" s="2">
+        <v>0</v>
+      </c>
+      <c r="D113" s="2">
+        <v>1</v>
+      </c>
+      <c r="E113" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>500143502</t>
+        </is>
+      </c>
+      <c r="B114" s="2">
+        <v>0</v>
+      </c>
+      <c r="C114" s="2">
+        <v>1</v>
+      </c>
+      <c r="D114" s="2">
+        <v>0</v>
+      </c>
+      <c r="E114" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>500143882</t>
+        </is>
+      </c>
+      <c r="B115" s="2">
+        <v>1</v>
+      </c>
+      <c r="C115" s="2">
+        <v>0</v>
+      </c>
+      <c r="D115" s="2">
+        <v>0</v>
+      </c>
+      <c r="E115" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>500146800</t>
+        </is>
+      </c>
+      <c r="B116" s="2">
+        <v>1</v>
+      </c>
+      <c r="C116" s="2">
+        <v>0</v>
+      </c>
+      <c r="D116" s="2">
+        <v>0</v>
+      </c>
+      <c r="E116" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>500185891</t>
+        </is>
+      </c>
+      <c r="B117" s="2">
+        <v>1</v>
+      </c>
+      <c r="C117" s="2">
+        <v>1</v>
+      </c>
+      <c r="D117" s="2">
+        <v>0</v>
+      </c>
+      <c r="E117" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>500187931</t>
+        </is>
+      </c>
+      <c r="B118" s="2">
+        <v>0</v>
+      </c>
+      <c r="C118" s="2">
+        <v>1</v>
+      </c>
+      <c r="D118" s="2">
+        <v>0</v>
+      </c>
+      <c r="E118" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>500211718</t>
+        </is>
+      </c>
+      <c r="B119" s="2">
+        <v>0</v>
+      </c>
+      <c r="C119" s="2">
+        <v>1</v>
+      </c>
+      <c r="D119" s="2">
+        <v>2</v>
+      </c>
+      <c r="E119" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>500217683</t>
+        </is>
+      </c>
+      <c r="B120" s="2">
+        <v>0</v>
+      </c>
+      <c r="C120" s="2">
+        <v>1</v>
+      </c>
+      <c r="D120" s="2">
+        <v>1</v>
+      </c>
+      <c r="E120" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>500236829</t>
+        </is>
+      </c>
+      <c r="B121" s="2">
+        <v>0</v>
+      </c>
+      <c r="C121" s="2">
+        <v>1</v>
+      </c>
+      <c r="D121" s="2">
+        <v>0</v>
+      </c>
+      <c r="E121" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>500240447</t>
+        </is>
+      </c>
+      <c r="B122" s="2">
+        <v>1</v>
+      </c>
+      <c r="C122" s="2">
+        <v>0</v>
+      </c>
+      <c r="D122" s="2">
+        <v>0</v>
+      </c>
+      <c r="E122" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>500241388</t>
+        </is>
+      </c>
+      <c r="B123" s="2">
+        <v>1</v>
+      </c>
+      <c r="C123" s="2">
+        <v>1</v>
+      </c>
+      <c r="D123" s="2">
+        <v>0</v>
+      </c>
+      <c r="E123" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
           <t>500255345</t>
         </is>
       </c>
-      <c r="B102" s="2">
-        <v>1</v>
-      </c>
-      <c r="C102" s="2">
-        <v>0</v>
-      </c>
-      <c r="D102" s="2">
-        <v>0</v>
+      <c r="B124" s="2">
+        <v>1</v>
+      </c>
+      <c r="C124" s="2">
+        <v>0</v>
+      </c>
+      <c r="D124" s="2">
+        <v>0</v>
+      </c>
+      <c r="E124" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>500258101</t>
+        </is>
+      </c>
+      <c r="B125" s="2">
+        <v>0</v>
+      </c>
+      <c r="C125" s="2">
+        <v>0</v>
+      </c>
+      <c r="D125" s="2">
+        <v>0</v>
+      </c>
+      <c r="E125" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>500272158</t>
+        </is>
+      </c>
+      <c r="B126" s="2">
+        <v>0</v>
+      </c>
+      <c r="C126" s="2">
+        <v>0</v>
+      </c>
+      <c r="D126" s="2">
+        <v>0</v>
+      </c>
+      <c r="E126" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D102"/>
+  <autoFilter ref="A1:E126"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q127"/>
+  <dimension ref="A1:Q164"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -11016,7 +11781,2708 @@
         <v>0.19</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>100146361</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>8346122966</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>국내산 100% 비비고 베이직 배추 포기김치 10kg, 1개</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G128" s="2">
+        <v>59900</v>
+      </c>
+      <c r="H128" s="2">
+        <v>74900</v>
+      </c>
+      <c r="I128" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/8346122966</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251017_138/1760661612141VJFt0_JPEG/2475005958370691_957401126.jpg</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N128" s="2">
+        <v>1</v>
+      </c>
+      <c r="O128" s="2">
+        <v>0</v>
+      </c>
+      <c r="P128" s="2">
+        <v>59900</v>
+      </c>
+      <c r="Q128" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>100187146</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>12673036936</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>살림의기술 실내 화장실 실발장 거실 냄새 제거 고체 탈취제 4개</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G129" s="2">
+        <v>48900</v>
+      </c>
+      <c r="H129" s="2">
+        <v>67600</v>
+      </c>
+      <c r="I129" s="3">
+        <v>0.27</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12673036936</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251113_145/1763025503784EaqFX_JPEG/97158480983360721_1925335750.jpg</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N129" s="2">
+        <v>1</v>
+      </c>
+      <c r="O129" s="2">
+        <v>0</v>
+      </c>
+      <c r="P129" s="2">
+        <v>48900</v>
+      </c>
+      <c r="Q129" s="3">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>100336563</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>7109327784</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>패밀리10포+ 비오비타 패밀리 유산균 낙산균 60포, 3개</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G130" s="2">
+        <v>50900</v>
+      </c>
+      <c r="H130" s="2">
+        <v>114000</v>
+      </c>
+      <c r="I130" s="3">
+        <v>0.55</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/7109327784</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260310_221/1773131911748gnDvb_JPEG/107264743865759182_831531806.jpg</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N130" s="2">
+        <v>1</v>
+      </c>
+      <c r="O130" s="2">
+        <v>0</v>
+      </c>
+      <c r="P130" s="2">
+        <v>50900</v>
+      </c>
+      <c r="Q130" s="3">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>100419781</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>12701437696</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>한우대창과 소내장을 푸짐하게 넣은 한우대창전골 1kg</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G131" s="2">
+        <v>9900</v>
+      </c>
+      <c r="H131" s="2">
+        <v>14500</v>
+      </c>
+      <c r="I131" s="3">
+        <v>0.31</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12701437696</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260106_138/1767702786057jFy4X_PNG/12201782966015439_1519739616.png</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N131" s="2">
+        <v>1</v>
+      </c>
+      <c r="O131" s="2">
+        <v>0</v>
+      </c>
+      <c r="P131" s="2">
+        <v>9900</v>
+      </c>
+      <c r="Q131" s="3">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>100449422</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>6663938938</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>[성경김본사] 지도표 맛난김 4g 12봉 x 4개 (총48봉) - 재래김 도시락김</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G132" s="2">
+        <v>16700</v>
+      </c>
+      <c r="H132" s="2">
+        <v>32000</v>
+      </c>
+      <c r="I132" s="3">
+        <v>0.47</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/6663938938</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20240812_229/1723426017896Ttd3V_JPEG/5156332697564351_15104990.jpg</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N132" s="2">
+        <v>1</v>
+      </c>
+      <c r="O132" s="2">
+        <v>0</v>
+      </c>
+      <c r="P132" s="2">
+        <v>16700</v>
+      </c>
+      <c r="Q132" s="3">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>100503327</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>6420055057</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>프레시누리 청정우 차돌박이(3초구이 샤브용) 250gX4팩</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G133" s="2">
+        <v>21300</v>
+      </c>
+      <c r="H133" s="2">
+        <v>25300</v>
+      </c>
+      <c r="I133" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/6420055057</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250703_107/1751489978831WOKBs_JPEG/85622849904601544_1800188648.jpg</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N133" s="2">
+        <v>1</v>
+      </c>
+      <c r="O133" s="2">
+        <v>0</v>
+      </c>
+      <c r="P133" s="2">
+        <v>21300</v>
+      </c>
+      <c r="Q133" s="3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>100586493</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>10566130307</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>[슈퍼적립] 스타벅스 프리미엄 스틱커피 미디엄로스트 100입+10입</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G134" s="2">
+        <v>36980</v>
+      </c>
+      <c r="H134" s="2">
+        <v>46900</v>
+      </c>
+      <c r="I134" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10566130307</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251209_146/1765280697650BOjG1_JPEG/100013356627118451_1909678785.jpg</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N134" s="2">
+        <v>1</v>
+      </c>
+      <c r="O134" s="2">
+        <v>0</v>
+      </c>
+      <c r="P134" s="2">
+        <v>36980</v>
+      </c>
+      <c r="Q134" s="3">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>100730113</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>5636612081</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>한우 선물 세트 1등급 소고기 구이용 설 추석 명절 어버이날 부모님</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G135" s="2">
+        <v>118000</v>
+      </c>
+      <c r="H135" s="2">
+        <v>235000</v>
+      </c>
+      <c r="I135" s="3">
+        <v>0.49</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5636612081</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260109_155/1767924256286cgNU7_JPEG/81413514610624960_531801502.jpg</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N135" s="2">
+        <v>1</v>
+      </c>
+      <c r="O135" s="2">
+        <v>0</v>
+      </c>
+      <c r="P135" s="2">
+        <v>118000</v>
+      </c>
+      <c r="Q135" s="3">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>100791832</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>7490520825</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>[내일배송] 신세계푸드 올반인생 왕교자 210g 5+5 (총10봉)</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G136" s="2">
+        <v>17900</v>
+      </c>
+      <c r="H136" s="2">
+        <v>30900</v>
+      </c>
+      <c r="I136" s="3">
+        <v>0.42</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/7490520825</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20230428_207/1682665478561uwmDN_JPEG/485586410367415_11628555.jpg</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N136" s="2">
+        <v>1</v>
+      </c>
+      <c r="O136" s="2">
+        <v>0</v>
+      </c>
+      <c r="P136" s="2">
+        <v>17900</v>
+      </c>
+      <c r="Q136" s="3">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>100827249</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>10592567505</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>[손상모발용][헤어에센스] 케라스타즈 시몽 테르미크 열보호 노워시 트리트먼트 150ml</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G137" s="2">
+        <v>56950</v>
+      </c>
+      <c r="H137" s="2">
+        <v>67000</v>
+      </c>
+      <c r="I137" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10592567505</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20240914_269/1726242290817uelzk_PNG/60375115002559847_380754954.png</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N137" s="2">
+        <v>1</v>
+      </c>
+      <c r="O137" s="2">
+        <v>0</v>
+      </c>
+      <c r="P137" s="2">
+        <v>56950</v>
+      </c>
+      <c r="Q137" s="3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>100862614</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>10258856820</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>익스트림 남성 올인원 영양제 멀티 종합 비타민 멀티팩 포맨 30포, 1개</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>뷰티/헬스</t>
+        </is>
+      </c>
+      <c r="G138" s="2">
+        <v>30900</v>
+      </c>
+      <c r="H138" s="2">
+        <v>50000</v>
+      </c>
+      <c r="I138" s="3">
+        <v>0.38</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10258856820</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260105_94/1767593043956huFQ4_JPEG/49292610638609588_1989289251.jpg</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N138" s="2">
+        <v>1</v>
+      </c>
+      <c r="O138" s="2">
+        <v>0</v>
+      </c>
+      <c r="P138" s="2">
+        <v>30900</v>
+      </c>
+      <c r="Q138" s="3">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>101034585</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>10961903874</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>[슈퍼적립] LED 귀이개 귀지 핀셋 귀파개 집게 귀후비개 제거 귀집게 청소</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>생활/주방</t>
+        </is>
+      </c>
+      <c r="G139" s="2">
+        <v>5090</v>
+      </c>
+      <c r="H139" s="2">
+        <v>12000</v>
+      </c>
+      <c r="I139" s="3">
+        <v>0.57</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10961903874</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260401_81/1775004316919g2Tdu_JPEG/20961390736367296_1155238884.jpg</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N139" s="2">
+        <v>1</v>
+      </c>
+      <c r="O139" s="2">
+        <v>0</v>
+      </c>
+      <c r="P139" s="2">
+        <v>5090</v>
+      </c>
+      <c r="Q139" s="3">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>101102225</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>5940546015</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>건국우유 건국 착한목장 소화가 잘되는 멸균우유 190ml 48팩</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G140" s="2">
+        <v>28900</v>
+      </c>
+      <c r="H140" s="2">
+        <v>56000</v>
+      </c>
+      <c r="I140" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5940546015</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251211_119/1765442298500rsI3l_PNG/2659081324406217_673003902.png</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N140" s="2">
+        <v>1</v>
+      </c>
+      <c r="O140" s="2">
+        <v>0</v>
+      </c>
+      <c r="P140" s="2">
+        <v>28900</v>
+      </c>
+      <c r="Q140" s="3">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>101174078</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>12863101446</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>옵티프리 렌즈세척액 에이오셉 플러스 360ml 2개</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G141" s="2">
+        <v>22400</v>
+      </c>
+      <c r="H141" s="2">
+        <v>27000</v>
+      </c>
+      <c r="I141" s="3">
+        <v>0.17</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12863101446</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251222_190/17663848144767WTEQ_JPEG/24842690599065329_1730071600.jpg</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N141" s="2">
+        <v>1</v>
+      </c>
+      <c r="O141" s="2">
+        <v>0</v>
+      </c>
+      <c r="P141" s="2">
+        <v>22400</v>
+      </c>
+      <c r="Q141" s="3">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>101336693</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>13279951821</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>[네이버 단독] 더미식 골든퀸 백미밥 180g x 12개 + [적립] N포인트 1,000원</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G142" s="2">
+        <v>14900</v>
+      </c>
+      <c r="H142" s="2">
+        <v>24000</v>
+      </c>
+      <c r="I142" s="3">
+        <v>0.37</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13279951821</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260330_80/1774877411333YQNeU_JPEG/20834485152063238_1352538070.jpg</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N142" s="2">
+        <v>1</v>
+      </c>
+      <c r="O142" s="2">
+        <v>0</v>
+      </c>
+      <c r="P142" s="2">
+        <v>14900</v>
+      </c>
+      <c r="Q142" s="3">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>101336693</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>13279954420</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>[네이버 단독] 더미식 골든퀸 백미밥180g x 24개입 + [적립] N포인트 2,000원</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G143" s="2">
+        <v>29610</v>
+      </c>
+      <c r="H143" s="2">
+        <v>47000</v>
+      </c>
+      <c r="I143" s="3">
+        <v>0.37</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13279954420</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260330_279/1774877449913bkBoB_JPEG/109010278069055866_930584108.jpg</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N143" s="2">
+        <v>1</v>
+      </c>
+      <c r="O143" s="2">
+        <v>0</v>
+      </c>
+      <c r="P143" s="2">
+        <v>29610</v>
+      </c>
+      <c r="Q143" s="3">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>101407817</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>11061381895</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>리포소홈 층간소음 안심 폴더매트 빅매트 아기 유아 거실 놀이방 200x240 아이보리</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>육아/반려</t>
+        </is>
+      </c>
+      <c r="G144" s="2">
+        <v>189000</v>
+      </c>
+      <c r="H144" s="2">
+        <v>324000</v>
+      </c>
+      <c r="I144" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11061381895</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250515_210/1747297866519L5REx_JPEG/81430706893360336_210642202.jpg</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N144" s="2">
+        <v>1</v>
+      </c>
+      <c r="O144" s="2">
+        <v>0</v>
+      </c>
+      <c r="P144" s="2">
+        <v>189000</v>
+      </c>
+      <c r="Q144" s="3">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>101875176</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>12199531008</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>엑스트라 버진 올리브 오일 스틱 (12ml x 15포) 15개입, 4개</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G145" s="2">
+        <v>113000</v>
+      </c>
+      <c r="H145" s="2">
+        <v>128000</v>
+      </c>
+      <c r="I145" s="3">
+        <v>0.11</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12199531008</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251030_105/1761784364222go2X0_JPEG/9760357230972513_2008396924.jpg</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N145" s="2">
+        <v>1</v>
+      </c>
+      <c r="O145" s="2">
+        <v>0</v>
+      </c>
+      <c r="P145" s="2">
+        <v>113000</v>
+      </c>
+      <c r="Q145" s="3">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>102050130</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>11687699981</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>케어사이드 모두 사메탑 60정 간 보조제</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G146" s="2">
+        <v>35000</v>
+      </c>
+      <c r="H146" s="2">
+        <v>60000</v>
+      </c>
+      <c r="I146" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11687699981</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250421_137/1745193498309j0xba_JPEG/15720353126802563_1722903241.jpg</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N146" s="2">
+        <v>1</v>
+      </c>
+      <c r="O146" s="2">
+        <v>0</v>
+      </c>
+      <c r="P146" s="2">
+        <v>35000</v>
+      </c>
+      <c r="Q146" s="3">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>102109244</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>10829472054</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>[슈퍼적립] 솔티스 눈 프로텍션 프로S3 3박스 눈 건강</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G147" s="2">
+        <v>36900</v>
+      </c>
+      <c r="H147" s="2">
+        <v>59700</v>
+      </c>
+      <c r="I147" s="3">
+        <v>0.38</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10829472054</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260129_198/1769682995229dApMP_JPEG/46085449353620871_1389349486.jpg</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N147" s="2">
+        <v>1</v>
+      </c>
+      <c r="O147" s="2">
+        <v>0</v>
+      </c>
+      <c r="P147" s="2">
+        <v>36900</v>
+      </c>
+      <c r="Q147" s="3">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>102203438</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>10243645898</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>네이처메이드 비타민C 구미 80구미, 1개</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>뷰티/헬스</t>
+        </is>
+      </c>
+      <c r="G148" s="2">
+        <v>23000</v>
+      </c>
+      <c r="H148" s="2">
+        <v>29500</v>
+      </c>
+      <c r="I148" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10243645898</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20240513_35/1715583347071fpn8d_JPEG/116719245768090833_751307332.jpg</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N148" s="2">
+        <v>1</v>
+      </c>
+      <c r="O148" s="2">
+        <v>0</v>
+      </c>
+      <c r="P148" s="2">
+        <v>23000</v>
+      </c>
+      <c r="Q148" s="3">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>102282059</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>13236848348</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>하이트진로음료 테라 제로 0.00 350ml 24캔 무알콜 맥주맛 음료</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G149" s="2">
+        <v>15900</v>
+      </c>
+      <c r="H149" s="2">
+        <v>22800</v>
+      </c>
+      <c r="I149" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13236848348</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260312_249/17732823668765jaeF_JPEG/107415237988172785_1992013375.jpg</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N149" s="2">
+        <v>1</v>
+      </c>
+      <c r="O149" s="2">
+        <v>0</v>
+      </c>
+      <c r="P149" s="2">
+        <v>15900</v>
+      </c>
+      <c r="Q149" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>102655931</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>12381375662</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>[2개 구매 시 9‚000원][전주 베테랑] 만두 2종 (택1)</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G150" s="2">
+        <v>10</v>
+      </c>
+      <c r="H150" s="2">
+        <v>10</v>
+      </c>
+      <c r="I150" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12381375662</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250910_39/1757490325761jktuN_JPEG/3936255891708665_1713910409.jpg</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N150" s="2">
+        <v>1</v>
+      </c>
+      <c r="O150" s="2">
+        <v>0</v>
+      </c>
+      <c r="P150" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q150" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>102655931</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>12390107297</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>[2개 구매시 15%][유혜광돈까스] 수제 경양식 통등심 돈까스 280g</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G151" s="2">
+        <v>5990</v>
+      </c>
+      <c r="H151" s="2">
+        <v>5990</v>
+      </c>
+      <c r="I151" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12390107297</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250912_213/17576417459915u4gv_JPEG/4087676120568818_1301872264.jpg</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N151" s="2">
+        <v>1</v>
+      </c>
+      <c r="O151" s="2">
+        <v>0</v>
+      </c>
+      <c r="P151" s="2">
+        <v>5990</v>
+      </c>
+      <c r="Q151" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>102793147</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>12588783457</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>[99.9% 항균] 마호가니 원목 도마 사각홈_김치국물방지 우드 나무 도마</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G152" s="2">
+        <v>18900</v>
+      </c>
+      <c r="H152" s="2">
+        <v>30000</v>
+      </c>
+      <c r="I152" s="3">
+        <v>0.37</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12588783457</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251025_108/1761353039043l93VI_JPEG/14145056006606597_94176125.jpg</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N152" s="2">
+        <v>1</v>
+      </c>
+      <c r="O152" s="2">
+        <v>0</v>
+      </c>
+      <c r="P152" s="2">
+        <v>18900</v>
+      </c>
+      <c r="Q152" s="3">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>500002685</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>5035409673</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>트리플에스 대용량 약산성 탈모샴푸 1350ml</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>뷰티/헬스</t>
+        </is>
+      </c>
+      <c r="G153" s="2">
+        <v>16900</v>
+      </c>
+      <c r="H153" s="2">
+        <v>25900</v>
+      </c>
+      <c r="I153" s="3">
+        <v>0.34</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5035409673</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250528_191/1748423431194nyEYk_JPEG/81057467757189760_816543235.jpg</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N153" s="2">
+        <v>1</v>
+      </c>
+      <c r="O153" s="2">
+        <v>0</v>
+      </c>
+      <c r="P153" s="2">
+        <v>16900</v>
+      </c>
+      <c r="Q153" s="3">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>500003682</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>6794759969</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>하이뮨 액티브 밀크쉐이크 제로 250ml 2박스 외 2종 (총 36팩)</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G154" s="2">
+        <v>57000</v>
+      </c>
+      <c r="H154" s="2">
+        <v>115200</v>
+      </c>
+      <c r="I154" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/6794759969</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260403_64/1775205011185o43fj_PNG/58820386162797501_166747001.png</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N154" s="2">
+        <v>1</v>
+      </c>
+      <c r="O154" s="2">
+        <v>0</v>
+      </c>
+      <c r="P154" s="2">
+        <v>57000</v>
+      </c>
+      <c r="Q154" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>500009413</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>11610332343</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>스테비아 대추방울 토망고 2kg (500gX4팩)</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G155" s="2">
+        <v>16900</v>
+      </c>
+      <c r="H155" s="2">
+        <v>29900</v>
+      </c>
+      <c r="I155" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11610332343</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260203_52/1770098127808UImbb_JPEG/22813688217306165_2062525811.jpg</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N155" s="2">
+        <v>1</v>
+      </c>
+      <c r="O155" s="2">
+        <v>0</v>
+      </c>
+      <c r="P155" s="2">
+        <v>16900</v>
+      </c>
+      <c r="Q155" s="3">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>500009413</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>11704510185</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>[농할쿠폰] 산지직송 국내산 26년 햇 양파 상(요리용크기) 5kg</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G156" s="2">
+        <v>11900</v>
+      </c>
+      <c r="H156" s="2">
+        <v>19900</v>
+      </c>
+      <c r="I156" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11704510185</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260407_73/1775542255094p6sm8_JPEG/38533715219389444_1493839568.jpg</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N156" s="2">
+        <v>1</v>
+      </c>
+      <c r="O156" s="2">
+        <v>0</v>
+      </c>
+      <c r="P156" s="2">
+        <v>11900</v>
+      </c>
+      <c r="Q156" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>500009413</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>4541129372</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>제스프리 골드키위 자이언트 점보과 골드 키위 10과</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G157" s="2">
+        <v>10900</v>
+      </c>
+      <c r="H157" s="2">
+        <v>70900</v>
+      </c>
+      <c r="I157" s="3">
+        <v>0.84</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/4541129372</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250711_17/1752219695773G4Yc4_JPEG/66619777621383124_1928490774.jpg</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N157" s="2">
+        <v>1</v>
+      </c>
+      <c r="O157" s="2">
+        <v>0</v>
+      </c>
+      <c r="P157" s="2">
+        <v>10900</v>
+      </c>
+      <c r="Q157" s="3">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>500020789</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>13263307347</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>자연원 냉동애플망고(페루) 2kg</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G158" s="2">
+        <v>10900</v>
+      </c>
+      <c r="H158" s="2">
+        <v>16900</v>
+      </c>
+      <c r="I158" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13263307347</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260317_181/1773725411836LOjhB_JPEG/5872689662511575_1011574894.jpg</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N158" s="2">
+        <v>1</v>
+      </c>
+      <c r="O158" s="2">
+        <v>0</v>
+      </c>
+      <c r="P158" s="2">
+        <v>10900</v>
+      </c>
+      <c r="Q158" s="3">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>500028485</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>12850878978</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>애사비 오리지널 500mL 12개+애사비 파인애플 500mL 12개</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G159" s="2">
+        <v>16600</v>
+      </c>
+      <c r="H159" s="2">
+        <v>29800</v>
+      </c>
+      <c r="I159" s="3">
+        <v>0.44</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12850878978</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260106_206/1767660899076xnSNc_PNG/22110109893808299_656888307.png</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N159" s="2">
+        <v>1</v>
+      </c>
+      <c r="O159" s="2">
+        <v>0</v>
+      </c>
+      <c r="P159" s="2">
+        <v>16600</v>
+      </c>
+      <c r="Q159" s="3">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>500028485</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>12967074020</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>가야워터 먹는샘물 무라벨 500ml, 100개</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G160" s="2">
+        <v>23900</v>
+      </c>
+      <c r="H160" s="2">
+        <v>34500</v>
+      </c>
+      <c r="I160" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12967074020</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260331_219/17749309361831j1Bo_PNG/24177203914979900_253875926.png</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N160" s="2">
+        <v>1</v>
+      </c>
+      <c r="O160" s="2">
+        <v>0</v>
+      </c>
+      <c r="P160" s="2">
+        <v>23900</v>
+      </c>
+      <c r="Q160" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>500037006</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>8363630938</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>쌈채소 당일수확 한박스</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G161" s="2">
+        <v>8900</v>
+      </c>
+      <c r="H161" s="2">
+        <v>14000</v>
+      </c>
+      <c r="I161" s="3">
+        <v>0.36</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/8363630938</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20230407_103/1680859261574KGEfK_JPEG/81995045204613201_276344550.jpg</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N161" s="2">
+        <v>1</v>
+      </c>
+      <c r="O161" s="2">
+        <v>0</v>
+      </c>
+      <c r="P161" s="2">
+        <v>8900</v>
+      </c>
+      <c r="Q161" s="3">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>500255345</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>4151526517</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>전라도식 국산 얼갈이김치 2kg 주문</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G162" s="2">
+        <v>10900</v>
+      </c>
+      <c r="H162" s="2">
+        <v>18000</v>
+      </c>
+      <c r="I162" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/4151526517</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20240701_251/1719823066573SbdSq_JPEG/27134669386076068_1491629302.jpg</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N162" s="2">
+        <v>1</v>
+      </c>
+      <c r="O162" s="2">
+        <v>0</v>
+      </c>
+      <c r="P162" s="2">
+        <v>10900</v>
+      </c>
+      <c r="Q162" s="3">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>500258101</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>6040856618</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>삼양식품 삼양라면 20입 외 BEST라면 시리즈</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G163" s="2">
+        <v>12770</v>
+      </c>
+      <c r="H163" s="2">
+        <v>15600</v>
+      </c>
+      <c r="I163" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/6040856618</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250708_257/1751953596041O2pXf_JPEG/6615978984147482_721180018.jpg</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N163" s="2">
+        <v>1</v>
+      </c>
+      <c r="O163" s="2">
+        <v>0</v>
+      </c>
+      <c r="P163" s="2">
+        <v>12770</v>
+      </c>
+      <c r="Q163" s="3">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>500272158</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>8794960077</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>[네이버단독] 뉴트리 에버콜라겐 타임비오틴업 3개월분+10일 GPH 저분자 트리 펩타이드</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G164" s="2">
+        <v>83900</v>
+      </c>
+      <c r="H164" s="2">
+        <v>138000</v>
+      </c>
+      <c r="I164" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/8794960077</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251102_299/1762044680370yRBR6_JPEG/77053174371961031_631631595.jpg</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="N164" s="2">
+        <v>1</v>
+      </c>
+      <c r="O164" s="2">
+        <v>0</v>
+      </c>
+      <c r="P164" s="2">
+        <v>83900</v>
+      </c>
+      <c r="Q164" s="3">
+        <v>0.39</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q127"/>
+  <autoFilter ref="A1:Q164"/>
 </worksheet>
 </file>
--- a/data/derived/todaysdeal-analysis.xlsx
+++ b/data/derived/todaysdeal-analysis.xlsx
@@ -57,13 +57,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:F152"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -92,6 +93,11 @@
           <t>2026-04-18</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -111,6 +117,9 @@
       <c r="E2" s="2">
         <v>0</v>
       </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -130,53 +139,62 @@
       <c r="E3" s="2">
         <v>0</v>
       </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>100146361</t>
+          <t>100136792</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>100181508</t>
+          <t>100146361</t>
         </is>
       </c>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
       </c>
       <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>100187146</t>
+          <t>100181508</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
@@ -185,32 +203,38 @@
         <v>0</v>
       </c>
       <c r="E6" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>100208089</t>
+          <t>100187146</t>
         </is>
       </c>
       <c r="B7" s="2">
         <v>0</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>100262120</t>
+          <t>100208089</t>
         </is>
       </c>
       <c r="B8" s="2">
@@ -223,13 +247,16 @@
         <v>0</v>
       </c>
       <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>100265766</t>
+          <t>100262120</t>
         </is>
       </c>
       <c r="B9" s="2">
@@ -242,13 +269,16 @@
         <v>0</v>
       </c>
       <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>100274539</t>
+          <t>100265766</t>
         </is>
       </c>
       <c r="B10" s="2">
@@ -261,51 +291,60 @@
         <v>0</v>
       </c>
       <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>100292269</t>
+          <t>100274539</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>100292757</t>
+          <t>100292269</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
       </c>
       <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>100305602</t>
+          <t>100292757</t>
         </is>
       </c>
       <c r="B13" s="2">
@@ -315,16 +354,19 @@
         <v>1</v>
       </c>
       <c r="D13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>100326348</t>
+          <t>100305602</t>
         </is>
       </c>
       <c r="B14" s="2">
@@ -334,39 +376,45 @@
         <v>1</v>
       </c>
       <c r="D14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>100327929</t>
+          <t>100326348</t>
         </is>
       </c>
       <c r="B15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
       </c>
       <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>100336563</t>
+          <t>100327929</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" s="2">
         <v>0</v>
@@ -375,13 +423,16 @@
         <v>0</v>
       </c>
       <c r="E16" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>100340418</t>
+          <t>100336563</t>
         </is>
       </c>
       <c r="B17" s="2">
@@ -391,54 +442,63 @@
         <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>100387111</t>
+          <t>100340418</t>
         </is>
       </c>
       <c r="B18" s="2">
         <v>0</v>
       </c>
       <c r="C18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>100419781</t>
+          <t>100387111</t>
         </is>
       </c>
       <c r="B19" s="2">
         <v>0</v>
       </c>
       <c r="C19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>100449422</t>
+          <t>100419781</t>
         </is>
       </c>
       <c r="B20" s="2">
@@ -452,16 +512,19 @@
       </c>
       <c r="E20" s="2">
         <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>100458264</t>
+          <t>100446531</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" s="2">
         <v>0</v>
@@ -471,12 +534,15 @@
       </c>
       <c r="E21" s="2">
         <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>100474685</t>
+          <t>100449422</t>
         </is>
       </c>
       <c r="B22" s="2">
@@ -486,35 +552,41 @@
         <v>0</v>
       </c>
       <c r="D22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>100492521</t>
+          <t>100458264</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" s="2">
         <v>0</v>
       </c>
       <c r="D23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>100503327</t>
+          <t>100474685</t>
         </is>
       </c>
       <c r="B24" s="2">
@@ -524,16 +596,19 @@
         <v>0</v>
       </c>
       <c r="D24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>100542499</t>
+          <t>100492521</t>
         </is>
       </c>
       <c r="B25" s="2">
@@ -546,13 +621,16 @@
         <v>1</v>
       </c>
       <c r="E25" s="2">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>100586493</t>
+          <t>100503327</t>
         </is>
       </c>
       <c r="B26" s="2">
@@ -566,12 +644,15 @@
       </c>
       <c r="E26" s="2">
         <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>100587614</t>
+          <t>100542499</t>
         </is>
       </c>
       <c r="B27" s="2">
@@ -584,17 +665,20 @@
         <v>1</v>
       </c>
       <c r="E27" s="2">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>100596797</t>
+          <t>100586493</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C28" s="2">
         <v>0</v>
@@ -603,36 +687,42 @@
         <v>0</v>
       </c>
       <c r="E28" s="2">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>100627146</t>
+          <t>100587614</t>
         </is>
       </c>
       <c r="B29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C29" s="2">
         <v>0</v>
       </c>
       <c r="D29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="2">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>100650054</t>
+          <t>100596797</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" s="2">
         <v>0</v>
@@ -641,17 +731,20 @@
         <v>0</v>
       </c>
       <c r="E30" s="2">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>100730113</t>
+          <t>100627146</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" s="2">
         <v>0</v>
@@ -660,36 +753,42 @@
         <v>0</v>
       </c>
       <c r="E31" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>100752133</t>
+          <t>100650054</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
       </c>
       <c r="D32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="2">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>100770404</t>
+          <t>100730113</t>
         </is>
       </c>
       <c r="B33" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" s="2">
         <v>0</v>
@@ -698,13 +797,16 @@
         <v>0</v>
       </c>
       <c r="E33" s="2">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>100774355</t>
+          <t>100752133</t>
         </is>
       </c>
       <c r="B34" s="2">
@@ -717,32 +819,38 @@
         <v>1</v>
       </c>
       <c r="E34" s="2">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>100791832</t>
+          <t>100770404</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
       </c>
       <c r="D35" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E35" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>100823000</t>
+          <t>100774355</t>
         </is>
       </c>
       <c r="B36" s="2">
@@ -752,35 +860,41 @@
         <v>0</v>
       </c>
       <c r="D36" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" s="2">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>100827249</t>
+          <t>100791007</t>
         </is>
       </c>
       <c r="B37" s="2">
         <v>0</v>
       </c>
       <c r="C37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" s="2">
         <v>0</v>
       </c>
       <c r="E37" s="2">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>100862614</t>
+          <t>100791832</t>
         </is>
       </c>
       <c r="B38" s="2">
@@ -790,92 +904,107 @@
         <v>0</v>
       </c>
       <c r="D38" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E38" s="2">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>100864321</t>
+          <t>100823000</t>
         </is>
       </c>
       <c r="B39" s="2">
         <v>0</v>
       </c>
       <c r="C39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E39" s="2">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>100888704</t>
+          <t>100827249</t>
         </is>
       </c>
       <c r="B40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
       </c>
       <c r="E40" s="2">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>100955968</t>
+          <t>100862614</t>
         </is>
       </c>
       <c r="B41" s="2">
         <v>0</v>
       </c>
       <c r="C41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" s="2">
         <v>0</v>
       </c>
       <c r="E41" s="2">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>100972973</t>
+          <t>100864321</t>
         </is>
       </c>
       <c r="B42" s="2">
         <v>0</v>
       </c>
       <c r="C42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="2">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>101034585</t>
+          <t>100864434</t>
         </is>
       </c>
       <c r="B43" s="2">
@@ -888,17 +1017,20 @@
         <v>0</v>
       </c>
       <c r="E43" s="2">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>101037405</t>
+          <t>100876713</t>
         </is>
       </c>
       <c r="B44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44" s="2">
         <v>0</v>
@@ -908,16 +1040,19 @@
       </c>
       <c r="E44" s="2">
         <v>0</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>101102225</t>
+          <t>100888704</t>
         </is>
       </c>
       <c r="B45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
@@ -926,13 +1061,16 @@
         <v>0</v>
       </c>
       <c r="E45" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>101111804</t>
+          <t>100890156</t>
         </is>
       </c>
       <c r="B46" s="2">
@@ -942,16 +1080,19 @@
         <v>0</v>
       </c>
       <c r="D46" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" s="2">
         <v>0</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>101161925</t>
+          <t>100938809</t>
         </is>
       </c>
       <c r="B47" s="2">
@@ -961,39 +1102,45 @@
         <v>0</v>
       </c>
       <c r="D47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" s="2">
         <v>0</v>
+      </c>
+      <c r="F47" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>101174078</t>
+          <t>100955968</t>
         </is>
       </c>
       <c r="B48" s="2">
         <v>0</v>
       </c>
       <c r="C48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48" s="2">
         <v>0</v>
       </c>
       <c r="E48" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F48" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>101195987</t>
+          <t>100961074</t>
         </is>
       </c>
       <c r="B49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
@@ -1003,50 +1150,59 @@
       </c>
       <c r="E49" s="2">
         <v>0</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>101232925</t>
+          <t>100972973</t>
         </is>
       </c>
       <c r="B50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" s="2">
         <v>0</v>
       </c>
       <c r="D50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="2">
+        <v>0</v>
+      </c>
+      <c r="F50" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>101295037</t>
+          <t>101013887</t>
         </is>
       </c>
       <c r="B51" s="2">
         <v>0</v>
       </c>
       <c r="C51" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" s="2">
         <v>0</v>
       </c>
       <c r="E51" s="2">
         <v>0</v>
+      </c>
+      <c r="F51" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>101336693</t>
+          <t>101034585</t>
         </is>
       </c>
       <c r="B52" s="2">
@@ -1059,32 +1215,38 @@
         <v>0</v>
       </c>
       <c r="E52" s="2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F52" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>101372175</t>
+          <t>101037405</t>
         </is>
       </c>
       <c r="B53" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
       </c>
       <c r="D53" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" s="2">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>101396394</t>
+          <t>101102225</t>
         </is>
       </c>
       <c r="B54" s="2">
@@ -1094,16 +1256,19 @@
         <v>0</v>
       </c>
       <c r="D54" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" s="2">
+        <v>1</v>
+      </c>
+      <c r="F54" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>101407817</t>
+          <t>101108628</t>
         </is>
       </c>
       <c r="B55" s="2">
@@ -1116,89 +1281,104 @@
         <v>0</v>
       </c>
       <c r="E55" s="2">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>101434241</t>
+          <t>101111804</t>
         </is>
       </c>
       <c r="B56" s="2">
         <v>0</v>
       </c>
       <c r="C56" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" s="2">
+        <v>0</v>
+      </c>
+      <c r="F56" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>101437685</t>
+          <t>101161925</t>
         </is>
       </c>
       <c r="B57" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C57" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="2">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>101467964</t>
+          <t>101174078</t>
         </is>
       </c>
       <c r="B58" s="2">
         <v>0</v>
       </c>
       <c r="C58" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
       </c>
       <c r="E58" s="2">
+        <v>1</v>
+      </c>
+      <c r="F58" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>101481537</t>
+          <t>101195987</t>
         </is>
       </c>
       <c r="B59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59" s="2">
         <v>0</v>
       </c>
       <c r="E59" s="2">
+        <v>0</v>
+      </c>
+      <c r="F59" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>101509593</t>
+          <t>101232925</t>
         </is>
       </c>
       <c r="B60" s="2">
@@ -1211,70 +1391,82 @@
         <v>0</v>
       </c>
       <c r="E60" s="2">
+        <v>0</v>
+      </c>
+      <c r="F60" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>101573499</t>
+          <t>101295037</t>
         </is>
       </c>
       <c r="B61" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C61" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61" s="2">
         <v>0</v>
       </c>
       <c r="E61" s="2">
+        <v>0</v>
+      </c>
+      <c r="F61" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>101836491</t>
+          <t>101336693</t>
         </is>
       </c>
       <c r="B62" s="2">
         <v>0</v>
       </c>
       <c r="C62" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" s="2">
         <v>0</v>
       </c>
       <c r="E62" s="2">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="F62" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>101863433</t>
+          <t>101372175</t>
         </is>
       </c>
       <c r="B63" s="2">
         <v>0</v>
       </c>
       <c r="C63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" s="2">
+        <v>0</v>
+      </c>
+      <c r="F63" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>101875176</t>
+          <t>101396394</t>
         </is>
       </c>
       <c r="B64" s="2">
@@ -1284,20 +1476,23 @@
         <v>0</v>
       </c>
       <c r="D64" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F64" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>101885140</t>
+          <t>101407817</t>
         </is>
       </c>
       <c r="B65" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C65" s="2">
         <v>0</v>
@@ -1306,17 +1501,20 @@
         <v>0</v>
       </c>
       <c r="E65" s="2">
+        <v>1</v>
+      </c>
+      <c r="F65" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>101888773</t>
+          <t>101434241</t>
         </is>
       </c>
       <c r="B66" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C66" s="2">
         <v>1</v>
@@ -1325,32 +1523,38 @@
         <v>0</v>
       </c>
       <c r="E66" s="2">
+        <v>0</v>
+      </c>
+      <c r="F66" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>102006080</t>
+          <t>101437685</t>
         </is>
       </c>
       <c r="B67" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C67" s="2">
         <v>1</v>
       </c>
       <c r="D67" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" s="2">
+        <v>0</v>
+      </c>
+      <c r="F67" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>102006845</t>
+          <t>101467964</t>
         </is>
       </c>
       <c r="B68" s="2">
@@ -1363,36 +1567,42 @@
         <v>0</v>
       </c>
       <c r="E68" s="2">
+        <v>0</v>
+      </c>
+      <c r="F68" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>102050130</t>
+          <t>101481537</t>
         </is>
       </c>
       <c r="B69" s="2">
         <v>0</v>
       </c>
       <c r="C69" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69" s="2">
         <v>0</v>
       </c>
       <c r="E69" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F69" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>102109244</t>
+          <t>101509593</t>
         </is>
       </c>
       <c r="B70" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C70" s="2">
         <v>0</v>
@@ -1401,13 +1611,16 @@
         <v>0</v>
       </c>
       <c r="E70" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F70" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>102203438</t>
+          <t>101533995</t>
         </is>
       </c>
       <c r="B71" s="2">
@@ -1420,32 +1633,38 @@
         <v>0</v>
       </c>
       <c r="E71" s="2">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>102227253</t>
+          <t>101573499</t>
         </is>
       </c>
       <c r="B72" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C72" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72" s="2">
         <v>0</v>
       </c>
       <c r="E72" s="2">
+        <v>0</v>
+      </c>
+      <c r="F72" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>102282059</t>
+          <t>101649796</t>
         </is>
       </c>
       <c r="B73" s="2">
@@ -1458,32 +1677,38 @@
         <v>0</v>
       </c>
       <c r="E73" s="2">
+        <v>0</v>
+      </c>
+      <c r="F73" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>102299090</t>
+          <t>101691981</t>
         </is>
       </c>
       <c r="B74" s="2">
         <v>0</v>
       </c>
       <c r="C74" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74" s="2">
         <v>0</v>
       </c>
       <c r="E74" s="2">
         <v>0</v>
+      </c>
+      <c r="F74" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>102307203</t>
+          <t>101800057</t>
         </is>
       </c>
       <c r="B75" s="2">
@@ -1493,16 +1718,19 @@
         <v>0</v>
       </c>
       <c r="D75" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" s="2">
         <v>0</v>
+      </c>
+      <c r="F75" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>102375097</t>
+          <t>101836491</t>
         </is>
       </c>
       <c r="B76" s="2">
@@ -1515,36 +1743,42 @@
         <v>0</v>
       </c>
       <c r="E76" s="2">
+        <v>0</v>
+      </c>
+      <c r="F76" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>102454744</t>
+          <t>101863433</t>
         </is>
       </c>
       <c r="B77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C77" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D77" s="2">
         <v>0</v>
       </c>
       <c r="E77" s="2">
+        <v>0</v>
+      </c>
+      <c r="F77" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>102497144</t>
+          <t>101875176</t>
         </is>
       </c>
       <c r="B78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
@@ -1553,13 +1787,16 @@
         <v>0</v>
       </c>
       <c r="E78" s="2">
+        <v>1</v>
+      </c>
+      <c r="F78" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>102600124</t>
+          <t>101885140</t>
         </is>
       </c>
       <c r="B79" s="2">
@@ -1572,89 +1809,104 @@
         <v>0</v>
       </c>
       <c r="E79" s="2">
+        <v>0</v>
+      </c>
+      <c r="F79" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>102655931</t>
+          <t>101888773</t>
         </is>
       </c>
       <c r="B80" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E80" s="2">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="F80" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>102673781</t>
+          <t>101903020</t>
         </is>
       </c>
       <c r="B81" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
       </c>
       <c r="D81" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" s="2">
         <v>0</v>
+      </c>
+      <c r="F81" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>102690829</t>
+          <t>102006080</t>
         </is>
       </c>
       <c r="B82" s="2">
         <v>0</v>
       </c>
       <c r="C82" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D82" s="2">
         <v>1</v>
       </c>
       <c r="E82" s="2">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>102698382</t>
+          <t>102006845</t>
         </is>
       </c>
       <c r="B83" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C83" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D83" s="2">
         <v>0</v>
       </c>
       <c r="E83" s="2">
+        <v>0</v>
+      </c>
+      <c r="F83" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>102705657</t>
+          <t>102050130</t>
         </is>
       </c>
       <c r="B84" s="2">
@@ -1664,35 +1916,41 @@
         <v>0</v>
       </c>
       <c r="D84" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84" s="2">
+        <v>1</v>
+      </c>
+      <c r="F84" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>102748593</t>
+          <t>102109244</t>
         </is>
       </c>
       <c r="B85" s="2">
         <v>0</v>
       </c>
       <c r="C85" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85" s="2">
         <v>0</v>
       </c>
       <c r="E85" s="2">
+        <v>1</v>
+      </c>
+      <c r="F85" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>102793147</t>
+          <t>102203438</t>
         </is>
       </c>
       <c r="B86" s="2">
@@ -1706,16 +1964,19 @@
       </c>
       <c r="E86" s="2">
         <v>1</v>
+      </c>
+      <c r="F86" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1100079588</t>
+          <t>102224443</t>
         </is>
       </c>
       <c r="B87" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C87" s="2">
         <v>0</v>
@@ -1725,12 +1986,15 @@
       </c>
       <c r="E87" s="2">
         <v>0</v>
+      </c>
+      <c r="F87" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>500000823</t>
+          <t>102227253</t>
         </is>
       </c>
       <c r="B88" s="2">
@@ -1743,13 +2007,16 @@
         <v>0</v>
       </c>
       <c r="E88" s="2">
+        <v>0</v>
+      </c>
+      <c r="F88" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>500000921</t>
+          <t>102282059</t>
         </is>
       </c>
       <c r="B89" s="2">
@@ -1759,54 +2026,63 @@
         <v>0</v>
       </c>
       <c r="D89" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" s="2">
+        <v>1</v>
+      </c>
+      <c r="F89" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>500002685</t>
+          <t>102299090</t>
         </is>
       </c>
       <c r="B90" s="2">
         <v>0</v>
       </c>
       <c r="C90" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90" s="2">
         <v>0</v>
       </c>
       <c r="E90" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F90" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>500003288</t>
+          <t>102307203</t>
         </is>
       </c>
       <c r="B91" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C91" s="2">
         <v>0</v>
       </c>
       <c r="D91" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91" s="2">
+        <v>0</v>
+      </c>
+      <c r="F91" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>500003682</t>
+          <t>102375097</t>
         </is>
       </c>
       <c r="B92" s="2">
@@ -1819,32 +2095,38 @@
         <v>0</v>
       </c>
       <c r="E92" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F92" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>500009413</t>
+          <t>102454744</t>
         </is>
       </c>
       <c r="B93" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D93" s="2">
         <v>0</v>
       </c>
       <c r="E93" s="2">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="F93" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>500016197</t>
+          <t>102497144</t>
         </is>
       </c>
       <c r="B94" s="2">
@@ -1857,13 +2139,16 @@
         <v>0</v>
       </c>
       <c r="E94" s="2">
+        <v>0</v>
+      </c>
+      <c r="F94" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>500020789</t>
+          <t>102569542</t>
         </is>
       </c>
       <c r="B95" s="2">
@@ -1876,13 +2161,16 @@
         <v>0</v>
       </c>
       <c r="E95" s="2">
+        <v>0</v>
+      </c>
+      <c r="F95" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>500023997</t>
+          <t>102600124</t>
         </is>
       </c>
       <c r="B96" s="2">
@@ -1895,36 +2183,42 @@
         <v>0</v>
       </c>
       <c r="E96" s="2">
+        <v>0</v>
+      </c>
+      <c r="F96" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>500024124</t>
+          <t>102655931</t>
         </is>
       </c>
       <c r="B97" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C97" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D97" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" s="2">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="F97" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>500028485</t>
+          <t>102673781</t>
         </is>
       </c>
       <c r="B98" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C98" s="2">
         <v>0</v>
@@ -1933,32 +2227,38 @@
         <v>1</v>
       </c>
       <c r="E98" s="2">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="F98" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>500031276</t>
+          <t>102690829</t>
         </is>
       </c>
       <c r="B99" s="2">
         <v>0</v>
       </c>
       <c r="C99" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" s="2">
+        <v>0</v>
+      </c>
+      <c r="F99" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>500032408</t>
+          <t>102698382</t>
         </is>
       </c>
       <c r="B100" s="2">
@@ -1971,13 +2271,16 @@
         <v>0</v>
       </c>
       <c r="E100" s="2">
+        <v>0</v>
+      </c>
+      <c r="F100" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>500035796</t>
+          <t>102705657</t>
         </is>
       </c>
       <c r="B101" s="2">
@@ -1990,32 +2293,38 @@
         <v>1</v>
       </c>
       <c r="E101" s="2">
+        <v>0</v>
+      </c>
+      <c r="F101" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>500036672</t>
+          <t>102748593</t>
         </is>
       </c>
       <c r="B102" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C102" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D102" s="2">
         <v>0</v>
       </c>
       <c r="E102" s="2">
+        <v>0</v>
+      </c>
+      <c r="F102" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>500037006</t>
+          <t>102793147</t>
         </is>
       </c>
       <c r="B103" s="2">
@@ -2029,54 +2338,63 @@
       </c>
       <c r="E103" s="2">
         <v>1</v>
+      </c>
+      <c r="F103" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>500052051</t>
+          <t>1100043267</t>
         </is>
       </c>
       <c r="B104" s="2">
         <v>0</v>
       </c>
       <c r="C104" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D104" s="2">
         <v>0</v>
       </c>
       <c r="E104" s="2">
         <v>0</v>
+      </c>
+      <c r="F104" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>500057619</t>
+          <t>1100079588</t>
         </is>
       </c>
       <c r="B105" s="2">
         <v>1</v>
       </c>
       <c r="C105" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D105" s="2">
         <v>0</v>
       </c>
       <c r="E105" s="2">
+        <v>0</v>
+      </c>
+      <c r="F105" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>500060661</t>
+          <t>500000823</t>
         </is>
       </c>
       <c r="B106" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C106" s="2">
         <v>1</v>
@@ -2085,17 +2403,20 @@
         <v>0</v>
       </c>
       <c r="E106" s="2">
+        <v>0</v>
+      </c>
+      <c r="F106" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>500061708</t>
+          <t>500000921</t>
         </is>
       </c>
       <c r="B107" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C107" s="2">
         <v>0</v>
@@ -2104,13 +2425,16 @@
         <v>1</v>
       </c>
       <c r="E107" s="2">
+        <v>0</v>
+      </c>
+      <c r="F107" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>500094507</t>
+          <t>500002685</t>
         </is>
       </c>
       <c r="B108" s="2">
@@ -2120,54 +2444,63 @@
         <v>0</v>
       </c>
       <c r="D108" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E108" s="2">
+        <v>1</v>
+      </c>
+      <c r="F108" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>500111404</t>
+          <t>500003288</t>
         </is>
       </c>
       <c r="B109" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C109" s="2">
         <v>0</v>
       </c>
       <c r="D109" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E109" s="2">
+        <v>0</v>
+      </c>
+      <c r="F109" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>500115640</t>
+          <t>500003682</t>
         </is>
       </c>
       <c r="B110" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C110" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D110" s="2">
         <v>0</v>
       </c>
       <c r="E110" s="2">
+        <v>1</v>
+      </c>
+      <c r="F110" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>500117284</t>
+          <t>500008320</t>
         </is>
       </c>
       <c r="B111" s="2">
@@ -2177,73 +2510,85 @@
         <v>0</v>
       </c>
       <c r="D111" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E111" s="2">
         <v>0</v>
+      </c>
+      <c r="F111" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>500120216</t>
+          <t>500009413</t>
         </is>
       </c>
       <c r="B112" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C112" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D112" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" s="2">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="F112" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>500126621</t>
+          <t>500016197</t>
         </is>
       </c>
       <c r="B113" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C113" s="2">
         <v>0</v>
       </c>
       <c r="D113" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113" s="2">
+        <v>0</v>
+      </c>
+      <c r="F113" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>500143502</t>
+          <t>500020789</t>
         </is>
       </c>
       <c r="B114" s="2">
         <v>0</v>
       </c>
       <c r="C114" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D114" s="2">
         <v>0</v>
       </c>
       <c r="E114" s="2">
+        <v>1</v>
+      </c>
+      <c r="F114" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>500143882</t>
+          <t>500023997</t>
         </is>
       </c>
       <c r="B115" s="2">
@@ -2256,70 +2601,82 @@
         <v>0</v>
       </c>
       <c r="E115" s="2">
+        <v>0</v>
+      </c>
+      <c r="F115" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>500146800</t>
+          <t>500024124</t>
         </is>
       </c>
       <c r="B116" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C116" s="2">
         <v>0</v>
       </c>
       <c r="D116" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" s="2">
+        <v>0</v>
+      </c>
+      <c r="F116" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>500185891</t>
+          <t>500028485</t>
         </is>
       </c>
       <c r="B117" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C117" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E117" s="2">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="F117" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>500187931</t>
+          <t>500031227</t>
         </is>
       </c>
       <c r="B118" s="2">
         <v>0</v>
       </c>
       <c r="C118" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D118" s="2">
         <v>0</v>
       </c>
       <c r="E118" s="2">
         <v>0</v>
+      </c>
+      <c r="F118" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>500211718</t>
+          <t>500031276</t>
         </is>
       </c>
       <c r="B119" s="2">
@@ -2329,54 +2686,63 @@
         <v>1</v>
       </c>
       <c r="D119" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E119" s="2">
+        <v>0</v>
+      </c>
+      <c r="F119" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>500217683</t>
+          <t>500032408</t>
         </is>
       </c>
       <c r="B120" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C120" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E120" s="2">
+        <v>0</v>
+      </c>
+      <c r="F120" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>500236829</t>
+          <t>500035796</t>
         </is>
       </c>
       <c r="B121" s="2">
         <v>0</v>
       </c>
       <c r="C121" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D121" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121" s="2">
+        <v>0</v>
+      </c>
+      <c r="F121" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>500240447</t>
+          <t>500036672</t>
         </is>
       </c>
       <c r="B122" s="2">
@@ -2389,93 +2755,680 @@
         <v>0</v>
       </c>
       <c r="E122" s="2">
+        <v>0</v>
+      </c>
+      <c r="F122" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>500241388</t>
+          <t>500037006</t>
         </is>
       </c>
       <c r="B123" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C123" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D123" s="2">
         <v>0</v>
       </c>
       <c r="E123" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F123" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>500255345</t>
+          <t>500052051</t>
         </is>
       </c>
       <c r="B124" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C124" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D124" s="2">
         <v>0</v>
       </c>
       <c r="E124" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F124" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>500258101</t>
+          <t>500057619</t>
         </is>
       </c>
       <c r="B125" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C125" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D125" s="2">
         <v>0</v>
       </c>
       <c r="E125" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F125" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
+          <t>500060661</t>
+        </is>
+      </c>
+      <c r="B126" s="2">
+        <v>1</v>
+      </c>
+      <c r="C126" s="2">
+        <v>1</v>
+      </c>
+      <c r="D126" s="2">
+        <v>0</v>
+      </c>
+      <c r="E126" s="2">
+        <v>0</v>
+      </c>
+      <c r="F126" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>500061708</t>
+        </is>
+      </c>
+      <c r="B127" s="2">
+        <v>1</v>
+      </c>
+      <c r="C127" s="2">
+        <v>0</v>
+      </c>
+      <c r="D127" s="2">
+        <v>1</v>
+      </c>
+      <c r="E127" s="2">
+        <v>0</v>
+      </c>
+      <c r="F127" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>500066176</t>
+        </is>
+      </c>
+      <c r="B128" s="2">
+        <v>0</v>
+      </c>
+      <c r="C128" s="2">
+        <v>0</v>
+      </c>
+      <c r="D128" s="2">
+        <v>0</v>
+      </c>
+      <c r="E128" s="2">
+        <v>0</v>
+      </c>
+      <c r="F128" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>500094507</t>
+        </is>
+      </c>
+      <c r="B129" s="2">
+        <v>0</v>
+      </c>
+      <c r="C129" s="2">
+        <v>0</v>
+      </c>
+      <c r="D129" s="2">
+        <v>1</v>
+      </c>
+      <c r="E129" s="2">
+        <v>0</v>
+      </c>
+      <c r="F129" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>500101533</t>
+        </is>
+      </c>
+      <c r="B130" s="2">
+        <v>0</v>
+      </c>
+      <c r="C130" s="2">
+        <v>0</v>
+      </c>
+      <c r="D130" s="2">
+        <v>0</v>
+      </c>
+      <c r="E130" s="2">
+        <v>0</v>
+      </c>
+      <c r="F130" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>500111404</t>
+        </is>
+      </c>
+      <c r="B131" s="2">
+        <v>0</v>
+      </c>
+      <c r="C131" s="2">
+        <v>0</v>
+      </c>
+      <c r="D131" s="2">
+        <v>1</v>
+      </c>
+      <c r="E131" s="2">
+        <v>0</v>
+      </c>
+      <c r="F131" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>500115640</t>
+        </is>
+      </c>
+      <c r="B132" s="2">
+        <v>1</v>
+      </c>
+      <c r="C132" s="2">
+        <v>0</v>
+      </c>
+      <c r="D132" s="2">
+        <v>0</v>
+      </c>
+      <c r="E132" s="2">
+        <v>0</v>
+      </c>
+      <c r="F132" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>500117284</t>
+        </is>
+      </c>
+      <c r="B133" s="2">
+        <v>0</v>
+      </c>
+      <c r="C133" s="2">
+        <v>0</v>
+      </c>
+      <c r="D133" s="2">
+        <v>1</v>
+      </c>
+      <c r="E133" s="2">
+        <v>0</v>
+      </c>
+      <c r="F133" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>500120216</t>
+        </is>
+      </c>
+      <c r="B134" s="2">
+        <v>1</v>
+      </c>
+      <c r="C134" s="2">
+        <v>0</v>
+      </c>
+      <c r="D134" s="2">
+        <v>1</v>
+      </c>
+      <c r="E134" s="2">
+        <v>0</v>
+      </c>
+      <c r="F134" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>500126621</t>
+        </is>
+      </c>
+      <c r="B135" s="2">
+        <v>0</v>
+      </c>
+      <c r="C135" s="2">
+        <v>0</v>
+      </c>
+      <c r="D135" s="2">
+        <v>1</v>
+      </c>
+      <c r="E135" s="2">
+        <v>0</v>
+      </c>
+      <c r="F135" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>500128032</t>
+        </is>
+      </c>
+      <c r="B136" s="2">
+        <v>0</v>
+      </c>
+      <c r="C136" s="2">
+        <v>0</v>
+      </c>
+      <c r="D136" s="2">
+        <v>0</v>
+      </c>
+      <c r="E136" s="2">
+        <v>0</v>
+      </c>
+      <c r="F136" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>500128657</t>
+        </is>
+      </c>
+      <c r="B137" s="2">
+        <v>0</v>
+      </c>
+      <c r="C137" s="2">
+        <v>0</v>
+      </c>
+      <c r="D137" s="2">
+        <v>0</v>
+      </c>
+      <c r="E137" s="2">
+        <v>0</v>
+      </c>
+      <c r="F137" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>500143502</t>
+        </is>
+      </c>
+      <c r="B138" s="2">
+        <v>0</v>
+      </c>
+      <c r="C138" s="2">
+        <v>1</v>
+      </c>
+      <c r="D138" s="2">
+        <v>0</v>
+      </c>
+      <c r="E138" s="2">
+        <v>0</v>
+      </c>
+      <c r="F138" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>500143882</t>
+        </is>
+      </c>
+      <c r="B139" s="2">
+        <v>1</v>
+      </c>
+      <c r="C139" s="2">
+        <v>0</v>
+      </c>
+      <c r="D139" s="2">
+        <v>0</v>
+      </c>
+      <c r="E139" s="2">
+        <v>0</v>
+      </c>
+      <c r="F139" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>500146800</t>
+        </is>
+      </c>
+      <c r="B140" s="2">
+        <v>1</v>
+      </c>
+      <c r="C140" s="2">
+        <v>0</v>
+      </c>
+      <c r="D140" s="2">
+        <v>0</v>
+      </c>
+      <c r="E140" s="2">
+        <v>0</v>
+      </c>
+      <c r="F140" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>500185891</t>
+        </is>
+      </c>
+      <c r="B141" s="2">
+        <v>1</v>
+      </c>
+      <c r="C141" s="2">
+        <v>1</v>
+      </c>
+      <c r="D141" s="2">
+        <v>0</v>
+      </c>
+      <c r="E141" s="2">
+        <v>0</v>
+      </c>
+      <c r="F141" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>500187931</t>
+        </is>
+      </c>
+      <c r="B142" s="2">
+        <v>0</v>
+      </c>
+      <c r="C142" s="2">
+        <v>1</v>
+      </c>
+      <c r="D142" s="2">
+        <v>0</v>
+      </c>
+      <c r="E142" s="2">
+        <v>0</v>
+      </c>
+      <c r="F142" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>500199878</t>
+        </is>
+      </c>
+      <c r="B143" s="2">
+        <v>0</v>
+      </c>
+      <c r="C143" s="2">
+        <v>0</v>
+      </c>
+      <c r="D143" s="2">
+        <v>0</v>
+      </c>
+      <c r="E143" s="2">
+        <v>0</v>
+      </c>
+      <c r="F143" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>500211718</t>
+        </is>
+      </c>
+      <c r="B144" s="2">
+        <v>0</v>
+      </c>
+      <c r="C144" s="2">
+        <v>1</v>
+      </c>
+      <c r="D144" s="2">
+        <v>2</v>
+      </c>
+      <c r="E144" s="2">
+        <v>0</v>
+      </c>
+      <c r="F144" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>500217683</t>
+        </is>
+      </c>
+      <c r="B145" s="2">
+        <v>0</v>
+      </c>
+      <c r="C145" s="2">
+        <v>1</v>
+      </c>
+      <c r="D145" s="2">
+        <v>1</v>
+      </c>
+      <c r="E145" s="2">
+        <v>0</v>
+      </c>
+      <c r="F145" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>500236829</t>
+        </is>
+      </c>
+      <c r="B146" s="2">
+        <v>0</v>
+      </c>
+      <c r="C146" s="2">
+        <v>1</v>
+      </c>
+      <c r="D146" s="2">
+        <v>0</v>
+      </c>
+      <c r="E146" s="2">
+        <v>0</v>
+      </c>
+      <c r="F146" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>500240447</t>
+        </is>
+      </c>
+      <c r="B147" s="2">
+        <v>1</v>
+      </c>
+      <c r="C147" s="2">
+        <v>0</v>
+      </c>
+      <c r="D147" s="2">
+        <v>0</v>
+      </c>
+      <c r="E147" s="2">
+        <v>0</v>
+      </c>
+      <c r="F147" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>500241388</t>
+        </is>
+      </c>
+      <c r="B148" s="2">
+        <v>1</v>
+      </c>
+      <c r="C148" s="2">
+        <v>1</v>
+      </c>
+      <c r="D148" s="2">
+        <v>0</v>
+      </c>
+      <c r="E148" s="2">
+        <v>0</v>
+      </c>
+      <c r="F148" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>500255345</t>
+        </is>
+      </c>
+      <c r="B149" s="2">
+        <v>1</v>
+      </c>
+      <c r="C149" s="2">
+        <v>0</v>
+      </c>
+      <c r="D149" s="2">
+        <v>0</v>
+      </c>
+      <c r="E149" s="2">
+        <v>1</v>
+      </c>
+      <c r="F149" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>500258101</t>
+        </is>
+      </c>
+      <c r="B150" s="2">
+        <v>0</v>
+      </c>
+      <c r="C150" s="2">
+        <v>0</v>
+      </c>
+      <c r="D150" s="2">
+        <v>0</v>
+      </c>
+      <c r="E150" s="2">
+        <v>1</v>
+      </c>
+      <c r="F150" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
           <t>500272158</t>
         </is>
       </c>
-      <c r="B126" s="2">
-        <v>0</v>
-      </c>
-      <c r="C126" s="2">
-        <v>0</v>
-      </c>
-      <c r="D126" s="2">
-        <v>0</v>
-      </c>
-      <c r="E126" s="2">
+      <c r="B151" s="2">
+        <v>0</v>
+      </c>
+      <c r="C151" s="2">
+        <v>0</v>
+      </c>
+      <c r="D151" s="2">
+        <v>0</v>
+      </c>
+      <c r="E151" s="2">
+        <v>1</v>
+      </c>
+      <c r="F151" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>500284150</t>
+        </is>
+      </c>
+      <c r="B152" s="2">
+        <v>0</v>
+      </c>
+      <c r="C152" s="2">
+        <v>0</v>
+      </c>
+      <c r="D152" s="2">
+        <v>0</v>
+      </c>
+      <c r="E152" s="2">
+        <v>0</v>
+      </c>
+      <c r="F152" s="2">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E126"/>
+  <autoFilter ref="A1:F152"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q164"/>
+  <dimension ref="A1:Q207"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -14482,7 +15435,3146 @@
         <v>0.39</v>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>100002411</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>13376053350</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>애슐리 주먹밥 5종 10개입(김치콘치즈2+케이준2+갈릭2+닭갈비2+소고기2)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G165" s="2">
+        <v>16600</v>
+      </c>
+      <c r="H165" s="2">
+        <v>25900</v>
+      </c>
+      <c r="I165" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13376053350</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260409_106/1775713965823BXi6O_JPEG/109846790616182613_140109288.jpg</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N165" s="2">
+        <v>1</v>
+      </c>
+      <c r="O165" s="2">
+        <v>0</v>
+      </c>
+      <c r="P165" s="2">
+        <v>16600</v>
+      </c>
+      <c r="Q165" s="3">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>100136792</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>13292894358</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>매일바이오 드링크 무가당플레인 150ml 12입_냉장</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G166" s="2">
+        <v>15900</v>
+      </c>
+      <c r="H166" s="2">
+        <v>22400</v>
+      </c>
+      <c r="I166" s="3">
+        <v>0.29</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13292894358</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260407_208/1775521598067KLKmw_JPEG/51924040176553298_457787524.jpg</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N166" s="2">
+        <v>1</v>
+      </c>
+      <c r="O166" s="2">
+        <v>0</v>
+      </c>
+      <c r="P166" s="2">
+        <v>15900</v>
+      </c>
+      <c r="Q166" s="3">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>100136792</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>6429237091</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>매일야채 고농축 당근의 힘 125ml 24팩 [+매일야채 스크래치 쿠폰, 호박의 힘 4팩 추가 증정] [도착보장]</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G167" s="2">
+        <v>22900</v>
+      </c>
+      <c r="H167" s="2">
+        <v>31200</v>
+      </c>
+      <c r="I167" s="3">
+        <v>0.26</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/6429237091</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260403_40/1775205014646FHJLl_JPEG/24784170521943757_1936233905.jpg</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N167" s="2">
+        <v>1</v>
+      </c>
+      <c r="O167" s="2">
+        <v>0</v>
+      </c>
+      <c r="P167" s="2">
+        <v>22900</v>
+      </c>
+      <c r="Q167" s="3">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>100446531</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>10533571737</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>[체험팩] 국내산 순살고기 가득한 닭곰탕 600 1팩 보양식 외 국물요리</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G168" s="2">
+        <v>4200</v>
+      </c>
+      <c r="H168" s="2">
+        <v>9200</v>
+      </c>
+      <c r="I168" s="3">
+        <v>0.54</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10533571737</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20240708_189/1720410550459kanTa_JPEG/31304230772702386_1223228881.jpg</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N168" s="2">
+        <v>1</v>
+      </c>
+      <c r="O168" s="2">
+        <v>0</v>
+      </c>
+      <c r="P168" s="2">
+        <v>4200</v>
+      </c>
+      <c r="Q168" s="3">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>100791007</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>5002901777</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>리큐 얼룩제거 올인원 세탁세제 2.1L 파우치 X5개 일반+섬유항균제 700ml</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>생활/주방</t>
+        </is>
+      </c>
+      <c r="G169" s="2">
+        <v>24900</v>
+      </c>
+      <c r="H169" s="2">
+        <v>65500</v>
+      </c>
+      <c r="I169" s="3">
+        <v>0.61</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5002901777</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260413_284/1776058868913CzC89_PNG/59674243860989457_1455896894.png</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N169" s="2">
+        <v>1</v>
+      </c>
+      <c r="O169" s="2">
+        <v>0</v>
+      </c>
+      <c r="P169" s="2">
+        <v>24900</v>
+      </c>
+      <c r="Q169" s="3">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>100791832</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>5279473553</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>신세계푸드 밀크앤허니 파운드 케이크 2종세트 (월넛파운드 + 소프트제리 롤) 외 초코 버터 얼그레이</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G170" s="2">
+        <v>15500</v>
+      </c>
+      <c r="H170" s="2">
+        <v>29900</v>
+      </c>
+      <c r="I170" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5279473553</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20230830_48/1693359115070d1TGh_JPEG/39199151848951427_1682566660.jpg</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N170" s="2">
+        <v>1</v>
+      </c>
+      <c r="O170" s="2">
+        <v>0</v>
+      </c>
+      <c r="P170" s="2">
+        <v>15500</v>
+      </c>
+      <c r="Q170" s="3">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>100864434</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>6345605475</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>[무료배송재구매묶음팩] 서민갑부 프리미엄등급 송쭈집 번들 패키지 Set</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G171" s="2">
+        <v>57600</v>
+      </c>
+      <c r="H171" s="2">
+        <v>83800</v>
+      </c>
+      <c r="I171" s="3">
+        <v>0.31</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/6345605475</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20240708_162/17204034107586wcDa_PNG/945619359821818_241010443.png</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N171" s="2">
+        <v>1</v>
+      </c>
+      <c r="O171" s="2">
+        <v>0</v>
+      </c>
+      <c r="P171" s="2">
+        <v>57600</v>
+      </c>
+      <c r="Q171" s="3">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>100876713</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>9811605356</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>[고단백2종] 연세두유 검은콩&amp;고칼슘 고단백두유 16팩 + 아몬드&amp;잣 190ml 16팩 (총32팩)/ 단백질, 시니어, 프로틴</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G172" s="2">
+        <v>23300</v>
+      </c>
+      <c r="H172" s="2">
+        <v>32000</v>
+      </c>
+      <c r="I172" s="3">
+        <v>0.27</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/9811605356</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260323_131/1774221980575n2aDk_JPEG/98483204979015496_1340173397.jpg</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N172" s="2">
+        <v>1</v>
+      </c>
+      <c r="O172" s="2">
+        <v>0</v>
+      </c>
+      <c r="P172" s="2">
+        <v>23300</v>
+      </c>
+      <c r="Q172" s="3">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>100890156</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>5655026936</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>마장동 생 LA갈비 선물 세트 2kg 어버이날 추석 소갈비 꽃갈비 일반포장</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G173" s="2">
+        <v>89000</v>
+      </c>
+      <c r="H173" s="2">
+        <v>280000</v>
+      </c>
+      <c r="I173" s="3">
+        <v>0.68</v>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5655026936</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20240708_59/1720403498896AbObJ_PNG/945707466979107_665950170.png</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N173" s="2">
+        <v>1</v>
+      </c>
+      <c r="O173" s="2">
+        <v>0</v>
+      </c>
+      <c r="P173" s="2">
+        <v>89000</v>
+      </c>
+      <c r="Q173" s="3">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>100938809</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>12133018849</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>별미! 탱글쫄깃한 생 메밀소바 대용량 6인분 세트</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G174" s="2">
+        <v>11900</v>
+      </c>
+      <c r="H174" s="2">
+        <v>20900</v>
+      </c>
+      <c r="I174" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12133018849</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260407_246/1775545549948zSj4K_JPEG/29140462079750248_523175454.jpg</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N174" s="2">
+        <v>1</v>
+      </c>
+      <c r="O174" s="2">
+        <v>0</v>
+      </c>
+      <c r="P174" s="2">
+        <v>11900</v>
+      </c>
+      <c r="Q174" s="3">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>100938809</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>12231822394</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>진짜 딱새우가 들어간! 연육함량 79% 딱새우 대포포 500G 대용량 1팩</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G175" s="2">
+        <v>11900</v>
+      </c>
+      <c r="H175" s="2">
+        <v>30900</v>
+      </c>
+      <c r="I175" s="3">
+        <v>0.61</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12231822394</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250811_83/1754880148401YSlYD_JPEG/89012959491791268_750324814.jpg</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N175" s="2">
+        <v>1</v>
+      </c>
+      <c r="O175" s="2">
+        <v>0</v>
+      </c>
+      <c r="P175" s="2">
+        <v>11900</v>
+      </c>
+      <c r="Q175" s="3">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>100938809</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>12476725736</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>[대구명물] 요즘 핫한! 대구 서문시장 명물 생땅콩 듬뿍! 대왕 땅콩빵 대용량 90개입!</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G176" s="2">
+        <v>10900</v>
+      </c>
+      <c r="H176" s="2">
+        <v>29900</v>
+      </c>
+      <c r="I176" s="3">
+        <v>0.63</v>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12476725736</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250929_53/1759118988236alWKT_JPEG/8982639770648850_1380154957.jpg</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N176" s="2">
+        <v>1</v>
+      </c>
+      <c r="O176" s="2">
+        <v>0</v>
+      </c>
+      <c r="P176" s="2">
+        <v>10900</v>
+      </c>
+      <c r="Q176" s="3">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>100961074</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>10561717399</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>시나모롤 헬로키티 헬로카봇 피카츄 GAP 아동 키즈 어린이 레인부츠 장화 30종</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G177" s="2">
+        <v>12900</v>
+      </c>
+      <c r="H177" s="2">
+        <v>39900</v>
+      </c>
+      <c r="I177" s="3">
+        <v>0.67</v>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10561717399</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250508_223/1746694648113KN8Js_JPEG/791694882795120_1632539945.jpg</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N177" s="2">
+        <v>1</v>
+      </c>
+      <c r="O177" s="2">
+        <v>0</v>
+      </c>
+      <c r="P177" s="2">
+        <v>12900</v>
+      </c>
+      <c r="Q177" s="3">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>101013887</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>8632170897</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>(광동 직영) 제주 삼다수 330ml 20입 + 20입 (유/무라벨 랜덤발송)</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G178" s="2">
+        <v>16400</v>
+      </c>
+      <c r="H178" s="2">
+        <v>17700</v>
+      </c>
+      <c r="I178" s="3">
+        <v>0.07</v>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/8632170897</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250410_44/17442427702855ryyU_JPEG/78375678851034586_1683985371.jpg</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N178" s="2">
+        <v>1</v>
+      </c>
+      <c r="O178" s="2">
+        <v>0</v>
+      </c>
+      <c r="P178" s="2">
+        <v>16400</v>
+      </c>
+      <c r="Q178" s="3">
+        <v>0.07</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>101108628</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>11629940090</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>이너홈 튼튼 니트릴 고무장갑 주방용 4개</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G179" s="2">
+        <v>11900</v>
+      </c>
+      <c r="H179" s="2">
+        <v>20900</v>
+      </c>
+      <c r="I179" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11629940090</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260317_80/1773713592070fkHGn_JPEG/8366424275859907_677805620.jpg</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N179" s="2">
+        <v>1</v>
+      </c>
+      <c r="O179" s="2">
+        <v>0</v>
+      </c>
+      <c r="P179" s="2">
+        <v>11900</v>
+      </c>
+      <c r="Q179" s="3">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>101336693</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>11390011981</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>더미식 덮밥소스 비프카레 3개 + 유니자장 2개+ 마파두부 2개 총 7개 골라담기 (7종 택3)</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G180" s="2">
+        <v>28000</v>
+      </c>
+      <c r="H180" s="2">
+        <v>28000</v>
+      </c>
+      <c r="I180" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11390011981</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260220_110/1771577020496P384j_JPEG/105709867629871410_1747881946.jpg</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N180" s="2">
+        <v>1</v>
+      </c>
+      <c r="O180" s="2">
+        <v>0</v>
+      </c>
+      <c r="P180" s="2">
+        <v>28000</v>
+      </c>
+      <c r="Q180" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>101336693</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>11746727732</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>맥시칸 순살 3종 + 양념치킨 볶음면 1매 SET</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G181" s="2">
+        <v>18900</v>
+      </c>
+      <c r="H181" s="2">
+        <v>31100</v>
+      </c>
+      <c r="I181" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11746727732</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260414_173/1776133175329cYXXb_JPEG/1334302425611305_1312722271.jpg</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N181" s="2">
+        <v>1</v>
+      </c>
+      <c r="O181" s="2">
+        <v>0</v>
+      </c>
+      <c r="P181" s="2">
+        <v>18900</v>
+      </c>
+      <c r="Q181" s="3">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>101336693</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>11952166422</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>하림 맛나면 4봉 + 양푼김치찌개라면 4봉 + 훌라면 4봉 (5종 택 3)</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G182" s="2">
+        <v>11900</v>
+      </c>
+      <c r="H182" s="2">
+        <v>15200</v>
+      </c>
+      <c r="I182" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11952166422</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260414_115/1776133278698syNfB_JPEG/122851598081513524_374195616.jpg</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N182" s="2">
+        <v>1</v>
+      </c>
+      <c r="O182" s="2">
+        <v>0</v>
+      </c>
+      <c r="P182" s="2">
+        <v>11900</v>
+      </c>
+      <c r="Q182" s="3">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>101336693</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>12638163250</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>맥시칸 크리스피 텐더 350g x 4개</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G183" s="2">
+        <v>19600</v>
+      </c>
+      <c r="H183" s="2">
+        <v>39200</v>
+      </c>
+      <c r="I183" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12638163250</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260414_159/17761334435206k1Pm_JPEG/30775675457492971_324995661.jpg</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N183" s="2">
+        <v>1</v>
+      </c>
+      <c r="O183" s="2">
+        <v>0</v>
+      </c>
+      <c r="P183" s="2">
+        <v>19600</v>
+      </c>
+      <c r="Q183" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>101533995</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>12575770421</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>쪄서가는 쫀득한 백찰옥수수 10개 특대</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G184" s="2">
+        <v>10900</v>
+      </c>
+      <c r="H184" s="2">
+        <v>34000</v>
+      </c>
+      <c r="I184" s="3">
+        <v>0.67</v>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12575770421</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251022_147/1761116853495cxXjD_PNG/46961192414796658_688831025.png</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N184" s="2">
+        <v>1</v>
+      </c>
+      <c r="O184" s="2">
+        <v>0</v>
+      </c>
+      <c r="P184" s="2">
+        <v>10900</v>
+      </c>
+      <c r="Q184" s="3">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>101649796</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>11819569278</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>삼성 뷰피니티 S6 LS27F610 68.4cm(27) QHD 모니터 100Hz 세로</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>디지털/가전</t>
+        </is>
+      </c>
+      <c r="G185" s="2">
+        <v>269000</v>
+      </c>
+      <c r="H185" s="2">
+        <v>350000</v>
+      </c>
+      <c r="I185" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11819569278</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260223_222/1771821330778GaE3K_PNG/24534213858357846_733209985.png</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N185" s="2">
+        <v>1</v>
+      </c>
+      <c r="O185" s="2">
+        <v>0</v>
+      </c>
+      <c r="P185" s="2">
+        <v>269000</v>
+      </c>
+      <c r="Q185" s="3">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>101691981</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>7710036529</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>농협식품 한국농협김치 포기김치 10kg</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G186" s="2">
+        <v>75900</v>
+      </c>
+      <c r="H186" s="2">
+        <v>84800</v>
+      </c>
+      <c r="I186" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/7710036529</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20221114_273/1668355798172J8Xfn_JPEG/69491696874697673_1316597162.jpg</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N186" s="2">
+        <v>1</v>
+      </c>
+      <c r="O186" s="2">
+        <v>0</v>
+      </c>
+      <c r="P186" s="2">
+        <v>75900</v>
+      </c>
+      <c r="Q186" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>101800057</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>8253710179</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>르네휘테르 포티샤 헤어리프팅 FLX 뿌리 볼륨 두피 앰플 세럼 100ml 듀오(+포티샤샴푸250ml&amp;파우치증정)</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>뷰티/헬스</t>
+        </is>
+      </c>
+      <c r="G187" s="2">
+        <v>78020</v>
+      </c>
+      <c r="H187" s="2">
+        <v>94000</v>
+      </c>
+      <c r="I187" s="3">
+        <v>0.17</v>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/8253710179</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260410_146/17757799775287OX7L_JPEG/25108786650064594_725871723.jpg</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N187" s="2">
+        <v>1</v>
+      </c>
+      <c r="O187" s="2">
+        <v>0</v>
+      </c>
+      <c r="P187" s="2">
+        <v>78020</v>
+      </c>
+      <c r="Q187" s="3">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>101888773</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>12465897985</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>[영양견과] 통째로 구워 더 맛있는! 구운견과 통 껍질캐슈넛 500g~</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G188" s="2">
+        <v>12900</v>
+      </c>
+      <c r="H188" s="2">
+        <v>25900</v>
+      </c>
+      <c r="I188" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12465897985</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250926_128/17588781290379qaxN_PNG/3122103477245625_493295315.png</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N188" s="2">
+        <v>1</v>
+      </c>
+      <c r="O188" s="2">
+        <v>0</v>
+      </c>
+      <c r="P188" s="2">
+        <v>12900</v>
+      </c>
+      <c r="Q188" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>101903020</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>10994941297</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>크리스피 허니 눈꽃 쌀과자 920gx2개, 아이 어른 간식 주전부리</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G189" s="2">
+        <v>19900</v>
+      </c>
+      <c r="H189" s="2">
+        <v>24900</v>
+      </c>
+      <c r="I189" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10994941297</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260205_99/1770271574861vwXo5_PNG/104404366890812706_798909605.png</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N189" s="2">
+        <v>1</v>
+      </c>
+      <c r="O189" s="2">
+        <v>0</v>
+      </c>
+      <c r="P189" s="2">
+        <v>19900</v>
+      </c>
+      <c r="Q189" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>102224443</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>12447545379</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>델라고 오일마스터 프라이팬 세트 올라운드 세트 3종</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G190" s="2">
+        <v>79900</v>
+      </c>
+      <c r="H190" s="2">
+        <v>149900</v>
+      </c>
+      <c r="I190" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12447545379</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251124_155/1763981517549IArMR_PNG/18582181558341685_301795033.png</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N190" s="2">
+        <v>1</v>
+      </c>
+      <c r="O190" s="2">
+        <v>0</v>
+      </c>
+      <c r="P190" s="2">
+        <v>79900</v>
+      </c>
+      <c r="Q190" s="3">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>102569542</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>11359985088</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>L2 혁명티슈 세정티슈 기름때 제거 다용도 청소 80매, 2팩</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>생활/주방</t>
+        </is>
+      </c>
+      <c r="G191" s="2">
+        <v>17900</v>
+      </c>
+      <c r="H191" s="2">
+        <v>25000</v>
+      </c>
+      <c r="I191" s="3">
+        <v>0.28</v>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11359985088</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260318_5/1773817941647RmpWy_JPEG/36796469296459116_208802707.jpg</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N191" s="2">
+        <v>1</v>
+      </c>
+      <c r="O191" s="2">
+        <v>0</v>
+      </c>
+      <c r="P191" s="2">
+        <v>17900</v>
+      </c>
+      <c r="Q191" s="3">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>102655931</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>12896857984</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>[2개 구매 시 50%][마이셰프] 한우 사골 떡만둣국</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G192" s="2">
+        <v>11900</v>
+      </c>
+      <c r="H192" s="2">
+        <v>11900</v>
+      </c>
+      <c r="I192" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12896857984</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260203_257/1770110898007K6Frn_JPEG/104243823120867483_1111433518.jpg</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N192" s="2">
+        <v>1</v>
+      </c>
+      <c r="O192" s="2">
+        <v>0</v>
+      </c>
+      <c r="P192" s="2">
+        <v>11900</v>
+      </c>
+      <c r="Q192" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>102655931</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>13153683703</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>[2개 구매 시 50%][차려낸] 국내산 닭가슴살 치킨너겟</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G193" s="2">
+        <v>9900</v>
+      </c>
+      <c r="H193" s="2">
+        <v>9900</v>
+      </c>
+      <c r="I193" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13153683703</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260223_61/1771801983693zmHj8_JPEG/6505362474723634_1465705497.jpg</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N193" s="2">
+        <v>1</v>
+      </c>
+      <c r="O193" s="2">
+        <v>0</v>
+      </c>
+      <c r="P193" s="2">
+        <v>9900</v>
+      </c>
+      <c r="Q193" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>1100043267</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>12994328918</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>고소한 참기름 350ml+참기름 350ml 1회착유</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G194" s="2">
+        <v>13900</v>
+      </c>
+      <c r="H194" s="2">
+        <v>18900</v>
+      </c>
+      <c r="I194" s="3">
+        <v>0.26</v>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12994328918</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260323_247/1774243083836yq8HR_JPEG/55942650521769597_2077104397.jpg</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N194" s="2">
+        <v>1</v>
+      </c>
+      <c r="O194" s="2">
+        <v>0</v>
+      </c>
+      <c r="P194" s="2">
+        <v>13900</v>
+      </c>
+      <c r="Q194" s="3">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>500008320</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>11923894595</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>원터치 롱바디 165cm 맥세이프 셀카봉 삼각대 원더스냅 맥핏 S581W</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G195" s="2">
+        <v>39900</v>
+      </c>
+      <c r="H195" s="2">
+        <v>55900</v>
+      </c>
+      <c r="I195" s="3">
+        <v>0.28</v>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11923894595</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260225_130/1772015824465Xzohx_JPEG/32638223293850397_622168072.jpg</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N195" s="2">
+        <v>1</v>
+      </c>
+      <c r="O195" s="2">
+        <v>0</v>
+      </c>
+      <c r="P195" s="2">
+        <v>39900</v>
+      </c>
+      <c r="Q195" s="3">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>500009413</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>6550524474</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>태국 마하차녹 무지개 망고 특대과 8~12과 4kg</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G196" s="2">
+        <v>29900</v>
+      </c>
+      <c r="H196" s="2">
+        <v>38900</v>
+      </c>
+      <c r="I196" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/6550524474</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20220415_220/1650001872953nlVla_JPEG/51137771644456613_1374539359.jpg</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N196" s="2">
+        <v>1</v>
+      </c>
+      <c r="O196" s="2">
+        <v>0</v>
+      </c>
+      <c r="P196" s="2">
+        <v>29900</v>
+      </c>
+      <c r="Q196" s="3">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>500028485</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>12304048367</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>하늘보리 500mL 20개+누룽지차 500mL 40개 외 6종</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G197" s="2">
+        <v>39900</v>
+      </c>
+      <c r="H197" s="2">
+        <v>58900</v>
+      </c>
+      <c r="I197" s="3">
+        <v>0.32</v>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12304048367</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251211_164/1765433390881c1f6c_PNG/99566274977013936_1415769122.png</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N197" s="2">
+        <v>1</v>
+      </c>
+      <c r="O197" s="2">
+        <v>0</v>
+      </c>
+      <c r="P197" s="2">
+        <v>39900</v>
+      </c>
+      <c r="Q197" s="3">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>500031227</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>11217819811</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>[네이버단독] 종근당건강 락토핏 골드 360 기획세트(360일분)</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G198" s="2">
+        <v>73900</v>
+      </c>
+      <c r="H198" s="2">
+        <v>105000</v>
+      </c>
+      <c r="I198" s="3">
+        <v>0.29</v>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11217819811</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251110_300/17627591884392kuim_PNG/12850135346104313_1672000222.png</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N198" s="2">
+        <v>1</v>
+      </c>
+      <c r="O198" s="2">
+        <v>0</v>
+      </c>
+      <c r="P198" s="2">
+        <v>73900</v>
+      </c>
+      <c r="Q198" s="3">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>500037006</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>12417661050</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>초이스등급 LA갈비 망고숙성 양념 갈비</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G199" s="2">
+        <v>21900</v>
+      </c>
+      <c r="H199" s="2">
+        <v>43500</v>
+      </c>
+      <c r="I199" s="3">
+        <v>0.49</v>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12417661050</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251015_206/1760505230385pUeAK_JPEG/14680483138820404_728004677.jpg</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N199" s="2">
+        <v>1</v>
+      </c>
+      <c r="O199" s="2">
+        <v>0</v>
+      </c>
+      <c r="P199" s="2">
+        <v>21900</v>
+      </c>
+      <c r="Q199" s="3">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>500066176</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>5210164377</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>100포+100포 6년근 홍삼정 진액 에브리데이 365 홍삼 스틱 순수식품</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G200" s="2">
+        <v>49400</v>
+      </c>
+      <c r="H200" s="2">
+        <v>120000</v>
+      </c>
+      <c r="I200" s="3">
+        <v>0.58</v>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5210164377</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260413_102/1776028795113nrt2q_JPEG/68753913387761034_250560370.jpg</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N200" s="2">
+        <v>1</v>
+      </c>
+      <c r="O200" s="2">
+        <v>0</v>
+      </c>
+      <c r="P200" s="2">
+        <v>49400</v>
+      </c>
+      <c r="Q200" s="3">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>500101533</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>5256847524</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>수율보장 제철홍게 박달 연지홍게</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G201" s="2">
+        <v>20900</v>
+      </c>
+      <c r="H201" s="2">
+        <v>31900</v>
+      </c>
+      <c r="I201" s="3">
+        <v>0.34</v>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5256847524</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20220308_191/1646701566712OjeiY_JPEG/47837400518794430_1439567854.jpg</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N201" s="2">
+        <v>1</v>
+      </c>
+      <c r="O201" s="2">
+        <v>0</v>
+      </c>
+      <c r="P201" s="2">
+        <v>20900</v>
+      </c>
+      <c r="Q201" s="3">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>500115640</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>12798285569</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>사과 경북 부사 못난이 꿀사과 3kg 명절 선물세트 설 추석</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G202" s="2">
+        <v>31900</v>
+      </c>
+      <c r="H202" s="2">
+        <v>59900</v>
+      </c>
+      <c r="I202" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12798285569</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251209_98/1765248642417a6k0t_PNG/99381507513891632_1856666062.png</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N202" s="2">
+        <v>1</v>
+      </c>
+      <c r="O202" s="2">
+        <v>0</v>
+      </c>
+      <c r="P202" s="2">
+        <v>31900</v>
+      </c>
+      <c r="Q202" s="3">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>500128032</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>6969444080</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>드시모네 프라임 (보장균수 1,000억) 60포, 1개</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G203" s="2">
+        <v>103500</v>
+      </c>
+      <c r="H203" s="2">
+        <v>138000</v>
+      </c>
+      <c r="I203" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/6969444080</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20220728_134/1658976358635fyMEI_JPEG/60112138357009628_1016492530.jpg</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N203" s="2">
+        <v>1</v>
+      </c>
+      <c r="O203" s="2">
+        <v>0</v>
+      </c>
+      <c r="P203" s="2">
+        <v>103500</v>
+      </c>
+      <c r="Q203" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>500128657</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>13278964570</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>[강원] 오크밸리 리조트 객실패키지 프로모션(조식 액티비티 수영장)</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G204" s="2">
+        <v>85000</v>
+      </c>
+      <c r="H204" s="2">
+        <v>85000</v>
+      </c>
+      <c r="I204" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13278964570</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260415_259/1776238218911lgslz_JPEG/110371141875724604_694345065.jpg</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N204" s="2">
+        <v>1</v>
+      </c>
+      <c r="O204" s="2">
+        <v>0</v>
+      </c>
+      <c r="P204" s="2">
+        <v>85000</v>
+      </c>
+      <c r="Q204" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>500199878</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>5269660116</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>지장샘농장 제주 하우스 한라봉 2kg</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G205" s="2">
+        <v>11900</v>
+      </c>
+      <c r="H205" s="2">
+        <v>39900</v>
+      </c>
+      <c r="I205" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5269660116</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260113_152/1768278218217YFoPa_JPEG/102411021543929271_1883589971.jpg</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N205" s="2">
+        <v>1</v>
+      </c>
+      <c r="O205" s="2">
+        <v>0</v>
+      </c>
+      <c r="P205" s="2">
+        <v>11900</v>
+      </c>
+      <c r="Q205" s="3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>500241388</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>12737056092</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>티젠 애플 사이다 비니거 더블비니거 30스틱x2박스 (애사비 골라담기)</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G206" s="2">
+        <v>19900</v>
+      </c>
+      <c r="H206" s="2">
+        <v>42000</v>
+      </c>
+      <c r="I206" s="3">
+        <v>0.52</v>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12737056092</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251229_241/1766989204220KQgBJ_JPEG/38956694337570055_2030935676.jpg</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N206" s="2">
+        <v>1</v>
+      </c>
+      <c r="O206" s="2">
+        <v>0</v>
+      </c>
+      <c r="P206" s="2">
+        <v>19900</v>
+      </c>
+      <c r="Q206" s="3">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>500284150</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>12839052602</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>바이탈플랜트 롤팬 차콜 뉴오리지널 자동회전냄비</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G207" s="2">
+        <v>115000</v>
+      </c>
+      <c r="H207" s="2">
+        <v>200000</v>
+      </c>
+      <c r="I207" s="3">
+        <v>0.42</v>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12839052602</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260114_156/1768381952404zw293_JPEG/922329369153165_238308842.jpg</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="N207" s="2">
+        <v>1</v>
+      </c>
+      <c r="O207" s="2">
+        <v>0</v>
+      </c>
+      <c r="P207" s="2">
+        <v>115000</v>
+      </c>
+      <c r="Q207" s="3">
+        <v>0.42</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q164"/>
+  <autoFilter ref="A1:Q207"/>
 </worksheet>
 </file>
--- a/data/derived/todaysdeal-analysis.xlsx
+++ b/data/derived/todaysdeal-analysis.xlsx
@@ -57,7 +57,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F152"/>
+  <dimension ref="A1:G176"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -65,6 +65,7 @@
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -98,6 +99,11 @@
           <t>2026-04-19</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -120,11 +126,14 @@
       <c r="F2" s="2">
         <v>1</v>
       </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>100131340</t>
+          <t>100035182</t>
         </is>
       </c>
       <c r="B3" s="2">
@@ -134,19 +143,22 @@
         <v>0</v>
       </c>
       <c r="D3" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2">
         <v>0</v>
       </c>
       <c r="F3" s="2">
         <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>100136792</t>
+          <t>100038886</t>
         </is>
       </c>
       <c r="B4" s="2">
@@ -162,57 +174,66 @@
         <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>100146361</t>
+          <t>100129181</t>
         </is>
       </c>
       <c r="B5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
       </c>
       <c r="E5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>100181508</t>
+          <t>100131340</t>
         </is>
       </c>
       <c r="B6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
       </c>
       <c r="D6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
       </c>
       <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>100187146</t>
+          <t>100136792</t>
         </is>
       </c>
       <c r="B7" s="2">
@@ -225,20 +246,23 @@
         <v>0</v>
       </c>
       <c r="E7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>100208089</t>
+          <t>100146361</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
@@ -247,23 +271,26 @@
         <v>0</v>
       </c>
       <c r="E8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>100262120</t>
+          <t>100181508</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
@@ -272,35 +299,41 @@
         <v>0</v>
       </c>
       <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>100265766</t>
+          <t>100187146</t>
         </is>
       </c>
       <c r="B10" s="2">
         <v>0</v>
       </c>
       <c r="C10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>100274539</t>
+          <t>100208089</t>
         </is>
       </c>
       <c r="B11" s="2">
@@ -316,17 +349,20 @@
         <v>0</v>
       </c>
       <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>100292269</t>
+          <t>100261289</t>
         </is>
       </c>
       <c r="B12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="2">
         <v>0</v>
@@ -339,12 +375,15 @@
       </c>
       <c r="F12" s="2">
         <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>100292757</t>
+          <t>100262120</t>
         </is>
       </c>
       <c r="B13" s="2">
@@ -360,35 +399,41 @@
         <v>0</v>
       </c>
       <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>100305602</t>
+          <t>100262284</t>
         </is>
       </c>
       <c r="B14" s="2">
         <v>0</v>
       </c>
       <c r="C14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>100326348</t>
+          <t>100265766</t>
         </is>
       </c>
       <c r="B15" s="2">
@@ -404,20 +449,23 @@
         <v>0</v>
       </c>
       <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>100327929</t>
+          <t>100274539</t>
         </is>
       </c>
       <c r="B16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
@@ -426,17 +474,20 @@
         <v>0</v>
       </c>
       <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>100336563</t>
+          <t>100292269</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="2">
         <v>0</v>
@@ -445,38 +496,44 @@
         <v>0</v>
       </c>
       <c r="E17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>100340418</t>
+          <t>100292757</t>
         </is>
       </c>
       <c r="B18" s="2">
         <v>0</v>
       </c>
       <c r="C18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2">
         <v>0</v>
       </c>
       <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>100387111</t>
+          <t>100305602</t>
         </is>
       </c>
       <c r="B19" s="2">
@@ -486,45 +543,51 @@
         <v>1</v>
       </c>
       <c r="D19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="2">
         <v>0</v>
       </c>
       <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>100419781</t>
+          <t>100326348</t>
         </is>
       </c>
       <c r="B20" s="2">
         <v>0</v>
       </c>
       <c r="C20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
       </c>
       <c r="E20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>100446531</t>
+          <t>100327929</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" s="2">
         <v>0</v>
@@ -536,13 +599,16 @@
         <v>0</v>
       </c>
       <c r="F21" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>100449422</t>
+          <t>100336563</t>
         </is>
       </c>
       <c r="B22" s="2">
@@ -558,57 +624,66 @@
         <v>1</v>
       </c>
       <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>100458264</t>
+          <t>100340418</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" s="2">
         <v>0</v>
       </c>
       <c r="D23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="2">
         <v>0</v>
       </c>
       <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>100474685</t>
+          <t>100387111</t>
         </is>
       </c>
       <c r="B24" s="2">
         <v>0</v>
       </c>
       <c r="C24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2">
         <v>0</v>
       </c>
       <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>100492521</t>
+          <t>100419781</t>
         </is>
       </c>
       <c r="B25" s="2">
@@ -618,19 +693,22 @@
         <v>0</v>
       </c>
       <c r="D25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>100503327</t>
+          <t>100446531</t>
         </is>
       </c>
       <c r="B26" s="2">
@@ -643,16 +721,19 @@
         <v>0</v>
       </c>
       <c r="E26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>100542499</t>
+          <t>100449422</t>
         </is>
       </c>
       <c r="B27" s="2">
@@ -662,23 +743,26 @@
         <v>0</v>
       </c>
       <c r="D27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>100586493</t>
+          <t>100458264</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" s="2">
         <v>0</v>
@@ -687,16 +771,19 @@
         <v>0</v>
       </c>
       <c r="E28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" s="2">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>100587614</t>
+          <t>100474685</t>
         </is>
       </c>
       <c r="B29" s="2">
@@ -712,39 +799,45 @@
         <v>0</v>
       </c>
       <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>100596797</t>
+          <t>100492521</t>
         </is>
       </c>
       <c r="B30" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C30" s="2">
         <v>0</v>
       </c>
       <c r="D30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="2">
         <v>0</v>
       </c>
       <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>100627146</t>
+          <t>100503327</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" s="2">
         <v>0</v>
@@ -753,38 +846,44 @@
         <v>0</v>
       </c>
       <c r="E31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="2">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>100650054</t>
+          <t>100542499</t>
         </is>
       </c>
       <c r="B32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
       </c>
       <c r="D32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="2">
         <v>0</v>
       </c>
       <c r="F32" s="2">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>100730113</t>
+          <t>100586493</t>
         </is>
       </c>
       <c r="B33" s="2">
@@ -800,13 +899,16 @@
         <v>1</v>
       </c>
       <c r="F33" s="2">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>100752133</t>
+          <t>100587614</t>
         </is>
       </c>
       <c r="B34" s="2">
@@ -822,17 +924,20 @@
         <v>0</v>
       </c>
       <c r="F34" s="2">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>100770404</t>
+          <t>100596797</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
@@ -844,13 +949,16 @@
         <v>0</v>
       </c>
       <c r="F35" s="2">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>100774355</t>
+          <t>100626189</t>
         </is>
       </c>
       <c r="B36" s="2">
@@ -860,23 +968,26 @@
         <v>0</v>
       </c>
       <c r="D36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="2">
         <v>0</v>
       </c>
       <c r="F36" s="2">
         <v>0</v>
+      </c>
+      <c r="G36" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>100791007</t>
+          <t>100627146</t>
         </is>
       </c>
       <c r="B37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
@@ -888,35 +999,41 @@
         <v>0</v>
       </c>
       <c r="F37" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G37" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>100791832</t>
+          <t>100650054</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
       </c>
       <c r="D38" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G38" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>100823000</t>
+          <t>100730113</t>
         </is>
       </c>
       <c r="B39" s="2">
@@ -926,41 +1043,47 @@
         <v>0</v>
       </c>
       <c r="D39" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="2">
+        <v>0</v>
+      </c>
+      <c r="G39" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>100827249</t>
+          <t>100752133</t>
         </is>
       </c>
       <c r="B40" s="2">
         <v>0</v>
       </c>
       <c r="C40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" s="2">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>100862614</t>
+          <t>100754913</t>
         </is>
       </c>
       <c r="B41" s="2">
@@ -973,23 +1096,26 @@
         <v>0</v>
       </c>
       <c r="E41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" s="2">
         <v>0</v>
+      </c>
+      <c r="G41" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>100864321</t>
+          <t>100770404</t>
         </is>
       </c>
       <c r="B42" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
@@ -998,13 +1124,16 @@
         <v>0</v>
       </c>
       <c r="F42" s="2">
+        <v>0</v>
+      </c>
+      <c r="G42" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>100864434</t>
+          <t>100774355</t>
         </is>
       </c>
       <c r="B43" s="2">
@@ -1014,19 +1143,22 @@
         <v>0</v>
       </c>
       <c r="D43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="2">
         <v>0</v>
       </c>
       <c r="F43" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>100876713</t>
+          <t>100791007</t>
         </is>
       </c>
       <c r="B44" s="2">
@@ -1043,34 +1175,40 @@
       </c>
       <c r="F44" s="2">
         <v>1</v>
+      </c>
+      <c r="G44" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>100888704</t>
+          <t>100791832</t>
         </is>
       </c>
       <c r="B45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
       </c>
       <c r="D45" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="2">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>100890156</t>
+          <t>100795594</t>
         </is>
       </c>
       <c r="B46" s="2">
@@ -1086,13 +1224,16 @@
         <v>0</v>
       </c>
       <c r="F46" s="2">
+        <v>0</v>
+      </c>
+      <c r="G46" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>100938809</t>
+          <t>100813952</t>
         </is>
       </c>
       <c r="B47" s="2">
@@ -1108,57 +1249,66 @@
         <v>0</v>
       </c>
       <c r="F47" s="2">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="G47" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>100955968</t>
+          <t>100823000</t>
         </is>
       </c>
       <c r="B48" s="2">
         <v>0</v>
       </c>
       <c r="C48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E48" s="2">
         <v>0</v>
       </c>
       <c r="F48" s="2">
+        <v>0</v>
+      </c>
+      <c r="G48" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>100961074</t>
+          <t>100827249</t>
         </is>
       </c>
       <c r="B49" s="2">
         <v>0</v>
       </c>
       <c r="C49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" s="2">
         <v>0</v>
       </c>
       <c r="E49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G49" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>100972973</t>
+          <t>100862614</t>
         </is>
       </c>
       <c r="B50" s="2">
@@ -1168,26 +1318,29 @@
         <v>0</v>
       </c>
       <c r="D50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="2">
         <v>0</v>
+      </c>
+      <c r="G50" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>101013887</t>
+          <t>100864321</t>
         </is>
       </c>
       <c r="B51" s="2">
         <v>0</v>
       </c>
       <c r="C51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" s="2">
         <v>0</v>
@@ -1196,13 +1349,16 @@
         <v>0</v>
       </c>
       <c r="F51" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G51" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>101034585</t>
+          <t>100864434</t>
         </is>
       </c>
       <c r="B52" s="2">
@@ -1215,20 +1371,23 @@
         <v>0</v>
       </c>
       <c r="E52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" s="2">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>101037405</t>
+          <t>100876713</t>
         </is>
       </c>
       <c r="B53" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53" s="2">
         <v>0</v>
@@ -1240,17 +1399,20 @@
         <v>0</v>
       </c>
       <c r="F53" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G53" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>101102225</t>
+          <t>100888704</t>
         </is>
       </c>
       <c r="B54" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54" s="2">
         <v>0</v>
@@ -1259,16 +1421,19 @@
         <v>0</v>
       </c>
       <c r="E54" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" s="2">
+        <v>0</v>
+      </c>
+      <c r="G54" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>101108628</t>
+          <t>100890156</t>
         </is>
       </c>
       <c r="B55" s="2">
@@ -1285,12 +1450,15 @@
       </c>
       <c r="F55" s="2">
         <v>1</v>
+      </c>
+      <c r="G55" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>101111804</t>
+          <t>100938809</t>
         </is>
       </c>
       <c r="B56" s="2">
@@ -1300,41 +1468,47 @@
         <v>0</v>
       </c>
       <c r="D56" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" s="2">
         <v>0</v>
       </c>
       <c r="F56" s="2">
+        <v>3</v>
+      </c>
+      <c r="G56" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>101161925</t>
+          <t>100955968</t>
         </is>
       </c>
       <c r="B57" s="2">
         <v>0</v>
       </c>
       <c r="C57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57" s="2">
         <v>0</v>
       </c>
       <c r="F57" s="2">
+        <v>0</v>
+      </c>
+      <c r="G57" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>101174078</t>
+          <t>100960111</t>
         </is>
       </c>
       <c r="B58" s="2">
@@ -1347,20 +1521,23 @@
         <v>0</v>
       </c>
       <c r="E58" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" s="2">
         <v>0</v>
+      </c>
+      <c r="G58" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>101195987</t>
+          <t>100961074</t>
         </is>
       </c>
       <c r="B59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C59" s="2">
         <v>0</v>
@@ -1372,42 +1549,48 @@
         <v>0</v>
       </c>
       <c r="F59" s="2">
+        <v>1</v>
+      </c>
+      <c r="G59" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>101232925</t>
+          <t>100972973</t>
         </is>
       </c>
       <c r="B60" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
       </c>
       <c r="D60" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="2">
         <v>0</v>
       </c>
       <c r="F60" s="2">
+        <v>0</v>
+      </c>
+      <c r="G60" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>101295037</t>
+          <t>101013887</t>
         </is>
       </c>
       <c r="B61" s="2">
         <v>0</v>
       </c>
       <c r="C61" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61" s="2">
         <v>0</v>
@@ -1416,13 +1599,16 @@
         <v>0</v>
       </c>
       <c r="F61" s="2">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>101336693</t>
+          <t>101015607</t>
         </is>
       </c>
       <c r="B62" s="2">
@@ -1435,16 +1621,19 @@
         <v>0</v>
       </c>
       <c r="E62" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F62" s="2">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="G62" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>101372175</t>
+          <t>101034585</t>
         </is>
       </c>
       <c r="B63" s="2">
@@ -1454,41 +1643,47 @@
         <v>0</v>
       </c>
       <c r="D63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="2">
+        <v>0</v>
+      </c>
+      <c r="G63" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>101396394</t>
+          <t>101037405</t>
         </is>
       </c>
       <c r="B64" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" s="2">
         <v>0</v>
       </c>
       <c r="D64" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" s="2">
         <v>0</v>
       </c>
       <c r="F64" s="2">
+        <v>0</v>
+      </c>
+      <c r="G64" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>101407817</t>
+          <t>101102225</t>
         </is>
       </c>
       <c r="B65" s="2">
@@ -1504,20 +1699,23 @@
         <v>1</v>
       </c>
       <c r="F65" s="2">
+        <v>0</v>
+      </c>
+      <c r="G65" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>101434241</t>
+          <t>101108628</t>
         </is>
       </c>
       <c r="B66" s="2">
         <v>0</v>
       </c>
       <c r="C66" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66" s="2">
         <v>0</v>
@@ -1526,79 +1724,91 @@
         <v>0</v>
       </c>
       <c r="F66" s="2">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>101437685</t>
+          <t>101111804</t>
         </is>
       </c>
       <c r="B67" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C67" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" s="2">
         <v>0</v>
       </c>
       <c r="F67" s="2">
+        <v>0</v>
+      </c>
+      <c r="G67" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>101467964</t>
+          <t>101161925</t>
         </is>
       </c>
       <c r="B68" s="2">
         <v>0</v>
       </c>
       <c r="C68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" s="2">
         <v>0</v>
       </c>
       <c r="F68" s="2">
+        <v>0</v>
+      </c>
+      <c r="G68" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>101481537</t>
+          <t>101174078</t>
         </is>
       </c>
       <c r="B69" s="2">
         <v>0</v>
       </c>
       <c r="C69" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69" s="2">
         <v>0</v>
       </c>
       <c r="E69" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="2">
+        <v>0</v>
+      </c>
+      <c r="G69" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>101509593</t>
+          <t>101195987</t>
         </is>
       </c>
       <c r="B70" s="2">
@@ -1614,17 +1824,20 @@
         <v>0</v>
       </c>
       <c r="F70" s="2">
+        <v>0</v>
+      </c>
+      <c r="G70" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>101533995</t>
+          <t>101232925</t>
         </is>
       </c>
       <c r="B71" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C71" s="2">
         <v>0</v>
@@ -1636,17 +1849,20 @@
         <v>0</v>
       </c>
       <c r="F71" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G71" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>101573499</t>
+          <t>101237859</t>
         </is>
       </c>
       <c r="B72" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C72" s="2">
         <v>0</v>
@@ -1659,12 +1875,15 @@
       </c>
       <c r="F72" s="2">
         <v>0</v>
+      </c>
+      <c r="G72" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>101649796</t>
+          <t>101251735</t>
         </is>
       </c>
       <c r="B73" s="2">
@@ -1680,20 +1899,23 @@
         <v>0</v>
       </c>
       <c r="F73" s="2">
+        <v>0</v>
+      </c>
+      <c r="G73" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>101691981</t>
+          <t>101295037</t>
         </is>
       </c>
       <c r="B74" s="2">
         <v>0</v>
       </c>
       <c r="C74" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74" s="2">
         <v>0</v>
@@ -1702,13 +1924,16 @@
         <v>0</v>
       </c>
       <c r="F74" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G74" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>101800057</t>
+          <t>101335538</t>
         </is>
       </c>
       <c r="B75" s="2">
@@ -1724,57 +1949,66 @@
         <v>0</v>
       </c>
       <c r="F75" s="2">
+        <v>0</v>
+      </c>
+      <c r="G75" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>101836491</t>
+          <t>101336693</t>
         </is>
       </c>
       <c r="B76" s="2">
         <v>0</v>
       </c>
       <c r="C76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76" s="2">
         <v>0</v>
       </c>
       <c r="E76" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F76" s="2">
+        <v>4</v>
+      </c>
+      <c r="G76" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>101863433</t>
+          <t>101372175</t>
         </is>
       </c>
       <c r="B77" s="2">
         <v>0</v>
       </c>
       <c r="C77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D77" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77" s="2">
         <v>0</v>
       </c>
       <c r="F77" s="2">
+        <v>0</v>
+      </c>
+      <c r="G77" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>101875176</t>
+          <t>101396394</t>
         </is>
       </c>
       <c r="B78" s="2">
@@ -1784,23 +2018,26 @@
         <v>0</v>
       </c>
       <c r="D78" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F78" s="2">
+        <v>0</v>
+      </c>
+      <c r="G78" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>101885140</t>
+          <t>101407817</t>
         </is>
       </c>
       <c r="B79" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C79" s="2">
         <v>0</v>
@@ -1809,20 +2046,23 @@
         <v>0</v>
       </c>
       <c r="E79" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="2">
+        <v>0</v>
+      </c>
+      <c r="G79" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>101888773</t>
+          <t>101434241</t>
         </is>
       </c>
       <c r="B80" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -1834,20 +2074,23 @@
         <v>0</v>
       </c>
       <c r="F80" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G80" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>101903020</t>
+          <t>101437685</t>
         </is>
       </c>
       <c r="B81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D81" s="2">
         <v>0</v>
@@ -1856,13 +2099,16 @@
         <v>0</v>
       </c>
       <c r="F81" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G81" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>102006080</t>
+          <t>101467964</t>
         </is>
       </c>
       <c r="B82" s="2">
@@ -1872,19 +2118,22 @@
         <v>1</v>
       </c>
       <c r="D82" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82" s="2">
         <v>0</v>
       </c>
       <c r="F82" s="2">
+        <v>0</v>
+      </c>
+      <c r="G82" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>102006845</t>
+          <t>101481537</t>
         </is>
       </c>
       <c r="B83" s="2">
@@ -1900,17 +2149,20 @@
         <v>0</v>
       </c>
       <c r="F83" s="2">
+        <v>0</v>
+      </c>
+      <c r="G83" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>102050130</t>
+          <t>101509593</t>
         </is>
       </c>
       <c r="B84" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C84" s="2">
         <v>0</v>
@@ -1919,16 +2171,19 @@
         <v>0</v>
       </c>
       <c r="E84" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" s="2">
+        <v>0</v>
+      </c>
+      <c r="G84" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>102109244</t>
+          <t>101533995</t>
         </is>
       </c>
       <c r="B85" s="2">
@@ -1941,20 +2196,23 @@
         <v>0</v>
       </c>
       <c r="E85" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" s="2">
+        <v>1</v>
+      </c>
+      <c r="G85" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>102203438</t>
+          <t>101573499</t>
         </is>
       </c>
       <c r="B86" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C86" s="2">
         <v>0</v>
@@ -1963,16 +2221,19 @@
         <v>0</v>
       </c>
       <c r="E86" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" s="2">
         <v>0</v>
+      </c>
+      <c r="G86" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>102224443</t>
+          <t>101639078</t>
         </is>
       </c>
       <c r="B87" s="2">
@@ -1988,20 +2249,23 @@
         <v>0</v>
       </c>
       <c r="F87" s="2">
+        <v>0</v>
+      </c>
+      <c r="G87" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>102227253</t>
+          <t>101649796</t>
         </is>
       </c>
       <c r="B88" s="2">
         <v>0</v>
       </c>
       <c r="C88" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88" s="2">
         <v>0</v>
@@ -2010,13 +2274,16 @@
         <v>0</v>
       </c>
       <c r="F88" s="2">
+        <v>1</v>
+      </c>
+      <c r="G88" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>102282059</t>
+          <t>101691981</t>
         </is>
       </c>
       <c r="B89" s="2">
@@ -2029,23 +2296,26 @@
         <v>0</v>
       </c>
       <c r="E89" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" s="2">
+        <v>1</v>
+      </c>
+      <c r="G89" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>102299090</t>
+          <t>101800057</t>
         </is>
       </c>
       <c r="B90" s="2">
         <v>0</v>
       </c>
       <c r="C90" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D90" s="2">
         <v>0</v>
@@ -2054,35 +2324,41 @@
         <v>0</v>
       </c>
       <c r="F90" s="2">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>102307203</t>
+          <t>101836491</t>
         </is>
       </c>
       <c r="B91" s="2">
         <v>0</v>
       </c>
       <c r="C91" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" s="2">
         <v>0</v>
       </c>
       <c r="F91" s="2">
+        <v>0</v>
+      </c>
+      <c r="G91" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>102375097</t>
+          <t>101863433</t>
         </is>
       </c>
       <c r="B92" s="2">
@@ -2098,17 +2374,20 @@
         <v>0</v>
       </c>
       <c r="F92" s="2">
+        <v>0</v>
+      </c>
+      <c r="G92" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>102454744</t>
+          <t>101875176</t>
         </is>
       </c>
       <c r="B93" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93" s="2">
         <v>0</v>
@@ -2117,16 +2396,19 @@
         <v>0</v>
       </c>
       <c r="E93" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" s="2">
+        <v>0</v>
+      </c>
+      <c r="G93" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>102497144</t>
+          <t>101885140</t>
         </is>
       </c>
       <c r="B94" s="2">
@@ -2142,20 +2424,23 @@
         <v>0</v>
       </c>
       <c r="F94" s="2">
+        <v>0</v>
+      </c>
+      <c r="G94" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>102569542</t>
+          <t>101888773</t>
         </is>
       </c>
       <c r="B95" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C95" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95" s="2">
         <v>0</v>
@@ -2164,17 +2449,20 @@
         <v>0</v>
       </c>
       <c r="F95" s="2">
+        <v>1</v>
+      </c>
+      <c r="G95" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>102600124</t>
+          <t>101903020</t>
         </is>
       </c>
       <c r="B96" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C96" s="2">
         <v>0</v>
@@ -2186,57 +2474,66 @@
         <v>0</v>
       </c>
       <c r="F96" s="2">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>102655931</t>
+          <t>102006080</t>
         </is>
       </c>
       <c r="B97" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C97" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D97" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F97" s="2">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="G97" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>102673781</t>
+          <t>102006845</t>
         </is>
       </c>
       <c r="B98" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C98" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" s="2">
         <v>0</v>
       </c>
       <c r="F98" s="2">
+        <v>0</v>
+      </c>
+      <c r="G98" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>102690829</t>
+          <t>102050130</t>
         </is>
       </c>
       <c r="B99" s="2">
@@ -2246,23 +2543,26 @@
         <v>0</v>
       </c>
       <c r="D99" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="2">
+        <v>0</v>
+      </c>
+      <c r="G99" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>102698382</t>
+          <t>102109244</t>
         </is>
       </c>
       <c r="B100" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C100" s="2">
         <v>0</v>
@@ -2271,16 +2571,19 @@
         <v>0</v>
       </c>
       <c r="E100" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="2">
+        <v>0</v>
+      </c>
+      <c r="G100" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>102705657</t>
+          <t>102203438</t>
         </is>
       </c>
       <c r="B101" s="2">
@@ -2290,26 +2593,29 @@
         <v>0</v>
       </c>
       <c r="D101" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="2">
+        <v>0</v>
+      </c>
+      <c r="G101" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>102748593</t>
+          <t>102224443</t>
         </is>
       </c>
       <c r="B102" s="2">
         <v>0</v>
       </c>
       <c r="C102" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D102" s="2">
         <v>0</v>
@@ -2318,35 +2624,41 @@
         <v>0</v>
       </c>
       <c r="F102" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G102" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>102793147</t>
+          <t>102227253</t>
         </is>
       </c>
       <c r="B103" s="2">
         <v>0</v>
       </c>
       <c r="C103" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D103" s="2">
         <v>0</v>
       </c>
       <c r="E103" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F103" s="2">
+        <v>0</v>
+      </c>
+      <c r="G103" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1100043267</t>
+          <t>102282059</t>
         </is>
       </c>
       <c r="B104" s="2">
@@ -2359,23 +2671,26 @@
         <v>0</v>
       </c>
       <c r="E104" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G104" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1100079588</t>
+          <t>102299090</t>
         </is>
       </c>
       <c r="B105" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C105" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D105" s="2">
         <v>0</v>
@@ -2384,61 +2699,70 @@
         <v>0</v>
       </c>
       <c r="F105" s="2">
+        <v>0</v>
+      </c>
+      <c r="G105" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>500000823</t>
+          <t>102307203</t>
         </is>
       </c>
       <c r="B106" s="2">
         <v>0</v>
       </c>
       <c r="C106" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D106" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106" s="2">
         <v>0</v>
       </c>
       <c r="F106" s="2">
+        <v>0</v>
+      </c>
+      <c r="G106" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>500000921</t>
+          <t>102375097</t>
         </is>
       </c>
       <c r="B107" s="2">
         <v>0</v>
       </c>
       <c r="C107" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D107" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E107" s="2">
         <v>0</v>
       </c>
       <c r="F107" s="2">
+        <v>0</v>
+      </c>
+      <c r="G107" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>500002685</t>
+          <t>102454744</t>
         </is>
       </c>
       <c r="B108" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C108" s="2">
         <v>0</v>
@@ -2447,16 +2771,19 @@
         <v>0</v>
       </c>
       <c r="E108" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F108" s="2">
+        <v>0</v>
+      </c>
+      <c r="G108" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>500003288</t>
+          <t>102497144</t>
         </is>
       </c>
       <c r="B109" s="2">
@@ -2472,39 +2799,45 @@
         <v>0</v>
       </c>
       <c r="F109" s="2">
+        <v>0</v>
+      </c>
+      <c r="G109" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>500003682</t>
+          <t>102569542</t>
         </is>
       </c>
       <c r="B110" s="2">
         <v>0</v>
       </c>
       <c r="C110" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110" s="2">
         <v>0</v>
       </c>
       <c r="E110" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" s="2">
+        <v>1</v>
+      </c>
+      <c r="G110" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>500008320</t>
+          <t>102600124</t>
         </is>
       </c>
       <c r="B111" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C111" s="2">
         <v>0</v>
@@ -2516,35 +2849,41 @@
         <v>0</v>
       </c>
       <c r="F111" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G111" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>500009413</t>
+          <t>102655931</t>
         </is>
       </c>
       <c r="B112" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C112" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D112" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E112" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F112" s="2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G112" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>500016197</t>
+          <t>102673781</t>
         </is>
       </c>
       <c r="B113" s="2">
@@ -2554,19 +2893,22 @@
         <v>0</v>
       </c>
       <c r="D113" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E113" s="2">
         <v>0</v>
       </c>
       <c r="F113" s="2">
+        <v>0</v>
+      </c>
+      <c r="G113" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>500020789</t>
+          <t>102690829</t>
         </is>
       </c>
       <c r="B114" s="2">
@@ -2576,19 +2918,22 @@
         <v>0</v>
       </c>
       <c r="D114" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114" s="2">
+        <v>0</v>
+      </c>
+      <c r="G114" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>500023997</t>
+          <t>102698382</t>
         </is>
       </c>
       <c r="B115" s="2">
@@ -2604,13 +2949,16 @@
         <v>0</v>
       </c>
       <c r="F115" s="2">
+        <v>0</v>
+      </c>
+      <c r="G115" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>500024124</t>
+          <t>102705657</t>
         </is>
       </c>
       <c r="B116" s="2">
@@ -2626,35 +2974,41 @@
         <v>0</v>
       </c>
       <c r="F116" s="2">
+        <v>0</v>
+      </c>
+      <c r="G116" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>500028485</t>
+          <t>102748593</t>
         </is>
       </c>
       <c r="B117" s="2">
         <v>0</v>
       </c>
       <c r="C117" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E117" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F117" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G117" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>500031227</t>
+          <t>102793147</t>
         </is>
       </c>
       <c r="B118" s="2">
@@ -2667,23 +3021,26 @@
         <v>0</v>
       </c>
       <c r="E118" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F118" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G118" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>500031276</t>
+          <t>102796686</t>
         </is>
       </c>
       <c r="B119" s="2">
         <v>0</v>
       </c>
       <c r="C119" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D119" s="2">
         <v>0</v>
@@ -2693,16 +3050,19 @@
       </c>
       <c r="F119" s="2">
         <v>0</v>
+      </c>
+      <c r="G119" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>500032408</t>
+          <t>1100043267</t>
         </is>
       </c>
       <c r="B120" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C120" s="2">
         <v>0</v>
@@ -2714,42 +3074,48 @@
         <v>0</v>
       </c>
       <c r="F120" s="2">
+        <v>1</v>
+      </c>
+      <c r="G120" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>500035796</t>
+          <t>1100079588</t>
         </is>
       </c>
       <c r="B121" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C121" s="2">
         <v>0</v>
       </c>
       <c r="D121" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" s="2">
         <v>0</v>
       </c>
       <c r="F121" s="2">
+        <v>0</v>
+      </c>
+      <c r="G121" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>500036672</t>
+          <t>500000823</t>
         </is>
       </c>
       <c r="B122" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C122" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D122" s="2">
         <v>0</v>
@@ -2758,13 +3124,16 @@
         <v>0</v>
       </c>
       <c r="F122" s="2">
+        <v>0</v>
+      </c>
+      <c r="G122" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>500037006</t>
+          <t>500000921</t>
         </is>
       </c>
       <c r="B123" s="2">
@@ -2774,48 +3143,54 @@
         <v>0</v>
       </c>
       <c r="D123" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E123" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F123" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G123" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>500052051</t>
+          <t>500002685</t>
         </is>
       </c>
       <c r="B124" s="2">
         <v>0</v>
       </c>
       <c r="C124" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D124" s="2">
         <v>0</v>
       </c>
       <c r="E124" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="2">
+        <v>0</v>
+      </c>
+      <c r="G124" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>500057619</t>
+          <t>500003288</t>
         </is>
       </c>
       <c r="B125" s="2">
         <v>1</v>
       </c>
       <c r="C125" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D125" s="2">
         <v>0</v>
@@ -2824,17 +3199,20 @@
         <v>0</v>
       </c>
       <c r="F125" s="2">
+        <v>0</v>
+      </c>
+      <c r="G125" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>500060661</t>
+          <t>500003682</t>
         </is>
       </c>
       <c r="B126" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C126" s="2">
         <v>1</v>
@@ -2843,82 +3221,94 @@
         <v>0</v>
       </c>
       <c r="E126" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" s="2">
+        <v>0</v>
+      </c>
+      <c r="G126" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>500061708</t>
+          <t>500008320</t>
         </is>
       </c>
       <c r="B127" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C127" s="2">
         <v>0</v>
       </c>
       <c r="D127" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E127" s="2">
         <v>0</v>
       </c>
       <c r="F127" s="2">
+        <v>1</v>
+      </c>
+      <c r="G127" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>500066176</t>
+          <t>500009413</t>
         </is>
       </c>
       <c r="B128" s="2">
         <v>0</v>
       </c>
       <c r="C128" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D128" s="2">
         <v>0</v>
       </c>
       <c r="E128" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F128" s="2">
         <v>1</v>
+      </c>
+      <c r="G128" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>500094507</t>
+          <t>500016197</t>
         </is>
       </c>
       <c r="B129" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C129" s="2">
         <v>0</v>
       </c>
       <c r="D129" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129" s="2">
         <v>0</v>
       </c>
       <c r="F129" s="2">
+        <v>0</v>
+      </c>
+      <c r="G129" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>500101533</t>
+          <t>500020789</t>
         </is>
       </c>
       <c r="B130" s="2">
@@ -2931,60 +3321,69 @@
         <v>0</v>
       </c>
       <c r="E130" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G130" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>500111404</t>
+          <t>500023997</t>
         </is>
       </c>
       <c r="B131" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C131" s="2">
         <v>0</v>
       </c>
       <c r="D131" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131" s="2">
         <v>0</v>
       </c>
       <c r="F131" s="2">
+        <v>0</v>
+      </c>
+      <c r="G131" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>500115640</t>
+          <t>500024124</t>
         </is>
       </c>
       <c r="B132" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C132" s="2">
         <v>0</v>
       </c>
       <c r="D132" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E132" s="2">
         <v>0</v>
       </c>
       <c r="F132" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G132" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>500117284</t>
+          <t>500028485</t>
         </is>
       </c>
       <c r="B133" s="2">
@@ -2997,38 +3396,44 @@
         <v>1</v>
       </c>
       <c r="E133" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F133" s="2">
+        <v>1</v>
+      </c>
+      <c r="G133" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>500120216</t>
+          <t>500030111</t>
         </is>
       </c>
       <c r="B134" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C134" s="2">
         <v>0</v>
       </c>
       <c r="D134" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134" s="2">
         <v>0</v>
       </c>
       <c r="F134" s="2">
         <v>0</v>
+      </c>
+      <c r="G134" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>500126621</t>
+          <t>500031227</t>
         </is>
       </c>
       <c r="B135" s="2">
@@ -3038,26 +3443,29 @@
         <v>0</v>
       </c>
       <c r="D135" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135" s="2">
         <v>0</v>
       </c>
       <c r="F135" s="2">
+        <v>1</v>
+      </c>
+      <c r="G135" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>500128032</t>
+          <t>500031276</t>
         </is>
       </c>
       <c r="B136" s="2">
         <v>0</v>
       </c>
       <c r="C136" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D136" s="2">
         <v>0</v>
@@ -3066,17 +3474,20 @@
         <v>0</v>
       </c>
       <c r="F136" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G136" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>500128657</t>
+          <t>500032408</t>
         </is>
       </c>
       <c r="B137" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C137" s="2">
         <v>0</v>
@@ -3088,35 +3499,41 @@
         <v>0</v>
       </c>
       <c r="F137" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G137" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>500143502</t>
+          <t>500035796</t>
         </is>
       </c>
       <c r="B138" s="2">
         <v>0</v>
       </c>
       <c r="C138" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D138" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E138" s="2">
         <v>0</v>
       </c>
       <c r="F138" s="2">
+        <v>0</v>
+      </c>
+      <c r="G138" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>500143882</t>
+          <t>500036672</t>
         </is>
       </c>
       <c r="B139" s="2">
@@ -3132,17 +3549,20 @@
         <v>0</v>
       </c>
       <c r="F139" s="2">
+        <v>0</v>
+      </c>
+      <c r="G139" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>500146800</t>
+          <t>500037006</t>
         </is>
       </c>
       <c r="B140" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C140" s="2">
         <v>0</v>
@@ -3151,23 +3571,26 @@
         <v>0</v>
       </c>
       <c r="E140" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" s="2">
+        <v>1</v>
+      </c>
+      <c r="G140" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>500185891</t>
+          <t>500050269</t>
         </is>
       </c>
       <c r="B141" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C141" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D141" s="2">
         <v>0</v>
@@ -3177,12 +3600,15 @@
       </c>
       <c r="F141" s="2">
         <v>0</v>
+      </c>
+      <c r="G141" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>500187931</t>
+          <t>500052051</t>
         </is>
       </c>
       <c r="B142" s="2">
@@ -3198,20 +3624,23 @@
         <v>0</v>
       </c>
       <c r="F142" s="2">
+        <v>0</v>
+      </c>
+      <c r="G142" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>500199878</t>
+          <t>500057619</t>
         </is>
       </c>
       <c r="B143" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C143" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D143" s="2">
         <v>0</v>
@@ -3220,42 +3649,48 @@
         <v>0</v>
       </c>
       <c r="F143" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G143" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>500211718</t>
+          <t>500060661</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C144" s="2">
         <v>1</v>
       </c>
       <c r="D144" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E144" s="2">
         <v>0</v>
       </c>
       <c r="F144" s="2">
+        <v>0</v>
+      </c>
+      <c r="G144" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>500217683</t>
+          <t>500061708</t>
         </is>
       </c>
       <c r="B145" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C145" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D145" s="2">
         <v>1</v>
@@ -3264,20 +3699,23 @@
         <v>0</v>
       </c>
       <c r="F145" s="2">
+        <v>0</v>
+      </c>
+      <c r="G145" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>500236829</t>
+          <t>500066176</t>
         </is>
       </c>
       <c r="B146" s="2">
         <v>0</v>
       </c>
       <c r="C146" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D146" s="2">
         <v>0</v>
@@ -3286,17 +3724,20 @@
         <v>0</v>
       </c>
       <c r="F146" s="2">
+        <v>1</v>
+      </c>
+      <c r="G146" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>500240447</t>
+          <t>500067801</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C147" s="2">
         <v>0</v>
@@ -3309,19 +3750,22 @@
       </c>
       <c r="F147" s="2">
         <v>0</v>
+      </c>
+      <c r="G147" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>500241388</t>
+          <t>500080387</t>
         </is>
       </c>
       <c r="B148" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C148" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D148" s="2">
         <v>0</v>
@@ -3330,35 +3774,41 @@
         <v>0</v>
       </c>
       <c r="F148" s="2">
+        <v>0</v>
+      </c>
+      <c r="G148" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>500255345</t>
+          <t>500094507</t>
         </is>
       </c>
       <c r="B149" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C149" s="2">
         <v>0</v>
       </c>
       <c r="D149" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E149" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F149" s="2">
+        <v>0</v>
+      </c>
+      <c r="G149" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>500258101</t>
+          <t>500101533</t>
         </is>
       </c>
       <c r="B150" s="2">
@@ -3371,16 +3821,19 @@
         <v>0</v>
       </c>
       <c r="E150" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F150" s="2">
+        <v>1</v>
+      </c>
+      <c r="G150" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>500272158</t>
+          <t>500111404</t>
         </is>
       </c>
       <c r="B151" s="2">
@@ -3390,45 +3843,651 @@
         <v>0</v>
       </c>
       <c r="D151" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F151" s="2">
+        <v>0</v>
+      </c>
+      <c r="G151" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
+          <t>500115640</t>
+        </is>
+      </c>
+      <c r="B152" s="2">
+        <v>1</v>
+      </c>
+      <c r="C152" s="2">
+        <v>0</v>
+      </c>
+      <c r="D152" s="2">
+        <v>0</v>
+      </c>
+      <c r="E152" s="2">
+        <v>0</v>
+      </c>
+      <c r="F152" s="2">
+        <v>1</v>
+      </c>
+      <c r="G152" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>500117284</t>
+        </is>
+      </c>
+      <c r="B153" s="2">
+        <v>0</v>
+      </c>
+      <c r="C153" s="2">
+        <v>0</v>
+      </c>
+      <c r="D153" s="2">
+        <v>1</v>
+      </c>
+      <c r="E153" s="2">
+        <v>0</v>
+      </c>
+      <c r="F153" s="2">
+        <v>0</v>
+      </c>
+      <c r="G153" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>500120216</t>
+        </is>
+      </c>
+      <c r="B154" s="2">
+        <v>1</v>
+      </c>
+      <c r="C154" s="2">
+        <v>0</v>
+      </c>
+      <c r="D154" s="2">
+        <v>1</v>
+      </c>
+      <c r="E154" s="2">
+        <v>0</v>
+      </c>
+      <c r="F154" s="2">
+        <v>0</v>
+      </c>
+      <c r="G154" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>500126621</t>
+        </is>
+      </c>
+      <c r="B155" s="2">
+        <v>0</v>
+      </c>
+      <c r="C155" s="2">
+        <v>0</v>
+      </c>
+      <c r="D155" s="2">
+        <v>1</v>
+      </c>
+      <c r="E155" s="2">
+        <v>0</v>
+      </c>
+      <c r="F155" s="2">
+        <v>0</v>
+      </c>
+      <c r="G155" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>500127435</t>
+        </is>
+      </c>
+      <c r="B156" s="2">
+        <v>0</v>
+      </c>
+      <c r="C156" s="2">
+        <v>0</v>
+      </c>
+      <c r="D156" s="2">
+        <v>0</v>
+      </c>
+      <c r="E156" s="2">
+        <v>0</v>
+      </c>
+      <c r="F156" s="2">
+        <v>0</v>
+      </c>
+      <c r="G156" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>500128032</t>
+        </is>
+      </c>
+      <c r="B157" s="2">
+        <v>0</v>
+      </c>
+      <c r="C157" s="2">
+        <v>0</v>
+      </c>
+      <c r="D157" s="2">
+        <v>0</v>
+      </c>
+      <c r="E157" s="2">
+        <v>0</v>
+      </c>
+      <c r="F157" s="2">
+        <v>1</v>
+      </c>
+      <c r="G157" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>500128657</t>
+        </is>
+      </c>
+      <c r="B158" s="2">
+        <v>0</v>
+      </c>
+      <c r="C158" s="2">
+        <v>0</v>
+      </c>
+      <c r="D158" s="2">
+        <v>0</v>
+      </c>
+      <c r="E158" s="2">
+        <v>0</v>
+      </c>
+      <c r="F158" s="2">
+        <v>1</v>
+      </c>
+      <c r="G158" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>500143502</t>
+        </is>
+      </c>
+      <c r="B159" s="2">
+        <v>0</v>
+      </c>
+      <c r="C159" s="2">
+        <v>1</v>
+      </c>
+      <c r="D159" s="2">
+        <v>0</v>
+      </c>
+      <c r="E159" s="2">
+        <v>0</v>
+      </c>
+      <c r="F159" s="2">
+        <v>0</v>
+      </c>
+      <c r="G159" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>500143882</t>
+        </is>
+      </c>
+      <c r="B160" s="2">
+        <v>1</v>
+      </c>
+      <c r="C160" s="2">
+        <v>0</v>
+      </c>
+      <c r="D160" s="2">
+        <v>0</v>
+      </c>
+      <c r="E160" s="2">
+        <v>0</v>
+      </c>
+      <c r="F160" s="2">
+        <v>0</v>
+      </c>
+      <c r="G160" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>500146800</t>
+        </is>
+      </c>
+      <c r="B161" s="2">
+        <v>1</v>
+      </c>
+      <c r="C161" s="2">
+        <v>0</v>
+      </c>
+      <c r="D161" s="2">
+        <v>0</v>
+      </c>
+      <c r="E161" s="2">
+        <v>0</v>
+      </c>
+      <c r="F161" s="2">
+        <v>0</v>
+      </c>
+      <c r="G161" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>500185891</t>
+        </is>
+      </c>
+      <c r="B162" s="2">
+        <v>1</v>
+      </c>
+      <c r="C162" s="2">
+        <v>1</v>
+      </c>
+      <c r="D162" s="2">
+        <v>0</v>
+      </c>
+      <c r="E162" s="2">
+        <v>0</v>
+      </c>
+      <c r="F162" s="2">
+        <v>0</v>
+      </c>
+      <c r="G162" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>500186481</t>
+        </is>
+      </c>
+      <c r="B163" s="2">
+        <v>0</v>
+      </c>
+      <c r="C163" s="2">
+        <v>0</v>
+      </c>
+      <c r="D163" s="2">
+        <v>0</v>
+      </c>
+      <c r="E163" s="2">
+        <v>0</v>
+      </c>
+      <c r="F163" s="2">
+        <v>0</v>
+      </c>
+      <c r="G163" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>500187931</t>
+        </is>
+      </c>
+      <c r="B164" s="2">
+        <v>0</v>
+      </c>
+      <c r="C164" s="2">
+        <v>1</v>
+      </c>
+      <c r="D164" s="2">
+        <v>0</v>
+      </c>
+      <c r="E164" s="2">
+        <v>0</v>
+      </c>
+      <c r="F164" s="2">
+        <v>0</v>
+      </c>
+      <c r="G164" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>500199878</t>
+        </is>
+      </c>
+      <c r="B165" s="2">
+        <v>0</v>
+      </c>
+      <c r="C165" s="2">
+        <v>0</v>
+      </c>
+      <c r="D165" s="2">
+        <v>0</v>
+      </c>
+      <c r="E165" s="2">
+        <v>0</v>
+      </c>
+      <c r="F165" s="2">
+        <v>1</v>
+      </c>
+      <c r="G165" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>500211718</t>
+        </is>
+      </c>
+      <c r="B166" s="2">
+        <v>0</v>
+      </c>
+      <c r="C166" s="2">
+        <v>1</v>
+      </c>
+      <c r="D166" s="2">
+        <v>2</v>
+      </c>
+      <c r="E166" s="2">
+        <v>0</v>
+      </c>
+      <c r="F166" s="2">
+        <v>0</v>
+      </c>
+      <c r="G166" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>500217683</t>
+        </is>
+      </c>
+      <c r="B167" s="2">
+        <v>0</v>
+      </c>
+      <c r="C167" s="2">
+        <v>1</v>
+      </c>
+      <c r="D167" s="2">
+        <v>1</v>
+      </c>
+      <c r="E167" s="2">
+        <v>0</v>
+      </c>
+      <c r="F167" s="2">
+        <v>0</v>
+      </c>
+      <c r="G167" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>500235468</t>
+        </is>
+      </c>
+      <c r="B168" s="2">
+        <v>0</v>
+      </c>
+      <c r="C168" s="2">
+        <v>0</v>
+      </c>
+      <c r="D168" s="2">
+        <v>0</v>
+      </c>
+      <c r="E168" s="2">
+        <v>0</v>
+      </c>
+      <c r="F168" s="2">
+        <v>0</v>
+      </c>
+      <c r="G168" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>500236829</t>
+        </is>
+      </c>
+      <c r="B169" s="2">
+        <v>0</v>
+      </c>
+      <c r="C169" s="2">
+        <v>1</v>
+      </c>
+      <c r="D169" s="2">
+        <v>0</v>
+      </c>
+      <c r="E169" s="2">
+        <v>0</v>
+      </c>
+      <c r="F169" s="2">
+        <v>0</v>
+      </c>
+      <c r="G169" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>500240447</t>
+        </is>
+      </c>
+      <c r="B170" s="2">
+        <v>1</v>
+      </c>
+      <c r="C170" s="2">
+        <v>0</v>
+      </c>
+      <c r="D170" s="2">
+        <v>0</v>
+      </c>
+      <c r="E170" s="2">
+        <v>0</v>
+      </c>
+      <c r="F170" s="2">
+        <v>0</v>
+      </c>
+      <c r="G170" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>500241388</t>
+        </is>
+      </c>
+      <c r="B171" s="2">
+        <v>1</v>
+      </c>
+      <c r="C171" s="2">
+        <v>1</v>
+      </c>
+      <c r="D171" s="2">
+        <v>0</v>
+      </c>
+      <c r="E171" s="2">
+        <v>0</v>
+      </c>
+      <c r="F171" s="2">
+        <v>1</v>
+      </c>
+      <c r="G171" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>500255345</t>
+        </is>
+      </c>
+      <c r="B172" s="2">
+        <v>1</v>
+      </c>
+      <c r="C172" s="2">
+        <v>0</v>
+      </c>
+      <c r="D172" s="2">
+        <v>0</v>
+      </c>
+      <c r="E172" s="2">
+        <v>1</v>
+      </c>
+      <c r="F172" s="2">
+        <v>0</v>
+      </c>
+      <c r="G172" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>500258101</t>
+        </is>
+      </c>
+      <c r="B173" s="2">
+        <v>0</v>
+      </c>
+      <c r="C173" s="2">
+        <v>0</v>
+      </c>
+      <c r="D173" s="2">
+        <v>0</v>
+      </c>
+      <c r="E173" s="2">
+        <v>1</v>
+      </c>
+      <c r="F173" s="2">
+        <v>0</v>
+      </c>
+      <c r="G173" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>500272158</t>
+        </is>
+      </c>
+      <c r="B174" s="2">
+        <v>0</v>
+      </c>
+      <c r="C174" s="2">
+        <v>0</v>
+      </c>
+      <c r="D174" s="2">
+        <v>0</v>
+      </c>
+      <c r="E174" s="2">
+        <v>1</v>
+      </c>
+      <c r="F174" s="2">
+        <v>0</v>
+      </c>
+      <c r="G174" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>500274670</t>
+        </is>
+      </c>
+      <c r="B175" s="2">
+        <v>0</v>
+      </c>
+      <c r="C175" s="2">
+        <v>0</v>
+      </c>
+      <c r="D175" s="2">
+        <v>0</v>
+      </c>
+      <c r="E175" s="2">
+        <v>0</v>
+      </c>
+      <c r="F175" s="2">
+        <v>0</v>
+      </c>
+      <c r="G175" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
           <t>500284150</t>
         </is>
       </c>
-      <c r="B152" s="2">
-        <v>0</v>
-      </c>
-      <c r="C152" s="2">
-        <v>0</v>
-      </c>
-      <c r="D152" s="2">
-        <v>0</v>
-      </c>
-      <c r="E152" s="2">
-        <v>0</v>
-      </c>
-      <c r="F152" s="2">
-        <v>1</v>
+      <c r="B176" s="2">
+        <v>0</v>
+      </c>
+      <c r="C176" s="2">
+        <v>0</v>
+      </c>
+      <c r="D176" s="2">
+        <v>0</v>
+      </c>
+      <c r="E176" s="2">
+        <v>0</v>
+      </c>
+      <c r="F176" s="2">
+        <v>1</v>
+      </c>
+      <c r="G176" s="2">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F152"/>
+  <autoFilter ref="A1:G176"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q207"/>
+  <dimension ref="A1:Q248"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -4834,11 +5893,11 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="N19" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" s="2">
         <v>0</v>
@@ -12718,20 +13777,20 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="N127" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O127" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P127" s="2">
-        <v>17800</v>
+        <v>17900</v>
       </c>
       <c r="Q127" s="3">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="128">
@@ -18574,7 +19633,3000 @@
         <v>0.42</v>
       </c>
     </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>100035182</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>12990048217</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>[벚꽃EVENT]삼성 공식 갤럭시 S26 울트라 256GB 자급제 SM-S948N AI폰</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G208" s="2">
+        <v>1797320</v>
+      </c>
+      <c r="H208" s="2">
+        <v>1797400</v>
+      </c>
+      <c r="I208" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12990048217</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260226_28/1772111494282cMY32_JPEG/21919741122085266_275818346.jpg</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N208" s="2">
+        <v>1</v>
+      </c>
+      <c r="O208" s="2">
+        <v>0</v>
+      </c>
+      <c r="P208" s="2">
+        <v>1797320</v>
+      </c>
+      <c r="Q208" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>100038886</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>5733596435</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>[불스원] 레인OK 에탄올 3in1 코팅 워셔액 1800ml 6개</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G209" s="2">
+        <v>25500</v>
+      </c>
+      <c r="H209" s="2">
+        <v>47400</v>
+      </c>
+      <c r="I209" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5733596435</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20241024_216/17297292926191ykWl_JPEG/4291226713147041_188289058.jpg</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N209" s="2">
+        <v>1</v>
+      </c>
+      <c r="O209" s="2">
+        <v>0</v>
+      </c>
+      <c r="P209" s="2">
+        <v>25500</v>
+      </c>
+      <c r="Q209" s="3">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>100129181</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>11994705561</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>베지밀 고단백 두유 플레인 설탕 무첨가 저당두유 190ml 48팩 정식품 신제품</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G210" s="2">
+        <v>30900</v>
+      </c>
+      <c r="H210" s="2">
+        <v>62700</v>
+      </c>
+      <c r="I210" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11994705561</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251211_177/176541594968113ooW_JPEG/99548799785301545_399277971.jpg</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N210" s="2">
+        <v>1</v>
+      </c>
+      <c r="O210" s="2">
+        <v>0</v>
+      </c>
+      <c r="P210" s="2">
+        <v>30900</v>
+      </c>
+      <c r="Q210" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>스페셜 멤버십</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>100136792</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>13227143096</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>[올데이 프로젝트 PICK] 아몬드브리즈 커피 제로슈거 190ml 24팩 [도착보장]</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G211" s="2">
+        <v>19500</v>
+      </c>
+      <c r="H211" s="2">
+        <v>36000</v>
+      </c>
+      <c r="I211" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13227143096</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260327_231/1774594724404HSCHH_JPEG/39317148214335067_1068153746.jpg</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N211" s="2">
+        <v>1</v>
+      </c>
+      <c r="O211" s="2">
+        <v>0</v>
+      </c>
+      <c r="P211" s="2">
+        <v>19500</v>
+      </c>
+      <c r="Q211" s="3">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>100146361</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>13393240277</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>햇반 잡곡밥 나눔에디션 작은공기 130g, 36개 네이버 Only</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G212" s="2">
+        <v>35900</v>
+      </c>
+      <c r="H212" s="2">
+        <v>81000</v>
+      </c>
+      <c r="I212" s="3">
+        <v>0.55</v>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13393240277</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260415_68/1776212094866602O5_PNG/110344919655745166_1297950722.png</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N212" s="2">
+        <v>1</v>
+      </c>
+      <c r="O212" s="2">
+        <v>0</v>
+      </c>
+      <c r="P212" s="2">
+        <v>35900</v>
+      </c>
+      <c r="Q212" s="3">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>100261289</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>12651169341</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>샬랑 드 파리 지속력 좋은 안 지워지는 쥬얼 샤인 립스틱, 4.5g</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G213" s="2">
+        <v>20720</v>
+      </c>
+      <c r="H213" s="2">
+        <v>68000</v>
+      </c>
+      <c r="I213" s="3">
+        <v>0.69</v>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12651169341</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260402_194/1775091411829LjX5q_JPEG/17167444758084762_443082044.jpg</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N213" s="2">
+        <v>1</v>
+      </c>
+      <c r="O213" s="2">
+        <v>0</v>
+      </c>
+      <c r="P213" s="2">
+        <v>20720</v>
+      </c>
+      <c r="Q213" s="3">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>100262284</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>13166827580</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>[26년봄한정판] 초고농축 피죤 체리블라썸 섬유유연제 1.3L X 3개 +포켓몬스프레이피죤120ml</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G214" s="2">
+        <v>12900</v>
+      </c>
+      <c r="H214" s="2">
+        <v>26900</v>
+      </c>
+      <c r="I214" s="3">
+        <v>0.52</v>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13166827580</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260401_285/17750001032858Vs7L_PNG/29692616277752192_1912428133.png</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N214" s="2">
+        <v>1</v>
+      </c>
+      <c r="O214" s="2">
+        <v>0</v>
+      </c>
+      <c r="P214" s="2">
+        <v>12900</v>
+      </c>
+      <c r="Q214" s="3">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>100446531</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>10774752592</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>[체험팩][3+1/5+2] 국민 분식 쫀득한 찰순대 300g 1팩 돼지부속 외 분식간식</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G215" s="2">
+        <v>4400</v>
+      </c>
+      <c r="H215" s="2">
+        <v>9400</v>
+      </c>
+      <c r="I215" s="3">
+        <v>0.53</v>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10774752592</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20240828_165/1724834582585QTUDX_JPEG/44769558545730079_1977058594.jpg</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N215" s="2">
+        <v>1</v>
+      </c>
+      <c r="O215" s="2">
+        <v>0</v>
+      </c>
+      <c r="P215" s="2">
+        <v>4400</v>
+      </c>
+      <c r="Q215" s="3">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>100626189</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>13347367776</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>옥화식품 전통 수제 옥돌 구이 도시락김 5g, 36개</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G216" s="2">
+        <v>22500</v>
+      </c>
+      <c r="H216" s="2">
+        <v>23900</v>
+      </c>
+      <c r="I216" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13347367776</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250703_25/1751508042431i3VoQ_JPEG/26678325236701613_1280625940.jpg</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N216" s="2">
+        <v>1</v>
+      </c>
+      <c r="O216" s="2">
+        <v>0</v>
+      </c>
+      <c r="P216" s="2">
+        <v>22500</v>
+      </c>
+      <c r="Q216" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>100754913</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>11458037801</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>[4/20 11시 특가 오픈][네이버단독/정품용량증정] 한율 어린쑥 수분진정크림 더블 세트</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>뷰티/헬스</t>
+        </is>
+      </c>
+      <c r="G217" s="2">
+        <v>55960</v>
+      </c>
+      <c r="H217" s="2">
+        <v>76000</v>
+      </c>
+      <c r="I217" s="3">
+        <v>0.26</v>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11458037801</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260417_132/1776403082473cgT8j_JPEG/131231637399059928_795534127.jpg</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N217" s="2">
+        <v>1</v>
+      </c>
+      <c r="O217" s="2">
+        <v>0</v>
+      </c>
+      <c r="P217" s="2">
+        <v>55960</v>
+      </c>
+      <c r="Q217" s="3">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>100754913</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>13136819830</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>[4/20 11시 특가 오픈] 한율 보들은행잎 모공핏 마스크 (8+2) 10매 세트</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G218" s="2">
+        <v>13800</v>
+      </c>
+      <c r="H218" s="2">
+        <v>32000</v>
+      </c>
+      <c r="I218" s="3">
+        <v>0.56</v>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13136819830</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260416_6/1776300659266E91Hu_JPEG/2579468049675229_1249827719.jpg</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N218" s="2">
+        <v>1</v>
+      </c>
+      <c r="O218" s="2">
+        <v>0</v>
+      </c>
+      <c r="P218" s="2">
+        <v>13800</v>
+      </c>
+      <c r="Q218" s="3">
+        <v>0.56</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>스페셜 멤버십</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>100795594</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>5344455520</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>사세 매콤 점보 닭다리 (냉동) 1.3kg</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G219" s="2">
+        <v>16900</v>
+      </c>
+      <c r="H219" s="2">
+        <v>35800</v>
+      </c>
+      <c r="I219" s="3">
+        <v>0.52</v>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5344455520</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250717_8/1752716049601fdIk9_JPEG/85533313494816291_172638110.jpg</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N219" s="2">
+        <v>1</v>
+      </c>
+      <c r="O219" s="2">
+        <v>0</v>
+      </c>
+      <c r="P219" s="2">
+        <v>16900</v>
+      </c>
+      <c r="Q219" s="3">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>100813952</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>13233708453</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>풀무원생수 퍼플에디션 500ml, 40개</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G220" s="2">
+        <v>10900</v>
+      </c>
+      <c r="H220" s="2">
+        <v>21900</v>
+      </c>
+      <c r="I220" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13233708453</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260417_274/1776414930135Q1VY9_JPEG/110547763607475573_1494110704.jpg</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N220" s="2">
+        <v>1</v>
+      </c>
+      <c r="O220" s="2">
+        <v>0</v>
+      </c>
+      <c r="P220" s="2">
+        <v>10900</v>
+      </c>
+      <c r="Q220" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>100862614</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>10680715226</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>[네이버단독] 익스트림 김종국 블랙마카 2500 120정, 1개</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G221" s="2">
+        <v>31900</v>
+      </c>
+      <c r="H221" s="2">
+        <v>45000</v>
+      </c>
+      <c r="I221" s="3">
+        <v>0.29</v>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10680715226</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260309_170/1773043580018tinf2_JPEG/25744154171603324_2040586831.jpg</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N221" s="2">
+        <v>1</v>
+      </c>
+      <c r="O221" s="2">
+        <v>0</v>
+      </c>
+      <c r="P221" s="2">
+        <v>31900</v>
+      </c>
+      <c r="Q221" s="3">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>스페셜 멤버십</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>100876713</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>12017180356</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>연세우유 세브란스 전용목장 A2단백우유 고칼슘 180ml, 32개</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G222" s="2">
+        <v>26600</v>
+      </c>
+      <c r="H222" s="2">
+        <v>44000</v>
+      </c>
+      <c r="I222" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12017180356</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250707_40/17518615466231pteX_JPEG/65241528459894804_2081920437.jpg</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N222" s="2">
+        <v>1</v>
+      </c>
+      <c r="O222" s="2">
+        <v>0</v>
+      </c>
+      <c r="P222" s="2">
+        <v>26600</v>
+      </c>
+      <c r="Q222" s="3">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>100960111</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>13242144485</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>아이오페 UV 쉴드 선 프로텍터 듀오(50ml+50ml) SPF50+/PA++++ (증정) UV선 50ml(10ml X5ea)</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G223" s="2">
+        <v>53200</v>
+      </c>
+      <c r="H223" s="2">
+        <v>76000</v>
+      </c>
+      <c r="I223" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13242144485</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260317_113/1773708030137qyWdy_JPEG/36686557803102085_848133808.jpg</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N223" s="2">
+        <v>1</v>
+      </c>
+      <c r="O223" s="2">
+        <v>0</v>
+      </c>
+      <c r="P223" s="2">
+        <v>53200</v>
+      </c>
+      <c r="Q223" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>101015607</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>6257408984</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>멀티비타민 오쏘몰 이뮨 비타민 30일분 2박스 총 60일분 + 2일분 + 쇼핑백 이뮨샷</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>뷰티/헬스</t>
+        </is>
+      </c>
+      <c r="G224" s="2">
+        <v>197000</v>
+      </c>
+      <c r="H224" s="2">
+        <v>258000</v>
+      </c>
+      <c r="I224" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/6257408984</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250430_71/1745995899666A0C3y_JPEG/80128840784646447_1384676777.jpg</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N224" s="2">
+        <v>1</v>
+      </c>
+      <c r="O224" s="2">
+        <v>0</v>
+      </c>
+      <c r="P224" s="2">
+        <v>197000</v>
+      </c>
+      <c r="Q224" s="3">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>101237859</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>6849966589</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>제철꽃 10송이 미니생화다발</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G225" s="2">
+        <v>5900</v>
+      </c>
+      <c r="H225" s="2">
+        <v>10900</v>
+      </c>
+      <c r="I225" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/6849966589</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20240604_110/1717486546937Rtk2z_JPEG/118622435645662427_1018939627.jpg</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N225" s="2">
+        <v>1</v>
+      </c>
+      <c r="O225" s="2">
+        <v>0</v>
+      </c>
+      <c r="P225" s="2">
+        <v>5900</v>
+      </c>
+      <c r="Q225" s="3">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>101251735</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>13233143395</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>70년 전통의 사리원 부대찌개 600g 1팩</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G226" s="2">
+        <v>4500</v>
+      </c>
+      <c r="H226" s="2">
+        <v>10400</v>
+      </c>
+      <c r="I226" s="3">
+        <v>0.56</v>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13233143395</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20231116_24/1700112242477JiN7h_JPEG/ld9Y7_101775_1.jpg</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N226" s="2">
+        <v>1</v>
+      </c>
+      <c r="O226" s="2">
+        <v>0</v>
+      </c>
+      <c r="P226" s="2">
+        <v>4500</v>
+      </c>
+      <c r="Q226" s="3">
+        <v>0.56</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>101335538</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>11393996618</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>연세 키즈텐 042 어린이 청소년 키 성장 성장기 건강하게 크는 HT042 1개월</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>생활/주방</t>
+        </is>
+      </c>
+      <c r="G227" s="2">
+        <v>204000</v>
+      </c>
+      <c r="H227" s="2">
+        <v>328000</v>
+      </c>
+      <c r="I227" s="3">
+        <v>0.37</v>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11393996618</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260305_18/1772678345256laGCQ_JPEG/106723665914867261_2133950139.jpg</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N227" s="2">
+        <v>1</v>
+      </c>
+      <c r="O227" s="2">
+        <v>0</v>
+      </c>
+      <c r="P227" s="2">
+        <v>204000</v>
+      </c>
+      <c r="Q227" s="3">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>101573499</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>7999337429</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>그레인온 골드 카무트 효소 30포, 3개</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G228" s="2">
+        <v>44900</v>
+      </c>
+      <c r="H228" s="2">
+        <v>105000</v>
+      </c>
+      <c r="I228" s="3">
+        <v>0.57</v>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/7999337429</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260201_287/1769871686613RSlvz_JPEG/22587247070318414_1847670825.jpg</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N228" s="2">
+        <v>2</v>
+      </c>
+      <c r="O228" s="2">
+        <v>0</v>
+      </c>
+      <c r="P228" s="2">
+        <v>44900</v>
+      </c>
+      <c r="Q228" s="3">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>101639078</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>13228665919</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>[특가] 스누피가든</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G229" s="2">
+        <v>11700</v>
+      </c>
+      <c r="H229" s="2">
+        <v>13000</v>
+      </c>
+      <c r="I229" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13228665919</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260402_256/1775110489628DhQTS_JPEG/58185954398437896_184888946.jpg</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N229" s="2">
+        <v>1</v>
+      </c>
+      <c r="O229" s="2">
+        <v>0</v>
+      </c>
+      <c r="P229" s="2">
+        <v>11700</v>
+      </c>
+      <c r="Q229" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>101888773</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>12617301731</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>[냉장제품] 100% 앞다리! 수비드 공법 마스터 통 족발 1,200g 내외</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G230" s="2">
+        <v>13900</v>
+      </c>
+      <c r="H230" s="2">
+        <v>50900</v>
+      </c>
+      <c r="I230" s="3">
+        <v>0.72</v>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12617301731</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251031_78/1761896283498lkkHp_JPEG/24881137212749329_1303087141.jpg</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N230" s="2">
+        <v>1</v>
+      </c>
+      <c r="O230" s="2">
+        <v>0</v>
+      </c>
+      <c r="P230" s="2">
+        <v>13900</v>
+      </c>
+      <c r="Q230" s="3">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>102224443</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>11793390592</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>[N단독구성]델라고 프라이팬 베로 세라믹 코팅 인덕션 후라이팬 24cm</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G231" s="2">
+        <v>32900</v>
+      </c>
+      <c r="H231" s="2">
+        <v>49900</v>
+      </c>
+      <c r="I231" s="3">
+        <v>0.34</v>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11793390592</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250830_38/1756553449258eQXcL_PNG/70881554122506831_581833876.png</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N231" s="2">
+        <v>1</v>
+      </c>
+      <c r="O231" s="2">
+        <v>0</v>
+      </c>
+      <c r="P231" s="2">
+        <v>32900</v>
+      </c>
+      <c r="Q231" s="3">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>102655931</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>13330866512</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>[부산 상국이네] 인기 떡볶이 2종 (택1)</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G232" s="2">
+        <v>10</v>
+      </c>
+      <c r="H232" s="2">
+        <v>10</v>
+      </c>
+      <c r="I232" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13330866512</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250707_298/1751863690478EBqKa_JPEG/6510577919251430_1011290889.jpg</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N232" s="2">
+        <v>1</v>
+      </c>
+      <c r="O232" s="2">
+        <v>0</v>
+      </c>
+      <c r="P232" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q232" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>102655931</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>13380513075</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>[99달걀] 99 백색 구운란 30구 (15구＊2개입)</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G233" s="2">
+        <v>10990</v>
+      </c>
+      <c r="H233" s="2">
+        <v>10990</v>
+      </c>
+      <c r="I233" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13380513075</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260407_14/1775522459598sf6SC_JPEG/30184842568929312_1968990783.jpg</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N233" s="2">
+        <v>1</v>
+      </c>
+      <c r="O233" s="2">
+        <v>0</v>
+      </c>
+      <c r="P233" s="2">
+        <v>10990</v>
+      </c>
+      <c r="Q233" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>102796686</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>13377143332</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>기프트 SET(배달의민족&amp;올리브영 결합권 2만원권)</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G234" s="2">
+        <v>19000</v>
+      </c>
+      <c r="H234" s="2">
+        <v>20000</v>
+      </c>
+      <c r="I234" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13377143332</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260417_251/1776402570157oScoM_PNG/110535448717330740_1038398991.png</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N234" s="2">
+        <v>1</v>
+      </c>
+      <c r="O234" s="2">
+        <v>0</v>
+      </c>
+      <c r="P234" s="2">
+        <v>19000</v>
+      </c>
+      <c r="Q234" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>102796686</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>13377145961</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>기프트 SET(배달의민족&amp;올리브영 결합권 6만원권)</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G235" s="2">
+        <v>57000</v>
+      </c>
+      <c r="H235" s="2">
+        <v>60000</v>
+      </c>
+      <c r="I235" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13377145961</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260417_31/1776403078642CJ7xh_PNG/30921070997605905_470982027.png</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N235" s="2">
+        <v>1</v>
+      </c>
+      <c r="O235" s="2">
+        <v>0</v>
+      </c>
+      <c r="P235" s="2">
+        <v>57000</v>
+      </c>
+      <c r="Q235" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>500030111</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>9138687147</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>[농협홍삼 한삼인] 대용량 홍삼스틱 진세노사이드 홍삼진 굿데이스틱+쇼핑백 60포, 1개</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G236" s="2">
+        <v>30500</v>
+      </c>
+      <c r="H236" s="2">
+        <v>59600</v>
+      </c>
+      <c r="I236" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/9138687147</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260210_101/1770687617530Td7By_JPEG/9223585513518539_1475902648.jpg</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N236" s="2">
+        <v>1</v>
+      </c>
+      <c r="O236" s="2">
+        <v>0</v>
+      </c>
+      <c r="P236" s="2">
+        <v>30500</v>
+      </c>
+      <c r="Q236" s="3">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>500050269</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>10730284372</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>필립스 면도기 S9000 프레스티지 전기면도기 SP9887/36</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G237" s="2">
+        <v>337510</v>
+      </c>
+      <c r="H237" s="2">
+        <v>649000</v>
+      </c>
+      <c r="I237" s="3">
+        <v>0.47</v>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10730284372</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20241030_157/1730266277044uBtYj_JPEG/80440779446642787_1547443893.jpg</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N237" s="2">
+        <v>1</v>
+      </c>
+      <c r="O237" s="2">
+        <v>0</v>
+      </c>
+      <c r="P237" s="2">
+        <v>337510</v>
+      </c>
+      <c r="Q237" s="3">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>500067801</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>12799575836</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>닥터포헤어 저자극 볼륨강화 탈모샴푸 폴리젠 씨크닝 샴푸 대용량 500ml+500ml리필+100ml</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>뷰티/헬스</t>
+        </is>
+      </c>
+      <c r="G238" s="2">
+        <v>30900</v>
+      </c>
+      <c r="H238" s="2">
+        <v>60000</v>
+      </c>
+      <c r="I238" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12799575836</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260419_32/17766096688331psSS_JPEG/110742521948388433_1339842838.jpg</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N238" s="2">
+        <v>1</v>
+      </c>
+      <c r="O238" s="2">
+        <v>0</v>
+      </c>
+      <c r="P238" s="2">
+        <v>30900</v>
+      </c>
+      <c r="Q238" s="3">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>500080387</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>13098960958</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>가온 TPE 카매트 오니핏 발매트 발판 고무 차량 코일 바닥 앞좌석</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G239" s="2">
+        <v>51900</v>
+      </c>
+      <c r="H239" s="2">
+        <v>96000</v>
+      </c>
+      <c r="I239" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13098960958</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260212_287/17708814941347hHHb_JPEG/21442268025919721_51179285.jpg</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N239" s="2">
+        <v>1</v>
+      </c>
+      <c r="O239" s="2">
+        <v>0</v>
+      </c>
+      <c r="P239" s="2">
+        <v>51900</v>
+      </c>
+      <c r="Q239" s="3">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>500115640</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>11620124819</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>고당도 프리미엄 오렌지</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G240" s="2">
+        <v>14900</v>
+      </c>
+      <c r="H240" s="2">
+        <v>30000</v>
+      </c>
+      <c r="I240" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11620124819</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260211_247/17707856374989j11s_JPEG/2487353364056894_679540330.jpg</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N240" s="2">
+        <v>1</v>
+      </c>
+      <c r="O240" s="2">
+        <v>0</v>
+      </c>
+      <c r="P240" s="2">
+        <v>14900</v>
+      </c>
+      <c r="Q240" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>500115640</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>4454797599</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>해남 고구마 꿀고구마 3kg 5kg 베니하루카 황금 호박고구마</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G241" s="2">
+        <v>9900</v>
+      </c>
+      <c r="H241" s="2">
+        <v>19200</v>
+      </c>
+      <c r="I241" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/4454797599</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20240708_11/1720400686064EUROn_JPEG/64960574792533730_1297508852.jpg</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N241" s="2">
+        <v>1</v>
+      </c>
+      <c r="O241" s="2">
+        <v>0</v>
+      </c>
+      <c r="P241" s="2">
+        <v>9900</v>
+      </c>
+      <c r="Q241" s="3">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>500126621</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2769814493</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>떡미당 리얼 인절미 2종 콩가루 / 호박카스테라 각300g</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G242" s="2">
+        <v>12500</v>
+      </c>
+      <c r="H242" s="2">
+        <v>17500</v>
+      </c>
+      <c r="I242" s="3">
+        <v>0.28</v>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/2769814493</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260317_90/1773708083020Yi1Sx_JPEG/108440741989453082_630582007.jpg</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N242" s="2">
+        <v>1</v>
+      </c>
+      <c r="O242" s="2">
+        <v>0</v>
+      </c>
+      <c r="P242" s="2">
+        <v>12500</v>
+      </c>
+      <c r="Q242" s="3">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>500127435</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>385581924</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>국산 새콤달콤 무농약 햇 블루베리 특사이즈 생과 500g 벌크형 대용량</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G243" s="2">
+        <v>33900</v>
+      </c>
+      <c r="H243" s="2">
+        <v>100000</v>
+      </c>
+      <c r="I243" s="3">
+        <v>0.66</v>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/385581924</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250508_88/1746690034960X5UqJ_JPEG/83053682345138998_2045128461.jpg</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N243" s="2">
+        <v>1</v>
+      </c>
+      <c r="O243" s="2">
+        <v>0</v>
+      </c>
+      <c r="P243" s="2">
+        <v>33900</v>
+      </c>
+      <c r="Q243" s="3">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>500146800</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>12827166492</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>[슈퍼적립 1+1세트] 엠앤엠즈 유리컵 기획팩(엠앤엠즈 밀크 145g)</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G244" s="2">
+        <v>14280</v>
+      </c>
+      <c r="H244" s="2">
+        <v>23800</v>
+      </c>
+      <c r="I244" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12827166492</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260415_276/1776226288648mjuaG_JPEG/110359191778230751_1935657921.jpg</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N244" s="2">
+        <v>1</v>
+      </c>
+      <c r="O244" s="2">
+        <v>0</v>
+      </c>
+      <c r="P244" s="2">
+        <v>14280</v>
+      </c>
+      <c r="Q244" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>500186481</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>453744143</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>[에버조이] 건식 좌훈 족욕기 (JOY-010)</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G245" s="2">
+        <v>122000</v>
+      </c>
+      <c r="H245" s="2">
+        <v>159000</v>
+      </c>
+      <c r="I245" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/453744143</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250619_255/1750299376455Ft2zo_PNG/84432192580468189_376866213.png</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N245" s="2">
+        <v>1</v>
+      </c>
+      <c r="O245" s="2">
+        <v>0</v>
+      </c>
+      <c r="P245" s="2">
+        <v>122000</v>
+      </c>
+      <c r="Q245" s="3">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>500217683</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>8038993732</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>(신선) 하림 자연실록 무항생제 IFF 닭가슴살 1kg 2봉</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G246" s="2">
+        <v>17900</v>
+      </c>
+      <c r="H246" s="2">
+        <v>22000</v>
+      </c>
+      <c r="I246" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/8038993732</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250314_28/1741926427395jIkTz_PNG/28001853186439274_1006461946.png</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N246" s="2">
+        <v>2</v>
+      </c>
+      <c r="O246" s="2">
+        <v>1</v>
+      </c>
+      <c r="P246" s="2">
+        <v>17900</v>
+      </c>
+      <c r="Q246" s="3">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>스페셜 체험딜</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>500235468</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>13161273678</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>[체험딜] 슈얼리 디지털 임신 테스트기 7개입</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G247" s="2">
+        <v>10900</v>
+      </c>
+      <c r="H247" s="2">
+        <v>23500</v>
+      </c>
+      <c r="I247" s="3">
+        <v>0.53</v>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13161273678</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260122_243/1769057294916cs2W0_JPEG/42044148066764022_1483900089.jpg</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N247" s="2">
+        <v>1</v>
+      </c>
+      <c r="O247" s="2">
+        <v>0</v>
+      </c>
+      <c r="P247" s="2">
+        <v>10900</v>
+      </c>
+      <c r="Q247" s="3">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>스페셜 체험딜</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>500274670</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>13297961693</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>홈트너 제습제 옷장제습제 습기제거제 서랍용 45g, 5개</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G248" s="2">
+        <v>2500</v>
+      </c>
+      <c r="H248" s="2">
+        <v>6900</v>
+      </c>
+      <c r="I248" s="3">
+        <v>0.63</v>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13297961693</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260324_232/17743348715836a2IQ_PNG/59291791634294585_1655335827.png</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N248" s="2">
+        <v>1</v>
+      </c>
+      <c r="O248" s="2">
+        <v>0</v>
+      </c>
+      <c r="P248" s="2">
+        <v>2500</v>
+      </c>
+      <c r="Q248" s="3">
+        <v>0.63</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q207"/>
+  <autoFilter ref="A1:Q248"/>
 </worksheet>
 </file>
--- a/data/derived/todaysdeal-analysis.xlsx
+++ b/data/derived/todaysdeal-analysis.xlsx
@@ -57,7 +57,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G176"/>
+  <dimension ref="A1:H204"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -66,6 +66,7 @@
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -104,6 +105,11 @@
           <t>2026-04-20</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -129,11 +135,14 @@
       <c r="G2" s="2">
         <v>0</v>
       </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>100035182</t>
+          <t>100003305</t>
         </is>
       </c>
       <c r="B3" s="2">
@@ -152,13 +161,16 @@
         <v>0</v>
       </c>
       <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>100038886</t>
+          <t>100035182</t>
         </is>
       </c>
       <c r="B4" s="2">
@@ -178,12 +190,15 @@
       </c>
       <c r="G4" s="2">
         <v>1</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>100129181</t>
+          <t>100038886</t>
         </is>
       </c>
       <c r="B5" s="2">
@@ -203,12 +218,15 @@
       </c>
       <c r="G5" s="2">
         <v>1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>100131340</t>
+          <t>100129181</t>
         </is>
       </c>
       <c r="B6" s="2">
@@ -218,7 +236,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="2">
         <v>0</v>
@@ -227,13 +245,16 @@
         <v>0</v>
       </c>
       <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>100136792</t>
+          <t>100131340</t>
         </is>
       </c>
       <c r="B7" s="2">
@@ -243,51 +264,57 @@
         <v>0</v>
       </c>
       <c r="D7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2">
         <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>100146361</t>
+          <t>100136792</t>
         </is>
       </c>
       <c r="B8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>100181508</t>
+          <t>100137620</t>
         </is>
       </c>
       <c r="B9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" s="2">
         <v>0</v>
@@ -303,19 +330,22 @@
       </c>
       <c r="G9" s="2">
         <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>100187146</t>
+          <t>100146361</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
@@ -327,20 +357,23 @@
         <v>0</v>
       </c>
       <c r="G10" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>100208089</t>
+          <t>100181508</t>
         </is>
       </c>
       <c r="B11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
@@ -352,13 +385,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>100261289</t>
+          <t>100187146</t>
         </is>
       </c>
       <c r="B12" s="2">
@@ -371,19 +407,22 @@
         <v>0</v>
       </c>
       <c r="E12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
       </c>
       <c r="G12" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>100262120</t>
+          <t>100208089</t>
         </is>
       </c>
       <c r="B13" s="2">
@@ -403,12 +442,15 @@
       </c>
       <c r="G13" s="2">
         <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>100262284</t>
+          <t>100261289</t>
         </is>
       </c>
       <c r="B14" s="2">
@@ -428,12 +470,15 @@
       </c>
       <c r="G14" s="2">
         <v>1</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>100265766</t>
+          <t>100262120</t>
         </is>
       </c>
       <c r="B15" s="2">
@@ -452,20 +497,23 @@
         <v>0</v>
       </c>
       <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>100274539</t>
+          <t>100262284</t>
         </is>
       </c>
       <c r="B16" s="2">
         <v>0</v>
       </c>
       <c r="C16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
@@ -477,17 +525,20 @@
         <v>0</v>
       </c>
       <c r="G16" s="2">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>100292269</t>
+          <t>100265349</t>
         </is>
       </c>
       <c r="B17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C17" s="2">
         <v>0</v>
@@ -503,12 +554,15 @@
       </c>
       <c r="G17" s="2">
         <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>100292757</t>
+          <t>100265766</t>
         </is>
       </c>
       <c r="B18" s="2">
@@ -527,13 +581,16 @@
         <v>0</v>
       </c>
       <c r="G18" s="2">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>100305602</t>
+          <t>100274539</t>
         </is>
       </c>
       <c r="B19" s="2">
@@ -543,7 +600,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2">
         <v>0</v>
@@ -552,20 +609,23 @@
         <v>0</v>
       </c>
       <c r="G19" s="2">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>100326348</t>
+          <t>100292269</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
@@ -577,20 +637,23 @@
         <v>0</v>
       </c>
       <c r="G20" s="2">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>100327929</t>
+          <t>100292757</t>
         </is>
       </c>
       <c r="B21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
@@ -602,48 +665,54 @@
         <v>0</v>
       </c>
       <c r="G21" s="2">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>100336563</t>
+          <t>100305602</t>
         </is>
       </c>
       <c r="B22" s="2">
         <v>0</v>
       </c>
       <c r="C22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2">
         <v>0</v>
       </c>
       <c r="G22" s="2">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>100340418</t>
+          <t>100326348</t>
         </is>
       </c>
       <c r="B23" s="2">
         <v>0</v>
       </c>
       <c r="C23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2">
         <v>0</v>
@@ -653,19 +722,22 @@
       </c>
       <c r="G23" s="2">
         <v>0</v>
+      </c>
+      <c r="H23" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>100387111</t>
+          <t>100327929</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
@@ -677,13 +749,16 @@
         <v>0</v>
       </c>
       <c r="G24" s="2">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>100419781</t>
+          <t>100336563</t>
         </is>
       </c>
       <c r="B25" s="2">
@@ -702,13 +777,16 @@
         <v>0</v>
       </c>
       <c r="G25" s="2">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>100446531</t>
+          <t>100340418</t>
         </is>
       </c>
       <c r="B26" s="2">
@@ -718,51 +796,57 @@
         <v>0</v>
       </c>
       <c r="D26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="2">
         <v>0</v>
       </c>
       <c r="F26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>100449422</t>
+          <t>100387111</t>
         </is>
       </c>
       <c r="B27" s="2">
         <v>0</v>
       </c>
       <c r="C27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
       </c>
       <c r="E27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2">
         <v>0</v>
       </c>
       <c r="G27" s="2">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>100458264</t>
+          <t>100419781</t>
         </is>
       </c>
       <c r="B28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" s="2">
         <v>0</v>
@@ -771,19 +855,22 @@
         <v>0</v>
       </c>
       <c r="E28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="2">
         <v>0</v>
       </c>
       <c r="G28" s="2">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>100474685</t>
+          <t>100446531</t>
         </is>
       </c>
       <c r="B29" s="2">
@@ -793,22 +880,25 @@
         <v>0</v>
       </c>
       <c r="D29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="2">
         <v>0</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H29" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>100492521</t>
+          <t>100449422</t>
         </is>
       </c>
       <c r="B30" s="2">
@@ -818,26 +908,29 @@
         <v>0</v>
       </c>
       <c r="D30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="2">
         <v>0</v>
       </c>
       <c r="G30" s="2">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>100503327</t>
+          <t>100458264</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C31" s="2">
         <v>0</v>
@@ -846,19 +939,22 @@
         <v>0</v>
       </c>
       <c r="E31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="2">
         <v>0</v>
       </c>
       <c r="G31" s="2">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>100542499</t>
+          <t>100474685</t>
         </is>
       </c>
       <c r="B32" s="2">
@@ -877,13 +973,16 @@
         <v>0</v>
       </c>
       <c r="G32" s="2">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>100586493</t>
+          <t>100492521</t>
         </is>
       </c>
       <c r="B33" s="2">
@@ -893,22 +992,25 @@
         <v>0</v>
       </c>
       <c r="D33" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" s="2">
         <v>0</v>
       </c>
       <c r="G33" s="2">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>100587614</t>
+          <t>100503327</t>
         </is>
       </c>
       <c r="B34" s="2">
@@ -918,32 +1020,35 @@
         <v>0</v>
       </c>
       <c r="D34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="2">
         <v>0</v>
       </c>
       <c r="G34" s="2">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>100596797</t>
+          <t>100542499</t>
         </is>
       </c>
       <c r="B35" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
       </c>
       <c r="D35" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="2">
         <v>0</v>
@@ -952,13 +1057,16 @@
         <v>0</v>
       </c>
       <c r="G35" s="2">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>100626189</t>
+          <t>100585383</t>
         </is>
       </c>
       <c r="B36" s="2">
@@ -977,17 +1085,20 @@
         <v>0</v>
       </c>
       <c r="G36" s="2">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>100627146</t>
+          <t>100586493</t>
         </is>
       </c>
       <c r="B37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
@@ -996,29 +1107,32 @@
         <v>0</v>
       </c>
       <c r="E37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="2">
         <v>0</v>
       </c>
       <c r="G37" s="2">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>100650054</t>
+          <t>100587614</t>
         </is>
       </c>
       <c r="B38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
       </c>
       <c r="D38" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="2">
         <v>0</v>
@@ -1027,17 +1141,20 @@
         <v>0</v>
       </c>
       <c r="G38" s="2">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>100730113</t>
+          <t>100596797</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
@@ -1046,19 +1163,22 @@
         <v>0</v>
       </c>
       <c r="E39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" s="2">
         <v>0</v>
       </c>
       <c r="G39" s="2">
         <v>0</v>
+      </c>
+      <c r="H39" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>100752133</t>
+          <t>100626189</t>
         </is>
       </c>
       <c r="B40" s="2">
@@ -1068,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" s="2">
         <v>0</v>
@@ -1077,17 +1197,20 @@
         <v>0</v>
       </c>
       <c r="G40" s="2">
+        <v>1</v>
+      </c>
+      <c r="H40" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>100754913</t>
+          <t>100627146</t>
         </is>
       </c>
       <c r="B41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
@@ -1102,13 +1225,16 @@
         <v>0</v>
       </c>
       <c r="G41" s="2">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="H41" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>100770404</t>
+          <t>100650054</t>
         </is>
       </c>
       <c r="B42" s="2">
@@ -1128,12 +1254,15 @@
       </c>
       <c r="G42" s="2">
         <v>0</v>
+      </c>
+      <c r="H42" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>100774355</t>
+          <t>100688696</t>
         </is>
       </c>
       <c r="B43" s="2">
@@ -1143,7 +1272,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" s="2">
         <v>0</v>
@@ -1153,12 +1282,15 @@
       </c>
       <c r="G43" s="2">
         <v>0</v>
+      </c>
+      <c r="H43" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>100791007</t>
+          <t>100697164</t>
         </is>
       </c>
       <c r="B44" s="2">
@@ -1174,16 +1306,19 @@
         <v>0</v>
       </c>
       <c r="F44" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" s="2">
         <v>0</v>
+      </c>
+      <c r="H44" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>100791832</t>
+          <t>100730113</t>
         </is>
       </c>
       <c r="B45" s="2">
@@ -1193,22 +1328,25 @@
         <v>0</v>
       </c>
       <c r="D45" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E45" s="2">
         <v>1</v>
       </c>
       <c r="F45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="2">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>100795594</t>
+          <t>100752133</t>
         </is>
       </c>
       <c r="B46" s="2">
@@ -1218,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" s="2">
         <v>0</v>
@@ -1227,13 +1365,16 @@
         <v>0</v>
       </c>
       <c r="G46" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H46" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>100813952</t>
+          <t>100754913</t>
         </is>
       </c>
       <c r="B47" s="2">
@@ -1252,23 +1393,26 @@
         <v>0</v>
       </c>
       <c r="G47" s="2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H47" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>100823000</t>
+          <t>100770404</t>
         </is>
       </c>
       <c r="B48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
       </c>
       <c r="D48" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E48" s="2">
         <v>0</v>
@@ -1277,38 +1421,44 @@
         <v>0</v>
       </c>
       <c r="G48" s="2">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>100827249</t>
+          <t>100774355</t>
         </is>
       </c>
       <c r="B49" s="2">
         <v>0</v>
       </c>
       <c r="C49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" s="2">
         <v>0</v>
       </c>
       <c r="G49" s="2">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>100862614</t>
+          <t>100791007</t>
         </is>
       </c>
       <c r="B50" s="2">
@@ -1321,44 +1471,50 @@
         <v>0</v>
       </c>
       <c r="E50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H50" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>100864321</t>
+          <t>100791832</t>
         </is>
       </c>
       <c r="B51" s="2">
         <v>0</v>
       </c>
       <c r="C51" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" s="2">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>100864434</t>
+          <t>100795594</t>
         </is>
       </c>
       <c r="B52" s="2">
@@ -1374,16 +1530,19 @@
         <v>0</v>
       </c>
       <c r="F52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" s="2">
+        <v>1</v>
+      </c>
+      <c r="H52" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>100876713</t>
+          <t>100813952</t>
         </is>
       </c>
       <c r="B53" s="2">
@@ -1399,26 +1558,29 @@
         <v>0</v>
       </c>
       <c r="F53" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" s="2">
         <v>1</v>
+      </c>
+      <c r="H53" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>100888704</t>
+          <t>100823000</t>
         </is>
       </c>
       <c r="B54" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54" s="2">
         <v>0</v>
       </c>
       <c r="D54" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E54" s="2">
         <v>0</v>
@@ -1427,38 +1589,44 @@
         <v>0</v>
       </c>
       <c r="G54" s="2">
+        <v>0</v>
+      </c>
+      <c r="H54" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>100890156</t>
+          <t>100827249</t>
         </is>
       </c>
       <c r="B55" s="2">
         <v>0</v>
       </c>
       <c r="C55" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" s="2">
         <v>0</v>
       </c>
       <c r="E55" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" s="2">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>100938809</t>
+          <t>100862614</t>
         </is>
       </c>
       <c r="B56" s="2">
@@ -1471,19 +1639,22 @@
         <v>0</v>
       </c>
       <c r="E56" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G56" s="2">
+        <v>1</v>
+      </c>
+      <c r="H56" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>100955968</t>
+          <t>100864321</t>
         </is>
       </c>
       <c r="B57" s="2">
@@ -1502,13 +1673,16 @@
         <v>0</v>
       </c>
       <c r="G57" s="2">
+        <v>0</v>
+      </c>
+      <c r="H57" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>100960111</t>
+          <t>100864434</t>
         </is>
       </c>
       <c r="B58" s="2">
@@ -1524,16 +1698,19 @@
         <v>0</v>
       </c>
       <c r="F58" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H58" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>100961074</t>
+          <t>100876713</t>
         </is>
       </c>
       <c r="B59" s="2">
@@ -1552,23 +1729,26 @@
         <v>1</v>
       </c>
       <c r="G59" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H59" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>100972973</t>
+          <t>100888704</t>
         </is>
       </c>
       <c r="B60" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
       </c>
       <c r="D60" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" s="2">
         <v>0</v>
@@ -1577,13 +1757,16 @@
         <v>0</v>
       </c>
       <c r="G60" s="2">
+        <v>0</v>
+      </c>
+      <c r="H60" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>101013887</t>
+          <t>100890156</t>
         </is>
       </c>
       <c r="B61" s="2">
@@ -1602,13 +1785,16 @@
         <v>1</v>
       </c>
       <c r="G61" s="2">
+        <v>0</v>
+      </c>
+      <c r="H61" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>101015607</t>
+          <t>100894278</t>
         </is>
       </c>
       <c r="B62" s="2">
@@ -1627,13 +1813,16 @@
         <v>0</v>
       </c>
       <c r="G62" s="2">
+        <v>0</v>
+      </c>
+      <c r="H62" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>101034585</t>
+          <t>100938809</t>
         </is>
       </c>
       <c r="B63" s="2">
@@ -1646,26 +1835,29 @@
         <v>0</v>
       </c>
       <c r="E63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G63" s="2">
+        <v>0</v>
+      </c>
+      <c r="H63" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>101037405</t>
+          <t>100955968</t>
         </is>
       </c>
       <c r="B64" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C64" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64" s="2">
         <v>0</v>
@@ -1677,13 +1869,16 @@
         <v>0</v>
       </c>
       <c r="G64" s="2">
+        <v>0</v>
+      </c>
+      <c r="H64" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>101102225</t>
+          <t>100960111</t>
         </is>
       </c>
       <c r="B65" s="2">
@@ -1696,19 +1891,22 @@
         <v>0</v>
       </c>
       <c r="E65" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" s="2">
         <v>0</v>
       </c>
       <c r="G65" s="2">
+        <v>1</v>
+      </c>
+      <c r="H65" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>101108628</t>
+          <t>100961074</t>
         </is>
       </c>
       <c r="B66" s="2">
@@ -1727,13 +1925,16 @@
         <v>1</v>
       </c>
       <c r="G66" s="2">
+        <v>0</v>
+      </c>
+      <c r="H66" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>101111804</t>
+          <t>100972973</t>
         </is>
       </c>
       <c r="B67" s="2">
@@ -1753,12 +1954,15 @@
       </c>
       <c r="G67" s="2">
         <v>0</v>
+      </c>
+      <c r="H67" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>101161925</t>
+          <t>100984090</t>
         </is>
       </c>
       <c r="B68" s="2">
@@ -1768,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" s="2">
         <v>0</v>
@@ -1778,12 +1982,15 @@
       </c>
       <c r="G68" s="2">
         <v>0</v>
+      </c>
+      <c r="H68" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>101174078</t>
+          <t>101013887</t>
         </is>
       </c>
       <c r="B69" s="2">
@@ -1796,23 +2003,26 @@
         <v>0</v>
       </c>
       <c r="E69" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" s="2">
+        <v>0</v>
+      </c>
+      <c r="H69" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>101195987</t>
+          <t>101015607</t>
         </is>
       </c>
       <c r="B70" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C70" s="2">
         <v>0</v>
@@ -1827,17 +2037,20 @@
         <v>0</v>
       </c>
       <c r="G70" s="2">
+        <v>1</v>
+      </c>
+      <c r="H70" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>101232925</t>
+          <t>101034585</t>
         </is>
       </c>
       <c r="B71" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C71" s="2">
         <v>0</v>
@@ -1846,23 +2059,26 @@
         <v>0</v>
       </c>
       <c r="E71" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="2">
         <v>0</v>
       </c>
       <c r="G71" s="2">
+        <v>0</v>
+      </c>
+      <c r="H71" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>101237859</t>
+          <t>101037405</t>
         </is>
       </c>
       <c r="B72" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C72" s="2">
         <v>0</v>
@@ -1877,13 +2093,16 @@
         <v>0</v>
       </c>
       <c r="G72" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H72" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>101251735</t>
+          <t>101102225</t>
         </is>
       </c>
       <c r="B73" s="2">
@@ -1896,26 +2115,29 @@
         <v>0</v>
       </c>
       <c r="E73" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="2">
         <v>0</v>
       </c>
       <c r="G73" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H73" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>101295037</t>
+          <t>101108628</t>
         </is>
       </c>
       <c r="B74" s="2">
         <v>0</v>
       </c>
       <c r="C74" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74" s="2">
         <v>0</v>
@@ -1924,16 +2146,19 @@
         <v>0</v>
       </c>
       <c r="F74" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" s="2">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>101335538</t>
+          <t>101111804</t>
         </is>
       </c>
       <c r="B75" s="2">
@@ -1943,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" s="2">
         <v>0</v>
@@ -1952,13 +2177,16 @@
         <v>0</v>
       </c>
       <c r="G75" s="2">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>101336693</t>
+          <t>101161925</t>
         </is>
       </c>
       <c r="B76" s="2">
@@ -1968,22 +2196,25 @@
         <v>0</v>
       </c>
       <c r="D76" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F76" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G76" s="2">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>101372175</t>
+          <t>101174078</t>
         </is>
       </c>
       <c r="B77" s="2">
@@ -1993,32 +2224,35 @@
         <v>0</v>
       </c>
       <c r="D77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="2">
         <v>0</v>
       </c>
       <c r="G77" s="2">
+        <v>0</v>
+      </c>
+      <c r="H77" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>101396394</t>
+          <t>101195987</t>
         </is>
       </c>
       <c r="B78" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
       </c>
       <c r="D78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" s="2">
         <v>0</v>
@@ -2027,13 +2261,16 @@
         <v>0</v>
       </c>
       <c r="G78" s="2">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>101407817</t>
+          <t>101214695</t>
         </is>
       </c>
       <c r="B79" s="2">
@@ -2046,26 +2283,29 @@
         <v>0</v>
       </c>
       <c r="E79" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F79" s="2">
         <v>0</v>
       </c>
       <c r="G79" s="2">
         <v>0</v>
+      </c>
+      <c r="H79" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>101434241</t>
+          <t>101232925</t>
         </is>
       </c>
       <c r="B80" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C80" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80" s="2">
         <v>0</v>
@@ -2077,20 +2317,23 @@
         <v>0</v>
       </c>
       <c r="G80" s="2">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>101437685</t>
+          <t>101236937</t>
         </is>
       </c>
       <c r="B81" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C81" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81" s="2">
         <v>0</v>
@@ -2103,19 +2346,22 @@
       </c>
       <c r="G81" s="2">
         <v>0</v>
+      </c>
+      <c r="H81" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>101467964</t>
+          <t>101237859</t>
         </is>
       </c>
       <c r="B82" s="2">
         <v>0</v>
       </c>
       <c r="C82" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D82" s="2">
         <v>0</v>
@@ -2127,20 +2373,23 @@
         <v>0</v>
       </c>
       <c r="G82" s="2">
+        <v>1</v>
+      </c>
+      <c r="H82" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>101481537</t>
+          <t>101251735</t>
         </is>
       </c>
       <c r="B83" s="2">
         <v>0</v>
       </c>
       <c r="C83" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83" s="2">
         <v>0</v>
@@ -2152,17 +2401,20 @@
         <v>0</v>
       </c>
       <c r="G83" s="2">
+        <v>1</v>
+      </c>
+      <c r="H83" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>101509593</t>
+          <t>101265962</t>
         </is>
       </c>
       <c r="B84" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C84" s="2">
         <v>0</v>
@@ -2178,19 +2430,22 @@
       </c>
       <c r="G84" s="2">
         <v>0</v>
+      </c>
+      <c r="H84" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>101533995</t>
+          <t>101295037</t>
         </is>
       </c>
       <c r="B85" s="2">
         <v>0</v>
       </c>
       <c r="C85" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85" s="2">
         <v>0</v>
@@ -2199,20 +2454,23 @@
         <v>0</v>
       </c>
       <c r="F85" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" s="2">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>101573499</t>
+          <t>101335538</t>
         </is>
       </c>
       <c r="B86" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C86" s="2">
         <v>0</v>
@@ -2228,12 +2486,15 @@
       </c>
       <c r="G86" s="2">
         <v>1</v>
+      </c>
+      <c r="H86" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>101639078</t>
+          <t>101336693</t>
         </is>
       </c>
       <c r="B87" s="2">
@@ -2246,19 +2507,22 @@
         <v>0</v>
       </c>
       <c r="E87" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F87" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G87" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H87" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>101649796</t>
+          <t>101372175</t>
         </is>
       </c>
       <c r="B88" s="2">
@@ -2268,22 +2532,25 @@
         <v>0</v>
       </c>
       <c r="D88" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" s="2">
         <v>0</v>
       </c>
       <c r="F88" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" s="2">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>101691981</t>
+          <t>101396394</t>
         </is>
       </c>
       <c r="B89" s="2">
@@ -2293,22 +2560,25 @@
         <v>0</v>
       </c>
       <c r="D89" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" s="2">
         <v>0</v>
       </c>
       <c r="F89" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" s="2">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>101800057</t>
+          <t>101407817</t>
         </is>
       </c>
       <c r="B90" s="2">
@@ -2321,19 +2591,22 @@
         <v>0</v>
       </c>
       <c r="E90" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" s="2">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>101836491</t>
+          <t>101434241</t>
         </is>
       </c>
       <c r="B91" s="2">
@@ -2352,17 +2625,20 @@
         <v>0</v>
       </c>
       <c r="G91" s="2">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>101863433</t>
+          <t>101437685</t>
         </is>
       </c>
       <c r="B92" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C92" s="2">
         <v>1</v>
@@ -2377,45 +2653,51 @@
         <v>0</v>
       </c>
       <c r="G92" s="2">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>101875176</t>
+          <t>101467964</t>
         </is>
       </c>
       <c r="B93" s="2">
         <v>0</v>
       </c>
       <c r="C93" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93" s="2">
         <v>0</v>
       </c>
       <c r="E93" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F93" s="2">
         <v>0</v>
       </c>
       <c r="G93" s="2">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>101885140</t>
+          <t>101481537</t>
         </is>
       </c>
       <c r="B94" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C94" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D94" s="2">
         <v>0</v>
@@ -2427,20 +2709,23 @@
         <v>0</v>
       </c>
       <c r="G94" s="2">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>101888773</t>
+          <t>101509593</t>
         </is>
       </c>
       <c r="B95" s="2">
         <v>1</v>
       </c>
       <c r="C95" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D95" s="2">
         <v>0</v>
@@ -2449,16 +2734,19 @@
         <v>0</v>
       </c>
       <c r="F95" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H95" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>101903020</t>
+          <t>101533995</t>
         </is>
       </c>
       <c r="B96" s="2">
@@ -2477,23 +2765,26 @@
         <v>1</v>
       </c>
       <c r="G96" s="2">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>102006080</t>
+          <t>101573499</t>
         </is>
       </c>
       <c r="B97" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C97" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" s="2">
         <v>0</v>
@@ -2502,20 +2793,23 @@
         <v>0</v>
       </c>
       <c r="G97" s="2">
+        <v>1</v>
+      </c>
+      <c r="H97" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>102006845</t>
+          <t>101623111</t>
         </is>
       </c>
       <c r="B98" s="2">
         <v>0</v>
       </c>
       <c r="C98" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98" s="2">
         <v>0</v>
@@ -2528,12 +2822,15 @@
       </c>
       <c r="G98" s="2">
         <v>0</v>
+      </c>
+      <c r="H98" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>102050130</t>
+          <t>101639078</t>
         </is>
       </c>
       <c r="B99" s="2">
@@ -2546,19 +2843,22 @@
         <v>0</v>
       </c>
       <c r="E99" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F99" s="2">
         <v>0</v>
       </c>
       <c r="G99" s="2">
+        <v>1</v>
+      </c>
+      <c r="H99" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>102109244</t>
+          <t>101649796</t>
         </is>
       </c>
       <c r="B100" s="2">
@@ -2571,19 +2871,22 @@
         <v>0</v>
       </c>
       <c r="E100" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G100" s="2">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>102203438</t>
+          <t>101691981</t>
         </is>
       </c>
       <c r="B101" s="2">
@@ -2596,19 +2899,22 @@
         <v>0</v>
       </c>
       <c r="E101" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F101" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" s="2">
         <v>0</v>
+      </c>
+      <c r="H101" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>102224443</t>
+          <t>101716663</t>
         </is>
       </c>
       <c r="B102" s="2">
@@ -2624,23 +2930,26 @@
         <v>0</v>
       </c>
       <c r="F102" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" s="2">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>102227253</t>
+          <t>101739204</t>
         </is>
       </c>
       <c r="B103" s="2">
         <v>0</v>
       </c>
       <c r="C103" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D103" s="2">
         <v>0</v>
@@ -2653,12 +2962,15 @@
       </c>
       <c r="G103" s="2">
         <v>0</v>
+      </c>
+      <c r="H103" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>102282059</t>
+          <t>101800057</t>
         </is>
       </c>
       <c r="B104" s="2">
@@ -2671,19 +2983,22 @@
         <v>0</v>
       </c>
       <c r="E104" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F104" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104" s="2">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>102299090</t>
+          <t>101836491</t>
         </is>
       </c>
       <c r="B105" s="2">
@@ -2702,23 +3017,26 @@
         <v>0</v>
       </c>
       <c r="G105" s="2">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>102307203</t>
+          <t>101863433</t>
         </is>
       </c>
       <c r="B106" s="2">
         <v>0</v>
       </c>
       <c r="C106" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E106" s="2">
         <v>0</v>
@@ -2727,38 +3045,44 @@
         <v>0</v>
       </c>
       <c r="G106" s="2">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>102375097</t>
+          <t>101875176</t>
         </is>
       </c>
       <c r="B107" s="2">
         <v>0</v>
       </c>
       <c r="C107" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107" s="2">
         <v>0</v>
       </c>
       <c r="E107" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107" s="2">
         <v>0</v>
       </c>
       <c r="G107" s="2">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>102454744</t>
+          <t>101885140</t>
         </is>
       </c>
       <c r="B108" s="2">
@@ -2777,20 +3101,23 @@
         <v>0</v>
       </c>
       <c r="G108" s="2">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>102497144</t>
+          <t>101888773</t>
         </is>
       </c>
       <c r="B109" s="2">
         <v>1</v>
       </c>
       <c r="C109" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D109" s="2">
         <v>0</v>
@@ -2799,16 +3126,19 @@
         <v>0</v>
       </c>
       <c r="F109" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G109" s="2">
+        <v>1</v>
+      </c>
+      <c r="H109" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>102569542</t>
+          <t>101903020</t>
         </is>
       </c>
       <c r="B110" s="2">
@@ -2827,17 +3157,20 @@
         <v>1</v>
       </c>
       <c r="G110" s="2">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>102600124</t>
+          <t>101983093</t>
         </is>
       </c>
       <c r="B111" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C111" s="2">
         <v>0</v>
@@ -2853,47 +3186,53 @@
       </c>
       <c r="G111" s="2">
         <v>0</v>
+      </c>
+      <c r="H111" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>102655931</t>
+          <t>102006080</t>
         </is>
       </c>
       <c r="B112" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C112" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D112" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E112" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F112" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G112" s="2">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="H112" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>102673781</t>
+          <t>102006845</t>
         </is>
       </c>
       <c r="B113" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C113" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D113" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113" s="2">
         <v>0</v>
@@ -2902,13 +3241,16 @@
         <v>0</v>
       </c>
       <c r="G113" s="2">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>102690829</t>
+          <t>102050130</t>
         </is>
       </c>
       <c r="B114" s="2">
@@ -2918,26 +3260,29 @@
         <v>0</v>
       </c>
       <c r="D114" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" s="2">
         <v>0</v>
       </c>
       <c r="G114" s="2">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>102698382</t>
+          <t>102109244</t>
         </is>
       </c>
       <c r="B115" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C115" s="2">
         <v>0</v>
@@ -2946,19 +3291,22 @@
         <v>0</v>
       </c>
       <c r="E115" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="2">
         <v>0</v>
       </c>
       <c r="G115" s="2">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>102705657</t>
+          <t>102125733</t>
         </is>
       </c>
       <c r="B116" s="2">
@@ -2968,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="D116" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E116" s="2">
         <v>0</v>
@@ -2978,37 +3326,43 @@
       </c>
       <c r="G116" s="2">
         <v>0</v>
+      </c>
+      <c r="H116" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>102748593</t>
+          <t>102203438</t>
         </is>
       </c>
       <c r="B117" s="2">
         <v>0</v>
       </c>
       <c r="C117" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117" s="2">
         <v>0</v>
       </c>
       <c r="E117" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="2">
         <v>0</v>
       </c>
       <c r="G117" s="2">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>102793147</t>
+          <t>102224443</t>
         </is>
       </c>
       <c r="B118" s="2">
@@ -3021,26 +3375,29 @@
         <v>0</v>
       </c>
       <c r="E118" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F118" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G118" s="2">
+        <v>1</v>
+      </c>
+      <c r="H118" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>102796686</t>
+          <t>102227253</t>
         </is>
       </c>
       <c r="B119" s="2">
         <v>0</v>
       </c>
       <c r="C119" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D119" s="2">
         <v>0</v>
@@ -3052,13 +3409,16 @@
         <v>0</v>
       </c>
       <c r="G119" s="2">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="H119" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1100043267</t>
+          <t>102282059</t>
         </is>
       </c>
       <c r="B120" s="2">
@@ -3071,26 +3431,29 @@
         <v>0</v>
       </c>
       <c r="E120" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120" s="2">
+        <v>0</v>
+      </c>
+      <c r="H120" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1100079588</t>
+          <t>102299090</t>
         </is>
       </c>
       <c r="B121" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C121" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D121" s="2">
         <v>0</v>
@@ -3102,23 +3465,26 @@
         <v>0</v>
       </c>
       <c r="G121" s="2">
+        <v>0</v>
+      </c>
+      <c r="H121" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>500000823</t>
+          <t>102307203</t>
         </is>
       </c>
       <c r="B122" s="2">
         <v>0</v>
       </c>
       <c r="C122" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D122" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E122" s="2">
         <v>0</v>
@@ -3127,23 +3493,26 @@
         <v>0</v>
       </c>
       <c r="G122" s="2">
+        <v>0</v>
+      </c>
+      <c r="H122" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>500000921</t>
+          <t>102375097</t>
         </is>
       </c>
       <c r="B123" s="2">
         <v>0</v>
       </c>
       <c r="C123" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D123" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123" s="2">
         <v>0</v>
@@ -3152,17 +3521,20 @@
         <v>0</v>
       </c>
       <c r="G123" s="2">
+        <v>0</v>
+      </c>
+      <c r="H123" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>500002685</t>
+          <t>102454744</t>
         </is>
       </c>
       <c r="B124" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C124" s="2">
         <v>0</v>
@@ -3171,19 +3543,22 @@
         <v>0</v>
       </c>
       <c r="E124" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F124" s="2">
         <v>0</v>
       </c>
       <c r="G124" s="2">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>500003288</t>
+          <t>102497144</t>
         </is>
       </c>
       <c r="B125" s="2">
@@ -3202,42 +3577,48 @@
         <v>0</v>
       </c>
       <c r="G125" s="2">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>500003682</t>
+          <t>102569542</t>
         </is>
       </c>
       <c r="B126" s="2">
         <v>0</v>
       </c>
       <c r="C126" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D126" s="2">
         <v>0</v>
       </c>
       <c r="E126" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F126" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" s="2">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>500008320</t>
+          <t>102600124</t>
         </is>
       </c>
       <c r="B127" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C127" s="2">
         <v>0</v>
@@ -3249,41 +3630,47 @@
         <v>0</v>
       </c>
       <c r="F127" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G127" s="2">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>500009413</t>
+          <t>102655931</t>
         </is>
       </c>
       <c r="B128" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C128" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D128" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E128" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F128" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G128" s="2">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="H128" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>500016197</t>
+          <t>102673781</t>
         </is>
       </c>
       <c r="B129" s="2">
@@ -3293,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="D129" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E129" s="2">
         <v>0</v>
@@ -3302,13 +3689,16 @@
         <v>0</v>
       </c>
       <c r="G129" s="2">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>500020789</t>
+          <t>102690829</t>
         </is>
       </c>
       <c r="B130" s="2">
@@ -3318,26 +3708,29 @@
         <v>0</v>
       </c>
       <c r="D130" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E130" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F130" s="2">
         <v>0</v>
       </c>
       <c r="G130" s="2">
+        <v>0</v>
+      </c>
+      <c r="H130" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>500023997</t>
+          <t>102697265</t>
         </is>
       </c>
       <c r="B131" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C131" s="2">
         <v>0</v>
@@ -3353,22 +3746,25 @@
       </c>
       <c r="G131" s="2">
         <v>0</v>
+      </c>
+      <c r="H131" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>500024124</t>
+          <t>102698382</t>
         </is>
       </c>
       <c r="B132" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C132" s="2">
         <v>0</v>
       </c>
       <c r="D132" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E132" s="2">
         <v>0</v>
@@ -3377,13 +3773,16 @@
         <v>0</v>
       </c>
       <c r="G132" s="2">
+        <v>0</v>
+      </c>
+      <c r="H132" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>500028485</t>
+          <t>102705657</t>
         </is>
       </c>
       <c r="B133" s="2">
@@ -3396,26 +3795,29 @@
         <v>1</v>
       </c>
       <c r="E133" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F133" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G133" s="2">
+        <v>0</v>
+      </c>
+      <c r="H133" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>500030111</t>
+          <t>102748593</t>
         </is>
       </c>
       <c r="B134" s="2">
         <v>0</v>
       </c>
       <c r="C134" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D134" s="2">
         <v>0</v>
@@ -3427,13 +3829,16 @@
         <v>0</v>
       </c>
       <c r="G134" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H134" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>500031227</t>
+          <t>102793147</t>
         </is>
       </c>
       <c r="B135" s="2">
@@ -3446,26 +3851,29 @@
         <v>0</v>
       </c>
       <c r="E135" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G135" s="2">
+        <v>0</v>
+      </c>
+      <c r="H135" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>500031276</t>
+          <t>102796686</t>
         </is>
       </c>
       <c r="B136" s="2">
         <v>0</v>
       </c>
       <c r="C136" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D136" s="2">
         <v>0</v>
@@ -3477,17 +3885,20 @@
         <v>0</v>
       </c>
       <c r="G136" s="2">
+        <v>2</v>
+      </c>
+      <c r="H136" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>500032408</t>
+          <t>1100043267</t>
         </is>
       </c>
       <c r="B137" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C137" s="2">
         <v>0</v>
@@ -3499,26 +3910,29 @@
         <v>0</v>
       </c>
       <c r="F137" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" s="2">
+        <v>0</v>
+      </c>
+      <c r="H137" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>500035796</t>
+          <t>1100079588</t>
         </is>
       </c>
       <c r="B138" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C138" s="2">
         <v>0</v>
       </c>
       <c r="D138" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E138" s="2">
         <v>0</v>
@@ -3527,20 +3941,23 @@
         <v>0</v>
       </c>
       <c r="G138" s="2">
+        <v>0</v>
+      </c>
+      <c r="H138" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>500036672</t>
+          <t>500000823</t>
         </is>
       </c>
       <c r="B139" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C139" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D139" s="2">
         <v>0</v>
@@ -3552,13 +3969,16 @@
         <v>0</v>
       </c>
       <c r="G139" s="2">
+        <v>0</v>
+      </c>
+      <c r="H139" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>500037006</t>
+          <t>500000921</t>
         </is>
       </c>
       <c r="B140" s="2">
@@ -3568,22 +3988,25 @@
         <v>0</v>
       </c>
       <c r="D140" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E140" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F140" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G140" s="2">
+        <v>0</v>
+      </c>
+      <c r="H140" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>500050269</t>
+          <t>500002685</t>
         </is>
       </c>
       <c r="B141" s="2">
@@ -3596,26 +4019,29 @@
         <v>0</v>
       </c>
       <c r="E141" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="2">
         <v>0</v>
       </c>
       <c r="G141" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H141" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>500052051</t>
+          <t>500003288</t>
         </is>
       </c>
       <c r="B142" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C142" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D142" s="2">
         <v>0</v>
@@ -3627,17 +4053,20 @@
         <v>0</v>
       </c>
       <c r="G142" s="2">
+        <v>0</v>
+      </c>
+      <c r="H142" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>500057619</t>
+          <t>500003682</t>
         </is>
       </c>
       <c r="B143" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C143" s="2">
         <v>1</v>
@@ -3646,26 +4075,29 @@
         <v>0</v>
       </c>
       <c r="E143" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" s="2">
         <v>0</v>
       </c>
       <c r="G143" s="2">
+        <v>0</v>
+      </c>
+      <c r="H143" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>500060661</t>
+          <t>500008320</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C144" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D144" s="2">
         <v>0</v>
@@ -3674,45 +4106,51 @@
         <v>0</v>
       </c>
       <c r="F144" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" s="2">
+        <v>0</v>
+      </c>
+      <c r="H144" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>500061708</t>
+          <t>500009413</t>
         </is>
       </c>
       <c r="B145" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C145" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D145" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E145" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F145" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145" s="2">
+        <v>0</v>
+      </c>
+      <c r="H145" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>500066176</t>
+          <t>500016197</t>
         </is>
       </c>
       <c r="B146" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C146" s="2">
         <v>0</v>
@@ -3724,16 +4162,19 @@
         <v>0</v>
       </c>
       <c r="F146" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G146" s="2">
+        <v>0</v>
+      </c>
+      <c r="H146" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>500067801</t>
+          <t>500020789</t>
         </is>
       </c>
       <c r="B147" s="2">
@@ -3746,23 +4187,26 @@
         <v>0</v>
       </c>
       <c r="E147" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" s="2">
         <v>0</v>
       </c>
       <c r="G147" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H147" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>500080387</t>
+          <t>500023997</t>
         </is>
       </c>
       <c r="B148" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C148" s="2">
         <v>0</v>
@@ -3777,13 +4221,16 @@
         <v>0</v>
       </c>
       <c r="G148" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H148" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>500094507</t>
+          <t>500024124</t>
         </is>
       </c>
       <c r="B149" s="2">
@@ -3802,13 +4249,16 @@
         <v>0</v>
       </c>
       <c r="G149" s="2">
+        <v>0</v>
+      </c>
+      <c r="H149" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>500101533</t>
+          <t>500028485</t>
         </is>
       </c>
       <c r="B150" s="2">
@@ -3818,22 +4268,25 @@
         <v>0</v>
       </c>
       <c r="D150" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F150" s="2">
         <v>1</v>
       </c>
       <c r="G150" s="2">
+        <v>0</v>
+      </c>
+      <c r="H150" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>500111404</t>
+          <t>500030111</t>
         </is>
       </c>
       <c r="B151" s="2">
@@ -3843,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="D151" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" s="2">
         <v>0</v>
@@ -3852,17 +4305,20 @@
         <v>0</v>
       </c>
       <c r="G151" s="2">
+        <v>1</v>
+      </c>
+      <c r="H151" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>500115640</t>
+          <t>500031227</t>
         </is>
       </c>
       <c r="B152" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C152" s="2">
         <v>0</v>
@@ -3877,23 +4333,26 @@
         <v>1</v>
       </c>
       <c r="G152" s="2">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="H152" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>500117284</t>
+          <t>500031276</t>
         </is>
       </c>
       <c r="B153" s="2">
         <v>0</v>
       </c>
       <c r="C153" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D153" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E153" s="2">
         <v>0</v>
@@ -3902,13 +4361,16 @@
         <v>0</v>
       </c>
       <c r="G153" s="2">
+        <v>0</v>
+      </c>
+      <c r="H153" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>500120216</t>
+          <t>500032408</t>
         </is>
       </c>
       <c r="B154" s="2">
@@ -3918,7 +4380,7 @@
         <v>0</v>
       </c>
       <c r="D154" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E154" s="2">
         <v>0</v>
@@ -3927,13 +4389,16 @@
         <v>0</v>
       </c>
       <c r="G154" s="2">
+        <v>0</v>
+      </c>
+      <c r="H154" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>500126621</t>
+          <t>500035796</t>
         </is>
       </c>
       <c r="B155" s="2">
@@ -3952,17 +4417,20 @@
         <v>0</v>
       </c>
       <c r="G155" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H155" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>500127435</t>
+          <t>500036672</t>
         </is>
       </c>
       <c r="B156" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C156" s="2">
         <v>0</v>
@@ -3977,13 +4445,16 @@
         <v>0</v>
       </c>
       <c r="G156" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H156" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>500128032</t>
+          <t>500037006</t>
         </is>
       </c>
       <c r="B157" s="2">
@@ -3996,19 +4467,22 @@
         <v>0</v>
       </c>
       <c r="E157" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F157" s="2">
         <v>1</v>
       </c>
       <c r="G157" s="2">
+        <v>0</v>
+      </c>
+      <c r="H157" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>500128657</t>
+          <t>500050269</t>
         </is>
       </c>
       <c r="B158" s="2">
@@ -4024,16 +4498,19 @@
         <v>0</v>
       </c>
       <c r="F158" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G158" s="2">
+        <v>1</v>
+      </c>
+      <c r="H158" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>500143502</t>
+          <t>500052051</t>
         </is>
       </c>
       <c r="B159" s="2">
@@ -4053,19 +4530,22 @@
       </c>
       <c r="G159" s="2">
         <v>0</v>
+      </c>
+      <c r="H159" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>500143882</t>
+          <t>500057619</t>
         </is>
       </c>
       <c r="B160" s="2">
         <v>1</v>
       </c>
       <c r="C160" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D160" s="2">
         <v>0</v>
@@ -4077,17 +4557,20 @@
         <v>0</v>
       </c>
       <c r="G160" s="2">
+        <v>0</v>
+      </c>
+      <c r="H160" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>500146800</t>
+          <t>500058721</t>
         </is>
       </c>
       <c r="B161" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C161" s="2">
         <v>0</v>
@@ -4102,13 +4585,16 @@
         <v>0</v>
       </c>
       <c r="G161" s="2">
+        <v>0</v>
+      </c>
+      <c r="H161" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>500185891</t>
+          <t>500060661</t>
         </is>
       </c>
       <c r="B162" s="2">
@@ -4127,23 +4613,26 @@
         <v>0</v>
       </c>
       <c r="G162" s="2">
+        <v>0</v>
+      </c>
+      <c r="H162" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>500186481</t>
+          <t>500061708</t>
         </is>
       </c>
       <c r="B163" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C163" s="2">
         <v>0</v>
       </c>
       <c r="D163" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E163" s="2">
         <v>0</v>
@@ -4152,20 +4641,23 @@
         <v>0</v>
       </c>
       <c r="G163" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H163" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>500187931</t>
+          <t>500066176</t>
         </is>
       </c>
       <c r="B164" s="2">
         <v>0</v>
       </c>
       <c r="C164" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D164" s="2">
         <v>0</v>
@@ -4174,16 +4666,19 @@
         <v>0</v>
       </c>
       <c r="F164" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G164" s="2">
+        <v>0</v>
+      </c>
+      <c r="H164" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>500199878</t>
+          <t>500067801</t>
         </is>
       </c>
       <c r="B165" s="2">
@@ -4199,26 +4694,29 @@
         <v>0</v>
       </c>
       <c r="F165" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G165" s="2">
+        <v>1</v>
+      </c>
+      <c r="H165" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>500211718</t>
+          <t>500080387</t>
         </is>
       </c>
       <c r="B166" s="2">
         <v>0</v>
       </c>
       <c r="C166" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D166" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E166" s="2">
         <v>0</v>
@@ -4227,23 +4725,26 @@
         <v>0</v>
       </c>
       <c r="G166" s="2">
+        <v>1</v>
+      </c>
+      <c r="H166" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>500217683</t>
+          <t>500092658</t>
         </is>
       </c>
       <c r="B167" s="2">
         <v>0</v>
       </c>
       <c r="C167" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D167" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E167" s="2">
         <v>0</v>
@@ -4252,13 +4753,16 @@
         <v>0</v>
       </c>
       <c r="G167" s="2">
+        <v>0</v>
+      </c>
+      <c r="H167" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>500235468</t>
+          <t>500094507</t>
         </is>
       </c>
       <c r="B168" s="2">
@@ -4268,7 +4772,7 @@
         <v>0</v>
       </c>
       <c r="D168" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E168" s="2">
         <v>0</v>
@@ -4277,20 +4781,23 @@
         <v>0</v>
       </c>
       <c r="G168" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H168" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>500236829</t>
+          <t>500101533</t>
         </is>
       </c>
       <c r="B169" s="2">
         <v>0</v>
       </c>
       <c r="C169" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D169" s="2">
         <v>0</v>
@@ -4299,20 +4806,23 @@
         <v>0</v>
       </c>
       <c r="F169" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G169" s="2">
+        <v>0</v>
+      </c>
+      <c r="H169" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>500240447</t>
+          <t>500104713</t>
         </is>
       </c>
       <c r="B170" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C170" s="2">
         <v>0</v>
@@ -4328,41 +4838,47 @@
       </c>
       <c r="G170" s="2">
         <v>0</v>
+      </c>
+      <c r="H170" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>500241388</t>
+          <t>500111404</t>
         </is>
       </c>
       <c r="B171" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C171" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D171" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E171" s="2">
         <v>0</v>
       </c>
       <c r="F171" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G171" s="2">
+        <v>0</v>
+      </c>
+      <c r="H171" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>500255345</t>
+          <t>500113054</t>
         </is>
       </c>
       <c r="B172" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C172" s="2">
         <v>0</v>
@@ -4371,23 +4887,26 @@
         <v>0</v>
       </c>
       <c r="E172" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F172" s="2">
         <v>0</v>
       </c>
       <c r="G172" s="2">
         <v>0</v>
+      </c>
+      <c r="H172" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>500258101</t>
+          <t>500115640</t>
         </is>
       </c>
       <c r="B173" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C173" s="2">
         <v>0</v>
@@ -4396,19 +4915,22 @@
         <v>0</v>
       </c>
       <c r="E173" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F173" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G173" s="2">
+        <v>2</v>
+      </c>
+      <c r="H173" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>500272158</t>
+          <t>500117284</t>
         </is>
       </c>
       <c r="B174" s="2">
@@ -4418,32 +4940,35 @@
         <v>0</v>
       </c>
       <c r="D174" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E174" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F174" s="2">
         <v>0</v>
       </c>
       <c r="G174" s="2">
+        <v>0</v>
+      </c>
+      <c r="H174" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>500274670</t>
+          <t>500120216</t>
         </is>
       </c>
       <c r="B175" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C175" s="2">
         <v>0</v>
       </c>
       <c r="D175" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E175" s="2">
         <v>0</v>
@@ -4452,42 +4977,832 @@
         <v>0</v>
       </c>
       <c r="G175" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="H175" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
+          <t>500126621</t>
+        </is>
+      </c>
+      <c r="B176" s="2">
+        <v>0</v>
+      </c>
+      <c r="C176" s="2">
+        <v>0</v>
+      </c>
+      <c r="D176" s="2">
+        <v>1</v>
+      </c>
+      <c r="E176" s="2">
+        <v>0</v>
+      </c>
+      <c r="F176" s="2">
+        <v>0</v>
+      </c>
+      <c r="G176" s="2">
+        <v>1</v>
+      </c>
+      <c r="H176" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>500127435</t>
+        </is>
+      </c>
+      <c r="B177" s="2">
+        <v>0</v>
+      </c>
+      <c r="C177" s="2">
+        <v>0</v>
+      </c>
+      <c r="D177" s="2">
+        <v>0</v>
+      </c>
+      <c r="E177" s="2">
+        <v>0</v>
+      </c>
+      <c r="F177" s="2">
+        <v>0</v>
+      </c>
+      <c r="G177" s="2">
+        <v>1</v>
+      </c>
+      <c r="H177" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>500128032</t>
+        </is>
+      </c>
+      <c r="B178" s="2">
+        <v>0</v>
+      </c>
+      <c r="C178" s="2">
+        <v>0</v>
+      </c>
+      <c r="D178" s="2">
+        <v>0</v>
+      </c>
+      <c r="E178" s="2">
+        <v>0</v>
+      </c>
+      <c r="F178" s="2">
+        <v>1</v>
+      </c>
+      <c r="G178" s="2">
+        <v>0</v>
+      </c>
+      <c r="H178" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>500128657</t>
+        </is>
+      </c>
+      <c r="B179" s="2">
+        <v>0</v>
+      </c>
+      <c r="C179" s="2">
+        <v>0</v>
+      </c>
+      <c r="D179" s="2">
+        <v>0</v>
+      </c>
+      <c r="E179" s="2">
+        <v>0</v>
+      </c>
+      <c r="F179" s="2">
+        <v>1</v>
+      </c>
+      <c r="G179" s="2">
+        <v>0</v>
+      </c>
+      <c r="H179" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>500128699</t>
+        </is>
+      </c>
+      <c r="B180" s="2">
+        <v>0</v>
+      </c>
+      <c r="C180" s="2">
+        <v>0</v>
+      </c>
+      <c r="D180" s="2">
+        <v>0</v>
+      </c>
+      <c r="E180" s="2">
+        <v>0</v>
+      </c>
+      <c r="F180" s="2">
+        <v>0</v>
+      </c>
+      <c r="G180" s="2">
+        <v>0</v>
+      </c>
+      <c r="H180" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>500143502</t>
+        </is>
+      </c>
+      <c r="B181" s="2">
+        <v>0</v>
+      </c>
+      <c r="C181" s="2">
+        <v>1</v>
+      </c>
+      <c r="D181" s="2">
+        <v>0</v>
+      </c>
+      <c r="E181" s="2">
+        <v>0</v>
+      </c>
+      <c r="F181" s="2">
+        <v>0</v>
+      </c>
+      <c r="G181" s="2">
+        <v>0</v>
+      </c>
+      <c r="H181" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>500143882</t>
+        </is>
+      </c>
+      <c r="B182" s="2">
+        <v>1</v>
+      </c>
+      <c r="C182" s="2">
+        <v>0</v>
+      </c>
+      <c r="D182" s="2">
+        <v>0</v>
+      </c>
+      <c r="E182" s="2">
+        <v>0</v>
+      </c>
+      <c r="F182" s="2">
+        <v>0</v>
+      </c>
+      <c r="G182" s="2">
+        <v>0</v>
+      </c>
+      <c r="H182" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>500146241</t>
+        </is>
+      </c>
+      <c r="B183" s="2">
+        <v>0</v>
+      </c>
+      <c r="C183" s="2">
+        <v>0</v>
+      </c>
+      <c r="D183" s="2">
+        <v>0</v>
+      </c>
+      <c r="E183" s="2">
+        <v>0</v>
+      </c>
+      <c r="F183" s="2">
+        <v>0</v>
+      </c>
+      <c r="G183" s="2">
+        <v>0</v>
+      </c>
+      <c r="H183" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>500146800</t>
+        </is>
+      </c>
+      <c r="B184" s="2">
+        <v>1</v>
+      </c>
+      <c r="C184" s="2">
+        <v>0</v>
+      </c>
+      <c r="D184" s="2">
+        <v>0</v>
+      </c>
+      <c r="E184" s="2">
+        <v>0</v>
+      </c>
+      <c r="F184" s="2">
+        <v>0</v>
+      </c>
+      <c r="G184" s="2">
+        <v>1</v>
+      </c>
+      <c r="H184" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>500148890</t>
+        </is>
+      </c>
+      <c r="B185" s="2">
+        <v>0</v>
+      </c>
+      <c r="C185" s="2">
+        <v>0</v>
+      </c>
+      <c r="D185" s="2">
+        <v>0</v>
+      </c>
+      <c r="E185" s="2">
+        <v>0</v>
+      </c>
+      <c r="F185" s="2">
+        <v>0</v>
+      </c>
+      <c r="G185" s="2">
+        <v>0</v>
+      </c>
+      <c r="H185" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>500185891</t>
+        </is>
+      </c>
+      <c r="B186" s="2">
+        <v>1</v>
+      </c>
+      <c r="C186" s="2">
+        <v>1</v>
+      </c>
+      <c r="D186" s="2">
+        <v>0</v>
+      </c>
+      <c r="E186" s="2">
+        <v>0</v>
+      </c>
+      <c r="F186" s="2">
+        <v>0</v>
+      </c>
+      <c r="G186" s="2">
+        <v>0</v>
+      </c>
+      <c r="H186" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>500186481</t>
+        </is>
+      </c>
+      <c r="B187" s="2">
+        <v>0</v>
+      </c>
+      <c r="C187" s="2">
+        <v>0</v>
+      </c>
+      <c r="D187" s="2">
+        <v>0</v>
+      </c>
+      <c r="E187" s="2">
+        <v>0</v>
+      </c>
+      <c r="F187" s="2">
+        <v>0</v>
+      </c>
+      <c r="G187" s="2">
+        <v>1</v>
+      </c>
+      <c r="H187" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>500187931</t>
+        </is>
+      </c>
+      <c r="B188" s="2">
+        <v>0</v>
+      </c>
+      <c r="C188" s="2">
+        <v>1</v>
+      </c>
+      <c r="D188" s="2">
+        <v>0</v>
+      </c>
+      <c r="E188" s="2">
+        <v>0</v>
+      </c>
+      <c r="F188" s="2">
+        <v>0</v>
+      </c>
+      <c r="G188" s="2">
+        <v>0</v>
+      </c>
+      <c r="H188" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>500192537</t>
+        </is>
+      </c>
+      <c r="B189" s="2">
+        <v>0</v>
+      </c>
+      <c r="C189" s="2">
+        <v>0</v>
+      </c>
+      <c r="D189" s="2">
+        <v>0</v>
+      </c>
+      <c r="E189" s="2">
+        <v>0</v>
+      </c>
+      <c r="F189" s="2">
+        <v>0</v>
+      </c>
+      <c r="G189" s="2">
+        <v>0</v>
+      </c>
+      <c r="H189" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>500199878</t>
+        </is>
+      </c>
+      <c r="B190" s="2">
+        <v>0</v>
+      </c>
+      <c r="C190" s="2">
+        <v>0</v>
+      </c>
+      <c r="D190" s="2">
+        <v>0</v>
+      </c>
+      <c r="E190" s="2">
+        <v>0</v>
+      </c>
+      <c r="F190" s="2">
+        <v>1</v>
+      </c>
+      <c r="G190" s="2">
+        <v>0</v>
+      </c>
+      <c r="H190" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>500201947</t>
+        </is>
+      </c>
+      <c r="B191" s="2">
+        <v>0</v>
+      </c>
+      <c r="C191" s="2">
+        <v>0</v>
+      </c>
+      <c r="D191" s="2">
+        <v>0</v>
+      </c>
+      <c r="E191" s="2">
+        <v>0</v>
+      </c>
+      <c r="F191" s="2">
+        <v>0</v>
+      </c>
+      <c r="G191" s="2">
+        <v>0</v>
+      </c>
+      <c r="H191" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>500211718</t>
+        </is>
+      </c>
+      <c r="B192" s="2">
+        <v>0</v>
+      </c>
+      <c r="C192" s="2">
+        <v>1</v>
+      </c>
+      <c r="D192" s="2">
+        <v>2</v>
+      </c>
+      <c r="E192" s="2">
+        <v>0</v>
+      </c>
+      <c r="F192" s="2">
+        <v>0</v>
+      </c>
+      <c r="G192" s="2">
+        <v>0</v>
+      </c>
+      <c r="H192" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>500217683</t>
+        </is>
+      </c>
+      <c r="B193" s="2">
+        <v>0</v>
+      </c>
+      <c r="C193" s="2">
+        <v>1</v>
+      </c>
+      <c r="D193" s="2">
+        <v>1</v>
+      </c>
+      <c r="E193" s="2">
+        <v>0</v>
+      </c>
+      <c r="F193" s="2">
+        <v>0</v>
+      </c>
+      <c r="G193" s="2">
+        <v>1</v>
+      </c>
+      <c r="H193" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>500219602</t>
+        </is>
+      </c>
+      <c r="B194" s="2">
+        <v>0</v>
+      </c>
+      <c r="C194" s="2">
+        <v>0</v>
+      </c>
+      <c r="D194" s="2">
+        <v>0</v>
+      </c>
+      <c r="E194" s="2">
+        <v>0</v>
+      </c>
+      <c r="F194" s="2">
+        <v>0</v>
+      </c>
+      <c r="G194" s="2">
+        <v>0</v>
+      </c>
+      <c r="H194" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>500235468</t>
+        </is>
+      </c>
+      <c r="B195" s="2">
+        <v>0</v>
+      </c>
+      <c r="C195" s="2">
+        <v>0</v>
+      </c>
+      <c r="D195" s="2">
+        <v>0</v>
+      </c>
+      <c r="E195" s="2">
+        <v>0</v>
+      </c>
+      <c r="F195" s="2">
+        <v>0</v>
+      </c>
+      <c r="G195" s="2">
+        <v>1</v>
+      </c>
+      <c r="H195" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>500236829</t>
+        </is>
+      </c>
+      <c r="B196" s="2">
+        <v>0</v>
+      </c>
+      <c r="C196" s="2">
+        <v>1</v>
+      </c>
+      <c r="D196" s="2">
+        <v>0</v>
+      </c>
+      <c r="E196" s="2">
+        <v>0</v>
+      </c>
+      <c r="F196" s="2">
+        <v>0</v>
+      </c>
+      <c r="G196" s="2">
+        <v>0</v>
+      </c>
+      <c r="H196" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>500240447</t>
+        </is>
+      </c>
+      <c r="B197" s="2">
+        <v>1</v>
+      </c>
+      <c r="C197" s="2">
+        <v>0</v>
+      </c>
+      <c r="D197" s="2">
+        <v>0</v>
+      </c>
+      <c r="E197" s="2">
+        <v>0</v>
+      </c>
+      <c r="F197" s="2">
+        <v>0</v>
+      </c>
+      <c r="G197" s="2">
+        <v>0</v>
+      </c>
+      <c r="H197" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>500241388</t>
+        </is>
+      </c>
+      <c r="B198" s="2">
+        <v>1</v>
+      </c>
+      <c r="C198" s="2">
+        <v>1</v>
+      </c>
+      <c r="D198" s="2">
+        <v>0</v>
+      </c>
+      <c r="E198" s="2">
+        <v>0</v>
+      </c>
+      <c r="F198" s="2">
+        <v>1</v>
+      </c>
+      <c r="G198" s="2">
+        <v>0</v>
+      </c>
+      <c r="H198" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>500255345</t>
+        </is>
+      </c>
+      <c r="B199" s="2">
+        <v>1</v>
+      </c>
+      <c r="C199" s="2">
+        <v>0</v>
+      </c>
+      <c r="D199" s="2">
+        <v>0</v>
+      </c>
+      <c r="E199" s="2">
+        <v>1</v>
+      </c>
+      <c r="F199" s="2">
+        <v>0</v>
+      </c>
+      <c r="G199" s="2">
+        <v>0</v>
+      </c>
+      <c r="H199" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>500258101</t>
+        </is>
+      </c>
+      <c r="B200" s="2">
+        <v>0</v>
+      </c>
+      <c r="C200" s="2">
+        <v>0</v>
+      </c>
+      <c r="D200" s="2">
+        <v>0</v>
+      </c>
+      <c r="E200" s="2">
+        <v>1</v>
+      </c>
+      <c r="F200" s="2">
+        <v>0</v>
+      </c>
+      <c r="G200" s="2">
+        <v>0</v>
+      </c>
+      <c r="H200" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>500272158</t>
+        </is>
+      </c>
+      <c r="B201" s="2">
+        <v>0</v>
+      </c>
+      <c r="C201" s="2">
+        <v>0</v>
+      </c>
+      <c r="D201" s="2">
+        <v>0</v>
+      </c>
+      <c r="E201" s="2">
+        <v>1</v>
+      </c>
+      <c r="F201" s="2">
+        <v>0</v>
+      </c>
+      <c r="G201" s="2">
+        <v>0</v>
+      </c>
+      <c r="H201" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>500274670</t>
+        </is>
+      </c>
+      <c r="B202" s="2">
+        <v>0</v>
+      </c>
+      <c r="C202" s="2">
+        <v>0</v>
+      </c>
+      <c r="D202" s="2">
+        <v>0</v>
+      </c>
+      <c r="E202" s="2">
+        <v>0</v>
+      </c>
+      <c r="F202" s="2">
+        <v>0</v>
+      </c>
+      <c r="G202" s="2">
+        <v>1</v>
+      </c>
+      <c r="H202" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
           <t>500284150</t>
         </is>
       </c>
-      <c r="B176" s="2">
-        <v>0</v>
-      </c>
-      <c r="C176" s="2">
-        <v>0</v>
-      </c>
-      <c r="D176" s="2">
-        <v>0</v>
-      </c>
-      <c r="E176" s="2">
-        <v>0</v>
-      </c>
-      <c r="F176" s="2">
-        <v>1</v>
-      </c>
-      <c r="G176" s="2">
-        <v>0</v>
+      <c r="B203" s="2">
+        <v>0</v>
+      </c>
+      <c r="C203" s="2">
+        <v>0</v>
+      </c>
+      <c r="D203" s="2">
+        <v>0</v>
+      </c>
+      <c r="E203" s="2">
+        <v>0</v>
+      </c>
+      <c r="F203" s="2">
+        <v>1</v>
+      </c>
+      <c r="G203" s="2">
+        <v>0</v>
+      </c>
+      <c r="H203" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>500286107</t>
+        </is>
+      </c>
+      <c r="B204" s="2">
+        <v>0</v>
+      </c>
+      <c r="C204" s="2">
+        <v>0</v>
+      </c>
+      <c r="D204" s="2">
+        <v>0</v>
+      </c>
+      <c r="E204" s="2">
+        <v>0</v>
+      </c>
+      <c r="F204" s="2">
+        <v>0</v>
+      </c>
+      <c r="G204" s="2">
+        <v>0</v>
+      </c>
+      <c r="H204" s="2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G176"/>
+  <autoFilter ref="A1:H204"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q248"/>
+  <dimension ref="A1:Q290"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -22626,7 +23941,3073 @@
         <v>0.63</v>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>100003305</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>10603785378</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>아리울떡공방 카스테라 호박인절미 외 개별포장 찰떡 2봉묶음 (택1)</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G249" s="2">
+        <v>14900</v>
+      </c>
+      <c r="H249" s="2">
+        <v>20000</v>
+      </c>
+      <c r="I249" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10603785378</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260422_184/1776843281554fkfca_JPEG/110976160088677113_1722171168.jpg</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N249" s="2">
+        <v>1</v>
+      </c>
+      <c r="O249" s="2">
+        <v>0</v>
+      </c>
+      <c r="P249" s="2">
+        <v>14900</v>
+      </c>
+      <c r="Q249" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>100137620</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>5434391165</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>제주 투어패스 프리패스 제주도 여행 패키지 체험 관광지 카트 승마 공연 관광</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G250" s="2">
+        <v>12900</v>
+      </c>
+      <c r="H250" s="2">
+        <v>17900</v>
+      </c>
+      <c r="I250" s="3">
+        <v>0.27</v>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5434391165</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250402_151/1743550254073izTGE_JPEG/77683049186317702_81298565.jpg</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N250" s="2">
+        <v>1</v>
+      </c>
+      <c r="O250" s="2">
+        <v>0</v>
+      </c>
+      <c r="P250" s="2">
+        <v>12900</v>
+      </c>
+      <c r="Q250" s="3">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>100146361</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>6018989978</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>[냉장] CJ 더건강한 닭가슴살 14개, 스팀 직화통살, 통살페퍼, 케이준</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G251" s="2">
+        <v>25900</v>
+      </c>
+      <c r="H251" s="2">
+        <v>62720</v>
+      </c>
+      <c r="I251" s="3">
+        <v>0.58</v>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/6018989978</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251217_43/1765937064469hdaqa_JPEG/8978054452910455_1480787040.jpg</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N251" s="2">
+        <v>1</v>
+      </c>
+      <c r="O251" s="2">
+        <v>0</v>
+      </c>
+      <c r="P251" s="2">
+        <v>25900</v>
+      </c>
+      <c r="Q251" s="3">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>100208089</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>11783643791</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>[손연재Pick] 보아르 엘레어 무풍 날개없는 선풍기 BLDC 가정용 저소음 아기방 접이식</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G252" s="2">
+        <v>98000</v>
+      </c>
+      <c r="H252" s="2">
+        <v>139000</v>
+      </c>
+      <c r="I252" s="3">
+        <v>0.29</v>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11783643791</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260417_73/17764065858597Htvd_JPEG/32389302971669705_320983410.jpg</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N252" s="2">
+        <v>1</v>
+      </c>
+      <c r="O252" s="2">
+        <v>0</v>
+      </c>
+      <c r="P252" s="2">
+        <v>98000</v>
+      </c>
+      <c r="Q252" s="3">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>100265349</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>12090482741</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>AMT 316Ti 통5중 2종세트(양수웍22+스마트쿡편수18)+사은품 미니스파츄라</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G253" s="2">
+        <v>338890</v>
+      </c>
+      <c r="H253" s="2">
+        <v>445000</v>
+      </c>
+      <c r="I253" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12090482741</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250917_40/1758111094912HfgVC_JPEG/21099326060081298_2073361470.jpg</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N253" s="2">
+        <v>1</v>
+      </c>
+      <c r="O253" s="2">
+        <v>0</v>
+      </c>
+      <c r="P253" s="2">
+        <v>338890</v>
+      </c>
+      <c r="Q253" s="3">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>100326348</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>5432307763</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>[평점 4.93] ++1등급 마장동 투뿔 한우 선물 세트 소고기 구이용 어버이날 가정의달</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G254" s="2">
+        <v>149900</v>
+      </c>
+      <c r="H254" s="2">
+        <v>598000</v>
+      </c>
+      <c r="I254" s="3">
+        <v>0.74</v>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5432307763</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260422_283/1776843076148Mr8bP_JPEG/0423_EC8AA4ED8E98EC859CEB949C_ED9994EBA0A4ED959CED959CE.jpg</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N254" s="2">
+        <v>1</v>
+      </c>
+      <c r="O254" s="2">
+        <v>0</v>
+      </c>
+      <c r="P254" s="2">
+        <v>149900</v>
+      </c>
+      <c r="Q254" s="3">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>100446531</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>10769889894</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>[체험팩] 당면이 들어간 부드러운 소불고기 400g 외 국물요리</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G255" s="2">
+        <v>5100</v>
+      </c>
+      <c r="H255" s="2">
+        <v>10100</v>
+      </c>
+      <c r="I255" s="3">
+        <v>0.49</v>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10769889894</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20240621_160/1718958787998jVGfN_JPEG/32811653883658832_1291388561.jpg</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N255" s="2">
+        <v>1</v>
+      </c>
+      <c r="O255" s="2">
+        <v>0</v>
+      </c>
+      <c r="P255" s="2">
+        <v>5100</v>
+      </c>
+      <c r="Q255" s="3">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>100585383</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>10703848922</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>냉동피자 나폴리 더블치즈피자 2판 외 마르게리따 고르곤졸라 페퍼로니</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G256" s="2">
+        <v>11900</v>
+      </c>
+      <c r="H256" s="2">
+        <v>19800</v>
+      </c>
+      <c r="I256" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10703848922</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260223_141/1771831320656MvcCC_JPEG/19192885496446441_1220211542.jpg</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N256" s="2">
+        <v>1</v>
+      </c>
+      <c r="O256" s="2">
+        <v>0</v>
+      </c>
+      <c r="P256" s="2">
+        <v>11900</v>
+      </c>
+      <c r="Q256" s="3">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>100596797</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>4775328206</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>프링글스 미니 오리지널 53g 12개 묶음 외 3종 골라담기</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G257" s="2">
+        <v>12500</v>
+      </c>
+      <c r="H257" s="2">
+        <v>20040</v>
+      </c>
+      <c r="I257" s="3">
+        <v>0.37</v>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/4775328206</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20240926_107/1727315271621ouVhR_JPEG/40559763426926135_1001613317.jpg</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N257" s="2">
+        <v>1</v>
+      </c>
+      <c r="O257" s="2">
+        <v>0</v>
+      </c>
+      <c r="P257" s="2">
+        <v>12500</v>
+      </c>
+      <c r="Q257" s="3">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>100650054</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>4890939517</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>제주반했어 제주 갈치 은갈치 어버이날 선물세트 가정의달 선물</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G258" s="2">
+        <v>79900</v>
+      </c>
+      <c r="H258" s="2">
+        <v>167200</v>
+      </c>
+      <c r="I258" s="3">
+        <v>0.52</v>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/4890939517</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250421_200/1745214772362Wcobd_JPEG/79347611477271628_684403218.jpg</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N258" s="2">
+        <v>1</v>
+      </c>
+      <c r="O258" s="2">
+        <v>0</v>
+      </c>
+      <c r="P258" s="2">
+        <v>79900</v>
+      </c>
+      <c r="Q258" s="3">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>100688696</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>12177030266</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>[공식][사은품증정]파나소닉 람대쉬 PRO 5중날 전기 면도기 ES-L550U</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G259" s="2">
+        <v>219000</v>
+      </c>
+      <c r="H259" s="2">
+        <v>349000</v>
+      </c>
+      <c r="I259" s="3">
+        <v>0.37</v>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12177030266</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251224_271/1766538852783GfpUO_JPEG/37931127598325378_454737606.jpg</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N259" s="2">
+        <v>1</v>
+      </c>
+      <c r="O259" s="2">
+        <v>0</v>
+      </c>
+      <c r="P259" s="2">
+        <v>219000</v>
+      </c>
+      <c r="Q259" s="3">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>100697164</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>13302270687</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>[오리온] 슈퍼스낵 14팩 (포카칩30g 3개 + 도도한나쵸 치즈맛50g 3개 + 썬 핫스파이시48g 4개 + 오징어땅콩 84g 4개)</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G260" s="2">
+        <v>13900</v>
+      </c>
+      <c r="H260" s="2">
+        <v>14000</v>
+      </c>
+      <c r="I260" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13302270687</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260407_197/1775522834197bkHcS_PNG/55560305266034860_1007663044.png</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N260" s="2">
+        <v>1</v>
+      </c>
+      <c r="O260" s="2">
+        <v>0</v>
+      </c>
+      <c r="P260" s="2">
+        <v>13900</v>
+      </c>
+      <c r="Q260" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>스페셜 멤버십</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>100876713</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>11291893389</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>연세두유 무가당 두유 190ml 오리지널 24팩 + 검은콩 24팩 (총 48팩)</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G261" s="2">
+        <v>22200</v>
+      </c>
+      <c r="H261" s="2">
+        <v>32000</v>
+      </c>
+      <c r="I261" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11291893389</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251224_88/1766555028696CkUP7_JPEG/46687451558119684_141189206.jpg</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N261" s="2">
+        <v>1</v>
+      </c>
+      <c r="O261" s="2">
+        <v>0</v>
+      </c>
+      <c r="P261" s="2">
+        <v>22200</v>
+      </c>
+      <c r="Q261" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>100894278</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>9968340523</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>폰타나 리조또 250g 8봉 세트 토마토 로제 트러플 전복 크림</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>뷰티/헬스</t>
+        </is>
+      </c>
+      <c r="G262" s="2">
+        <v>19980</v>
+      </c>
+      <c r="H262" s="2">
+        <v>39840</v>
+      </c>
+      <c r="I262" s="3">
+        <v>0.49</v>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/9968340523</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251113_75/1763010413956sD4DC_JPEG/24347661043276608_1024354793.jpg</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N262" s="2">
+        <v>1</v>
+      </c>
+      <c r="O262" s="2">
+        <v>0</v>
+      </c>
+      <c r="P262" s="2">
+        <v>19980</v>
+      </c>
+      <c r="Q262" s="3">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>100972973</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>13312553270</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>플라이밀 단백질 쉐이크 대용량 리얼초코, 630g, 1개</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G263" s="2">
+        <v>25900</v>
+      </c>
+      <c r="H263" s="2">
+        <v>42900</v>
+      </c>
+      <c r="I263" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13312553270</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260330_289/1774836276931rYMtd_JPEG/3977008535808148_220228328.jpg</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N263" s="2">
+        <v>1</v>
+      </c>
+      <c r="O263" s="2">
+        <v>0</v>
+      </c>
+      <c r="P263" s="2">
+        <v>25900</v>
+      </c>
+      <c r="Q263" s="3">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>100984090</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>12275406188</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>글라스락 훈맹정음 햇밥용기 혼합4조 세트 (베리핑크)</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G264" s="2">
+        <v>15900</v>
+      </c>
+      <c r="H264" s="2">
+        <v>29600</v>
+      </c>
+      <c r="I264" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12275406188</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250820_31/1755668723084tt75D_JPEG/89801554194840781_219026893.jpg</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N264" s="2">
+        <v>1</v>
+      </c>
+      <c r="O264" s="2">
+        <v>0</v>
+      </c>
+      <c r="P264" s="2">
+        <v>15900</v>
+      </c>
+      <c r="Q264" s="3">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>101111804</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>12154127416</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>[슈퍼적립 / 6개월분] CJ 바이오코어 500억 보장 부자 화사 유산균 상온보관 프로바이오틱스 90캡슐, 4개</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G265" s="2">
+        <v>175000</v>
+      </c>
+      <c r="H265" s="2">
+        <v>388000</v>
+      </c>
+      <c r="I265" s="3">
+        <v>0.54</v>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12154127416</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260325_103/1774417217459hn8Hj_JPEG/43076652301548162_1943318827.jpg</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N265" s="2">
+        <v>1</v>
+      </c>
+      <c r="O265" s="2">
+        <v>0</v>
+      </c>
+      <c r="P265" s="2">
+        <v>175000</v>
+      </c>
+      <c r="Q265" s="3">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>101214695</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>5654048425</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>투뿔 원뿔 한우 등심 구이용 설로인 소고기 선물세트</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G266" s="2">
+        <v>7900</v>
+      </c>
+      <c r="H266" s="2">
+        <v>49000</v>
+      </c>
+      <c r="I266" s="3">
+        <v>0.83</v>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5654048425</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260319_165/1773887368471vjv2Q_PNG/99062234208391936_1740167650.png</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N266" s="2">
+        <v>1</v>
+      </c>
+      <c r="O266" s="2">
+        <v>0</v>
+      </c>
+      <c r="P266" s="2">
+        <v>7900</v>
+      </c>
+      <c r="Q266" s="3">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>101236937</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>9949281398</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>바이브랩 리바이브 테라피 헤어 스칼프 앤 브로우 앰플 두피 탈모 앰플 시트러스, 15ml, 2개</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G267" s="2">
+        <v>37900</v>
+      </c>
+      <c r="H267" s="2">
+        <v>39900</v>
+      </c>
+      <c r="I267" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/9949281398</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251230_139/1767074044097oeGt5_JPEG/101206891197020431_975009107.jpg</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N267" s="2">
+        <v>1</v>
+      </c>
+      <c r="O267" s="2">
+        <v>0</v>
+      </c>
+      <c r="P267" s="2">
+        <v>37900</v>
+      </c>
+      <c r="Q267" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>101265962</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>13268206981</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>[8매]메종드코튼 옐로우 8종 호텔타올 + 옐로우 비숑 핸드 수건 선물세트 코마 40수</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G268" s="2">
+        <v>88000</v>
+      </c>
+      <c r="H268" s="2">
+        <v>112000</v>
+      </c>
+      <c r="I268" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13268206981</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260318_35/1773809267785vU0ig_JPEG/7873640669647115_42776490.jpg</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N268" s="2">
+        <v>1</v>
+      </c>
+      <c r="O268" s="2">
+        <v>0</v>
+      </c>
+      <c r="P268" s="2">
+        <v>88000</v>
+      </c>
+      <c r="Q268" s="3">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>101623111</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>13401302430</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>[오영주 PICK!] 카누 에스프레소 쇼콜라 라떼 8개입</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G269" s="2">
+        <v>4950</v>
+      </c>
+      <c r="H269" s="2">
+        <v>5250</v>
+      </c>
+      <c r="I269" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13401302430</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260421_82/17767583988708XS4r_JPEG/31291616947744061_133071915.jpg</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N269" s="2">
+        <v>1</v>
+      </c>
+      <c r="O269" s="2">
+        <v>0</v>
+      </c>
+      <c r="P269" s="2">
+        <v>4950</v>
+      </c>
+      <c r="Q269" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>101691981</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>7514709651</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>농협식품 한국농협김치 포기김치 8kg</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G270" s="2">
+        <v>60900</v>
+      </c>
+      <c r="H270" s="2">
+        <v>70500</v>
+      </c>
+      <c r="I270" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/7514709651</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20221114_219/1668355813406IR3fk_JPEG/69491712106791588_668621267.jpg</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N270" s="2">
+        <v>1</v>
+      </c>
+      <c r="O270" s="2">
+        <v>0</v>
+      </c>
+      <c r="P270" s="2">
+        <v>60900</v>
+      </c>
+      <c r="Q270" s="3">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>101716663</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>7467727208</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>제주 레드 블러드 오렌지 3kg 5kg 산지직송 붉은과육 피 모로 타로코</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G271" s="2">
+        <v>27000</v>
+      </c>
+      <c r="H271" s="2">
+        <v>56010</v>
+      </c>
+      <c r="I271" s="3">
+        <v>0.51</v>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/7467727208</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260303_21/1772500347839tt2Ow_PNG/19861912653290452_1062633955.png</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N271" s="2">
+        <v>1</v>
+      </c>
+      <c r="O271" s="2">
+        <v>0</v>
+      </c>
+      <c r="P271" s="2">
+        <v>27000</v>
+      </c>
+      <c r="Q271" s="3">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>101739204</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>13330453274</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>[라운지전용] 올라플렉스 본드 리페어 4종 스타터 세트 (30ml x 4)</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G272" s="2">
+        <v>34000</v>
+      </c>
+      <c r="H272" s="2">
+        <v>40000</v>
+      </c>
+      <c r="I272" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13330453274</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260406_68/1775443053925NcHvk_JPEG/90451547946446064_1087407969.jpg</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N272" s="2">
+        <v>1</v>
+      </c>
+      <c r="O272" s="2">
+        <v>0</v>
+      </c>
+      <c r="P272" s="2">
+        <v>34000</v>
+      </c>
+      <c r="Q272" s="3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>101983093</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>13364295769</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>당일작업 신선 한우 투뿔 꽃등심 1++등급, 200g, 3개</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G273" s="2">
+        <v>54900</v>
+      </c>
+      <c r="H273" s="2">
+        <v>89900</v>
+      </c>
+      <c r="I273" s="3">
+        <v>0.38</v>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13364295769</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250327_231/1743039849830O4YCn_JPEG/34763625764510742_1822067959.jpg</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N273" s="2">
+        <v>1</v>
+      </c>
+      <c r="O273" s="2">
+        <v>0</v>
+      </c>
+      <c r="P273" s="2">
+        <v>54900</v>
+      </c>
+      <c r="Q273" s="3">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>102125733</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>12865150072</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>동화약품 부채표 까스활 소화제 생약성분 75ml, 30개</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G274" s="2">
+        <v>22600</v>
+      </c>
+      <c r="H274" s="2">
+        <v>36000</v>
+      </c>
+      <c r="I274" s="3">
+        <v>0.37</v>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12865150072</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260413_146/1776006151986htR6E_JPEG/17152881698810618_138946562.jpg</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N274" s="2">
+        <v>1</v>
+      </c>
+      <c r="O274" s="2">
+        <v>0</v>
+      </c>
+      <c r="P274" s="2">
+        <v>22600</v>
+      </c>
+      <c r="Q274" s="3">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>102655931</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>12274347011</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>[2개 구매 시 30%][올바르고 반듯한] 슈퍼크런치 치킨텐더</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G275" s="2">
+        <v>8960</v>
+      </c>
+      <c r="H275" s="2">
+        <v>8960</v>
+      </c>
+      <c r="I275" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12274347011</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250707_165/1751863615393coaex_JPEG/6386656708622106_561133368.jpg</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N275" s="2">
+        <v>1</v>
+      </c>
+      <c r="O275" s="2">
+        <v>0</v>
+      </c>
+      <c r="P275" s="2">
+        <v>8960</v>
+      </c>
+      <c r="Q275" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>102655931</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>12274668708</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>[Kurly's] 순살 생선 4종 (택1)</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G276" s="2">
+        <v>10</v>
+      </c>
+      <c r="H276" s="2">
+        <v>10</v>
+      </c>
+      <c r="I276" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12274668708</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250820_102/17556592155346c6Xd_JPEG/14037311830422111_111507286.jpg</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N276" s="2">
+        <v>1</v>
+      </c>
+      <c r="O276" s="2">
+        <v>0</v>
+      </c>
+      <c r="P276" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q276" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>102697265</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>12695509167</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>리퀴드 1챔버 라벤더 캡슐 200개입</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G277" s="2">
+        <v>9900</v>
+      </c>
+      <c r="H277" s="2">
+        <v>19800</v>
+      </c>
+      <c r="I277" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12695509167</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260421_96/1776732337847TNUhC_JPEG/131560892767327796_258608049.jpg</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N277" s="2">
+        <v>1</v>
+      </c>
+      <c r="O277" s="2">
+        <v>0</v>
+      </c>
+      <c r="P277" s="2">
+        <v>9900</v>
+      </c>
+      <c r="Q277" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>500052051</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>13039971075</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>[콜라보 기획] 바나나맛우유 x 스크럽대디 한정판 선물세트(바나나맛우유 240ml X 6개 + 스크럽대디 수세미 2팩)</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G278" s="2">
+        <v>22500</v>
+      </c>
+      <c r="H278" s="2">
+        <v>33200</v>
+      </c>
+      <c r="I278" s="3">
+        <v>0.32</v>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13039971075</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260305_191/1772696138021fIhjx_PNG/90654613814085026_1917351241.png</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N278" s="2">
+        <v>1</v>
+      </c>
+      <c r="O278" s="2">
+        <v>0</v>
+      </c>
+      <c r="P278" s="2">
+        <v>22500</v>
+      </c>
+      <c r="Q278" s="3">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>500058721</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>12799898430</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>테이크핏 맥스 혼합 250ml, 20개</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G279" s="2">
+        <v>26200</v>
+      </c>
+      <c r="H279" s="2">
+        <v>50000</v>
+      </c>
+      <c r="I279" s="3">
+        <v>0.47</v>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12799898430</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260402_188/1775119501096tOJiX_JPEG/28714413239266561_1030809156.jpg</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N279" s="2">
+        <v>1</v>
+      </c>
+      <c r="O279" s="2">
+        <v>0</v>
+      </c>
+      <c r="P279" s="2">
+        <v>26200</v>
+      </c>
+      <c r="Q279" s="3">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>500092658</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>11778601625</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>필립스 휴대용 파워 초경량 진동 무선 미니 마사지건 목 어깨 등 PPM7308</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G280" s="2">
+        <v>94900</v>
+      </c>
+      <c r="H280" s="2">
+        <v>267400</v>
+      </c>
+      <c r="I280" s="3">
+        <v>0.64</v>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11778601625</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250820_146/1755657079579jTmuW_JPEG/69037061431340171_897043549.jpg</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N280" s="2">
+        <v>1</v>
+      </c>
+      <c r="O280" s="2">
+        <v>0</v>
+      </c>
+      <c r="P280" s="2">
+        <v>94900</v>
+      </c>
+      <c r="Q280" s="3">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>500104713</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>12864085409</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>얌 황치즈 꾸덕파이10입 1박스 외 (슈크림/소보로/호떡)</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>뷰티/헬스</t>
+        </is>
+      </c>
+      <c r="G281" s="2">
+        <v>12900</v>
+      </c>
+      <c r="H281" s="2">
+        <v>16900</v>
+      </c>
+      <c r="I281" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12864085409</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251224_216/1766563496246SzCsf_JPEG/42331798333071156_722306175.jpg</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N281" s="2">
+        <v>1</v>
+      </c>
+      <c r="O281" s="2">
+        <v>0</v>
+      </c>
+      <c r="P281" s="2">
+        <v>12900</v>
+      </c>
+      <c r="Q281" s="3">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>500113054</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>13069776991</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>투디터 빅사이즈 UV차단 선글라스 데일리 패션 가벼운 긱시크 호피 나일론렌즈 MARS</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G282" s="2">
+        <v>39900</v>
+      </c>
+      <c r="H282" s="2">
+        <v>100000</v>
+      </c>
+      <c r="I282" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13069776991</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260205_93/17702790959021s0c6_JPEG/17640660754326438_2024291869.jpg</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N282" s="2">
+        <v>1</v>
+      </c>
+      <c r="O282" s="2">
+        <v>0</v>
+      </c>
+      <c r="P282" s="2">
+        <v>39900</v>
+      </c>
+      <c r="Q282" s="3">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>스페셜 멤버십</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>500128699</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>4982502523</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>대천김 곱창김 캔김 30g 15캔</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G283" s="2">
+        <v>63900</v>
+      </c>
+      <c r="H283" s="2">
+        <v>67000</v>
+      </c>
+      <c r="I283" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/4982502523</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20240820_27/1724116332516RTuSL_JPEG/4087975345574906_870166074.jpg</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N283" s="2">
+        <v>1</v>
+      </c>
+      <c r="O283" s="2">
+        <v>0</v>
+      </c>
+      <c r="P283" s="2">
+        <v>63900</v>
+      </c>
+      <c r="Q283" s="3">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>500146241</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>9570948941</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>[스페셜딜][슈퍼적립] 다루마낫또 (30일분/90일분) 일본 나또 나토 44.8g, 30개</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G284" s="2">
+        <v>26900</v>
+      </c>
+      <c r="H284" s="2">
+        <v>45000</v>
+      </c>
+      <c r="I284" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/9570948941</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250516_167/1747383638914eujee_JPEG/1986727059704282_1811047042.jpg</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N284" s="2">
+        <v>1</v>
+      </c>
+      <c r="O284" s="2">
+        <v>0</v>
+      </c>
+      <c r="P284" s="2">
+        <v>26900</v>
+      </c>
+      <c r="Q284" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>500148890</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>13409811316</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>[1박스] 아침 집밥 아침밥 국산쌀 (210gx12개입)</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G285" s="2">
+        <v>9900</v>
+      </c>
+      <c r="H285" s="2">
+        <v>15600</v>
+      </c>
+      <c r="I285" s="3">
+        <v>0.36</v>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13409811316</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260420_242/1776669819404TpbHq_JPEG/56066340560738725_1389432615.jpg</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N285" s="2">
+        <v>1</v>
+      </c>
+      <c r="O285" s="2">
+        <v>0</v>
+      </c>
+      <c r="P285" s="2">
+        <v>9900</v>
+      </c>
+      <c r="Q285" s="3">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>스페셜 체험딜</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>500192537</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>13279257016</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>이온 스플래쉬 수분 캡슐 크림 10ml+안심 마스크팩 1매</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>뷰티/헬스</t>
+        </is>
+      </c>
+      <c r="G286" s="2">
+        <v>990</v>
+      </c>
+      <c r="H286" s="2">
+        <v>3000</v>
+      </c>
+      <c r="I286" s="3">
+        <v>0.67</v>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13279257016</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260414_249/17761297526999OFy0_JPEG/25708908593244042_1603348128.jpg</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N286" s="2">
+        <v>1</v>
+      </c>
+      <c r="O286" s="2">
+        <v>0</v>
+      </c>
+      <c r="P286" s="2">
+        <v>990</v>
+      </c>
+      <c r="Q286" s="3">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>500201947</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>12994639337</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>[스케쳐스] 여성 고워크 나우 슬립인스 오버레이</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G287" s="2">
+        <v>89000</v>
+      </c>
+      <c r="H287" s="2">
+        <v>129000</v>
+      </c>
+      <c r="I287" s="3">
+        <v>0.31</v>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12994639337</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260423_282/1776902481785y0pz4_JPEG/10799504801541243_581598595.jpg</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N287" s="2">
+        <v>1</v>
+      </c>
+      <c r="O287" s="2">
+        <v>0</v>
+      </c>
+      <c r="P287" s="2">
+        <v>89000</v>
+      </c>
+      <c r="Q287" s="3">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>500219602</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>13331919661</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>[2+2] 틈새싹 초슬림 줄눈 청소솔 욕실 주방용 구석 청소 브러쉬 (총 4P)</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>생활/주방</t>
+        </is>
+      </c>
+      <c r="G288" s="2">
+        <v>4900</v>
+      </c>
+      <c r="H288" s="2">
+        <v>10900</v>
+      </c>
+      <c r="I288" s="3">
+        <v>0.55</v>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13331919661</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260409_68/1775718040792FO4ir_JPEG/20545133292467335_674570372.jpg</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N288" s="2">
+        <v>1</v>
+      </c>
+      <c r="O288" s="2">
+        <v>0</v>
+      </c>
+      <c r="P288" s="2">
+        <v>4900</v>
+      </c>
+      <c r="Q288" s="3">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>500240447</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>8570473906</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>아이깨끗해 핸드워시 250ml 본품 2개+200ml 리필 4개+100ml 증정</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>생활/주방</t>
+        </is>
+      </c>
+      <c r="G289" s="2">
+        <v>10900</v>
+      </c>
+      <c r="H289" s="2">
+        <v>21900</v>
+      </c>
+      <c r="I289" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/8570473906</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260422_150/1776846433288lAo8G_JPEG/31364425664344694_1765054873.jpg</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N289" s="2">
+        <v>1</v>
+      </c>
+      <c r="O289" s="2">
+        <v>0</v>
+      </c>
+      <c r="P289" s="2">
+        <v>10900</v>
+      </c>
+      <c r="Q289" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>500286107</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>7595414146</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>더리얼 캣 그레인프리 크런치 고양이 사료 3.2kg (닭고기+연어 어덜트)</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G290" s="2">
+        <v>58650</v>
+      </c>
+      <c r="H290" s="2">
+        <v>69000</v>
+      </c>
+      <c r="I290" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/7595414146</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250707_41/1751847943011btMGA_JPEG/4562255125269758_2073168089.jpg</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="N290" s="2">
+        <v>1</v>
+      </c>
+      <c r="O290" s="2">
+        <v>0</v>
+      </c>
+      <c r="P290" s="2">
+        <v>58650</v>
+      </c>
+      <c r="Q290" s="3">
+        <v>0.15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q248"/>
+  <autoFilter ref="A1:Q290"/>
 </worksheet>
 </file>
--- a/data/derived/todaysdeal-analysis.xlsx
+++ b/data/derived/todaysdeal-analysis.xlsx
@@ -57,7 +57,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H204"/>
+  <dimension ref="A1:I223"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -67,6 +67,7 @@
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -110,6 +111,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -138,6 +144,9 @@
       <c r="H2" s="2">
         <v>0</v>
       </c>
+      <c r="I2" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -166,6 +175,9 @@
       <c r="H3" s="2">
         <v>1</v>
       </c>
+      <c r="I3" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -194,6 +206,9 @@
       <c r="H4" s="2">
         <v>0</v>
       </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -222,11 +237,14 @@
       <c r="H5" s="2">
         <v>0</v>
       </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>100129181</t>
+          <t>100102221</t>
         </is>
       </c>
       <c r="B6" s="2">
@@ -245,16 +263,19 @@
         <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2">
         <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>100131340</t>
+          <t>100129181</t>
         </is>
       </c>
       <c r="B7" s="2">
@@ -264,7 +285,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2">
         <v>0</v>
@@ -273,16 +294,19 @@
         <v>0</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>100136792</t>
+          <t>100131340</t>
         </is>
       </c>
       <c r="B8" s="2">
@@ -292,25 +316,28 @@
         <v>0</v>
       </c>
       <c r="D8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>100137620</t>
+          <t>100136792</t>
         </is>
       </c>
       <c r="B9" s="2">
@@ -326,75 +353,84 @@
         <v>0</v>
       </c>
       <c r="F9" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>100146361</t>
+          <t>100137620</t>
         </is>
       </c>
       <c r="B10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
       </c>
       <c r="G10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>100181508</t>
+          <t>100146361</t>
         </is>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2">
         <v>0</v>
       </c>
       <c r="G11" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>100187146</t>
+          <t>100165024</t>
         </is>
       </c>
       <c r="B12" s="2">
@@ -407,7 +443,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="2">
         <v>0</v>
@@ -417,19 +453,22 @@
       </c>
       <c r="H12" s="2">
         <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>100208089</t>
+          <t>100181508</t>
         </is>
       </c>
       <c r="B13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
@@ -444,13 +483,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>100261289</t>
+          <t>100187146</t>
         </is>
       </c>
       <c r="B14" s="2">
@@ -463,22 +505,25 @@
         <v>0</v>
       </c>
       <c r="E14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
       </c>
       <c r="G14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>100262120</t>
+          <t>100208089</t>
         </is>
       </c>
       <c r="B15" s="2">
@@ -500,13 +545,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>100262284</t>
+          <t>100252160</t>
         </is>
       </c>
       <c r="B16" s="2">
@@ -525,16 +573,19 @@
         <v>0</v>
       </c>
       <c r="G16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="2">
         <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>100265349</t>
+          <t>100261289</t>
         </is>
       </c>
       <c r="B17" s="2">
@@ -553,16 +604,19 @@
         <v>0</v>
       </c>
       <c r="G17" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>100265766</t>
+          <t>100262120</t>
         </is>
       </c>
       <c r="B18" s="2">
@@ -584,20 +638,23 @@
         <v>0</v>
       </c>
       <c r="H18" s="2">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>100274539</t>
+          <t>100262284</t>
         </is>
       </c>
       <c r="B19" s="2">
         <v>0</v>
       </c>
       <c r="C19" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="2">
         <v>0</v>
@@ -609,20 +666,23 @@
         <v>0</v>
       </c>
       <c r="G19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="2">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>100292269</t>
+          <t>100265349</t>
         </is>
       </c>
       <c r="B20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
@@ -640,13 +700,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>100292757</t>
+          <t>100265766</t>
         </is>
       </c>
       <c r="B21" s="2">
@@ -668,13 +731,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>100305602</t>
+          <t>100274539</t>
         </is>
       </c>
       <c r="B22" s="2">
@@ -684,7 +750,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2">
         <v>0</v>
@@ -696,20 +762,23 @@
         <v>0</v>
       </c>
       <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>100326348</t>
+          <t>100292269</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
@@ -724,20 +793,23 @@
         <v>0</v>
       </c>
       <c r="H23" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>100327929</t>
+          <t>100292757</t>
         </is>
       </c>
       <c r="B24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2">
         <v>0</v>
@@ -752,26 +824,29 @@
         <v>0</v>
       </c>
       <c r="H24" s="2">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>100336563</t>
+          <t>100305602</t>
         </is>
       </c>
       <c r="B25" s="2">
         <v>0</v>
       </c>
       <c r="C25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2">
         <v>0</v>
@@ -780,23 +855,26 @@
         <v>0</v>
       </c>
       <c r="H25" s="2">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>100340418</t>
+          <t>100326348</t>
         </is>
       </c>
       <c r="B26" s="2">
         <v>0</v>
       </c>
       <c r="C26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="2">
         <v>0</v>
@@ -808,20 +886,23 @@
         <v>0</v>
       </c>
       <c r="H26" s="2">
+        <v>1</v>
+      </c>
+      <c r="I26" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>100387111</t>
+          <t>100327929</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="2">
         <v>0</v>
@@ -836,13 +917,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>100419781</t>
+          <t>100336563</t>
         </is>
       </c>
       <c r="B28" s="2">
@@ -864,13 +948,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>100446531</t>
+          <t>100336757</t>
         </is>
       </c>
       <c r="B29" s="2">
@@ -886,19 +973,22 @@
         <v>0</v>
       </c>
       <c r="F29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="2">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>100449422</t>
+          <t>100340418</t>
         </is>
       </c>
       <c r="B30" s="2">
@@ -908,10 +998,10 @@
         <v>0</v>
       </c>
       <c r="D30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="2">
         <v>0</v>
@@ -921,19 +1011,22 @@
       </c>
       <c r="H30" s="2">
         <v>0</v>
+      </c>
+      <c r="I30" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>100458264</t>
+          <t>100387111</t>
         </is>
       </c>
       <c r="B31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
@@ -948,13 +1041,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>100474685</t>
+          <t>100419781</t>
         </is>
       </c>
       <c r="B32" s="2">
@@ -964,10 +1060,10 @@
         <v>0</v>
       </c>
       <c r="D32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="2">
         <v>0</v>
@@ -976,13 +1072,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>100492521</t>
+          <t>100433029</t>
         </is>
       </c>
       <c r="B33" s="2">
@@ -992,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="2">
         <v>0</v>
@@ -1005,12 +1104,15 @@
       </c>
       <c r="H33" s="2">
         <v>0</v>
+      </c>
+      <c r="I33" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>100503327</t>
+          <t>100446531</t>
         </is>
       </c>
       <c r="B34" s="2">
@@ -1023,22 +1125,25 @@
         <v>0</v>
       </c>
       <c r="E34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="2">
+        <v>1</v>
+      </c>
+      <c r="I34" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>100542499</t>
+          <t>100449422</t>
         </is>
       </c>
       <c r="B35" s="2">
@@ -1048,10 +1153,10 @@
         <v>0</v>
       </c>
       <c r="D35" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="2">
         <v>0</v>
@@ -1060,13 +1165,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2">
+        <v>0</v>
+      </c>
+      <c r="I35" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>100585383</t>
+          <t>100449469</t>
         </is>
       </c>
       <c r="B36" s="2">
@@ -1088,17 +1196,20 @@
         <v>0</v>
       </c>
       <c r="H36" s="2">
+        <v>0</v>
+      </c>
+      <c r="I36" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>100586493</t>
+          <t>100458264</t>
         </is>
       </c>
       <c r="B37" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
@@ -1107,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="2">
         <v>0</v>
@@ -1116,13 +1227,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2">
+        <v>0</v>
+      </c>
+      <c r="I37" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>100587614</t>
+          <t>100474685</t>
         </is>
       </c>
       <c r="B38" s="2">
@@ -1144,23 +1258,26 @@
         <v>0</v>
       </c>
       <c r="H38" s="2">
+        <v>0</v>
+      </c>
+      <c r="I38" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>100596797</t>
+          <t>100492521</t>
         </is>
       </c>
       <c r="B39" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C39" s="2">
         <v>0</v>
       </c>
       <c r="D39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="2">
         <v>0</v>
@@ -1172,13 +1289,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I39" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>100626189</t>
+          <t>100503327</t>
         </is>
       </c>
       <c r="B40" s="2">
@@ -1191,32 +1311,35 @@
         <v>0</v>
       </c>
       <c r="E40" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="2">
         <v>0</v>
       </c>
       <c r="G40" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="2">
+        <v>0</v>
+      </c>
+      <c r="I40" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>100627146</t>
+          <t>100542499</t>
         </is>
       </c>
       <c r="B41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" s="2">
         <v>0</v>
       </c>
       <c r="D41" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="2">
         <v>0</v>
@@ -1228,17 +1351,20 @@
         <v>0</v>
       </c>
       <c r="H41" s="2">
+        <v>0</v>
+      </c>
+      <c r="I41" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>100650054</t>
+          <t>100585383</t>
         </is>
       </c>
       <c r="B42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C42" s="2">
         <v>0</v>
@@ -1257,12 +1383,15 @@
       </c>
       <c r="H42" s="2">
         <v>1</v>
+      </c>
+      <c r="I42" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>100688696</t>
+          <t>100586493</t>
         </is>
       </c>
       <c r="B43" s="2">
@@ -1275,7 +1404,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="2">
         <v>0</v>
@@ -1284,13 +1413,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I43" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>100697164</t>
+          <t>100587614</t>
         </is>
       </c>
       <c r="B44" s="2">
@@ -1300,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="2">
         <v>0</v>
@@ -1312,17 +1444,20 @@
         <v>0</v>
       </c>
       <c r="H44" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I44" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>100730113</t>
+          <t>100596797</t>
         </is>
       </c>
       <c r="B45" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
@@ -1331,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" s="2">
         <v>0</v>
@@ -1340,13 +1475,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2">
+        <v>1</v>
+      </c>
+      <c r="I45" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>100752133</t>
+          <t>100597188</t>
         </is>
       </c>
       <c r="B46" s="2">
@@ -1356,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" s="2">
         <v>0</v>
@@ -1369,12 +1507,15 @@
       </c>
       <c r="H46" s="2">
         <v>0</v>
+      </c>
+      <c r="I46" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>100754913</t>
+          <t>100626189</t>
         </is>
       </c>
       <c r="B47" s="2">
@@ -1393,16 +1534,19 @@
         <v>0</v>
       </c>
       <c r="G47" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47" s="2">
+        <v>0</v>
+      </c>
+      <c r="I47" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>100770404</t>
+          <t>100627146</t>
         </is>
       </c>
       <c r="B48" s="2">
@@ -1425,22 +1569,25 @@
       </c>
       <c r="H48" s="2">
         <v>0</v>
+      </c>
+      <c r="I48" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>100774355</t>
+          <t>100650054</t>
         </is>
       </c>
       <c r="B49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
       </c>
       <c r="D49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" s="2">
         <v>0</v>
@@ -1452,13 +1599,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2">
+        <v>1</v>
+      </c>
+      <c r="I49" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>100791007</t>
+          <t>100688696</t>
         </is>
       </c>
       <c r="B50" s="2">
@@ -1474,19 +1624,22 @@
         <v>0</v>
       </c>
       <c r="F50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" s="2">
         <v>0</v>
       </c>
       <c r="H50" s="2">
+        <v>1</v>
+      </c>
+      <c r="I50" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>100791832</t>
+          <t>100697164</t>
         </is>
       </c>
       <c r="B51" s="2">
@@ -1496,25 +1649,28 @@
         <v>0</v>
       </c>
       <c r="D51" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E51" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" s="2">
         <v>0</v>
       </c>
       <c r="H51" s="2">
+        <v>1</v>
+      </c>
+      <c r="I51" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>100795594</t>
+          <t>100730113</t>
         </is>
       </c>
       <c r="B52" s="2">
@@ -1527,22 +1683,25 @@
         <v>0</v>
       </c>
       <c r="E52" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="2">
         <v>0</v>
       </c>
       <c r="G52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" s="2">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>100813952</t>
+          <t>100752133</t>
         </is>
       </c>
       <c r="B53" s="2">
@@ -1552,7 +1711,7 @@
         <v>0</v>
       </c>
       <c r="D53" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" s="2">
         <v>0</v>
@@ -1561,16 +1720,19 @@
         <v>0</v>
       </c>
       <c r="G53" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" s="2">
+        <v>0</v>
+      </c>
+      <c r="I53" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>100823000</t>
+          <t>100754913</t>
         </is>
       </c>
       <c r="B54" s="2">
@@ -1580,38 +1742,41 @@
         <v>0</v>
       </c>
       <c r="D54" s="2">
+        <v>0</v>
+      </c>
+      <c r="E54" s="2">
+        <v>0</v>
+      </c>
+      <c r="F54" s="2">
+        <v>0</v>
+      </c>
+      <c r="G54" s="2">
         <v>2</v>
       </c>
-      <c r="E54" s="2">
-        <v>0</v>
-      </c>
-      <c r="F54" s="2">
-        <v>0</v>
-      </c>
-      <c r="G54" s="2">
-        <v>0</v>
-      </c>
       <c r="H54" s="2">
+        <v>0</v>
+      </c>
+      <c r="I54" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>100827249</t>
+          <t>100770404</t>
         </is>
       </c>
       <c r="B55" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55" s="2">
         <v>0</v>
       </c>
       <c r="E55" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" s="2">
         <v>0</v>
@@ -1620,13 +1785,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2">
+        <v>0</v>
+      </c>
+      <c r="I55" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>100862614</t>
+          <t>100774355</t>
         </is>
       </c>
       <c r="B56" s="2">
@@ -1636,32 +1804,35 @@
         <v>0</v>
       </c>
       <c r="D56" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" s="2">
         <v>0</v>
       </c>
       <c r="G56" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" s="2">
         <v>0</v>
+      </c>
+      <c r="I56" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>100864321</t>
+          <t>100791007</t>
         </is>
       </c>
       <c r="B57" s="2">
         <v>0</v>
       </c>
       <c r="C57" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57" s="2">
         <v>0</v>
@@ -1670,19 +1841,22 @@
         <v>0</v>
       </c>
       <c r="F57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
+        <v>0</v>
+      </c>
+      <c r="I57" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>100864434</t>
+          <t>100791832</t>
         </is>
       </c>
       <c r="B58" s="2">
@@ -1692,10 +1866,10 @@
         <v>0</v>
       </c>
       <c r="D58" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E58" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="2">
         <v>1</v>
@@ -1704,13 +1878,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2">
+        <v>0</v>
+      </c>
+      <c r="I58" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>100876713</t>
+          <t>100795594</t>
         </is>
       </c>
       <c r="B59" s="2">
@@ -1726,23 +1903,26 @@
         <v>0</v>
       </c>
       <c r="F59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" s="2">
         <v>1</v>
       </c>
       <c r="H59" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I59" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>100888704</t>
+          <t>100813952</t>
         </is>
       </c>
       <c r="B60" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C60" s="2">
         <v>0</v>
@@ -1757,16 +1937,19 @@
         <v>0</v>
       </c>
       <c r="G60" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" s="2">
         <v>0</v>
+      </c>
+      <c r="I60" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>100890156</t>
+          <t>100823000</t>
         </is>
       </c>
       <c r="B61" s="2">
@@ -1776,38 +1959,41 @@
         <v>0</v>
       </c>
       <c r="D61" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E61" s="2">
         <v>0</v>
       </c>
       <c r="F61" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" s="2">
         <v>0</v>
       </c>
       <c r="H61" s="2">
+        <v>0</v>
+      </c>
+      <c r="I61" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>100894278</t>
+          <t>100827249</t>
         </is>
       </c>
       <c r="B62" s="2">
         <v>0</v>
       </c>
       <c r="C62" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62" s="2">
         <v>0</v>
       </c>
       <c r="E62" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="2">
         <v>0</v>
@@ -1816,13 +2002,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I62" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>100938809</t>
+          <t>100840656</t>
         </is>
       </c>
       <c r="B63" s="2">
@@ -1838,54 +2027,60 @@
         <v>0</v>
       </c>
       <c r="F63" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G63" s="2">
         <v>0</v>
       </c>
       <c r="H63" s="2">
         <v>0</v>
+      </c>
+      <c r="I63" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>100955968</t>
+          <t>100862614</t>
         </is>
       </c>
       <c r="B64" s="2">
         <v>0</v>
       </c>
       <c r="C64" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64" s="2">
         <v>0</v>
       </c>
       <c r="E64" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" s="2">
         <v>0</v>
       </c>
       <c r="G64" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" s="2">
+        <v>0</v>
+      </c>
+      <c r="I64" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>100960111</t>
+          <t>100864321</t>
         </is>
       </c>
       <c r="B65" s="2">
         <v>0</v>
       </c>
       <c r="C65" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65" s="2">
         <v>0</v>
@@ -1897,16 +2092,19 @@
         <v>0</v>
       </c>
       <c r="G65" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" s="2">
+        <v>0</v>
+      </c>
+      <c r="I65" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>100961074</t>
+          <t>100864434</t>
         </is>
       </c>
       <c r="B66" s="2">
@@ -1928,13 +2126,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2">
+        <v>0</v>
+      </c>
+      <c r="I66" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>100972973</t>
+          <t>100876713</t>
         </is>
       </c>
       <c r="B67" s="2">
@@ -1944,29 +2145,32 @@
         <v>0</v>
       </c>
       <c r="D67" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" s="2">
         <v>0</v>
       </c>
       <c r="F67" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" s="2">
         <v>1</v>
+      </c>
+      <c r="I67" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>100984090</t>
+          <t>100888704</t>
         </is>
       </c>
       <c r="B68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68" s="2">
         <v>0</v>
@@ -1984,13 +2188,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I68" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>101013887</t>
+          <t>100890156</t>
         </is>
       </c>
       <c r="B69" s="2">
@@ -2012,13 +2219,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2">
+        <v>0</v>
+      </c>
+      <c r="I69" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>101015607</t>
+          <t>100894278</t>
         </is>
       </c>
       <c r="B70" s="2">
@@ -2037,16 +2247,19 @@
         <v>0</v>
       </c>
       <c r="G70" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" s="2">
+        <v>1</v>
+      </c>
+      <c r="I70" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>101034585</t>
+          <t>100937343</t>
         </is>
       </c>
       <c r="B71" s="2">
@@ -2059,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" s="2">
         <v>0</v>
@@ -2069,16 +2282,19 @@
       </c>
       <c r="H71" s="2">
         <v>0</v>
+      </c>
+      <c r="I71" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>101037405</t>
+          <t>100938809</t>
         </is>
       </c>
       <c r="B72" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C72" s="2">
         <v>0</v>
@@ -2090,32 +2306,35 @@
         <v>0</v>
       </c>
       <c r="F72" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G72" s="2">
         <v>0</v>
       </c>
       <c r="H72" s="2">
+        <v>0</v>
+      </c>
+      <c r="I72" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>101102225</t>
+          <t>100955968</t>
         </is>
       </c>
       <c r="B73" s="2">
         <v>0</v>
       </c>
       <c r="C73" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73" s="2">
         <v>0</v>
       </c>
       <c r="E73" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" s="2">
         <v>0</v>
@@ -2124,13 +2343,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2">
+        <v>0</v>
+      </c>
+      <c r="I73" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>101108628</t>
+          <t>100960111</t>
         </is>
       </c>
       <c r="B74" s="2">
@@ -2146,19 +2368,22 @@
         <v>0</v>
       </c>
       <c r="F74" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" s="2">
+        <v>0</v>
+      </c>
+      <c r="I74" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>101111804</t>
+          <t>100961074</t>
         </is>
       </c>
       <c r="B75" s="2">
@@ -2168,25 +2393,28 @@
         <v>0</v>
       </c>
       <c r="D75" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" s="2">
         <v>0</v>
       </c>
       <c r="F75" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
       </c>
       <c r="H75" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I75" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>101161925</t>
+          <t>100972973</t>
         </is>
       </c>
       <c r="B76" s="2">
@@ -2208,13 +2436,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2">
+        <v>1</v>
+      </c>
+      <c r="I76" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>101174078</t>
+          <t>100984090</t>
         </is>
       </c>
       <c r="B77" s="2">
@@ -2227,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="E77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77" s="2">
         <v>0</v>
@@ -2236,17 +2467,20 @@
         <v>0</v>
       </c>
       <c r="H77" s="2">
+        <v>1</v>
+      </c>
+      <c r="I77" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>101195987</t>
+          <t>101013887</t>
         </is>
       </c>
       <c r="B78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C78" s="2">
         <v>0</v>
@@ -2258,19 +2492,22 @@
         <v>0</v>
       </c>
       <c r="F78" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
       </c>
       <c r="H78" s="2">
+        <v>0</v>
+      </c>
+      <c r="I78" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>101214695</t>
+          <t>101015607</t>
         </is>
       </c>
       <c r="B79" s="2">
@@ -2289,20 +2526,23 @@
         <v>0</v>
       </c>
       <c r="G79" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" s="2">
+        <v>0</v>
+      </c>
+      <c r="I79" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>101232925</t>
+          <t>101034585</t>
         </is>
       </c>
       <c r="B80" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C80" s="2">
         <v>0</v>
@@ -2311,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="E80" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="2">
         <v>0</v>
@@ -2320,17 +2560,20 @@
         <v>0</v>
       </c>
       <c r="H80" s="2">
+        <v>0</v>
+      </c>
+      <c r="I80" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>101236937</t>
+          <t>101037405</t>
         </is>
       </c>
       <c r="B81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C81" s="2">
         <v>0</v>
@@ -2348,13 +2591,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I81" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>101237859</t>
+          <t>101078690</t>
         </is>
       </c>
       <c r="B82" s="2">
@@ -2373,16 +2619,19 @@
         <v>0</v>
       </c>
       <c r="G82" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" s="2">
         <v>0</v>
+      </c>
+      <c r="I82" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>101251735</t>
+          <t>101102225</t>
         </is>
       </c>
       <c r="B83" s="2">
@@ -2395,22 +2644,25 @@
         <v>0</v>
       </c>
       <c r="E83" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="2">
         <v>0</v>
       </c>
       <c r="G83" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" s="2">
+        <v>0</v>
+      </c>
+      <c r="I83" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>101265962</t>
+          <t>101108628</t>
         </is>
       </c>
       <c r="B84" s="2">
@@ -2426,29 +2678,32 @@
         <v>0</v>
       </c>
       <c r="F84" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
       </c>
       <c r="H84" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I84" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>101295037</t>
+          <t>101111804</t>
         </is>
       </c>
       <c r="B85" s="2">
         <v>0</v>
       </c>
       <c r="C85" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85" s="2">
         <v>0</v>
@@ -2460,13 +2715,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I85" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>101335538</t>
+          <t>101161925</t>
         </is>
       </c>
       <c r="B86" s="2">
@@ -2476,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="D86" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" s="2">
         <v>0</v>
@@ -2485,16 +2743,19 @@
         <v>0</v>
       </c>
       <c r="G86" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" s="2">
+        <v>0</v>
+      </c>
+      <c r="I86" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>101336693</t>
+          <t>101174078</t>
         </is>
       </c>
       <c r="B87" s="2">
@@ -2507,22 +2768,25 @@
         <v>0</v>
       </c>
       <c r="E87" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G87" s="2">
         <v>0</v>
       </c>
       <c r="H87" s="2">
+        <v>0</v>
+      </c>
+      <c r="I87" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>101372175</t>
+          <t>101192951</t>
         </is>
       </c>
       <c r="B88" s="2">
@@ -2532,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="D88" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" s="2">
         <v>0</v>
@@ -2545,22 +2809,25 @@
       </c>
       <c r="H88" s="2">
         <v>0</v>
+      </c>
+      <c r="I88" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>101396394</t>
+          <t>101195987</t>
         </is>
       </c>
       <c r="B89" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
       </c>
       <c r="D89" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" s="2">
         <v>0</v>
@@ -2572,13 +2839,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2">
+        <v>0</v>
+      </c>
+      <c r="I89" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>101407817</t>
+          <t>101214695</t>
         </is>
       </c>
       <c r="B90" s="2">
@@ -2591,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="E90" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F90" s="2">
         <v>0</v>
@@ -2600,20 +2870,23 @@
         <v>0</v>
       </c>
       <c r="H90" s="2">
+        <v>1</v>
+      </c>
+      <c r="I90" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>101434241</t>
+          <t>101232925</t>
         </is>
       </c>
       <c r="B91" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C91" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D91" s="2">
         <v>0</v>
@@ -2628,20 +2901,23 @@
         <v>0</v>
       </c>
       <c r="H91" s="2">
+        <v>0</v>
+      </c>
+      <c r="I91" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>101437685</t>
+          <t>101236937</t>
         </is>
       </c>
       <c r="B92" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C92" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92" s="2">
         <v>0</v>
@@ -2656,20 +2932,23 @@
         <v>0</v>
       </c>
       <c r="H92" s="2">
+        <v>1</v>
+      </c>
+      <c r="I92" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>101467964</t>
+          <t>101237859</t>
         </is>
       </c>
       <c r="B93" s="2">
         <v>0</v>
       </c>
       <c r="C93" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D93" s="2">
         <v>0</v>
@@ -2681,23 +2960,26 @@
         <v>0</v>
       </c>
       <c r="G93" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" s="2">
+        <v>0</v>
+      </c>
+      <c r="I93" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>101481537</t>
+          <t>101251735</t>
         </is>
       </c>
       <c r="B94" s="2">
         <v>0</v>
       </c>
       <c r="C94" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D94" s="2">
         <v>0</v>
@@ -2709,20 +2991,23 @@
         <v>0</v>
       </c>
       <c r="G94" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" s="2">
+        <v>0</v>
+      </c>
+      <c r="I94" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>101509593</t>
+          <t>101265962</t>
         </is>
       </c>
       <c r="B95" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C95" s="2">
         <v>0</v>
@@ -2740,20 +3025,23 @@
         <v>0</v>
       </c>
       <c r="H95" s="2">
+        <v>1</v>
+      </c>
+      <c r="I95" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>101533995</t>
+          <t>101295037</t>
         </is>
       </c>
       <c r="B96" s="2">
         <v>0</v>
       </c>
       <c r="C96" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96" s="2">
         <v>0</v>
@@ -2762,23 +3050,26 @@
         <v>0</v>
       </c>
       <c r="F96" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" s="2">
         <v>0</v>
       </c>
       <c r="H96" s="2">
+        <v>0</v>
+      </c>
+      <c r="I96" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>101573499</t>
+          <t>101331865</t>
         </is>
       </c>
       <c r="B97" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C97" s="2">
         <v>0</v>
@@ -2793,16 +3084,19 @@
         <v>0</v>
       </c>
       <c r="G97" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97" s="2">
         <v>0</v>
+      </c>
+      <c r="I97" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>101623111</t>
+          <t>101335538</t>
         </is>
       </c>
       <c r="B98" s="2">
@@ -2821,16 +3115,19 @@
         <v>0</v>
       </c>
       <c r="G98" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I98" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>101639078</t>
+          <t>101336693</t>
         </is>
       </c>
       <c r="B99" s="2">
@@ -2843,22 +3140,25 @@
         <v>0</v>
       </c>
       <c r="E99" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F99" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G99" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" s="2">
+        <v>0</v>
+      </c>
+      <c r="I99" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>101649796</t>
+          <t>101342244</t>
         </is>
       </c>
       <c r="B100" s="2">
@@ -2874,19 +3174,22 @@
         <v>0</v>
       </c>
       <c r="F100" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" s="2">
         <v>0</v>
       </c>
       <c r="H100" s="2">
         <v>0</v>
+      </c>
+      <c r="I100" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>101691981</t>
+          <t>101372175</t>
         </is>
       </c>
       <c r="B101" s="2">
@@ -2896,25 +3199,28 @@
         <v>0</v>
       </c>
       <c r="D101" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" s="2">
         <v>0</v>
       </c>
       <c r="F101" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" s="2">
         <v>0</v>
       </c>
       <c r="H101" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I101" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>101716663</t>
+          <t>101396394</t>
         </is>
       </c>
       <c r="B102" s="2">
@@ -2924,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="D102" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E102" s="2">
         <v>0</v>
@@ -2936,13 +3242,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I102" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>101739204</t>
+          <t>101407817</t>
         </is>
       </c>
       <c r="B103" s="2">
@@ -2955,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="E103" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="2">
         <v>0</v>
@@ -2964,20 +3273,23 @@
         <v>0</v>
       </c>
       <c r="H103" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I103" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>101800057</t>
+          <t>101434241</t>
         </is>
       </c>
       <c r="B104" s="2">
         <v>0</v>
       </c>
       <c r="C104" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D104" s="2">
         <v>0</v>
@@ -2986,23 +3298,26 @@
         <v>0</v>
       </c>
       <c r="F104" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104" s="2">
         <v>0</v>
       </c>
       <c r="H104" s="2">
+        <v>0</v>
+      </c>
+      <c r="I104" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>101836491</t>
+          <t>101437685</t>
         </is>
       </c>
       <c r="B105" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -3020,13 +3335,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2">
+        <v>0</v>
+      </c>
+      <c r="I105" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>101863433</t>
+          <t>101467964</t>
         </is>
       </c>
       <c r="B106" s="2">
@@ -3048,26 +3366,29 @@
         <v>0</v>
       </c>
       <c r="H106" s="2">
+        <v>0</v>
+      </c>
+      <c r="I106" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>101875176</t>
+          <t>101481537</t>
         </is>
       </c>
       <c r="B107" s="2">
         <v>0</v>
       </c>
       <c r="C107" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D107" s="2">
         <v>0</v>
       </c>
       <c r="E107" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F107" s="2">
         <v>0</v>
@@ -3076,13 +3397,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2">
+        <v>0</v>
+      </c>
+      <c r="I107" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>101885140</t>
+          <t>101509593</t>
         </is>
       </c>
       <c r="B108" s="2">
@@ -3104,20 +3428,23 @@
         <v>0</v>
       </c>
       <c r="H108" s="2">
+        <v>0</v>
+      </c>
+      <c r="I108" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>101888773</t>
+          <t>101533995</t>
         </is>
       </c>
       <c r="B109" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C109" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D109" s="2">
         <v>0</v>
@@ -3129,20 +3456,23 @@
         <v>1</v>
       </c>
       <c r="G109" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H109" s="2">
+        <v>0</v>
+      </c>
+      <c r="I109" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>101903020</t>
+          <t>101573499</t>
         </is>
       </c>
       <c r="B110" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C110" s="2">
         <v>0</v>
@@ -3154,19 +3484,22 @@
         <v>0</v>
       </c>
       <c r="F110" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" s="2">
         <v>0</v>
+      </c>
+      <c r="I110" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>101983093</t>
+          <t>101623111</t>
         </is>
       </c>
       <c r="B111" s="2">
@@ -3189,22 +3522,25 @@
       </c>
       <c r="H111" s="2">
         <v>1</v>
+      </c>
+      <c r="I111" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>102006080</t>
+          <t>101639078</t>
         </is>
       </c>
       <c r="B112" s="2">
         <v>0</v>
       </c>
       <c r="C112" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D112" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" s="2">
         <v>0</v>
@@ -3213,23 +3549,26 @@
         <v>0</v>
       </c>
       <c r="G112" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" s="2">
+        <v>0</v>
+      </c>
+      <c r="I112" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>102006845</t>
+          <t>101649796</t>
         </is>
       </c>
       <c r="B113" s="2">
         <v>0</v>
       </c>
       <c r="C113" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D113" s="2">
         <v>0</v>
@@ -3238,19 +3577,22 @@
         <v>0</v>
       </c>
       <c r="F113" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" s="2">
         <v>0</v>
       </c>
       <c r="H113" s="2">
+        <v>0</v>
+      </c>
+      <c r="I113" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>102050130</t>
+          <t>101691981</t>
         </is>
       </c>
       <c r="B114" s="2">
@@ -3263,22 +3605,25 @@
         <v>0</v>
       </c>
       <c r="E114" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G114" s="2">
         <v>0</v>
       </c>
       <c r="H114" s="2">
+        <v>1</v>
+      </c>
+      <c r="I114" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>102109244</t>
+          <t>101716663</t>
         </is>
       </c>
       <c r="B115" s="2">
@@ -3291,7 +3636,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F115" s="2">
         <v>0</v>
@@ -3300,13 +3645,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2">
+        <v>1</v>
+      </c>
+      <c r="I115" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>102125733</t>
+          <t>101739204</t>
         </is>
       </c>
       <c r="B116" s="2">
@@ -3329,12 +3677,15 @@
       </c>
       <c r="H116" s="2">
         <v>1</v>
+      </c>
+      <c r="I116" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>102203438</t>
+          <t>101800057</t>
         </is>
       </c>
       <c r="B117" s="2">
@@ -3347,29 +3698,32 @@
         <v>0</v>
       </c>
       <c r="E117" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F117" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G117" s="2">
         <v>0</v>
       </c>
       <c r="H117" s="2">
+        <v>0</v>
+      </c>
+      <c r="I117" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>102224443</t>
+          <t>101836491</t>
         </is>
       </c>
       <c r="B118" s="2">
         <v>0</v>
       </c>
       <c r="C118" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D118" s="2">
         <v>0</v>
@@ -3378,19 +3732,22 @@
         <v>0</v>
       </c>
       <c r="F118" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" s="2">
+        <v>0</v>
+      </c>
+      <c r="I118" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>102227253</t>
+          <t>101863433</t>
         </is>
       </c>
       <c r="B119" s="2">
@@ -3412,13 +3769,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2">
+        <v>0</v>
+      </c>
+      <c r="I119" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>102282059</t>
+          <t>101875176</t>
         </is>
       </c>
       <c r="B120" s="2">
@@ -3440,20 +3800,23 @@
         <v>0</v>
       </c>
       <c r="H120" s="2">
+        <v>0</v>
+      </c>
+      <c r="I120" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>102299090</t>
+          <t>101885140</t>
         </is>
       </c>
       <c r="B121" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C121" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D121" s="2">
         <v>0</v>
@@ -3468,48 +3831,54 @@
         <v>0</v>
       </c>
       <c r="H121" s="2">
+        <v>0</v>
+      </c>
+      <c r="I121" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>102307203</t>
+          <t>101888773</t>
         </is>
       </c>
       <c r="B122" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C122" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D122" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E122" s="2">
         <v>0</v>
       </c>
       <c r="F122" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H122" s="2">
+        <v>0</v>
+      </c>
+      <c r="I122" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>102375097</t>
+          <t>101903020</t>
         </is>
       </c>
       <c r="B123" s="2">
         <v>0</v>
       </c>
       <c r="C123" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D123" s="2">
         <v>0</v>
@@ -3518,23 +3887,26 @@
         <v>0</v>
       </c>
       <c r="F123" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G123" s="2">
         <v>0</v>
       </c>
       <c r="H123" s="2">
+        <v>0</v>
+      </c>
+      <c r="I123" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>102454744</t>
+          <t>101910440</t>
         </is>
       </c>
       <c r="B124" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C124" s="2">
         <v>0</v>
@@ -3553,16 +3925,19 @@
       </c>
       <c r="H124" s="2">
         <v>0</v>
+      </c>
+      <c r="I124" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>102497144</t>
+          <t>101983093</t>
         </is>
       </c>
       <c r="B125" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C125" s="2">
         <v>0</v>
@@ -3580,13 +3955,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2">
+        <v>1</v>
+      </c>
+      <c r="I125" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>102569542</t>
+          <t>101996505</t>
         </is>
       </c>
       <c r="B126" s="2">
@@ -3602,29 +3980,32 @@
         <v>0</v>
       </c>
       <c r="F126" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126" s="2">
         <v>0</v>
       </c>
       <c r="H126" s="2">
         <v>0</v>
+      </c>
+      <c r="I126" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>102600124</t>
+          <t>102006080</t>
         </is>
       </c>
       <c r="B127" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C127" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D127" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E127" s="2">
         <v>0</v>
@@ -3636,54 +4017,60 @@
         <v>0</v>
       </c>
       <c r="H127" s="2">
+        <v>0</v>
+      </c>
+      <c r="I127" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>102655931</t>
+          <t>102006845</t>
         </is>
       </c>
       <c r="B128" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C128" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D128" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E128" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F128" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G128" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H128" s="2">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="I128" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>102673781</t>
+          <t>102050130</t>
         </is>
       </c>
       <c r="B129" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C129" s="2">
         <v>0</v>
       </c>
       <c r="D129" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" s="2">
         <v>0</v>
@@ -3692,13 +4079,16 @@
         <v>0</v>
       </c>
       <c r="H129" s="2">
+        <v>0</v>
+      </c>
+      <c r="I129" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>102690829</t>
+          <t>102109244</t>
         </is>
       </c>
       <c r="B130" s="2">
@@ -3708,10 +4098,10 @@
         <v>0</v>
       </c>
       <c r="D130" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" s="2">
         <v>0</v>
@@ -3720,13 +4110,16 @@
         <v>0</v>
       </c>
       <c r="H130" s="2">
+        <v>0</v>
+      </c>
+      <c r="I130" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>102697265</t>
+          <t>102125733</t>
         </is>
       </c>
       <c r="B131" s="2">
@@ -3749,16 +4142,19 @@
       </c>
       <c r="H131" s="2">
         <v>1</v>
+      </c>
+      <c r="I131" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>102698382</t>
+          <t>102203438</t>
         </is>
       </c>
       <c r="B132" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C132" s="2">
         <v>0</v>
@@ -3767,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="E132" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" s="2">
         <v>0</v>
@@ -3776,13 +4172,16 @@
         <v>0</v>
       </c>
       <c r="H132" s="2">
+        <v>0</v>
+      </c>
+      <c r="I132" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>102705657</t>
+          <t>102224443</t>
         </is>
       </c>
       <c r="B133" s="2">
@@ -3792,25 +4191,28 @@
         <v>0</v>
       </c>
       <c r="D133" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E133" s="2">
         <v>0</v>
       </c>
       <c r="F133" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G133" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H133" s="2">
+        <v>0</v>
+      </c>
+      <c r="I133" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>102748593</t>
+          <t>102227253</t>
         </is>
       </c>
       <c r="B134" s="2">
@@ -3832,13 +4234,16 @@
         <v>0</v>
       </c>
       <c r="H134" s="2">
+        <v>0</v>
+      </c>
+      <c r="I134" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>102793147</t>
+          <t>102282059</t>
         </is>
       </c>
       <c r="B135" s="2">
@@ -3860,20 +4265,23 @@
         <v>0</v>
       </c>
       <c r="H135" s="2">
+        <v>0</v>
+      </c>
+      <c r="I135" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>102796686</t>
+          <t>102299090</t>
         </is>
       </c>
       <c r="B136" s="2">
         <v>0</v>
       </c>
       <c r="C136" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D136" s="2">
         <v>0</v>
@@ -3885,16 +4293,19 @@
         <v>0</v>
       </c>
       <c r="G136" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H136" s="2">
+        <v>0</v>
+      </c>
+      <c r="I136" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1100043267</t>
+          <t>102307203</t>
         </is>
       </c>
       <c r="B137" s="2">
@@ -3904,32 +4315,35 @@
         <v>0</v>
       </c>
       <c r="D137" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137" s="2">
         <v>0</v>
       </c>
       <c r="F137" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" s="2">
         <v>0</v>
       </c>
       <c r="H137" s="2">
+        <v>0</v>
+      </c>
+      <c r="I137" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1100079588</t>
+          <t>102375097</t>
         </is>
       </c>
       <c r="B138" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C138" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D138" s="2">
         <v>0</v>
@@ -3944,20 +4358,23 @@
         <v>0</v>
       </c>
       <c r="H138" s="2">
+        <v>0</v>
+      </c>
+      <c r="I138" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>500000823</t>
+          <t>102454744</t>
         </is>
       </c>
       <c r="B139" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C139" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D139" s="2">
         <v>0</v>
@@ -3972,23 +4389,26 @@
         <v>0</v>
       </c>
       <c r="H139" s="2">
+        <v>0</v>
+      </c>
+      <c r="I139" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>500000921</t>
+          <t>102497144</t>
         </is>
       </c>
       <c r="B140" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C140" s="2">
         <v>0</v>
       </c>
       <c r="D140" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E140" s="2">
         <v>0</v>
@@ -4000,13 +4420,16 @@
         <v>0</v>
       </c>
       <c r="H140" s="2">
+        <v>0</v>
+      </c>
+      <c r="I140" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>500002685</t>
+          <t>102569542</t>
         </is>
       </c>
       <c r="B141" s="2">
@@ -4019,22 +4442,25 @@
         <v>0</v>
       </c>
       <c r="E141" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F141" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" s="2">
         <v>0</v>
       </c>
       <c r="H141" s="2">
+        <v>0</v>
+      </c>
+      <c r="I141" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>500003288</t>
+          <t>102600124</t>
         </is>
       </c>
       <c r="B142" s="2">
@@ -4056,101 +4482,113 @@
         <v>0</v>
       </c>
       <c r="H142" s="2">
+        <v>0</v>
+      </c>
+      <c r="I142" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>500003682</t>
+          <t>102655931</t>
         </is>
       </c>
       <c r="B143" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C143" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D143" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E143" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G143" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H143" s="2">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I143" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>500008320</t>
+          <t>102673781</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C144" s="2">
         <v>0</v>
       </c>
       <c r="D144" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E144" s="2">
         <v>0</v>
       </c>
       <c r="F144" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G144" s="2">
         <v>0</v>
       </c>
       <c r="H144" s="2">
+        <v>0</v>
+      </c>
+      <c r="I144" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>500009413</t>
+          <t>102690829</t>
         </is>
       </c>
       <c r="B145" s="2">
         <v>0</v>
       </c>
       <c r="C145" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D145" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E145" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F145" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145" s="2">
         <v>0</v>
       </c>
       <c r="H145" s="2">
+        <v>0</v>
+      </c>
+      <c r="I145" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>500016197</t>
+          <t>102697265</t>
         </is>
       </c>
       <c r="B146" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C146" s="2">
         <v>0</v>
@@ -4168,17 +4606,20 @@
         <v>0</v>
       </c>
       <c r="H146" s="2">
+        <v>1</v>
+      </c>
+      <c r="I146" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>500020789</t>
+          <t>102698382</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C147" s="2">
         <v>0</v>
@@ -4187,7 +4628,7 @@
         <v>0</v>
       </c>
       <c r="E147" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F147" s="2">
         <v>0</v>
@@ -4196,23 +4637,26 @@
         <v>0</v>
       </c>
       <c r="H147" s="2">
+        <v>0</v>
+      </c>
+      <c r="I147" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>500023997</t>
+          <t>102705657</t>
         </is>
       </c>
       <c r="B148" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C148" s="2">
         <v>0</v>
       </c>
       <c r="D148" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E148" s="2">
         <v>0</v>
@@ -4224,23 +4668,26 @@
         <v>0</v>
       </c>
       <c r="H148" s="2">
+        <v>0</v>
+      </c>
+      <c r="I148" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>500024124</t>
+          <t>102748593</t>
         </is>
       </c>
       <c r="B149" s="2">
         <v>0</v>
       </c>
       <c r="C149" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D149" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149" s="2">
         <v>0</v>
@@ -4252,13 +4699,16 @@
         <v>0</v>
       </c>
       <c r="H149" s="2">
+        <v>0</v>
+      </c>
+      <c r="I149" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>500028485</t>
+          <t>102793147</t>
         </is>
       </c>
       <c r="B150" s="2">
@@ -4268,25 +4718,28 @@
         <v>0</v>
       </c>
       <c r="D150" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F150" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G150" s="2">
         <v>0</v>
       </c>
       <c r="H150" s="2">
+        <v>0</v>
+      </c>
+      <c r="I150" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>500030111</t>
+          <t>102796686</t>
         </is>
       </c>
       <c r="B151" s="2">
@@ -4305,16 +4758,19 @@
         <v>0</v>
       </c>
       <c r="G151" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H151" s="2">
+        <v>0</v>
+      </c>
+      <c r="I151" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>500031227</t>
+          <t>1100043267</t>
         </is>
       </c>
       <c r="B152" s="2">
@@ -4336,20 +4792,23 @@
         <v>0</v>
       </c>
       <c r="H152" s="2">
+        <v>0</v>
+      </c>
+      <c r="I152" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>500031276</t>
+          <t>1100063691</t>
         </is>
       </c>
       <c r="B153" s="2">
         <v>0</v>
       </c>
       <c r="C153" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D153" s="2">
         <v>0</v>
@@ -4365,12 +4824,15 @@
       </c>
       <c r="H153" s="2">
         <v>0</v>
+      </c>
+      <c r="I153" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>500032408</t>
+          <t>1100079588</t>
         </is>
       </c>
       <c r="B154" s="2">
@@ -4392,23 +4854,26 @@
         <v>0</v>
       </c>
       <c r="H154" s="2">
+        <v>0</v>
+      </c>
+      <c r="I154" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>500035796</t>
+          <t>500000823</t>
         </is>
       </c>
       <c r="B155" s="2">
         <v>0</v>
       </c>
       <c r="C155" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D155" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E155" s="2">
         <v>0</v>
@@ -4420,23 +4885,26 @@
         <v>0</v>
       </c>
       <c r="H155" s="2">
+        <v>0</v>
+      </c>
+      <c r="I155" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>500036672</t>
+          <t>500000921</t>
         </is>
       </c>
       <c r="B156" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C156" s="2">
         <v>0</v>
       </c>
       <c r="D156" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E156" s="2">
         <v>0</v>
@@ -4448,13 +4916,16 @@
         <v>0</v>
       </c>
       <c r="H156" s="2">
+        <v>0</v>
+      </c>
+      <c r="I156" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>500037006</t>
+          <t>500002685</t>
         </is>
       </c>
       <c r="B157" s="2">
@@ -4470,23 +4941,26 @@
         <v>1</v>
       </c>
       <c r="F157" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G157" s="2">
         <v>0</v>
       </c>
       <c r="H157" s="2">
+        <v>0</v>
+      </c>
+      <c r="I157" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>500050269</t>
+          <t>500003288</t>
         </is>
       </c>
       <c r="B158" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C158" s="2">
         <v>0</v>
@@ -4501,23 +4975,26 @@
         <v>0</v>
       </c>
       <c r="G158" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H158" s="2">
+        <v>0</v>
+      </c>
+      <c r="I158" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>500052051</t>
+          <t>500003337</t>
         </is>
       </c>
       <c r="B159" s="2">
         <v>0</v>
       </c>
       <c r="C159" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D159" s="2">
         <v>0</v>
@@ -4532,17 +5009,20 @@
         <v>0</v>
       </c>
       <c r="H159" s="2">
+        <v>0</v>
+      </c>
+      <c r="I159" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>500057619</t>
+          <t>500003682</t>
         </is>
       </c>
       <c r="B160" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C160" s="2">
         <v>1</v>
@@ -4551,7 +5031,7 @@
         <v>0</v>
       </c>
       <c r="E160" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F160" s="2">
         <v>0</v>
@@ -4560,13 +5040,16 @@
         <v>0</v>
       </c>
       <c r="H160" s="2">
+        <v>0</v>
+      </c>
+      <c r="I160" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>500058721</t>
+          <t>500008320</t>
         </is>
       </c>
       <c r="B161" s="2">
@@ -4582,23 +5065,26 @@
         <v>0</v>
       </c>
       <c r="F161" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G161" s="2">
         <v>0</v>
       </c>
       <c r="H161" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I161" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>500060661</t>
+          <t>500009413</t>
         </is>
       </c>
       <c r="B162" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C162" s="2">
         <v>1</v>
@@ -4607,22 +5093,25 @@
         <v>0</v>
       </c>
       <c r="E162" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F162" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G162" s="2">
         <v>0</v>
       </c>
       <c r="H162" s="2">
+        <v>0</v>
+      </c>
+      <c r="I162" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>500061708</t>
+          <t>500016197</t>
         </is>
       </c>
       <c r="B163" s="2">
@@ -4632,7 +5121,7 @@
         <v>0</v>
       </c>
       <c r="D163" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E163" s="2">
         <v>0</v>
@@ -4645,12 +5134,15 @@
       </c>
       <c r="H163" s="2">
         <v>0</v>
+      </c>
+      <c r="I163" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>500066176</t>
+          <t>500020789</t>
         </is>
       </c>
       <c r="B164" s="2">
@@ -4663,26 +5155,29 @@
         <v>0</v>
       </c>
       <c r="E164" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F164" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G164" s="2">
         <v>0</v>
       </c>
       <c r="H164" s="2">
+        <v>0</v>
+      </c>
+      <c r="I164" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>500067801</t>
+          <t>500023997</t>
         </is>
       </c>
       <c r="B165" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C165" s="2">
         <v>0</v>
@@ -4697,16 +5192,19 @@
         <v>0</v>
       </c>
       <c r="G165" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H165" s="2">
+        <v>0</v>
+      </c>
+      <c r="I165" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>500080387</t>
+          <t>500024124</t>
         </is>
       </c>
       <c r="B166" s="2">
@@ -4716,7 +5214,7 @@
         <v>0</v>
       </c>
       <c r="D166" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E166" s="2">
         <v>0</v>
@@ -4725,16 +5223,19 @@
         <v>0</v>
       </c>
       <c r="G166" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H166" s="2">
+        <v>0</v>
+      </c>
+      <c r="I166" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>500092658</t>
+          <t>500028485</t>
         </is>
       </c>
       <c r="B167" s="2">
@@ -4744,25 +5245,28 @@
         <v>0</v>
       </c>
       <c r="D167" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E167" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F167" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G167" s="2">
         <v>0</v>
       </c>
       <c r="H167" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I167" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>500094507</t>
+          <t>500030111</t>
         </is>
       </c>
       <c r="B168" s="2">
@@ -4772,7 +5276,7 @@
         <v>0</v>
       </c>
       <c r="D168" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E168" s="2">
         <v>0</v>
@@ -4781,16 +5285,19 @@
         <v>0</v>
       </c>
       <c r="G168" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H168" s="2">
+        <v>0</v>
+      </c>
+      <c r="I168" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>500101533</t>
+          <t>500031227</t>
         </is>
       </c>
       <c r="B169" s="2">
@@ -4812,20 +5319,23 @@
         <v>0</v>
       </c>
       <c r="H169" s="2">
+        <v>0</v>
+      </c>
+      <c r="I169" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>500104713</t>
+          <t>500031276</t>
         </is>
       </c>
       <c r="B170" s="2">
         <v>0</v>
       </c>
       <c r="C170" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D170" s="2">
         <v>0</v>
@@ -4840,23 +5350,26 @@
         <v>0</v>
       </c>
       <c r="H170" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I170" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>500111404</t>
+          <t>500032408</t>
         </is>
       </c>
       <c r="B171" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C171" s="2">
         <v>0</v>
       </c>
       <c r="D171" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E171" s="2">
         <v>0</v>
@@ -4868,13 +5381,16 @@
         <v>0</v>
       </c>
       <c r="H171" s="2">
+        <v>0</v>
+      </c>
+      <c r="I171" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>500113054</t>
+          <t>500035796</t>
         </is>
       </c>
       <c r="B172" s="2">
@@ -4884,7 +5400,7 @@
         <v>0</v>
       </c>
       <c r="D172" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E172" s="2">
         <v>0</v>
@@ -4896,13 +5412,16 @@
         <v>0</v>
       </c>
       <c r="H172" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I172" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>500115640</t>
+          <t>500036672</t>
         </is>
       </c>
       <c r="B173" s="2">
@@ -4918,19 +5437,22 @@
         <v>0</v>
       </c>
       <c r="F173" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G173" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H173" s="2">
+        <v>0</v>
+      </c>
+      <c r="I173" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>500117284</t>
+          <t>500037006</t>
         </is>
       </c>
       <c r="B174" s="2">
@@ -4940,35 +5462,38 @@
         <v>0</v>
       </c>
       <c r="D174" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E174" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F174" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G174" s="2">
         <v>0</v>
       </c>
       <c r="H174" s="2">
         <v>0</v>
+      </c>
+      <c r="I174" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>500120216</t>
+          <t>500043218</t>
         </is>
       </c>
       <c r="B175" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C175" s="2">
         <v>0</v>
       </c>
       <c r="D175" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E175" s="2">
         <v>0</v>
@@ -4981,12 +5506,15 @@
       </c>
       <c r="H175" s="2">
         <v>0</v>
+      </c>
+      <c r="I175" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>500126621</t>
+          <t>500050269</t>
         </is>
       </c>
       <c r="B176" s="2">
@@ -4996,7 +5524,7 @@
         <v>0</v>
       </c>
       <c r="D176" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E176" s="2">
         <v>0</v>
@@ -5008,20 +5536,23 @@
         <v>1</v>
       </c>
       <c r="H176" s="2">
+        <v>0</v>
+      </c>
+      <c r="I176" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>500127435</t>
+          <t>500052051</t>
         </is>
       </c>
       <c r="B177" s="2">
         <v>0</v>
       </c>
       <c r="C177" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D177" s="2">
         <v>0</v>
@@ -5033,23 +5564,26 @@
         <v>0</v>
       </c>
       <c r="G177" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H177" s="2">
+        <v>1</v>
+      </c>
+      <c r="I177" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>500128032</t>
+          <t>500057619</t>
         </is>
       </c>
       <c r="B178" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C178" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D178" s="2">
         <v>0</v>
@@ -5058,19 +5592,22 @@
         <v>0</v>
       </c>
       <c r="F178" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G178" s="2">
         <v>0</v>
       </c>
       <c r="H178" s="2">
+        <v>0</v>
+      </c>
+      <c r="I178" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>500128657</t>
+          <t>500058721</t>
         </is>
       </c>
       <c r="B179" s="2">
@@ -5086,26 +5623,29 @@
         <v>0</v>
       </c>
       <c r="F179" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G179" s="2">
         <v>0</v>
       </c>
       <c r="H179" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I179" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>500128699</t>
+          <t>500060661</t>
         </is>
       </c>
       <c r="B180" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C180" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D180" s="2">
         <v>0</v>
@@ -5120,23 +5660,26 @@
         <v>0</v>
       </c>
       <c r="H180" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I180" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>500143502</t>
+          <t>500061708</t>
         </is>
       </c>
       <c r="B181" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C181" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D181" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E181" s="2">
         <v>0</v>
@@ -5148,17 +5691,20 @@
         <v>0</v>
       </c>
       <c r="H181" s="2">
+        <v>0</v>
+      </c>
+      <c r="I181" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>500143882</t>
+          <t>500066176</t>
         </is>
       </c>
       <c r="B182" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C182" s="2">
         <v>0</v>
@@ -5170,19 +5716,22 @@
         <v>0</v>
       </c>
       <c r="F182" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G182" s="2">
         <v>0</v>
       </c>
       <c r="H182" s="2">
+        <v>0</v>
+      </c>
+      <c r="I182" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>500146241</t>
+          <t>500067801</t>
         </is>
       </c>
       <c r="B183" s="2">
@@ -5201,20 +5750,23 @@
         <v>0</v>
       </c>
       <c r="G183" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H183" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I183" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>500146800</t>
+          <t>500080387</t>
         </is>
       </c>
       <c r="B184" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C184" s="2">
         <v>0</v>
@@ -5232,13 +5784,16 @@
         <v>1</v>
       </c>
       <c r="H184" s="2">
+        <v>0</v>
+      </c>
+      <c r="I184" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>500148890</t>
+          <t>500092658</t>
         </is>
       </c>
       <c r="B185" s="2">
@@ -5261,22 +5816,25 @@
       </c>
       <c r="H185" s="2">
         <v>1</v>
+      </c>
+      <c r="I185" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>500185891</t>
+          <t>500094507</t>
         </is>
       </c>
       <c r="B186" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C186" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D186" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E186" s="2">
         <v>0</v>
@@ -5288,13 +5846,16 @@
         <v>0</v>
       </c>
       <c r="H186" s="2">
+        <v>0</v>
+      </c>
+      <c r="I186" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>500186481</t>
+          <t>500101533</t>
         </is>
       </c>
       <c r="B187" s="2">
@@ -5310,26 +5871,29 @@
         <v>0</v>
       </c>
       <c r="F187" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G187" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H187" s="2">
+        <v>0</v>
+      </c>
+      <c r="I187" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>500187931</t>
+          <t>500104713</t>
         </is>
       </c>
       <c r="B188" s="2">
         <v>0</v>
       </c>
       <c r="C188" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D188" s="2">
         <v>0</v>
@@ -5344,13 +5908,16 @@
         <v>0</v>
       </c>
       <c r="H188" s="2">
+        <v>1</v>
+      </c>
+      <c r="I188" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>500192537</t>
+          <t>500111404</t>
         </is>
       </c>
       <c r="B189" s="2">
@@ -5360,7 +5927,7 @@
         <v>0</v>
       </c>
       <c r="D189" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E189" s="2">
         <v>0</v>
@@ -5372,13 +5939,16 @@
         <v>0</v>
       </c>
       <c r="H189" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I189" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>500199878</t>
+          <t>500113054</t>
         </is>
       </c>
       <c r="B190" s="2">
@@ -5394,23 +5964,26 @@
         <v>0</v>
       </c>
       <c r="F190" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G190" s="2">
         <v>0</v>
       </c>
       <c r="H190" s="2">
+        <v>1</v>
+      </c>
+      <c r="I190" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>500201947</t>
+          <t>500115640</t>
         </is>
       </c>
       <c r="B191" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C191" s="2">
         <v>0</v>
@@ -5422,29 +5995,32 @@
         <v>0</v>
       </c>
       <c r="F191" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G191" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H191" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I191" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>500211718</t>
+          <t>500117284</t>
         </is>
       </c>
       <c r="B192" s="2">
         <v>0</v>
       </c>
       <c r="C192" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D192" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E192" s="2">
         <v>0</v>
@@ -5456,20 +6032,23 @@
         <v>0</v>
       </c>
       <c r="H192" s="2">
+        <v>0</v>
+      </c>
+      <c r="I192" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>500217683</t>
+          <t>500120216</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C193" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D193" s="2">
         <v>1</v>
@@ -5481,16 +6060,19 @@
         <v>0</v>
       </c>
       <c r="G193" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H193" s="2">
+        <v>0</v>
+      </c>
+      <c r="I193" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>500219602</t>
+          <t>500126621</t>
         </is>
       </c>
       <c r="B194" s="2">
@@ -5500,7 +6082,7 @@
         <v>0</v>
       </c>
       <c r="D194" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E194" s="2">
         <v>0</v>
@@ -5509,16 +6091,19 @@
         <v>0</v>
       </c>
       <c r="G194" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H194" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I194" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>500235468</t>
+          <t>500127435</t>
         </is>
       </c>
       <c r="B195" s="2">
@@ -5540,20 +6125,23 @@
         <v>1</v>
       </c>
       <c r="H195" s="2">
+        <v>0</v>
+      </c>
+      <c r="I195" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>500236829</t>
+          <t>500128032</t>
         </is>
       </c>
       <c r="B196" s="2">
         <v>0</v>
       </c>
       <c r="C196" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D196" s="2">
         <v>0</v>
@@ -5562,23 +6150,26 @@
         <v>0</v>
       </c>
       <c r="F196" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G196" s="2">
         <v>0</v>
       </c>
       <c r="H196" s="2">
+        <v>0</v>
+      </c>
+      <c r="I196" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>500240447</t>
+          <t>500128657</t>
         </is>
       </c>
       <c r="B197" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C197" s="2">
         <v>0</v>
@@ -5590,26 +6181,29 @@
         <v>0</v>
       </c>
       <c r="F197" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G197" s="2">
         <v>0</v>
       </c>
       <c r="H197" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I197" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>500241388</t>
+          <t>500128699</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C198" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D198" s="2">
         <v>0</v>
@@ -5618,32 +6212,35 @@
         <v>0</v>
       </c>
       <c r="F198" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G198" s="2">
         <v>0</v>
       </c>
       <c r="H198" s="2">
+        <v>1</v>
+      </c>
+      <c r="I198" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>500255345</t>
+          <t>500143502</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C199" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D199" s="2">
         <v>0</v>
       </c>
       <c r="E199" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F199" s="2">
         <v>0</v>
@@ -5652,17 +6249,20 @@
         <v>0</v>
       </c>
       <c r="H199" s="2">
+        <v>0</v>
+      </c>
+      <c r="I199" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>500258101</t>
+          <t>500143882</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C200" s="2">
         <v>0</v>
@@ -5671,7 +6271,7 @@
         <v>0</v>
       </c>
       <c r="E200" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F200" s="2">
         <v>0</v>
@@ -5680,13 +6280,16 @@
         <v>0</v>
       </c>
       <c r="H200" s="2">
+        <v>0</v>
+      </c>
+      <c r="I200" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>500272158</t>
+          <t>500146241</t>
         </is>
       </c>
       <c r="B201" s="2">
@@ -5699,7 +6302,7 @@
         <v>0</v>
       </c>
       <c r="E201" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F201" s="2">
         <v>0</v>
@@ -5708,17 +6311,20 @@
         <v>0</v>
       </c>
       <c r="H201" s="2">
+        <v>1</v>
+      </c>
+      <c r="I201" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>500274670</t>
+          <t>500146800</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C202" s="2">
         <v>0</v>
@@ -5736,13 +6342,16 @@
         <v>1</v>
       </c>
       <c r="H202" s="2">
+        <v>0</v>
+      </c>
+      <c r="I202" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>500284150</t>
+          <t>500148890</t>
         </is>
       </c>
       <c r="B203" s="2">
@@ -5758,51 +6367,646 @@
         <v>0</v>
       </c>
       <c r="F203" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G203" s="2">
         <v>0</v>
       </c>
       <c r="H203" s="2">
+        <v>1</v>
+      </c>
+      <c r="I203" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
+          <t>500185891</t>
+        </is>
+      </c>
+      <c r="B204" s="2">
+        <v>1</v>
+      </c>
+      <c r="C204" s="2">
+        <v>1</v>
+      </c>
+      <c r="D204" s="2">
+        <v>0</v>
+      </c>
+      <c r="E204" s="2">
+        <v>0</v>
+      </c>
+      <c r="F204" s="2">
+        <v>0</v>
+      </c>
+      <c r="G204" s="2">
+        <v>0</v>
+      </c>
+      <c r="H204" s="2">
+        <v>0</v>
+      </c>
+      <c r="I204" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>500186481</t>
+        </is>
+      </c>
+      <c r="B205" s="2">
+        <v>0</v>
+      </c>
+      <c r="C205" s="2">
+        <v>0</v>
+      </c>
+      <c r="D205" s="2">
+        <v>0</v>
+      </c>
+      <c r="E205" s="2">
+        <v>0</v>
+      </c>
+      <c r="F205" s="2">
+        <v>0</v>
+      </c>
+      <c r="G205" s="2">
+        <v>1</v>
+      </c>
+      <c r="H205" s="2">
+        <v>0</v>
+      </c>
+      <c r="I205" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>500187931</t>
+        </is>
+      </c>
+      <c r="B206" s="2">
+        <v>0</v>
+      </c>
+      <c r="C206" s="2">
+        <v>1</v>
+      </c>
+      <c r="D206" s="2">
+        <v>0</v>
+      </c>
+      <c r="E206" s="2">
+        <v>0</v>
+      </c>
+      <c r="F206" s="2">
+        <v>0</v>
+      </c>
+      <c r="G206" s="2">
+        <v>0</v>
+      </c>
+      <c r="H206" s="2">
+        <v>0</v>
+      </c>
+      <c r="I206" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>500192537</t>
+        </is>
+      </c>
+      <c r="B207" s="2">
+        <v>0</v>
+      </c>
+      <c r="C207" s="2">
+        <v>0</v>
+      </c>
+      <c r="D207" s="2">
+        <v>0</v>
+      </c>
+      <c r="E207" s="2">
+        <v>0</v>
+      </c>
+      <c r="F207" s="2">
+        <v>0</v>
+      </c>
+      <c r="G207" s="2">
+        <v>0</v>
+      </c>
+      <c r="H207" s="2">
+        <v>1</v>
+      </c>
+      <c r="I207" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>500199878</t>
+        </is>
+      </c>
+      <c r="B208" s="2">
+        <v>0</v>
+      </c>
+      <c r="C208" s="2">
+        <v>0</v>
+      </c>
+      <c r="D208" s="2">
+        <v>0</v>
+      </c>
+      <c r="E208" s="2">
+        <v>0</v>
+      </c>
+      <c r="F208" s="2">
+        <v>1</v>
+      </c>
+      <c r="G208" s="2">
+        <v>0</v>
+      </c>
+      <c r="H208" s="2">
+        <v>0</v>
+      </c>
+      <c r="I208" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>500201947</t>
+        </is>
+      </c>
+      <c r="B209" s="2">
+        <v>0</v>
+      </c>
+      <c r="C209" s="2">
+        <v>0</v>
+      </c>
+      <c r="D209" s="2">
+        <v>0</v>
+      </c>
+      <c r="E209" s="2">
+        <v>0</v>
+      </c>
+      <c r="F209" s="2">
+        <v>0</v>
+      </c>
+      <c r="G209" s="2">
+        <v>0</v>
+      </c>
+      <c r="H209" s="2">
+        <v>1</v>
+      </c>
+      <c r="I209" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>500211718</t>
+        </is>
+      </c>
+      <c r="B210" s="2">
+        <v>0</v>
+      </c>
+      <c r="C210" s="2">
+        <v>1</v>
+      </c>
+      <c r="D210" s="2">
+        <v>2</v>
+      </c>
+      <c r="E210" s="2">
+        <v>0</v>
+      </c>
+      <c r="F210" s="2">
+        <v>0</v>
+      </c>
+      <c r="G210" s="2">
+        <v>0</v>
+      </c>
+      <c r="H210" s="2">
+        <v>0</v>
+      </c>
+      <c r="I210" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>500217683</t>
+        </is>
+      </c>
+      <c r="B211" s="2">
+        <v>0</v>
+      </c>
+      <c r="C211" s="2">
+        <v>1</v>
+      </c>
+      <c r="D211" s="2">
+        <v>1</v>
+      </c>
+      <c r="E211" s="2">
+        <v>0</v>
+      </c>
+      <c r="F211" s="2">
+        <v>0</v>
+      </c>
+      <c r="G211" s="2">
+        <v>1</v>
+      </c>
+      <c r="H211" s="2">
+        <v>0</v>
+      </c>
+      <c r="I211" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>500219602</t>
+        </is>
+      </c>
+      <c r="B212" s="2">
+        <v>0</v>
+      </c>
+      <c r="C212" s="2">
+        <v>0</v>
+      </c>
+      <c r="D212" s="2">
+        <v>0</v>
+      </c>
+      <c r="E212" s="2">
+        <v>0</v>
+      </c>
+      <c r="F212" s="2">
+        <v>0</v>
+      </c>
+      <c r="G212" s="2">
+        <v>0</v>
+      </c>
+      <c r="H212" s="2">
+        <v>1</v>
+      </c>
+      <c r="I212" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>500235468</t>
+        </is>
+      </c>
+      <c r="B213" s="2">
+        <v>0</v>
+      </c>
+      <c r="C213" s="2">
+        <v>0</v>
+      </c>
+      <c r="D213" s="2">
+        <v>0</v>
+      </c>
+      <c r="E213" s="2">
+        <v>0</v>
+      </c>
+      <c r="F213" s="2">
+        <v>0</v>
+      </c>
+      <c r="G213" s="2">
+        <v>1</v>
+      </c>
+      <c r="H213" s="2">
+        <v>0</v>
+      </c>
+      <c r="I213" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>500236829</t>
+        </is>
+      </c>
+      <c r="B214" s="2">
+        <v>0</v>
+      </c>
+      <c r="C214" s="2">
+        <v>1</v>
+      </c>
+      <c r="D214" s="2">
+        <v>0</v>
+      </c>
+      <c r="E214" s="2">
+        <v>0</v>
+      </c>
+      <c r="F214" s="2">
+        <v>0</v>
+      </c>
+      <c r="G214" s="2">
+        <v>0</v>
+      </c>
+      <c r="H214" s="2">
+        <v>0</v>
+      </c>
+      <c r="I214" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>500240447</t>
+        </is>
+      </c>
+      <c r="B215" s="2">
+        <v>1</v>
+      </c>
+      <c r="C215" s="2">
+        <v>0</v>
+      </c>
+      <c r="D215" s="2">
+        <v>0</v>
+      </c>
+      <c r="E215" s="2">
+        <v>0</v>
+      </c>
+      <c r="F215" s="2">
+        <v>0</v>
+      </c>
+      <c r="G215" s="2">
+        <v>0</v>
+      </c>
+      <c r="H215" s="2">
+        <v>1</v>
+      </c>
+      <c r="I215" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>500241388</t>
+        </is>
+      </c>
+      <c r="B216" s="2">
+        <v>1</v>
+      </c>
+      <c r="C216" s="2">
+        <v>1</v>
+      </c>
+      <c r="D216" s="2">
+        <v>0</v>
+      </c>
+      <c r="E216" s="2">
+        <v>0</v>
+      </c>
+      <c r="F216" s="2">
+        <v>1</v>
+      </c>
+      <c r="G216" s="2">
+        <v>0</v>
+      </c>
+      <c r="H216" s="2">
+        <v>0</v>
+      </c>
+      <c r="I216" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>500255345</t>
+        </is>
+      </c>
+      <c r="B217" s="2">
+        <v>1</v>
+      </c>
+      <c r="C217" s="2">
+        <v>0</v>
+      </c>
+      <c r="D217" s="2">
+        <v>0</v>
+      </c>
+      <c r="E217" s="2">
+        <v>1</v>
+      </c>
+      <c r="F217" s="2">
+        <v>0</v>
+      </c>
+      <c r="G217" s="2">
+        <v>0</v>
+      </c>
+      <c r="H217" s="2">
+        <v>0</v>
+      </c>
+      <c r="I217" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>500255732</t>
+        </is>
+      </c>
+      <c r="B218" s="2">
+        <v>0</v>
+      </c>
+      <c r="C218" s="2">
+        <v>0</v>
+      </c>
+      <c r="D218" s="2">
+        <v>0</v>
+      </c>
+      <c r="E218" s="2">
+        <v>0</v>
+      </c>
+      <c r="F218" s="2">
+        <v>0</v>
+      </c>
+      <c r="G218" s="2">
+        <v>0</v>
+      </c>
+      <c r="H218" s="2">
+        <v>0</v>
+      </c>
+      <c r="I218" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>500258101</t>
+        </is>
+      </c>
+      <c r="B219" s="2">
+        <v>0</v>
+      </c>
+      <c r="C219" s="2">
+        <v>0</v>
+      </c>
+      <c r="D219" s="2">
+        <v>0</v>
+      </c>
+      <c r="E219" s="2">
+        <v>1</v>
+      </c>
+      <c r="F219" s="2">
+        <v>0</v>
+      </c>
+      <c r="G219" s="2">
+        <v>0</v>
+      </c>
+      <c r="H219" s="2">
+        <v>0</v>
+      </c>
+      <c r="I219" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>500272158</t>
+        </is>
+      </c>
+      <c r="B220" s="2">
+        <v>0</v>
+      </c>
+      <c r="C220" s="2">
+        <v>0</v>
+      </c>
+      <c r="D220" s="2">
+        <v>0</v>
+      </c>
+      <c r="E220" s="2">
+        <v>1</v>
+      </c>
+      <c r="F220" s="2">
+        <v>0</v>
+      </c>
+      <c r="G220" s="2">
+        <v>0</v>
+      </c>
+      <c r="H220" s="2">
+        <v>0</v>
+      </c>
+      <c r="I220" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>500274670</t>
+        </is>
+      </c>
+      <c r="B221" s="2">
+        <v>0</v>
+      </c>
+      <c r="C221" s="2">
+        <v>0</v>
+      </c>
+      <c r="D221" s="2">
+        <v>0</v>
+      </c>
+      <c r="E221" s="2">
+        <v>0</v>
+      </c>
+      <c r="F221" s="2">
+        <v>0</v>
+      </c>
+      <c r="G221" s="2">
+        <v>1</v>
+      </c>
+      <c r="H221" s="2">
+        <v>0</v>
+      </c>
+      <c r="I221" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>500284150</t>
+        </is>
+      </c>
+      <c r="B222" s="2">
+        <v>0</v>
+      </c>
+      <c r="C222" s="2">
+        <v>0</v>
+      </c>
+      <c r="D222" s="2">
+        <v>0</v>
+      </c>
+      <c r="E222" s="2">
+        <v>0</v>
+      </c>
+      <c r="F222" s="2">
+        <v>1</v>
+      </c>
+      <c r="G222" s="2">
+        <v>0</v>
+      </c>
+      <c r="H222" s="2">
+        <v>0</v>
+      </c>
+      <c r="I222" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
           <t>500286107</t>
         </is>
       </c>
-      <c r="B204" s="2">
-        <v>0</v>
-      </c>
-      <c r="C204" s="2">
-        <v>0</v>
-      </c>
-      <c r="D204" s="2">
-        <v>0</v>
-      </c>
-      <c r="E204" s="2">
-        <v>0</v>
-      </c>
-      <c r="F204" s="2">
-        <v>0</v>
-      </c>
-      <c r="G204" s="2">
-        <v>0</v>
-      </c>
-      <c r="H204" s="2">
-        <v>1</v>
+      <c r="B223" s="2">
+        <v>0</v>
+      </c>
+      <c r="C223" s="2">
+        <v>0</v>
+      </c>
+      <c r="D223" s="2">
+        <v>0</v>
+      </c>
+      <c r="E223" s="2">
+        <v>0</v>
+      </c>
+      <c r="F223" s="2">
+        <v>0</v>
+      </c>
+      <c r="G223" s="2">
+        <v>0</v>
+      </c>
+      <c r="H223" s="2">
+        <v>1</v>
+      </c>
+      <c r="I223" s="2">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H204"/>
+  <autoFilter ref="A1:I223"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q290"/>
+  <dimension ref="A1:Q325"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -13413,11 +14617,11 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="N104" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O104" s="2">
         <v>0</v>
@@ -27007,7 +28211,2562 @@
         <v>0.15</v>
       </c>
     </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>100102221</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>5027165121</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>[광천김] 3대째 달인 혼합도시락김 (재래김+파래김) 4g, 48개</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G291" s="2">
+        <v>16720</v>
+      </c>
+      <c r="H291" s="2">
+        <v>20900</v>
+      </c>
+      <c r="I291" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5027165121</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20240924_150/1727164037303am0nT_JPEG/8259443196310666_700411941.jpg</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N291" s="2">
+        <v>1</v>
+      </c>
+      <c r="O291" s="2">
+        <v>0</v>
+      </c>
+      <c r="P291" s="2">
+        <v>16720</v>
+      </c>
+      <c r="Q291" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>100136792</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>10504209102</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>[슈퍼적립] 매일두유 고단백 검은콩 저당두유 190ml 24팩 [도착보장]</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G292" s="2">
+        <v>18900</v>
+      </c>
+      <c r="H292" s="2">
+        <v>36000</v>
+      </c>
+      <c r="I292" s="3">
+        <v>0.47</v>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10504209102</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251027_204/1761551036902XQFAv_JPEG/1614817077312096_1267790828.jpg</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N292" s="2">
+        <v>1</v>
+      </c>
+      <c r="O292" s="2">
+        <v>0</v>
+      </c>
+      <c r="P292" s="2">
+        <v>18900</v>
+      </c>
+      <c r="Q292" s="3">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>100146361</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>12133342063</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>[슈퍼적립] 1분링 200g 4종 몰아담기(멸치/사골 외) 코인육수 동전육수 한알</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G293" s="2">
+        <v>27500</v>
+      </c>
+      <c r="H293" s="2">
+        <v>75920</v>
+      </c>
+      <c r="I293" s="3">
+        <v>0.63</v>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12133342063</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260417_272/1776400390616lOBDi_JPEG/2644188714305709_325784895.jpg</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N293" s="2">
+        <v>1</v>
+      </c>
+      <c r="O293" s="2">
+        <v>0</v>
+      </c>
+      <c r="P293" s="2">
+        <v>27500</v>
+      </c>
+      <c r="Q293" s="3">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>100146361</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>12147943255</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>햇반 황금현미밥 210g 36개, 네이버 Only</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G294" s="2">
+        <v>42900</v>
+      </c>
+      <c r="H294" s="2">
+        <v>72000</v>
+      </c>
+      <c r="I294" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12147943255</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250922_39/1758523490484hoJce_JPEG/13710637530066268_1368331491.jpg</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N294" s="2">
+        <v>1</v>
+      </c>
+      <c r="O294" s="2">
+        <v>0</v>
+      </c>
+      <c r="P294" s="2">
+        <v>42900</v>
+      </c>
+      <c r="Q294" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>100165024</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>8907168291</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>헤드스파7 샴트리 샴푸 740g 3종 택2</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>뷰티/헬스</t>
+        </is>
+      </c>
+      <c r="G295" s="2">
+        <v>28900</v>
+      </c>
+      <c r="H295" s="2">
+        <v>70000</v>
+      </c>
+      <c r="I295" s="3">
+        <v>0.58</v>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/8907168291</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250528_292/1748394992895i9wrA_JPEG/1274737046952427_708609604.jpg</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N295" s="2">
+        <v>1</v>
+      </c>
+      <c r="O295" s="2">
+        <v>0</v>
+      </c>
+      <c r="P295" s="2">
+        <v>28900</v>
+      </c>
+      <c r="Q295" s="3">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>100252160</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>6383830537</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>모나리자 뽑아쓰는 도톰한 3겹 천연펄프 100% 키친티슈 100매 4+4+1개 총 900매</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>생활/주방</t>
+        </is>
+      </c>
+      <c r="G296" s="2">
+        <v>8900</v>
+      </c>
+      <c r="H296" s="2">
+        <v>19900</v>
+      </c>
+      <c r="I296" s="3">
+        <v>0.55</v>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/6383830537</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250509_25/1746761069210s6L5d_JPEG/22379077740654964_1339362734.jpg</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N296" s="2">
+        <v>1</v>
+      </c>
+      <c r="O296" s="2">
+        <v>0</v>
+      </c>
+      <c r="P296" s="2">
+        <v>8900</v>
+      </c>
+      <c r="Q296" s="3">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>100336757</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>13242455485</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>[더주]국내산 백오이 백다다기 오이 2kg</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G297" s="2">
+        <v>9900</v>
+      </c>
+      <c r="H297" s="2">
+        <v>27900</v>
+      </c>
+      <c r="I297" s="3">
+        <v>0.64</v>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13242455485</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250401_242/1743492126510Yb9wT_JPEG/77624918609387209_911084960.jpg</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N297" s="2">
+        <v>1</v>
+      </c>
+      <c r="O297" s="2">
+        <v>0</v>
+      </c>
+      <c r="P297" s="2">
+        <v>9900</v>
+      </c>
+      <c r="Q297" s="3">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>100340418</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>13308098614</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>[N배송] 크리오 쓸모아 베이킹소다 100% 3kg+3kg</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G298" s="2">
+        <v>10900</v>
+      </c>
+      <c r="H298" s="2">
+        <v>19800</v>
+      </c>
+      <c r="I298" s="3">
+        <v>0.44</v>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13308098614</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260421_24/1776751341209K0DUV_JPEG/110884194331099765_364153151.jpg</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N298" s="2">
+        <v>1</v>
+      </c>
+      <c r="O298" s="2">
+        <v>0</v>
+      </c>
+      <c r="P298" s="2">
+        <v>10900</v>
+      </c>
+      <c r="Q298" s="3">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>100433029</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>12963480283</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>모달 누빔 올인원 매트리스커버 슈퍼싱글 침대커버 침대시트 보 SS</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>생활/주방</t>
+        </is>
+      </c>
+      <c r="G299" s="2">
+        <v>49900</v>
+      </c>
+      <c r="H299" s="2">
+        <v>79900</v>
+      </c>
+      <c r="I299" s="3">
+        <v>0.37</v>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12963480283</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260113_11/1768289765516Xhgs5_JPEG/34475592953781925_2111640019.jpg</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N299" s="2">
+        <v>1</v>
+      </c>
+      <c r="O299" s="2">
+        <v>0</v>
+      </c>
+      <c r="P299" s="2">
+        <v>49900</v>
+      </c>
+      <c r="Q299" s="3">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>100449469</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>12913969396</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>[네이버 단독 100일분] 닥터린 송중기 하이퍼셀 대마종자유 알파 햄프씨드오일 카나비노이드 100캡슐, 1개</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G300" s="2">
+        <v>56900</v>
+      </c>
+      <c r="H300" s="2">
+        <v>113000</v>
+      </c>
+      <c r="I300" s="3">
+        <v>0.49</v>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12913969396</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260421_18/1776738938364l9NTN_JPEG/566917495197852_732023608.jpg</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N300" s="2">
+        <v>1</v>
+      </c>
+      <c r="O300" s="2">
+        <v>0</v>
+      </c>
+      <c r="P300" s="2">
+        <v>56900</v>
+      </c>
+      <c r="Q300" s="3">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>100597188</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>4786198789</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>[코디] 친환경 3겹 내추럴소프트 27m 30롤 1+1 (추가 1팩, 총 3팩)</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G301" s="2">
+        <v>28900</v>
+      </c>
+      <c r="H301" s="2">
+        <v>59900</v>
+      </c>
+      <c r="I301" s="3">
+        <v>0.51</v>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/4786198789</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20241104_79/1730701228363NKPmz_JPEG/5265048476879523_1245265731.jpg</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N301" s="2">
+        <v>1</v>
+      </c>
+      <c r="O301" s="2">
+        <v>0</v>
+      </c>
+      <c r="P301" s="2">
+        <v>28900</v>
+      </c>
+      <c r="Q301" s="3">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>100627146</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>8016701268</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>마이밀 뉴프로틴 오리지널 190 mL 30팩+30팩 단백질음료</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G302" s="2">
+        <v>63900</v>
+      </c>
+      <c r="H302" s="2">
+        <v>123000</v>
+      </c>
+      <c r="I302" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/8016701268</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250224_223/1740355035652IyqOJ_PNG/24128856113928982_671583771.png</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N302" s="2">
+        <v>1</v>
+      </c>
+      <c r="O302" s="2">
+        <v>0</v>
+      </c>
+      <c r="P302" s="2">
+        <v>63900</v>
+      </c>
+      <c r="Q302" s="3">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>100774355</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>10169026628</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>농가살리기 전라도 할매손맛 칠왕 찹쌀약밥 900g 1.8kg</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G303" s="2">
+        <v>16900</v>
+      </c>
+      <c r="H303" s="2">
+        <v>34900</v>
+      </c>
+      <c r="I303" s="3">
+        <v>0.51</v>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10169026628</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20240405_21/1712290137918UkHU9_JPEG/113426036610415503_2026888775.jpg</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N303" s="2">
+        <v>1</v>
+      </c>
+      <c r="O303" s="2">
+        <v>0</v>
+      </c>
+      <c r="P303" s="2">
+        <v>16900</v>
+      </c>
+      <c r="Q303" s="3">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>100813952</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>13233695932</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>풀무원생수 퍼플에디션 2L, 12개</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G304" s="2">
+        <v>8900</v>
+      </c>
+      <c r="H304" s="2">
+        <v>20900</v>
+      </c>
+      <c r="I304" s="3">
+        <v>0.57</v>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13233695932</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260417_121/1776414869457AkFAB_JPEG/110547702934977118_1136383113.jpg</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N304" s="2">
+        <v>1</v>
+      </c>
+      <c r="O304" s="2">
+        <v>0</v>
+      </c>
+      <c r="P304" s="2">
+        <v>8900</v>
+      </c>
+      <c r="Q304" s="3">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>100840656</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>10269096092</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>갓 담근 얼갈이열무김치 전라도 국산 1kg+1kg</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G305" s="2">
+        <v>11800</v>
+      </c>
+      <c r="H305" s="2">
+        <v>22900</v>
+      </c>
+      <c r="I305" s="3">
+        <v>0.48</v>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10269096092</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250407_106/1743988264839m9iqB_PNG/78121096979334404_1857512855.png</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N305" s="2">
+        <v>1</v>
+      </c>
+      <c r="O305" s="2">
+        <v>0</v>
+      </c>
+      <c r="P305" s="2">
+        <v>11800</v>
+      </c>
+      <c r="Q305" s="3">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>100937343</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>13313676828</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>[본사]해피즈 혼합패키지 355ML 18캔(팝핑체리6+레몬라임6+트로피칼믹스6) +유리컵 증정</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G306" s="2">
+        <v>27000</v>
+      </c>
+      <c r="H306" s="2">
+        <v>27000</v>
+      </c>
+      <c r="I306" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13313676828</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260413_14/1776042380950CMh3r_JPEG/25621536836210150_1620657972.jpg</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N306" s="2">
+        <v>1</v>
+      </c>
+      <c r="O306" s="2">
+        <v>0</v>
+      </c>
+      <c r="P306" s="2">
+        <v>27000</v>
+      </c>
+      <c r="Q306" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>101015607</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>12443616177</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>(1+1) 멀티비타민 오쏘몰 이뮨 7일분 x 2박스 (총 2박스 배송) 유통기한 26년 7월 4일</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>뷰티/헬스</t>
+        </is>
+      </c>
+      <c r="G307" s="2">
+        <v>39180</v>
+      </c>
+      <c r="H307" s="2">
+        <v>78360</v>
+      </c>
+      <c r="I307" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12443616177</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251017_278/1760673732030GwEgL_JPEG/1780895820138739_371550353.jpg</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N307" s="2">
+        <v>1</v>
+      </c>
+      <c r="O307" s="2">
+        <v>0</v>
+      </c>
+      <c r="P307" s="2">
+        <v>39180</v>
+      </c>
+      <c r="Q307" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>101078690</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>11341978437</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>[슈퍼적립] [10+10] 오뚜기 가뿐한끼 촉촉스팀 닭가슴살 갈릭/닭강정맛/숯불바베큐맛/블랙페퍼/레드페퍼/고기만두/김치만두/핫도그</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G308" s="2">
+        <v>36900</v>
+      </c>
+      <c r="H308" s="2">
+        <v>63600</v>
+      </c>
+      <c r="I308" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11341978437</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260204_198/17701697810173AszP_JPEG/80300242696997417_47799408.jpg</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N308" s="2">
+        <v>1</v>
+      </c>
+      <c r="O308" s="2">
+        <v>0</v>
+      </c>
+      <c r="P308" s="2">
+        <v>36900</v>
+      </c>
+      <c r="Q308" s="3">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>101111804</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>9900926969</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>[슈퍼적립] CJ 바이오코어 화사 효소 카무트 곡물콤부 저분자 효소 (한포당 2g) 30포, 3개</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G309" s="2">
+        <v>28900</v>
+      </c>
+      <c r="H309" s="2">
+        <v>69800</v>
+      </c>
+      <c r="I309" s="3">
+        <v>0.58</v>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/9900926969</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260408_63/1775609160706aMw9P_JPEG/122327480088809503_1457070131.jpg</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N309" s="2">
+        <v>2</v>
+      </c>
+      <c r="O309" s="2">
+        <v>0</v>
+      </c>
+      <c r="P309" s="2">
+        <v>28900</v>
+      </c>
+      <c r="Q309" s="3">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>101192951</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>11705429297</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>진주햄 천하장사 The 건강하닭 700g (28gX25개입) X 2개</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G310" s="2">
+        <v>17480</v>
+      </c>
+      <c r="H310" s="2">
+        <v>29200</v>
+      </c>
+      <c r="I310" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11705429297</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250924_77/1758673759635lgpEn_JPEG/42346042755540409_1637945212.jpg</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N310" s="2">
+        <v>1</v>
+      </c>
+      <c r="O310" s="2">
+        <v>0</v>
+      </c>
+      <c r="P310" s="2">
+        <v>17480</v>
+      </c>
+      <c r="Q310" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>101331865</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>13262768878</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>만토바 골든 엑스트라버진 올리브오일 냉압착 압착 대용량 공복 먹는 이탈리아 프리미엄 1L</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G311" s="2">
+        <v>19900</v>
+      </c>
+      <c r="H311" s="2">
+        <v>42980</v>
+      </c>
+      <c r="I311" s="3">
+        <v>0.53</v>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13262768878</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260317_211/1773736121278CzbpI_JPEG/36714648926696148_53246637.jpg</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N311" s="2">
+        <v>1</v>
+      </c>
+      <c r="O311" s="2">
+        <v>0</v>
+      </c>
+      <c r="P311" s="2">
+        <v>19900</v>
+      </c>
+      <c r="Q311" s="3">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>101342244</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>13233774619</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>셀렉스 프로핏 Sports 드링크 와일드 초코, 350ml, 20개</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G312" s="2">
+        <v>58900</v>
+      </c>
+      <c r="H312" s="2">
+        <v>78000</v>
+      </c>
+      <c r="I312" s="3">
+        <v>0.24</v>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13233774619</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260412_197/1776002241075fM9fO_JPEG/68727359374004031_1368701440.jpg</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N312" s="2">
+        <v>1</v>
+      </c>
+      <c r="O312" s="2">
+        <v>0</v>
+      </c>
+      <c r="P312" s="2">
+        <v>58900</v>
+      </c>
+      <c r="Q312" s="3">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>101573499</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>10057091557</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>그레인온 카무트 브랜드밀 프리미엄효소90 30포, 3개</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G313" s="2">
+        <v>49900</v>
+      </c>
+      <c r="H313" s="2">
+        <v>297000</v>
+      </c>
+      <c r="I313" s="3">
+        <v>0.83</v>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10057091557</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260424_273/17770160472899cGYX_PNG/10913070293530979_2034300786.png</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N313" s="2">
+        <v>1</v>
+      </c>
+      <c r="O313" s="2">
+        <v>0</v>
+      </c>
+      <c r="P313" s="2">
+        <v>49900</v>
+      </c>
+      <c r="Q313" s="3">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>101910440</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>13107097229</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>에이스 스윗바닐라 1챔버 캡슐 200개입 /고농축 중성세제 실내건조</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>생활/주방</t>
+        </is>
+      </c>
+      <c r="G314" s="2">
+        <v>9900</v>
+      </c>
+      <c r="H314" s="2">
+        <v>19800</v>
+      </c>
+      <c r="I314" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13107097229</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260212_8/1770903494217l4z2c_JPEG/17644898358250152_1297155440.jpg</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N314" s="2">
+        <v>1</v>
+      </c>
+      <c r="O314" s="2">
+        <v>0</v>
+      </c>
+      <c r="P314" s="2">
+        <v>9900</v>
+      </c>
+      <c r="Q314" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>101996505</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>9122745603</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>모스스토리 분말육수 오리지널 140g 가루 육수 만능 코인 분말 스틱 멸치 한우 덱스트린</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G315" s="2">
+        <v>11500</v>
+      </c>
+      <c r="H315" s="2">
+        <v>15900</v>
+      </c>
+      <c r="I315" s="3">
+        <v>0.27</v>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/9122745603</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260312_21/1773308909483nPfup_JPEG/28588666968679423_997831750.jpg</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N315" s="2">
+        <v>1</v>
+      </c>
+      <c r="O315" s="2">
+        <v>0</v>
+      </c>
+      <c r="P315" s="2">
+        <v>11500</v>
+      </c>
+      <c r="Q315" s="3">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>102655931</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>12270859988</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>[하림] The미식 교자만두 4종(2개입) (택1)</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G316" s="2">
+        <v>10</v>
+      </c>
+      <c r="H316" s="2">
+        <v>10</v>
+      </c>
+      <c r="I316" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12270859988</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250819_121/1755590131197YLmqo_JPEG/13213226739505936_513824798.jpg</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N316" s="2">
+        <v>1</v>
+      </c>
+      <c r="O316" s="2">
+        <v>0</v>
+      </c>
+      <c r="P316" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q316" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>102655931</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>12274564857</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>[KF365] 간편한 6가지 해물 모듬</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G317" s="2">
+        <v>10900</v>
+      </c>
+      <c r="H317" s="2">
+        <v>10900</v>
+      </c>
+      <c r="I317" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12274564857</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250707_242/1751871537962tVgeW_JPEG/14270386889376450_1988947555.jpg</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N317" s="2">
+        <v>1</v>
+      </c>
+      <c r="O317" s="2">
+        <v>0</v>
+      </c>
+      <c r="P317" s="2">
+        <v>10900</v>
+      </c>
+      <c r="Q317" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>1100063691</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>13396949474</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>2026 웰컴썸머페스티벌 WELCOME SUMMER FESTIVAL (2인 이용권)</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G318" s="2">
+        <v>94290</v>
+      </c>
+      <c r="H318" s="2">
+        <v>180000</v>
+      </c>
+      <c r="I318" s="3">
+        <v>0.47</v>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13396949474</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260421_201/1776753632911a5nYQ_PNG/581611993297533_2146335268.png</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N318" s="2">
+        <v>1</v>
+      </c>
+      <c r="O318" s="2">
+        <v>0</v>
+      </c>
+      <c r="P318" s="2">
+        <v>94290</v>
+      </c>
+      <c r="Q318" s="3">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>500003337</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>6751858398</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>라뽐므 마들렌 피치스킨 사계절 차렵이불 S/SS</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G319" s="2">
+        <v>19900</v>
+      </c>
+      <c r="H319" s="2">
+        <v>156100</v>
+      </c>
+      <c r="I319" s="3">
+        <v>0.87</v>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/6751858398</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250220_168/1740031888951hUqQ0_JPEG/74164666470792071_1055244400.jpg</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N319" s="2">
+        <v>1</v>
+      </c>
+      <c r="O319" s="2">
+        <v>0</v>
+      </c>
+      <c r="P319" s="2">
+        <v>19900</v>
+      </c>
+      <c r="Q319" s="3">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>500016197</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>12491548795</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>[N배송] 더자리 항균 솔리드 누빔 고정밴드형 침대패드 SS/Q/K 사계절용</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G320" s="2">
+        <v>13900</v>
+      </c>
+      <c r="H320" s="2">
+        <v>74900</v>
+      </c>
+      <c r="I320" s="3">
+        <v>0.81</v>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12491548795</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251112_51/1762929982866RkD72_JPEG/50128589712035028_1913218371.jpg</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N320" s="2">
+        <v>1</v>
+      </c>
+      <c r="O320" s="2">
+        <v>0</v>
+      </c>
+      <c r="P320" s="2">
+        <v>13900</v>
+      </c>
+      <c r="Q320" s="3">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>스페셜 체험딜</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>500037006</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>12533219932</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>오리지널 군고구마빠 고구마말랭이 고구마간식 군고구마바</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G321" s="2">
+        <v>1500</v>
+      </c>
+      <c r="H321" s="2">
+        <v>3600</v>
+      </c>
+      <c r="I321" s="3">
+        <v>0.58</v>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12533219932</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260408_115/1775633840484Dd7db_JPEG/109766767569321555_1110936560.jpg</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N321" s="2">
+        <v>1</v>
+      </c>
+      <c r="O321" s="2">
+        <v>0</v>
+      </c>
+      <c r="P321" s="2">
+        <v>1500</v>
+      </c>
+      <c r="Q321" s="3">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>500043218</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>10763703963</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>[+쇼핑백&amp;로션본품] 밀크바오밥 퍼퓸 샴푸+트리트먼트+바디워시 화이트머스크, 500ml, 3개</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>뷰티/헬스</t>
+        </is>
+      </c>
+      <c r="G322" s="2">
+        <v>21400</v>
+      </c>
+      <c r="H322" s="2">
+        <v>37700</v>
+      </c>
+      <c r="I322" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10763703963</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260422_242/1776848330792RTzKm_JPEG/0425_EC8AA4ED8E98EC859CEB949C_EBB080ED81ACEBB094EC98A4E.jpg</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N322" s="2">
+        <v>1</v>
+      </c>
+      <c r="O322" s="2">
+        <v>0</v>
+      </c>
+      <c r="P322" s="2">
+        <v>21400</v>
+      </c>
+      <c r="Q322" s="3">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>500058721</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>12276343094</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>테이크핏 몬스터 혼합팩 (고소한맛+초코바나나) 350ml, 12개</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G323" s="2">
+        <v>29700</v>
+      </c>
+      <c r="H323" s="2">
+        <v>46800</v>
+      </c>
+      <c r="I323" s="3">
+        <v>0.36</v>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12276343094</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260402_83/1775112612291CgqI7_JPEG/90121106310935894_1470810122.jpg</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N323" s="2">
+        <v>1</v>
+      </c>
+      <c r="O323" s="2">
+        <v>0</v>
+      </c>
+      <c r="P323" s="2">
+        <v>29700</v>
+      </c>
+      <c r="Q323" s="3">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>500255345</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>11251868537</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>쪄서가는 냉동 찰옥수수 홍찰 백찰 옥수수 10개</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G324" s="2">
+        <v>9900</v>
+      </c>
+      <c r="H324" s="2">
+        <v>20000</v>
+      </c>
+      <c r="I324" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11251868537</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250226_135/1740547347001fdK7m_JPEG/18739287090363103_993979382.jpg</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N324" s="2">
+        <v>1</v>
+      </c>
+      <c r="O324" s="2">
+        <v>0</v>
+      </c>
+      <c r="P324" s="2">
+        <v>9900</v>
+      </c>
+      <c r="Q324" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>500255732</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>12863731318</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>[원가이하 최저가] 러브핑코 원가이하 잠옷바지 홈웨어 소진시 종료</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G325" s="2">
+        <v>4900</v>
+      </c>
+      <c r="H325" s="2">
+        <v>19900</v>
+      </c>
+      <c r="I325" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12863731318</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251223_77/1766478446053GmIo6_JPEG/18576954913203197_694502108.jpg</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N325" s="2">
+        <v>1</v>
+      </c>
+      <c r="O325" s="2">
+        <v>0</v>
+      </c>
+      <c r="P325" s="2">
+        <v>4900</v>
+      </c>
+      <c r="Q325" s="3">
+        <v>0.75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q290"/>
+  <autoFilter ref="A1:Q325"/>
 </worksheet>
 </file>
--- a/data/derived/todaysdeal-analysis.xlsx
+++ b/data/derived/todaysdeal-analysis.xlsx
@@ -57,7 +57,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I223"/>
+  <dimension ref="A1:J245"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -68,6 +68,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -116,6 +117,11 @@
           <t>2026-04-25</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -147,6 +153,9 @@
       <c r="I2" s="2">
         <v>0</v>
       </c>
+      <c r="J2" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -178,6 +187,9 @@
       <c r="I3" s="2">
         <v>0</v>
       </c>
+      <c r="J3" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -209,6 +221,9 @@
       <c r="I4" s="2">
         <v>0</v>
       </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -240,6 +255,9 @@
       <c r="I5" s="2">
         <v>0</v>
       </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -271,6 +289,9 @@
       <c r="I6" s="2">
         <v>1</v>
       </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -302,6 +323,9 @@
       <c r="I7" s="2">
         <v>0</v>
       </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -333,6 +357,9 @@
       <c r="I8" s="2">
         <v>0</v>
       </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -364,6 +391,9 @@
       <c r="I9" s="2">
         <v>1</v>
       </c>
+      <c r="J9" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -395,6 +425,9 @@
       <c r="I10" s="2">
         <v>0</v>
       </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -426,6 +459,9 @@
       <c r="I11" s="2">
         <v>2</v>
       </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -457,6 +493,9 @@
       <c r="I12" s="2">
         <v>1</v>
       </c>
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -488,6 +527,9 @@
       <c r="I13" s="2">
         <v>0</v>
       </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -519,18 +561,21 @@
       <c r="I14" s="2">
         <v>0</v>
       </c>
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>100208089</t>
+          <t>100200351</t>
         </is>
       </c>
       <c r="B15" s="2">
         <v>0</v>
       </c>
       <c r="C15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2">
         <v>0</v>
@@ -545,23 +590,26 @@
         <v>0</v>
       </c>
       <c r="H15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
         <v>0</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>100252160</t>
+          <t>100208089</t>
         </is>
       </c>
       <c r="B16" s="2">
         <v>0</v>
       </c>
       <c r="C16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
@@ -576,16 +624,19 @@
         <v>0</v>
       </c>
       <c r="H16" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>100261289</t>
+          <t>100252160</t>
         </is>
       </c>
       <c r="B17" s="2">
@@ -604,26 +655,29 @@
         <v>0</v>
       </c>
       <c r="G17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="2">
         <v>0</v>
       </c>
       <c r="I17" s="2">
+        <v>1</v>
+      </c>
+      <c r="J17" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>100262120</t>
+          <t>100259128</t>
         </is>
       </c>
       <c r="B18" s="2">
         <v>0</v>
       </c>
       <c r="C18" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
@@ -642,12 +696,15 @@
       </c>
       <c r="I18" s="2">
         <v>0</v>
+      </c>
+      <c r="J18" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>100262284</t>
+          <t>100261289</t>
         </is>
       </c>
       <c r="B19" s="2">
@@ -672,20 +729,23 @@
         <v>0</v>
       </c>
       <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>100265349</t>
+          <t>100262120</t>
         </is>
       </c>
       <c r="B20" s="2">
         <v>0</v>
       </c>
       <c r="C20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2">
         <v>0</v>
@@ -700,23 +760,26 @@
         <v>0</v>
       </c>
       <c r="H20" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>100265766</t>
+          <t>100262284</t>
         </is>
       </c>
       <c r="B21" s="2">
         <v>0</v>
       </c>
       <c r="C21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
@@ -728,26 +791,29 @@
         <v>0</v>
       </c>
       <c r="G21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="2">
         <v>0</v>
       </c>
       <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>100274539</t>
+          <t>100265349</t>
         </is>
       </c>
       <c r="B22" s="2">
         <v>0</v>
       </c>
       <c r="C22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
@@ -762,23 +828,26 @@
         <v>0</v>
       </c>
       <c r="H22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>100292269</t>
+          <t>100265766</t>
         </is>
       </c>
       <c r="B23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
@@ -796,13 +865,16 @@
         <v>0</v>
       </c>
       <c r="I23" s="2">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>100292757</t>
+          <t>100274539</t>
         </is>
       </c>
       <c r="B24" s="2">
@@ -827,23 +899,26 @@
         <v>0</v>
       </c>
       <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>100305602</t>
+          <t>100292269</t>
         </is>
       </c>
       <c r="B25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2">
         <v>0</v>
@@ -858,13 +933,16 @@
         <v>0</v>
       </c>
       <c r="I25" s="2">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>100326348</t>
+          <t>100292757</t>
         </is>
       </c>
       <c r="B26" s="2">
@@ -886,26 +964,29 @@
         <v>0</v>
       </c>
       <c r="H26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>100327929</t>
+          <t>100305602</t>
         </is>
       </c>
       <c r="B27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="2">
         <v>0</v>
@@ -920,26 +1001,29 @@
         <v>0</v>
       </c>
       <c r="I27" s="2">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>100336563</t>
+          <t>100326348</t>
         </is>
       </c>
       <c r="B28" s="2">
         <v>0</v>
       </c>
       <c r="C28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
       </c>
       <c r="E28" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" s="2">
         <v>0</v>
@@ -948,20 +1032,23 @@
         <v>0</v>
       </c>
       <c r="H28" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="2">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>100336757</t>
+          <t>100327929</t>
         </is>
       </c>
       <c r="B29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" s="2">
         <v>0</v>
@@ -982,13 +1069,16 @@
         <v>0</v>
       </c>
       <c r="I29" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J29" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>100340418</t>
+          <t>100336563</t>
         </is>
       </c>
       <c r="B30" s="2">
@@ -998,10 +1088,10 @@
         <v>0</v>
       </c>
       <c r="D30" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="2">
         <v>0</v>
@@ -1013,20 +1103,23 @@
         <v>0</v>
       </c>
       <c r="I30" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>100387111</t>
+          <t>100336757</t>
         </is>
       </c>
       <c r="B31" s="2">
         <v>0</v>
       </c>
       <c r="C31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="2">
         <v>0</v>
@@ -1044,13 +1137,16 @@
         <v>0</v>
       </c>
       <c r="I31" s="2">
+        <v>1</v>
+      </c>
+      <c r="J31" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>100419781</t>
+          <t>100340418</t>
         </is>
       </c>
       <c r="B32" s="2">
@@ -1060,10 +1156,10 @@
         <v>0</v>
       </c>
       <c r="D32" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" s="2">
         <v>0</v>
@@ -1075,13 +1171,16 @@
         <v>0</v>
       </c>
       <c r="I32" s="2">
+        <v>1</v>
+      </c>
+      <c r="J32" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>100433029</t>
+          <t>100368280</t>
         </is>
       </c>
       <c r="B33" s="2">
@@ -1106,13 +1205,16 @@
         <v>0</v>
       </c>
       <c r="I33" s="2">
+        <v>0</v>
+      </c>
+      <c r="J33" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>100446531</t>
+          <t>100369232</t>
         </is>
       </c>
       <c r="B34" s="2">
@@ -1128,35 +1230,38 @@
         <v>0</v>
       </c>
       <c r="F34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" s="2">
         <v>0</v>
+      </c>
+      <c r="J34" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>100449422</t>
+          <t>100387111</t>
         </is>
       </c>
       <c r="B35" s="2">
         <v>0</v>
       </c>
       <c r="C35" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" s="2">
         <v>0</v>
       </c>
       <c r="E35" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="2">
         <v>0</v>
@@ -1168,13 +1273,16 @@
         <v>0</v>
       </c>
       <c r="I35" s="2">
+        <v>0</v>
+      </c>
+      <c r="J35" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>100449469</t>
+          <t>100419781</t>
         </is>
       </c>
       <c r="B36" s="2">
@@ -1187,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="2">
         <v>0</v>
@@ -1199,17 +1307,20 @@
         <v>0</v>
       </c>
       <c r="I36" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J36" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>100458264</t>
+          <t>100433029</t>
         </is>
       </c>
       <c r="B37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
@@ -1230,13 +1341,16 @@
         <v>0</v>
       </c>
       <c r="I37" s="2">
+        <v>1</v>
+      </c>
+      <c r="J37" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>100474685</t>
+          <t>100437155</t>
         </is>
       </c>
       <c r="B38" s="2">
@@ -1246,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" s="2">
         <v>0</v>
@@ -1262,12 +1376,15 @@
       </c>
       <c r="I38" s="2">
         <v>0</v>
+      </c>
+      <c r="J38" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>100492521</t>
+          <t>100446531</t>
         </is>
       </c>
       <c r="B39" s="2">
@@ -1277,28 +1394,31 @@
         <v>0</v>
       </c>
       <c r="D39" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="2">
         <v>0</v>
       </c>
       <c r="F39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="2">
+        <v>0</v>
+      </c>
+      <c r="J39" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>100503327</t>
+          <t>100449422</t>
         </is>
       </c>
       <c r="B40" s="2">
@@ -1323,13 +1443,16 @@
         <v>0</v>
       </c>
       <c r="I40" s="2">
+        <v>0</v>
+      </c>
+      <c r="J40" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>100542499</t>
+          <t>100449469</t>
         </is>
       </c>
       <c r="B41" s="2">
@@ -1339,7 +1462,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" s="2">
         <v>0</v>
@@ -1354,13 +1477,16 @@
         <v>0</v>
       </c>
       <c r="I41" s="2">
+        <v>1</v>
+      </c>
+      <c r="J41" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>100585383</t>
+          <t>100449673</t>
         </is>
       </c>
       <c r="B42" s="2">
@@ -1382,20 +1508,23 @@
         <v>0</v>
       </c>
       <c r="H42" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" s="2">
         <v>0</v>
+      </c>
+      <c r="J42" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>100586493</t>
+          <t>100458264</t>
         </is>
       </c>
       <c r="B43" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43" s="2">
         <v>0</v>
@@ -1404,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" s="2">
         <v>0</v>
@@ -1416,13 +1545,16 @@
         <v>0</v>
       </c>
       <c r="I43" s="2">
+        <v>0</v>
+      </c>
+      <c r="J43" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>100587614</t>
+          <t>100474685</t>
         </is>
       </c>
       <c r="B44" s="2">
@@ -1447,23 +1579,26 @@
         <v>0</v>
       </c>
       <c r="I44" s="2">
+        <v>0</v>
+      </c>
+      <c r="J44" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>100596797</t>
+          <t>100492521</t>
         </is>
       </c>
       <c r="B45" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C45" s="2">
         <v>0</v>
       </c>
       <c r="D45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" s="2">
         <v>0</v>
@@ -1475,16 +1610,19 @@
         <v>0</v>
       </c>
       <c r="H45" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" s="2">
+        <v>0</v>
+      </c>
+      <c r="J45" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>100597188</t>
+          <t>100503327</t>
         </is>
       </c>
       <c r="B46" s="2">
@@ -1497,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="E46" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="2">
         <v>0</v>
@@ -1509,13 +1647,16 @@
         <v>0</v>
       </c>
       <c r="I46" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J46" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>100626189</t>
+          <t>100542499</t>
         </is>
       </c>
       <c r="B47" s="2">
@@ -1525,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="D47" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" s="2">
         <v>0</v>
@@ -1534,23 +1675,26 @@
         <v>0</v>
       </c>
       <c r="G47" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" s="2">
         <v>0</v>
       </c>
       <c r="I47" s="2">
+        <v>0</v>
+      </c>
+      <c r="J47" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>100627146</t>
+          <t>100585383</t>
         </is>
       </c>
       <c r="B48" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" s="2">
         <v>0</v>
@@ -1568,20 +1712,23 @@
         <v>0</v>
       </c>
       <c r="H48" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J48" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>100650054</t>
+          <t>100586493</t>
         </is>
       </c>
       <c r="B49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C49" s="2">
         <v>0</v>
@@ -1590,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="2">
         <v>0</v>
@@ -1599,16 +1746,19 @@
         <v>0</v>
       </c>
       <c r="H49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" s="2">
+        <v>0</v>
+      </c>
+      <c r="J49" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>100688696</t>
+          <t>100587614</t>
         </is>
       </c>
       <c r="B50" s="2">
@@ -1618,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="2">
         <v>0</v>
@@ -1630,20 +1780,23 @@
         <v>0</v>
       </c>
       <c r="H50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" s="2">
+        <v>0</v>
+      </c>
+      <c r="J50" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>100697164</t>
+          <t>100596797</t>
         </is>
       </c>
       <c r="B51" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C51" s="2">
         <v>0</v>
@@ -1664,13 +1817,16 @@
         <v>1</v>
       </c>
       <c r="I51" s="2">
+        <v>0</v>
+      </c>
+      <c r="J51" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>100730113</t>
+          <t>100597188</t>
         </is>
       </c>
       <c r="B52" s="2">
@@ -1683,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" s="2">
         <v>0</v>
@@ -1695,13 +1851,16 @@
         <v>0</v>
       </c>
       <c r="I52" s="2">
+        <v>1</v>
+      </c>
+      <c r="J52" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>100752133</t>
+          <t>100626189</t>
         </is>
       </c>
       <c r="B53" s="2">
@@ -1711,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="D53" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" s="2">
         <v>0</v>
@@ -1720,23 +1879,26 @@
         <v>0</v>
       </c>
       <c r="G53" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" s="2">
         <v>0</v>
       </c>
       <c r="I53" s="2">
+        <v>0</v>
+      </c>
+      <c r="J53" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>100754913</t>
+          <t>100627146</t>
         </is>
       </c>
       <c r="B54" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54" s="2">
         <v>0</v>
@@ -1751,19 +1913,22 @@
         <v>0</v>
       </c>
       <c r="G54" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H54" s="2">
         <v>0</v>
       </c>
       <c r="I54" s="2">
+        <v>1</v>
+      </c>
+      <c r="J54" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>100770404</t>
+          <t>100650054</t>
         </is>
       </c>
       <c r="B55" s="2">
@@ -1785,16 +1950,19 @@
         <v>0</v>
       </c>
       <c r="H55" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="2">
+        <v>0</v>
+      </c>
+      <c r="J55" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>100774355</t>
+          <t>100688696</t>
         </is>
       </c>
       <c r="B56" s="2">
@@ -1804,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="D56" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" s="2">
         <v>0</v>
@@ -1816,16 +1984,19 @@
         <v>0</v>
       </c>
       <c r="H56" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J56" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>100791007</t>
+          <t>100697164</t>
         </is>
       </c>
       <c r="B57" s="2">
@@ -1841,22 +2012,25 @@
         <v>0</v>
       </c>
       <c r="F57" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="2">
         <v>0</v>
       </c>
       <c r="H57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="2">
+        <v>0</v>
+      </c>
+      <c r="J57" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>100791832</t>
+          <t>100730113</t>
         </is>
       </c>
       <c r="B58" s="2">
@@ -1866,13 +2040,13 @@
         <v>0</v>
       </c>
       <c r="D58" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E58" s="2">
         <v>1</v>
       </c>
       <c r="F58" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" s="2">
         <v>0</v>
@@ -1881,13 +2055,16 @@
         <v>0</v>
       </c>
       <c r="I58" s="2">
+        <v>0</v>
+      </c>
+      <c r="J58" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>100795594</t>
+          <t>100752133</t>
         </is>
       </c>
       <c r="B59" s="2">
@@ -1897,7 +2074,7 @@
         <v>0</v>
       </c>
       <c r="D59" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" s="2">
         <v>0</v>
@@ -1906,19 +2083,22 @@
         <v>0</v>
       </c>
       <c r="G59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" s="2">
         <v>0</v>
       </c>
       <c r="I59" s="2">
+        <v>0</v>
+      </c>
+      <c r="J59" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>100813952</t>
+          <t>100754913</t>
         </is>
       </c>
       <c r="B60" s="2">
@@ -1937,29 +2117,32 @@
         <v>0</v>
       </c>
       <c r="G60" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H60" s="2">
         <v>0</v>
       </c>
       <c r="I60" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J60" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>100823000</t>
+          <t>100770404</t>
         </is>
       </c>
       <c r="B61" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" s="2">
         <v>0</v>
       </c>
       <c r="D61" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E61" s="2">
         <v>0</v>
@@ -1974,26 +2157,29 @@
         <v>0</v>
       </c>
       <c r="I61" s="2">
+        <v>0</v>
+      </c>
+      <c r="J61" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>100827249</t>
+          <t>100774355</t>
         </is>
       </c>
       <c r="B62" s="2">
         <v>0</v>
       </c>
       <c r="C62" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" s="2">
         <v>0</v>
@@ -2005,13 +2191,16 @@
         <v>0</v>
       </c>
       <c r="I62" s="2">
+        <v>1</v>
+      </c>
+      <c r="J62" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>100840656</t>
+          <t>100791007</t>
         </is>
       </c>
       <c r="B63" s="2">
@@ -2027,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" s="2">
         <v>0</v>
@@ -2036,13 +2225,16 @@
         <v>0</v>
       </c>
       <c r="I63" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J63" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>100862614</t>
+          <t>100791832</t>
         </is>
       </c>
       <c r="B64" s="2">
@@ -2052,35 +2244,38 @@
         <v>0</v>
       </c>
       <c r="D64" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E64" s="2">
         <v>1</v>
       </c>
       <c r="F64" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" s="2">
         <v>0</v>
       </c>
       <c r="I64" s="2">
         <v>0</v>
+      </c>
+      <c r="J64" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>100864321</t>
+          <t>100795594</t>
         </is>
       </c>
       <c r="B65" s="2">
         <v>0</v>
       </c>
       <c r="C65" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65" s="2">
         <v>0</v>
@@ -2092,19 +2287,22 @@
         <v>0</v>
       </c>
       <c r="G65" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" s="2">
         <v>0</v>
       </c>
       <c r="I65" s="2">
+        <v>0</v>
+      </c>
+      <c r="J65" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>100864434</t>
+          <t>100813952</t>
         </is>
       </c>
       <c r="B66" s="2">
@@ -2120,22 +2318,25 @@
         <v>0</v>
       </c>
       <c r="F66" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="2">
         <v>0</v>
       </c>
       <c r="I66" s="2">
+        <v>1</v>
+      </c>
+      <c r="J66" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>100876713</t>
+          <t>100823000</t>
         </is>
       </c>
       <c r="B67" s="2">
@@ -2145,41 +2346,44 @@
         <v>0</v>
       </c>
       <c r="D67" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E67" s="2">
         <v>0</v>
       </c>
       <c r="F67" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" s="2">
+        <v>0</v>
+      </c>
+      <c r="J67" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>100888704</t>
+          <t>100827249</t>
         </is>
       </c>
       <c r="B68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68" s="2">
         <v>0</v>
       </c>
       <c r="E68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="2">
         <v>0</v>
@@ -2191,13 +2395,16 @@
         <v>0</v>
       </c>
       <c r="I68" s="2">
+        <v>0</v>
+      </c>
+      <c r="J68" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>100890156</t>
+          <t>100840656</t>
         </is>
       </c>
       <c r="B69" s="2">
@@ -2213,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="F69" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" s="2">
         <v>0</v>
@@ -2222,13 +2429,16 @@
         <v>0</v>
       </c>
       <c r="I69" s="2">
+        <v>1</v>
+      </c>
+      <c r="J69" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>100894278</t>
+          <t>100862614</t>
         </is>
       </c>
       <c r="B70" s="2">
@@ -2241,32 +2451,35 @@
         <v>0</v>
       </c>
       <c r="E70" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="2">
         <v>0</v>
       </c>
       <c r="G70" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70" s="2">
+        <v>0</v>
+      </c>
+      <c r="J70" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>100937343</t>
+          <t>100864321</t>
         </is>
       </c>
       <c r="B71" s="2">
         <v>0</v>
       </c>
       <c r="C71" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71" s="2">
         <v>0</v>
@@ -2284,13 +2497,16 @@
         <v>0</v>
       </c>
       <c r="I71" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J71" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>100938809</t>
+          <t>100864434</t>
         </is>
       </c>
       <c r="B72" s="2">
@@ -2306,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G72" s="2">
         <v>0</v>
@@ -2315,20 +2531,23 @@
         <v>0</v>
       </c>
       <c r="I72" s="2">
+        <v>0</v>
+      </c>
+      <c r="J72" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>100955968</t>
+          <t>100876713</t>
         </is>
       </c>
       <c r="B73" s="2">
         <v>0</v>
       </c>
       <c r="C73" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73" s="2">
         <v>0</v>
@@ -2337,26 +2556,29 @@
         <v>0</v>
       </c>
       <c r="F73" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" s="2">
+        <v>0</v>
+      </c>
+      <c r="J73" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>100960111</t>
+          <t>100888704</t>
         </is>
       </c>
       <c r="B74" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C74" s="2">
         <v>0</v>
@@ -2371,19 +2593,22 @@
         <v>0</v>
       </c>
       <c r="G74" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" s="2">
         <v>0</v>
       </c>
       <c r="I74" s="2">
+        <v>0</v>
+      </c>
+      <c r="J74" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>100961074</t>
+          <t>100890156</t>
         </is>
       </c>
       <c r="B75" s="2">
@@ -2408,13 +2633,16 @@
         <v>0</v>
       </c>
       <c r="I75" s="2">
+        <v>0</v>
+      </c>
+      <c r="J75" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>100972973</t>
+          <t>100894278</t>
         </is>
       </c>
       <c r="B76" s="2">
@@ -2424,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="D76" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" s="2">
         <v>0</v>
@@ -2439,13 +2667,16 @@
         <v>1</v>
       </c>
       <c r="I76" s="2">
+        <v>0</v>
+      </c>
+      <c r="J76" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>100984090</t>
+          <t>100903790</t>
         </is>
       </c>
       <c r="B77" s="2">
@@ -2467,16 +2698,19 @@
         <v>0</v>
       </c>
       <c r="H77" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" s="2">
         <v>0</v>
+      </c>
+      <c r="J77" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>101013887</t>
+          <t>100937343</t>
         </is>
       </c>
       <c r="B78" s="2">
@@ -2492,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="F78" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="2">
         <v>0</v>
@@ -2501,13 +2735,16 @@
         <v>0</v>
       </c>
       <c r="I78" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J78" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>101015607</t>
+          <t>100938809</t>
         </is>
       </c>
       <c r="B79" s="2">
@@ -2523,22 +2760,25 @@
         <v>0</v>
       </c>
       <c r="F79" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G79" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" s="2">
         <v>0</v>
       </c>
       <c r="I79" s="2">
+        <v>0</v>
+      </c>
+      <c r="J79" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>101034585</t>
+          <t>100945557</t>
         </is>
       </c>
       <c r="B80" s="2">
@@ -2551,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="E80" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" s="2">
         <v>0</v>
@@ -2564,19 +2804,22 @@
       </c>
       <c r="I80" s="2">
         <v>0</v>
+      </c>
+      <c r="J80" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>101037405</t>
+          <t>100955968</t>
         </is>
       </c>
       <c r="B81" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C81" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D81" s="2">
         <v>0</v>
@@ -2594,13 +2837,16 @@
         <v>0</v>
       </c>
       <c r="I81" s="2">
+        <v>0</v>
+      </c>
+      <c r="J81" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>101078690</t>
+          <t>100960111</t>
         </is>
       </c>
       <c r="B82" s="2">
@@ -2619,19 +2865,22 @@
         <v>0</v>
       </c>
       <c r="G82" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" s="2">
         <v>0</v>
       </c>
       <c r="I82" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J82" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>101102225</t>
+          <t>100961074</t>
         </is>
       </c>
       <c r="B83" s="2">
@@ -2644,10 +2893,10 @@
         <v>0</v>
       </c>
       <c r="E83" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="2">
         <v>0</v>
@@ -2656,13 +2905,16 @@
         <v>0</v>
       </c>
       <c r="I83" s="2">
+        <v>0</v>
+      </c>
+      <c r="J83" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>101108628</t>
+          <t>100969228</t>
         </is>
       </c>
       <c r="B84" s="2">
@@ -2678,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="F84" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" s="2">
         <v>0</v>
@@ -2688,12 +2940,15 @@
       </c>
       <c r="I84" s="2">
         <v>0</v>
+      </c>
+      <c r="J84" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>101111804</t>
+          <t>100972973</t>
         </is>
       </c>
       <c r="B85" s="2">
@@ -2718,13 +2973,16 @@
         <v>1</v>
       </c>
       <c r="I85" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J85" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>101161925</t>
+          <t>100984090</t>
         </is>
       </c>
       <c r="B86" s="2">
@@ -2734,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="D86" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86" s="2">
         <v>0</v>
@@ -2746,16 +3004,19 @@
         <v>0</v>
       </c>
       <c r="H86" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" s="2">
+        <v>0</v>
+      </c>
+      <c r="J86" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>101174078</t>
+          <t>100984156</t>
         </is>
       </c>
       <c r="B87" s="2">
@@ -2768,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="E87" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" s="2">
         <v>0</v>
@@ -2781,12 +3042,15 @@
       </c>
       <c r="I87" s="2">
         <v>0</v>
+      </c>
+      <c r="J87" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>101192951</t>
+          <t>100997360</t>
         </is>
       </c>
       <c r="B88" s="2">
@@ -2811,17 +3075,20 @@
         <v>0</v>
       </c>
       <c r="I88" s="2">
+        <v>0</v>
+      </c>
+      <c r="J88" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>101195987</t>
+          <t>101013887</t>
         </is>
       </c>
       <c r="B89" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89" s="2">
         <v>0</v>
@@ -2833,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="F89" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" s="2">
         <v>0</v>
@@ -2842,13 +3109,16 @@
         <v>0</v>
       </c>
       <c r="I89" s="2">
+        <v>0</v>
+      </c>
+      <c r="J89" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>101214695</t>
+          <t>101015607</t>
         </is>
       </c>
       <c r="B90" s="2">
@@ -2867,23 +3137,26 @@
         <v>0</v>
       </c>
       <c r="G90" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J90" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>101232925</t>
+          <t>101020603</t>
         </is>
       </c>
       <c r="B91" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C91" s="2">
         <v>0</v>
@@ -2905,12 +3178,15 @@
       </c>
       <c r="I91" s="2">
         <v>0</v>
+      </c>
+      <c r="J91" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>101236937</t>
+          <t>101034585</t>
         </is>
       </c>
       <c r="B92" s="2">
@@ -2923,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="E92" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="2">
         <v>0</v>
@@ -2932,20 +3208,23 @@
         <v>0</v>
       </c>
       <c r="H92" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I92" s="2">
+        <v>0</v>
+      </c>
+      <c r="J92" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>101237859</t>
+          <t>101037405</t>
         </is>
       </c>
       <c r="B93" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93" s="2">
         <v>0</v>
@@ -2960,19 +3239,22 @@
         <v>0</v>
       </c>
       <c r="G93" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" s="2">
         <v>0</v>
       </c>
       <c r="I93" s="2">
+        <v>0</v>
+      </c>
+      <c r="J93" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>101251735</t>
+          <t>101058434</t>
         </is>
       </c>
       <c r="B94" s="2">
@@ -2991,19 +3273,22 @@
         <v>0</v>
       </c>
       <c r="G94" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" s="2">
         <v>0</v>
       </c>
       <c r="I94" s="2">
         <v>0</v>
+      </c>
+      <c r="J94" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>101265962</t>
+          <t>101078690</t>
         </is>
       </c>
       <c r="B95" s="2">
@@ -3025,29 +3310,32 @@
         <v>0</v>
       </c>
       <c r="H95" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I95" s="2">
+        <v>1</v>
+      </c>
+      <c r="J95" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>101295037</t>
+          <t>101102225</t>
         </is>
       </c>
       <c r="B96" s="2">
         <v>0</v>
       </c>
       <c r="C96" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96" s="2">
         <v>0</v>
       </c>
       <c r="E96" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="2">
         <v>0</v>
@@ -3059,13 +3347,16 @@
         <v>0</v>
       </c>
       <c r="I96" s="2">
+        <v>0</v>
+      </c>
+      <c r="J96" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>101331865</t>
+          <t>101108628</t>
         </is>
       </c>
       <c r="B97" s="2">
@@ -3081,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="F97" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" s="2">
         <v>0</v>
@@ -3090,13 +3381,16 @@
         <v>0</v>
       </c>
       <c r="I97" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J97" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>101335538</t>
+          <t>101111804</t>
         </is>
       </c>
       <c r="B98" s="2">
@@ -3106,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="D98" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" s="2">
         <v>0</v>
@@ -3115,19 +3409,22 @@
         <v>0</v>
       </c>
       <c r="G98" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I98" s="2">
+        <v>1</v>
+      </c>
+      <c r="J98" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>101336693</t>
+          <t>101161925</t>
         </is>
       </c>
       <c r="B99" s="2">
@@ -3137,13 +3434,13 @@
         <v>0</v>
       </c>
       <c r="D99" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E99" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F99" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G99" s="2">
         <v>0</v>
@@ -3152,13 +3449,16 @@
         <v>0</v>
       </c>
       <c r="I99" s="2">
+        <v>0</v>
+      </c>
+      <c r="J99" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>101342244</t>
+          <t>101174078</t>
         </is>
       </c>
       <c r="B100" s="2">
@@ -3171,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="2">
         <v>0</v>
@@ -3183,13 +3483,16 @@
         <v>0</v>
       </c>
       <c r="I100" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J100" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>101372175</t>
+          <t>101192951</t>
         </is>
       </c>
       <c r="B101" s="2">
@@ -3199,7 +3502,7 @@
         <v>0</v>
       </c>
       <c r="D101" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" s="2">
         <v>0</v>
@@ -3214,23 +3517,26 @@
         <v>0</v>
       </c>
       <c r="I101" s="2">
+        <v>1</v>
+      </c>
+      <c r="J101" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>101396394</t>
+          <t>101195987</t>
         </is>
       </c>
       <c r="B102" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C102" s="2">
         <v>0</v>
       </c>
       <c r="D102" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102" s="2">
         <v>0</v>
@@ -3245,13 +3551,16 @@
         <v>0</v>
       </c>
       <c r="I102" s="2">
+        <v>0</v>
+      </c>
+      <c r="J102" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>101407817</t>
+          <t>101214695</t>
         </is>
       </c>
       <c r="B103" s="2">
@@ -3264,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="E103" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F103" s="2">
         <v>0</v>
@@ -3273,23 +3582,26 @@
         <v>0</v>
       </c>
       <c r="H103" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" s="2">
         <v>0</v>
+      </c>
+      <c r="J103" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>101434241</t>
+          <t>101232925</t>
         </is>
       </c>
       <c r="B104" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C104" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D104" s="2">
         <v>0</v>
@@ -3307,20 +3619,23 @@
         <v>0</v>
       </c>
       <c r="I104" s="2">
+        <v>0</v>
+      </c>
+      <c r="J104" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>101437685</t>
+          <t>101236937</t>
         </is>
       </c>
       <c r="B105" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C105" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D105" s="2">
         <v>0</v>
@@ -3335,23 +3650,26 @@
         <v>0</v>
       </c>
       <c r="H105" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" s="2">
+        <v>0</v>
+      </c>
+      <c r="J105" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>101467964</t>
+          <t>101237859</t>
         </is>
       </c>
       <c r="B106" s="2">
         <v>0</v>
       </c>
       <c r="C106" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D106" s="2">
         <v>0</v>
@@ -3363,26 +3681,29 @@
         <v>0</v>
       </c>
       <c r="G106" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" s="2">
         <v>0</v>
       </c>
       <c r="I106" s="2">
+        <v>0</v>
+      </c>
+      <c r="J106" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>101481537</t>
+          <t>101251735</t>
         </is>
       </c>
       <c r="B107" s="2">
         <v>0</v>
       </c>
       <c r="C107" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107" s="2">
         <v>0</v>
@@ -3394,23 +3715,26 @@
         <v>0</v>
       </c>
       <c r="G107" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" s="2">
         <v>0</v>
       </c>
       <c r="I107" s="2">
+        <v>0</v>
+      </c>
+      <c r="J107" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>101509593</t>
+          <t>101265962</t>
         </is>
       </c>
       <c r="B108" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C108" s="2">
         <v>0</v>
@@ -3428,23 +3752,26 @@
         <v>0</v>
       </c>
       <c r="H108" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I108" s="2">
+        <v>0</v>
+      </c>
+      <c r="J108" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>101533995</t>
+          <t>101295037</t>
         </is>
       </c>
       <c r="B109" s="2">
         <v>0</v>
       </c>
       <c r="C109" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D109" s="2">
         <v>0</v>
@@ -3453,7 +3780,7 @@
         <v>0</v>
       </c>
       <c r="F109" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G109" s="2">
         <v>0</v>
@@ -3462,17 +3789,20 @@
         <v>0</v>
       </c>
       <c r="I109" s="2">
+        <v>0</v>
+      </c>
+      <c r="J109" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>101573499</t>
+          <t>101331865</t>
         </is>
       </c>
       <c r="B110" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C110" s="2">
         <v>0</v>
@@ -3487,19 +3817,22 @@
         <v>0</v>
       </c>
       <c r="G110" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110" s="2">
         <v>0</v>
       </c>
       <c r="I110" s="2">
         <v>1</v>
+      </c>
+      <c r="J110" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>101623111</t>
+          <t>101335538</t>
         </is>
       </c>
       <c r="B111" s="2">
@@ -3518,19 +3851,22 @@
         <v>0</v>
       </c>
       <c r="G111" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I111" s="2">
+        <v>0</v>
+      </c>
+      <c r="J111" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>101639078</t>
+          <t>101336693</t>
         </is>
       </c>
       <c r="B112" s="2">
@@ -3543,25 +3879,28 @@
         <v>0</v>
       </c>
       <c r="E112" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F112" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G112" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112" s="2">
         <v>0</v>
       </c>
       <c r="I112" s="2">
         <v>0</v>
+      </c>
+      <c r="J112" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>101649796</t>
+          <t>101342244</t>
         </is>
       </c>
       <c r="B113" s="2">
@@ -3577,7 +3916,7 @@
         <v>0</v>
       </c>
       <c r="F113" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113" s="2">
         <v>0</v>
@@ -3586,13 +3925,16 @@
         <v>0</v>
       </c>
       <c r="I113" s="2">
+        <v>1</v>
+      </c>
+      <c r="J113" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>101691981</t>
+          <t>101372175</t>
         </is>
       </c>
       <c r="B114" s="2">
@@ -3602,28 +3944,31 @@
         <v>0</v>
       </c>
       <c r="D114" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114" s="2">
         <v>0</v>
       </c>
       <c r="F114" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G114" s="2">
         <v>0</v>
       </c>
       <c r="H114" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I114" s="2">
+        <v>0</v>
+      </c>
+      <c r="J114" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>101716663</t>
+          <t>101396394</t>
         </is>
       </c>
       <c r="B115" s="2">
@@ -3633,7 +3978,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115" s="2">
         <v>0</v>
@@ -3645,16 +3990,19 @@
         <v>0</v>
       </c>
       <c r="H115" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I115" s="2">
+        <v>0</v>
+      </c>
+      <c r="J115" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>101739204</t>
+          <t>101407817</t>
         </is>
       </c>
       <c r="B116" s="2">
@@ -3667,7 +4015,7 @@
         <v>0</v>
       </c>
       <c r="E116" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="2">
         <v>0</v>
@@ -3676,16 +4024,19 @@
         <v>0</v>
       </c>
       <c r="H116" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I116" s="2">
+        <v>0</v>
+      </c>
+      <c r="J116" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>101800057</t>
+          <t>101424907</t>
         </is>
       </c>
       <c r="B117" s="2">
@@ -3701,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="F117" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G117" s="2">
         <v>0</v>
@@ -3711,12 +4062,15 @@
       </c>
       <c r="I117" s="2">
         <v>0</v>
+      </c>
+      <c r="J117" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>101836491</t>
+          <t>101434241</t>
         </is>
       </c>
       <c r="B118" s="2">
@@ -3741,17 +4095,20 @@
         <v>0</v>
       </c>
       <c r="I118" s="2">
+        <v>0</v>
+      </c>
+      <c r="J118" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>101863433</t>
+          <t>101437685</t>
         </is>
       </c>
       <c r="B119" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C119" s="2">
         <v>1</v>
@@ -3772,26 +4129,29 @@
         <v>0</v>
       </c>
       <c r="I119" s="2">
+        <v>0</v>
+      </c>
+      <c r="J119" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>101875176</t>
+          <t>101467964</t>
         </is>
       </c>
       <c r="B120" s="2">
         <v>0</v>
       </c>
       <c r="C120" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D120" s="2">
         <v>0</v>
       </c>
       <c r="E120" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F120" s="2">
         <v>0</v>
@@ -3803,20 +4163,23 @@
         <v>0</v>
       </c>
       <c r="I120" s="2">
+        <v>0</v>
+      </c>
+      <c r="J120" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>101885140</t>
+          <t>101481537</t>
         </is>
       </c>
       <c r="B121" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C121" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D121" s="2">
         <v>0</v>
@@ -3834,20 +4197,23 @@
         <v>0</v>
       </c>
       <c r="I121" s="2">
+        <v>0</v>
+      </c>
+      <c r="J121" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>101888773</t>
+          <t>101509593</t>
         </is>
       </c>
       <c r="B122" s="2">
         <v>1</v>
       </c>
       <c r="C122" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D122" s="2">
         <v>0</v>
@@ -3856,22 +4222,25 @@
         <v>0</v>
       </c>
       <c r="F122" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H122" s="2">
         <v>0</v>
       </c>
       <c r="I122" s="2">
+        <v>0</v>
+      </c>
+      <c r="J122" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>101903020</t>
+          <t>101533995</t>
         </is>
       </c>
       <c r="B123" s="2">
@@ -3896,17 +4265,20 @@
         <v>0</v>
       </c>
       <c r="I123" s="2">
+        <v>0</v>
+      </c>
+      <c r="J123" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>101910440</t>
+          <t>101573499</t>
         </is>
       </c>
       <c r="B124" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C124" s="2">
         <v>0</v>
@@ -3921,19 +4293,22 @@
         <v>0</v>
       </c>
       <c r="G124" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H124" s="2">
         <v>0</v>
       </c>
       <c r="I124" s="2">
         <v>1</v>
+      </c>
+      <c r="J124" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>101983093</t>
+          <t>101623111</t>
         </is>
       </c>
       <c r="B125" s="2">
@@ -3958,13 +4333,16 @@
         <v>1</v>
       </c>
       <c r="I125" s="2">
+        <v>0</v>
+      </c>
+      <c r="J125" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>101996505</t>
+          <t>101639078</t>
         </is>
       </c>
       <c r="B126" s="2">
@@ -3983,35 +4361,38 @@
         <v>0</v>
       </c>
       <c r="G126" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H126" s="2">
         <v>0</v>
       </c>
       <c r="I126" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J126" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>102006080</t>
+          <t>101649796</t>
         </is>
       </c>
       <c r="B127" s="2">
         <v>0</v>
       </c>
       <c r="C127" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D127" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E127" s="2">
         <v>0</v>
       </c>
       <c r="F127" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G127" s="2">
         <v>0</v>
@@ -4020,20 +4401,23 @@
         <v>0</v>
       </c>
       <c r="I127" s="2">
+        <v>0</v>
+      </c>
+      <c r="J127" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>102006845</t>
+          <t>101691981</t>
         </is>
       </c>
       <c r="B128" s="2">
         <v>0</v>
       </c>
       <c r="C128" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D128" s="2">
         <v>0</v>
@@ -4042,22 +4426,25 @@
         <v>0</v>
       </c>
       <c r="F128" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G128" s="2">
         <v>0</v>
       </c>
       <c r="H128" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I128" s="2">
+        <v>0</v>
+      </c>
+      <c r="J128" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>102050130</t>
+          <t>101708491</t>
         </is>
       </c>
       <c r="B129" s="2">
@@ -4070,7 +4457,7 @@
         <v>0</v>
       </c>
       <c r="E129" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F129" s="2">
         <v>0</v>
@@ -4083,12 +4470,15 @@
       </c>
       <c r="I129" s="2">
         <v>0</v>
+      </c>
+      <c r="J129" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>102109244</t>
+          <t>101716663</t>
         </is>
       </c>
       <c r="B130" s="2">
@@ -4101,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="E130" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F130" s="2">
         <v>0</v>
@@ -4110,16 +4500,19 @@
         <v>0</v>
       </c>
       <c r="H130" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I130" s="2">
+        <v>0</v>
+      </c>
+      <c r="J130" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>102125733</t>
+          <t>101739204</t>
         </is>
       </c>
       <c r="B131" s="2">
@@ -4144,13 +4537,16 @@
         <v>1</v>
       </c>
       <c r="I131" s="2">
+        <v>0</v>
+      </c>
+      <c r="J131" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>102203438</t>
+          <t>101800057</t>
         </is>
       </c>
       <c r="B132" s="2">
@@ -4163,10 +4559,10 @@
         <v>0</v>
       </c>
       <c r="E132" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F132" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G132" s="2">
         <v>0</v>
@@ -4175,20 +4571,23 @@
         <v>0</v>
       </c>
       <c r="I132" s="2">
+        <v>0</v>
+      </c>
+      <c r="J132" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>102224443</t>
+          <t>101836491</t>
         </is>
       </c>
       <c r="B133" s="2">
         <v>0</v>
       </c>
       <c r="C133" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D133" s="2">
         <v>0</v>
@@ -4197,22 +4596,25 @@
         <v>0</v>
       </c>
       <c r="F133" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G133" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H133" s="2">
         <v>0</v>
       </c>
       <c r="I133" s="2">
+        <v>0</v>
+      </c>
+      <c r="J133" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>102227253</t>
+          <t>101863433</t>
         </is>
       </c>
       <c r="B134" s="2">
@@ -4237,13 +4639,16 @@
         <v>0</v>
       </c>
       <c r="I134" s="2">
+        <v>0</v>
+      </c>
+      <c r="J134" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>102282059</t>
+          <t>101875176</t>
         </is>
       </c>
       <c r="B135" s="2">
@@ -4268,20 +4673,23 @@
         <v>0</v>
       </c>
       <c r="I135" s="2">
+        <v>0</v>
+      </c>
+      <c r="J135" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>102299090</t>
+          <t>101885140</t>
         </is>
       </c>
       <c r="B136" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C136" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D136" s="2">
         <v>0</v>
@@ -4299,51 +4707,57 @@
         <v>0</v>
       </c>
       <c r="I136" s="2">
+        <v>0</v>
+      </c>
+      <c r="J136" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>102307203</t>
+          <t>101888773</t>
         </is>
       </c>
       <c r="B137" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C137" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D137" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E137" s="2">
         <v>0</v>
       </c>
       <c r="F137" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H137" s="2">
         <v>0</v>
       </c>
       <c r="I137" s="2">
+        <v>0</v>
+      </c>
+      <c r="J137" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>102375097</t>
+          <t>101903020</t>
         </is>
       </c>
       <c r="B138" s="2">
         <v>0</v>
       </c>
       <c r="C138" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D138" s="2">
         <v>0</v>
@@ -4352,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="F138" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" s="2">
         <v>0</v>
@@ -4361,17 +4775,20 @@
         <v>0</v>
       </c>
       <c r="I138" s="2">
+        <v>0</v>
+      </c>
+      <c r="J138" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>102454744</t>
+          <t>101910440</t>
         </is>
       </c>
       <c r="B139" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C139" s="2">
         <v>0</v>
@@ -4392,17 +4809,20 @@
         <v>0</v>
       </c>
       <c r="I139" s="2">
+        <v>1</v>
+      </c>
+      <c r="J139" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>102497144</t>
+          <t>101983093</t>
         </is>
       </c>
       <c r="B140" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C140" s="2">
         <v>0</v>
@@ -4420,16 +4840,19 @@
         <v>0</v>
       </c>
       <c r="H140" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I140" s="2">
+        <v>0</v>
+      </c>
+      <c r="J140" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>102569542</t>
+          <t>101996505</t>
         </is>
       </c>
       <c r="B141" s="2">
@@ -4445,7 +4868,7 @@
         <v>0</v>
       </c>
       <c r="F141" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G141" s="2">
         <v>0</v>
@@ -4454,23 +4877,26 @@
         <v>0</v>
       </c>
       <c r="I141" s="2">
+        <v>1</v>
+      </c>
+      <c r="J141" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>102600124</t>
+          <t>102006080</t>
         </is>
       </c>
       <c r="B142" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C142" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D142" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142" s="2">
         <v>0</v>
@@ -4485,57 +4911,63 @@
         <v>0</v>
       </c>
       <c r="I142" s="2">
+        <v>0</v>
+      </c>
+      <c r="J142" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>102655931</t>
+          <t>102006845</t>
         </is>
       </c>
       <c r="B143" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C143" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D143" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E143" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F143" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G143" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H143" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I143" s="2">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="J143" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>102673781</t>
+          <t>102050130</t>
         </is>
       </c>
       <c r="B144" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C144" s="2">
         <v>0</v>
       </c>
       <c r="D144" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E144" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" s="2">
         <v>0</v>
@@ -4547,13 +4979,16 @@
         <v>0</v>
       </c>
       <c r="I144" s="2">
+        <v>0</v>
+      </c>
+      <c r="J144" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>102690829</t>
+          <t>102109244</t>
         </is>
       </c>
       <c r="B145" s="2">
@@ -4563,10 +4998,10 @@
         <v>0</v>
       </c>
       <c r="D145" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E145" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="2">
         <v>0</v>
@@ -4578,13 +5013,16 @@
         <v>0</v>
       </c>
       <c r="I145" s="2">
+        <v>0</v>
+      </c>
+      <c r="J145" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>102697265</t>
+          <t>102125733</t>
         </is>
       </c>
       <c r="B146" s="2">
@@ -4609,17 +5047,20 @@
         <v>1</v>
       </c>
       <c r="I146" s="2">
+        <v>0</v>
+      </c>
+      <c r="J146" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>102698382</t>
+          <t>102203438</t>
         </is>
       </c>
       <c r="B147" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C147" s="2">
         <v>0</v>
@@ -4628,7 +5069,7 @@
         <v>0</v>
       </c>
       <c r="E147" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" s="2">
         <v>0</v>
@@ -4640,13 +5081,16 @@
         <v>0</v>
       </c>
       <c r="I147" s="2">
+        <v>0</v>
+      </c>
+      <c r="J147" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>102705657</t>
+          <t>102224443</t>
         </is>
       </c>
       <c r="B148" s="2">
@@ -4656,28 +5100,31 @@
         <v>0</v>
       </c>
       <c r="D148" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" s="2">
         <v>0</v>
       </c>
       <c r="F148" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G148" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H148" s="2">
         <v>0</v>
       </c>
       <c r="I148" s="2">
+        <v>0</v>
+      </c>
+      <c r="J148" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>102748593</t>
+          <t>102227253</t>
         </is>
       </c>
       <c r="B149" s="2">
@@ -4702,13 +5149,16 @@
         <v>0</v>
       </c>
       <c r="I149" s="2">
+        <v>0</v>
+      </c>
+      <c r="J149" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>102793147</t>
+          <t>102282059</t>
         </is>
       </c>
       <c r="B150" s="2">
@@ -4733,20 +5183,23 @@
         <v>0</v>
       </c>
       <c r="I150" s="2">
+        <v>0</v>
+      </c>
+      <c r="J150" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>102796686</t>
+          <t>102299090</t>
         </is>
       </c>
       <c r="B151" s="2">
         <v>0</v>
       </c>
       <c r="C151" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D151" s="2">
         <v>0</v>
@@ -4758,19 +5211,22 @@
         <v>0</v>
       </c>
       <c r="G151" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H151" s="2">
         <v>0</v>
       </c>
       <c r="I151" s="2">
+        <v>0</v>
+      </c>
+      <c r="J151" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1100043267</t>
+          <t>102307203</t>
         </is>
       </c>
       <c r="B152" s="2">
@@ -4780,13 +5236,13 @@
         <v>0</v>
       </c>
       <c r="D152" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152" s="2">
         <v>0</v>
       </c>
       <c r="F152" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G152" s="2">
         <v>0</v>
@@ -4796,19 +5252,22 @@
       </c>
       <c r="I152" s="2">
         <v>0</v>
+      </c>
+      <c r="J152" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1100063691</t>
+          <t>102375097</t>
         </is>
       </c>
       <c r="B153" s="2">
         <v>0</v>
       </c>
       <c r="C153" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D153" s="2">
         <v>0</v>
@@ -4826,13 +5285,16 @@
         <v>0</v>
       </c>
       <c r="I153" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J153" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1100079588</t>
+          <t>102454744</t>
         </is>
       </c>
       <c r="B154" s="2">
@@ -4857,20 +5319,23 @@
         <v>0</v>
       </c>
       <c r="I154" s="2">
+        <v>0</v>
+      </c>
+      <c r="J154" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>500000823</t>
+          <t>102497144</t>
         </is>
       </c>
       <c r="B155" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C155" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D155" s="2">
         <v>0</v>
@@ -4888,13 +5353,16 @@
         <v>0</v>
       </c>
       <c r="I155" s="2">
+        <v>0</v>
+      </c>
+      <c r="J155" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>500000921</t>
+          <t>102569542</t>
         </is>
       </c>
       <c r="B156" s="2">
@@ -4904,13 +5372,13 @@
         <v>0</v>
       </c>
       <c r="D156" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156" s="2">
         <v>0</v>
       </c>
       <c r="F156" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G156" s="2">
         <v>0</v>
@@ -4919,13 +5387,16 @@
         <v>0</v>
       </c>
       <c r="I156" s="2">
+        <v>0</v>
+      </c>
+      <c r="J156" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>500002685</t>
+          <t>102591998</t>
         </is>
       </c>
       <c r="B157" s="2">
@@ -4938,7 +5409,7 @@
         <v>0</v>
       </c>
       <c r="E157" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F157" s="2">
         <v>0</v>
@@ -4951,12 +5422,15 @@
       </c>
       <c r="I157" s="2">
         <v>0</v>
+      </c>
+      <c r="J157" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>500003288</t>
+          <t>102600124</t>
         </is>
       </c>
       <c r="B158" s="2">
@@ -4981,57 +5455,63 @@
         <v>0</v>
       </c>
       <c r="I158" s="2">
+        <v>0</v>
+      </c>
+      <c r="J158" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>500003337</t>
+          <t>102655931</t>
         </is>
       </c>
       <c r="B159" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C159" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D159" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E159" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F159" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G159" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H159" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I159" s="2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J159" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>500003682</t>
+          <t>102673781</t>
         </is>
       </c>
       <c r="B160" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C160" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D160" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E160" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F160" s="2">
         <v>0</v>
@@ -5043,13 +5523,16 @@
         <v>0</v>
       </c>
       <c r="I160" s="2">
+        <v>0</v>
+      </c>
+      <c r="J160" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>500008320</t>
+          <t>102690829</t>
         </is>
       </c>
       <c r="B161" s="2">
@@ -5059,13 +5542,13 @@
         <v>0</v>
       </c>
       <c r="D161" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E161" s="2">
         <v>0</v>
       </c>
       <c r="F161" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G161" s="2">
         <v>0</v>
@@ -5074,44 +5557,50 @@
         <v>0</v>
       </c>
       <c r="I161" s="2">
+        <v>0</v>
+      </c>
+      <c r="J161" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>500009413</t>
+          <t>102697265</t>
         </is>
       </c>
       <c r="B162" s="2">
         <v>0</v>
       </c>
       <c r="C162" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D162" s="2">
         <v>0</v>
       </c>
       <c r="E162" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F162" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G162" s="2">
         <v>0</v>
       </c>
       <c r="H162" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162" s="2">
+        <v>0</v>
+      </c>
+      <c r="J162" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>500016197</t>
+          <t>102698382</t>
         </is>
       </c>
       <c r="B163" s="2">
@@ -5136,13 +5625,16 @@
         <v>0</v>
       </c>
       <c r="I163" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J163" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>500020789</t>
+          <t>102705657</t>
         </is>
       </c>
       <c r="B164" s="2">
@@ -5152,10 +5644,10 @@
         <v>0</v>
       </c>
       <c r="D164" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E164" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F164" s="2">
         <v>0</v>
@@ -5167,20 +5659,23 @@
         <v>0</v>
       </c>
       <c r="I164" s="2">
+        <v>0</v>
+      </c>
+      <c r="J164" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>500023997</t>
+          <t>102748593</t>
         </is>
       </c>
       <c r="B165" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C165" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D165" s="2">
         <v>0</v>
@@ -5198,13 +5693,16 @@
         <v>0</v>
       </c>
       <c r="I165" s="2">
+        <v>0</v>
+      </c>
+      <c r="J165" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>500024124</t>
+          <t>102793147</t>
         </is>
       </c>
       <c r="B166" s="2">
@@ -5214,10 +5712,10 @@
         <v>0</v>
       </c>
       <c r="D166" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E166" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F166" s="2">
         <v>0</v>
@@ -5229,13 +5727,16 @@
         <v>0</v>
       </c>
       <c r="I166" s="2">
+        <v>0</v>
+      </c>
+      <c r="J166" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>500028485</t>
+          <t>102796686</t>
         </is>
       </c>
       <c r="B167" s="2">
@@ -5245,28 +5746,31 @@
         <v>0</v>
       </c>
       <c r="D167" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E167" s="2">
+        <v>0</v>
+      </c>
+      <c r="F167" s="2">
+        <v>0</v>
+      </c>
+      <c r="G167" s="2">
         <v>2</v>
       </c>
-      <c r="F167" s="2">
-        <v>1</v>
-      </c>
-      <c r="G167" s="2">
-        <v>0</v>
-      </c>
       <c r="H167" s="2">
         <v>0</v>
       </c>
       <c r="I167" s="2">
+        <v>0</v>
+      </c>
+      <c r="J167" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>500030111</t>
+          <t>1100043267</t>
         </is>
       </c>
       <c r="B168" s="2">
@@ -5282,22 +5786,25 @@
         <v>0</v>
       </c>
       <c r="F168" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G168" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H168" s="2">
         <v>0</v>
       </c>
       <c r="I168" s="2">
+        <v>0</v>
+      </c>
+      <c r="J168" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>500031227</t>
+          <t>1100063691</t>
         </is>
       </c>
       <c r="B169" s="2">
@@ -5313,7 +5820,7 @@
         <v>0</v>
       </c>
       <c r="F169" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G169" s="2">
         <v>0</v>
@@ -5322,20 +5829,23 @@
         <v>0</v>
       </c>
       <c r="I169" s="2">
+        <v>1</v>
+      </c>
+      <c r="J169" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>500031276</t>
+          <t>1100075478</t>
         </is>
       </c>
       <c r="B170" s="2">
         <v>0</v>
       </c>
       <c r="C170" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D170" s="2">
         <v>0</v>
@@ -5354,12 +5864,15 @@
       </c>
       <c r="I170" s="2">
         <v>0</v>
+      </c>
+      <c r="J170" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>500032408</t>
+          <t>1100079588</t>
         </is>
       </c>
       <c r="B171" s="2">
@@ -5384,13 +5897,16 @@
         <v>0</v>
       </c>
       <c r="I171" s="2">
+        <v>0</v>
+      </c>
+      <c r="J171" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>500035796</t>
+          <t>500000438</t>
         </is>
       </c>
       <c r="B172" s="2">
@@ -5400,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="D172" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E172" s="2">
         <v>0</v>
@@ -5416,19 +5932,22 @@
       </c>
       <c r="I172" s="2">
         <v>0</v>
+      </c>
+      <c r="J172" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>500036672</t>
+          <t>500000823</t>
         </is>
       </c>
       <c r="B173" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C173" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D173" s="2">
         <v>0</v>
@@ -5447,12 +5966,15 @@
       </c>
       <c r="I173" s="2">
         <v>0</v>
+      </c>
+      <c r="J173" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>500037006</t>
+          <t>500000921</t>
         </is>
       </c>
       <c r="B174" s="2">
@@ -5462,13 +5984,13 @@
         <v>0</v>
       </c>
       <c r="D174" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E174" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F174" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G174" s="2">
         <v>0</v>
@@ -5477,13 +5999,16 @@
         <v>0</v>
       </c>
       <c r="I174" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J174" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>500043218</t>
+          <t>500002685</t>
         </is>
       </c>
       <c r="B175" s="2">
@@ -5496,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="E175" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F175" s="2">
         <v>0</v>
@@ -5508,17 +6033,20 @@
         <v>0</v>
       </c>
       <c r="I175" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J175" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>500050269</t>
+          <t>500003288</t>
         </is>
       </c>
       <c r="B176" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C176" s="2">
         <v>0</v>
@@ -5533,26 +6061,29 @@
         <v>0</v>
       </c>
       <c r="G176" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H176" s="2">
         <v>0</v>
       </c>
       <c r="I176" s="2">
+        <v>0</v>
+      </c>
+      <c r="J176" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>500052051</t>
+          <t>500003337</t>
         </is>
       </c>
       <c r="B177" s="2">
         <v>0</v>
       </c>
       <c r="C177" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D177" s="2">
         <v>0</v>
@@ -5567,20 +6098,23 @@
         <v>0</v>
       </c>
       <c r="H177" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I177" s="2">
+        <v>1</v>
+      </c>
+      <c r="J177" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>500057619</t>
+          <t>500003682</t>
         </is>
       </c>
       <c r="B178" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C178" s="2">
         <v>1</v>
@@ -5589,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="E178" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F178" s="2">
         <v>0</v>
@@ -5601,13 +6135,16 @@
         <v>0</v>
       </c>
       <c r="I178" s="2">
+        <v>0</v>
+      </c>
+      <c r="J178" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>500058721</t>
+          <t>500008320</t>
         </is>
       </c>
       <c r="B179" s="2">
@@ -5623,26 +6160,29 @@
         <v>0</v>
       </c>
       <c r="F179" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G179" s="2">
         <v>0</v>
       </c>
       <c r="H179" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I179" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J179" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>500060661</t>
+          <t>500009413</t>
         </is>
       </c>
       <c r="B180" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C180" s="2">
         <v>1</v>
@@ -5651,10 +6191,10 @@
         <v>0</v>
       </c>
       <c r="E180" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F180" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G180" s="2">
         <v>0</v>
@@ -5663,13 +6203,16 @@
         <v>0</v>
       </c>
       <c r="I180" s="2">
+        <v>0</v>
+      </c>
+      <c r="J180" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>500061708</t>
+          <t>500016197</t>
         </is>
       </c>
       <c r="B181" s="2">
@@ -5679,7 +6222,7 @@
         <v>0</v>
       </c>
       <c r="D181" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E181" s="2">
         <v>0</v>
@@ -5694,13 +6237,16 @@
         <v>0</v>
       </c>
       <c r="I181" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J181" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>500066176</t>
+          <t>500020789</t>
         </is>
       </c>
       <c r="B182" s="2">
@@ -5713,10 +6259,10 @@
         <v>0</v>
       </c>
       <c r="E182" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F182" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G182" s="2">
         <v>0</v>
@@ -5725,17 +6271,20 @@
         <v>0</v>
       </c>
       <c r="I182" s="2">
+        <v>0</v>
+      </c>
+      <c r="J182" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>500067801</t>
+          <t>500023997</t>
         </is>
       </c>
       <c r="B183" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C183" s="2">
         <v>0</v>
@@ -5750,19 +6299,22 @@
         <v>0</v>
       </c>
       <c r="G183" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H183" s="2">
         <v>0</v>
       </c>
       <c r="I183" s="2">
+        <v>0</v>
+      </c>
+      <c r="J183" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>500080387</t>
+          <t>500024124</t>
         </is>
       </c>
       <c r="B184" s="2">
@@ -5772,7 +6324,7 @@
         <v>0</v>
       </c>
       <c r="D184" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E184" s="2">
         <v>0</v>
@@ -5781,19 +6333,22 @@
         <v>0</v>
       </c>
       <c r="G184" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H184" s="2">
         <v>0</v>
       </c>
       <c r="I184" s="2">
+        <v>0</v>
+      </c>
+      <c r="J184" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>500092658</t>
+          <t>500028485</t>
         </is>
       </c>
       <c r="B185" s="2">
@@ -5803,28 +6358,31 @@
         <v>0</v>
       </c>
       <c r="D185" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E185" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F185" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G185" s="2">
         <v>0</v>
       </c>
       <c r="H185" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I185" s="2">
         <v>0</v>
+      </c>
+      <c r="J185" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>500094507</t>
+          <t>500030111</t>
         </is>
       </c>
       <c r="B186" s="2">
@@ -5834,7 +6392,7 @@
         <v>0</v>
       </c>
       <c r="D186" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E186" s="2">
         <v>0</v>
@@ -5843,19 +6401,22 @@
         <v>0</v>
       </c>
       <c r="G186" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H186" s="2">
         <v>0</v>
       </c>
       <c r="I186" s="2">
+        <v>0</v>
+      </c>
+      <c r="J186" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>500101533</t>
+          <t>500031227</t>
         </is>
       </c>
       <c r="B187" s="2">
@@ -5880,20 +6441,23 @@
         <v>0</v>
       </c>
       <c r="I187" s="2">
+        <v>0</v>
+      </c>
+      <c r="J187" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>500104713</t>
+          <t>500031276</t>
         </is>
       </c>
       <c r="B188" s="2">
         <v>0</v>
       </c>
       <c r="C188" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D188" s="2">
         <v>0</v>
@@ -5908,26 +6472,29 @@
         <v>0</v>
       </c>
       <c r="H188" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I188" s="2">
+        <v>0</v>
+      </c>
+      <c r="J188" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>500111404</t>
+          <t>500032408</t>
         </is>
       </c>
       <c r="B189" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C189" s="2">
         <v>0</v>
       </c>
       <c r="D189" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E189" s="2">
         <v>0</v>
@@ -5942,13 +6509,16 @@
         <v>0</v>
       </c>
       <c r="I189" s="2">
+        <v>0</v>
+      </c>
+      <c r="J189" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>500113054</t>
+          <t>500035796</t>
         </is>
       </c>
       <c r="B190" s="2">
@@ -5958,7 +6528,7 @@
         <v>0</v>
       </c>
       <c r="D190" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E190" s="2">
         <v>0</v>
@@ -5970,16 +6540,19 @@
         <v>0</v>
       </c>
       <c r="H190" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I190" s="2">
+        <v>0</v>
+      </c>
+      <c r="J190" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>500115640</t>
+          <t>500036672</t>
         </is>
       </c>
       <c r="B191" s="2">
@@ -5995,22 +6568,25 @@
         <v>0</v>
       </c>
       <c r="F191" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G191" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H191" s="2">
         <v>0</v>
       </c>
       <c r="I191" s="2">
+        <v>0</v>
+      </c>
+      <c r="J191" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>500117284</t>
+          <t>500037006</t>
         </is>
       </c>
       <c r="B192" s="2">
@@ -6020,13 +6596,13 @@
         <v>0</v>
       </c>
       <c r="D192" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E192" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F192" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G192" s="2">
         <v>0</v>
@@ -6035,23 +6611,26 @@
         <v>0</v>
       </c>
       <c r="I192" s="2">
+        <v>1</v>
+      </c>
+      <c r="J192" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>500120216</t>
+          <t>500043218</t>
         </is>
       </c>
       <c r="B193" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C193" s="2">
         <v>0</v>
       </c>
       <c r="D193" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E193" s="2">
         <v>0</v>
@@ -6066,13 +6645,16 @@
         <v>0</v>
       </c>
       <c r="I193" s="2">
+        <v>1</v>
+      </c>
+      <c r="J193" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>500126621</t>
+          <t>500050269</t>
         </is>
       </c>
       <c r="B194" s="2">
@@ -6082,7 +6664,7 @@
         <v>0</v>
       </c>
       <c r="D194" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E194" s="2">
         <v>0</v>
@@ -6097,20 +6679,23 @@
         <v>0</v>
       </c>
       <c r="I194" s="2">
+        <v>0</v>
+      </c>
+      <c r="J194" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>500127435</t>
+          <t>500052051</t>
         </is>
       </c>
       <c r="B195" s="2">
         <v>0</v>
       </c>
       <c r="C195" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D195" s="2">
         <v>0</v>
@@ -6122,26 +6707,29 @@
         <v>0</v>
       </c>
       <c r="G195" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H195" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I195" s="2">
+        <v>0</v>
+      </c>
+      <c r="J195" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>500128032</t>
+          <t>500057619</t>
         </is>
       </c>
       <c r="B196" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C196" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D196" s="2">
         <v>0</v>
@@ -6150,7 +6738,7 @@
         <v>0</v>
       </c>
       <c r="F196" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G196" s="2">
         <v>0</v>
@@ -6159,13 +6747,16 @@
         <v>0</v>
       </c>
       <c r="I196" s="2">
+        <v>0</v>
+      </c>
+      <c r="J196" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>500128657</t>
+          <t>500058721</t>
         </is>
       </c>
       <c r="B197" s="2">
@@ -6181,29 +6772,32 @@
         <v>0</v>
       </c>
       <c r="F197" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G197" s="2">
         <v>0</v>
       </c>
       <c r="H197" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I197" s="2">
+        <v>1</v>
+      </c>
+      <c r="J197" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>500128699</t>
+          <t>500060661</t>
         </is>
       </c>
       <c r="B198" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C198" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D198" s="2">
         <v>0</v>
@@ -6218,26 +6812,29 @@
         <v>0</v>
       </c>
       <c r="H198" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I198" s="2">
+        <v>0</v>
+      </c>
+      <c r="J198" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>500143502</t>
+          <t>500061708</t>
         </is>
       </c>
       <c r="B199" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C199" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D199" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E199" s="2">
         <v>0</v>
@@ -6252,17 +6849,20 @@
         <v>0</v>
       </c>
       <c r="I199" s="2">
+        <v>0</v>
+      </c>
+      <c r="J199" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>500143882</t>
+          <t>500066176</t>
         </is>
       </c>
       <c r="B200" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C200" s="2">
         <v>0</v>
@@ -6274,7 +6874,7 @@
         <v>0</v>
       </c>
       <c r="F200" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G200" s="2">
         <v>0</v>
@@ -6283,13 +6883,16 @@
         <v>0</v>
       </c>
       <c r="I200" s="2">
+        <v>0</v>
+      </c>
+      <c r="J200" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>500146241</t>
+          <t>500067801</t>
         </is>
       </c>
       <c r="B201" s="2">
@@ -6308,23 +6911,26 @@
         <v>0</v>
       </c>
       <c r="G201" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H201" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I201" s="2">
+        <v>0</v>
+      </c>
+      <c r="J201" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>500146800</t>
+          <t>500070063</t>
         </is>
       </c>
       <c r="B202" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C202" s="2">
         <v>0</v>
@@ -6339,19 +6945,22 @@
         <v>0</v>
       </c>
       <c r="G202" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H202" s="2">
         <v>0</v>
       </c>
       <c r="I202" s="2">
         <v>0</v>
+      </c>
+      <c r="J202" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>500148890</t>
+          <t>500080387</t>
         </is>
       </c>
       <c r="B203" s="2">
@@ -6370,26 +6979,29 @@
         <v>0</v>
       </c>
       <c r="G203" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H203" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I203" s="2">
+        <v>0</v>
+      </c>
+      <c r="J203" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>500185891</t>
+          <t>500091839</t>
         </is>
       </c>
       <c r="B204" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C204" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D204" s="2">
         <v>0</v>
@@ -6408,12 +7020,15 @@
       </c>
       <c r="I204" s="2">
         <v>0</v>
+      </c>
+      <c r="J204" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>500186481</t>
+          <t>500092658</t>
         </is>
       </c>
       <c r="B205" s="2">
@@ -6432,29 +7047,32 @@
         <v>0</v>
       </c>
       <c r="G205" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H205" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I205" s="2">
+        <v>0</v>
+      </c>
+      <c r="J205" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>500187931</t>
+          <t>500094507</t>
         </is>
       </c>
       <c r="B206" s="2">
         <v>0</v>
       </c>
       <c r="C206" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D206" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E206" s="2">
         <v>0</v>
@@ -6469,13 +7087,16 @@
         <v>0</v>
       </c>
       <c r="I206" s="2">
+        <v>0</v>
+      </c>
+      <c r="J206" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>500192537</t>
+          <t>500101533</t>
         </is>
       </c>
       <c r="B207" s="2">
@@ -6491,22 +7112,25 @@
         <v>0</v>
       </c>
       <c r="F207" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G207" s="2">
         <v>0</v>
       </c>
       <c r="H207" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I207" s="2">
+        <v>0</v>
+      </c>
+      <c r="J207" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>500199878</t>
+          <t>500104713</t>
         </is>
       </c>
       <c r="B208" s="2">
@@ -6522,22 +7146,25 @@
         <v>0</v>
       </c>
       <c r="F208" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G208" s="2">
         <v>0</v>
       </c>
       <c r="H208" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I208" s="2">
+        <v>0</v>
+      </c>
+      <c r="J208" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>500201947</t>
+          <t>500111404</t>
         </is>
       </c>
       <c r="B209" s="2">
@@ -6547,7 +7174,7 @@
         <v>0</v>
       </c>
       <c r="D209" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E209" s="2">
         <v>0</v>
@@ -6559,26 +7186,29 @@
         <v>0</v>
       </c>
       <c r="H209" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I209" s="2">
+        <v>0</v>
+      </c>
+      <c r="J209" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>500211718</t>
+          <t>500113054</t>
         </is>
       </c>
       <c r="B210" s="2">
         <v>0</v>
       </c>
       <c r="C210" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D210" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E210" s="2">
         <v>0</v>
@@ -6590,47 +7220,53 @@
         <v>0</v>
       </c>
       <c r="H210" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I210" s="2">
+        <v>0</v>
+      </c>
+      <c r="J210" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>500217683</t>
+          <t>500115640</t>
         </is>
       </c>
       <c r="B211" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C211" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D211" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E211" s="2">
         <v>0</v>
       </c>
       <c r="F211" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G211" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H211" s="2">
         <v>0</v>
       </c>
       <c r="I211" s="2">
+        <v>0</v>
+      </c>
+      <c r="J211" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>500219602</t>
+          <t>500117284</t>
         </is>
       </c>
       <c r="B212" s="2">
@@ -6640,7 +7276,7 @@
         <v>0</v>
       </c>
       <c r="D212" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E212" s="2">
         <v>0</v>
@@ -6652,26 +7288,29 @@
         <v>0</v>
       </c>
       <c r="H212" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I212" s="2">
+        <v>0</v>
+      </c>
+      <c r="J212" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>500235468</t>
+          <t>500120216</t>
         </is>
       </c>
       <c r="B213" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C213" s="2">
         <v>0</v>
       </c>
       <c r="D213" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E213" s="2">
         <v>0</v>
@@ -6680,26 +7319,29 @@
         <v>0</v>
       </c>
       <c r="G213" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H213" s="2">
         <v>0</v>
       </c>
       <c r="I213" s="2">
+        <v>0</v>
+      </c>
+      <c r="J213" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>500236829</t>
+          <t>500120286</t>
         </is>
       </c>
       <c r="B214" s="2">
         <v>0</v>
       </c>
       <c r="C214" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D214" s="2">
         <v>0</v>
@@ -6718,22 +7360,25 @@
       </c>
       <c r="I214" s="2">
         <v>0</v>
+      </c>
+      <c r="J214" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>500240447</t>
+          <t>500126621</t>
         </is>
       </c>
       <c r="B215" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C215" s="2">
         <v>0</v>
       </c>
       <c r="D215" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E215" s="2">
         <v>0</v>
@@ -6742,26 +7387,29 @@
         <v>0</v>
       </c>
       <c r="G215" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H215" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I215" s="2">
+        <v>0</v>
+      </c>
+      <c r="J215" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>500241388</t>
+          <t>500127435</t>
         </is>
       </c>
       <c r="B216" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C216" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D216" s="2">
         <v>0</v>
@@ -6770,26 +7418,29 @@
         <v>0</v>
       </c>
       <c r="F216" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G216" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H216" s="2">
         <v>0</v>
       </c>
       <c r="I216" s="2">
+        <v>0</v>
+      </c>
+      <c r="J216" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>500255345</t>
+          <t>500128032</t>
         </is>
       </c>
       <c r="B217" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C217" s="2">
         <v>0</v>
@@ -6798,10 +7449,10 @@
         <v>0</v>
       </c>
       <c r="E217" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F217" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G217" s="2">
         <v>0</v>
@@ -6810,13 +7461,16 @@
         <v>0</v>
       </c>
       <c r="I217" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J217" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>500255732</t>
+          <t>500128657</t>
         </is>
       </c>
       <c r="B218" s="2">
@@ -6832,7 +7486,7 @@
         <v>0</v>
       </c>
       <c r="F218" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G218" s="2">
         <v>0</v>
@@ -6841,13 +7495,16 @@
         <v>0</v>
       </c>
       <c r="I218" s="2">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J218" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>500258101</t>
+          <t>500128699</t>
         </is>
       </c>
       <c r="B219" s="2">
@@ -6860,7 +7517,7 @@
         <v>0</v>
       </c>
       <c r="E219" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F219" s="2">
         <v>0</v>
@@ -6869,29 +7526,32 @@
         <v>0</v>
       </c>
       <c r="H219" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I219" s="2">
+        <v>0</v>
+      </c>
+      <c r="J219" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>500272158</t>
+          <t>500143502</t>
         </is>
       </c>
       <c r="B220" s="2">
         <v>0</v>
       </c>
       <c r="C220" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D220" s="2">
         <v>0</v>
       </c>
       <c r="E220" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F220" s="2">
         <v>0</v>
@@ -6903,17 +7563,20 @@
         <v>0</v>
       </c>
       <c r="I220" s="2">
+        <v>0</v>
+      </c>
+      <c r="J220" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>500274670</t>
+          <t>500143882</t>
         </is>
       </c>
       <c r="B221" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C221" s="2">
         <v>0</v>
@@ -6928,19 +7591,22 @@
         <v>0</v>
       </c>
       <c r="G221" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H221" s="2">
         <v>0</v>
       </c>
       <c r="I221" s="2">
+        <v>0</v>
+      </c>
+      <c r="J221" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>500284150</t>
+          <t>500146241</t>
         </is>
       </c>
       <c r="B222" s="2">
@@ -6956,57 +7622,811 @@
         <v>0</v>
       </c>
       <c r="F222" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G222" s="2">
         <v>0</v>
       </c>
       <c r="H222" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I222" s="2">
         <v>0</v>
+      </c>
+      <c r="J222" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
+          <t>500146800</t>
+        </is>
+      </c>
+      <c r="B223" s="2">
+        <v>1</v>
+      </c>
+      <c r="C223" s="2">
+        <v>0</v>
+      </c>
+      <c r="D223" s="2">
+        <v>0</v>
+      </c>
+      <c r="E223" s="2">
+        <v>0</v>
+      </c>
+      <c r="F223" s="2">
+        <v>0</v>
+      </c>
+      <c r="G223" s="2">
+        <v>1</v>
+      </c>
+      <c r="H223" s="2">
+        <v>0</v>
+      </c>
+      <c r="I223" s="2">
+        <v>0</v>
+      </c>
+      <c r="J223" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>500148890</t>
+        </is>
+      </c>
+      <c r="B224" s="2">
+        <v>0</v>
+      </c>
+      <c r="C224" s="2">
+        <v>0</v>
+      </c>
+      <c r="D224" s="2">
+        <v>0</v>
+      </c>
+      <c r="E224" s="2">
+        <v>0</v>
+      </c>
+      <c r="F224" s="2">
+        <v>0</v>
+      </c>
+      <c r="G224" s="2">
+        <v>0</v>
+      </c>
+      <c r="H224" s="2">
+        <v>1</v>
+      </c>
+      <c r="I224" s="2">
+        <v>0</v>
+      </c>
+      <c r="J224" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>500185891</t>
+        </is>
+      </c>
+      <c r="B225" s="2">
+        <v>1</v>
+      </c>
+      <c r="C225" s="2">
+        <v>1</v>
+      </c>
+      <c r="D225" s="2">
+        <v>0</v>
+      </c>
+      <c r="E225" s="2">
+        <v>0</v>
+      </c>
+      <c r="F225" s="2">
+        <v>0</v>
+      </c>
+      <c r="G225" s="2">
+        <v>0</v>
+      </c>
+      <c r="H225" s="2">
+        <v>0</v>
+      </c>
+      <c r="I225" s="2">
+        <v>0</v>
+      </c>
+      <c r="J225" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>500186481</t>
+        </is>
+      </c>
+      <c r="B226" s="2">
+        <v>0</v>
+      </c>
+      <c r="C226" s="2">
+        <v>0</v>
+      </c>
+      <c r="D226" s="2">
+        <v>0</v>
+      </c>
+      <c r="E226" s="2">
+        <v>0</v>
+      </c>
+      <c r="F226" s="2">
+        <v>0</v>
+      </c>
+      <c r="G226" s="2">
+        <v>1</v>
+      </c>
+      <c r="H226" s="2">
+        <v>0</v>
+      </c>
+      <c r="I226" s="2">
+        <v>0</v>
+      </c>
+      <c r="J226" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>500187931</t>
+        </is>
+      </c>
+      <c r="B227" s="2">
+        <v>0</v>
+      </c>
+      <c r="C227" s="2">
+        <v>1</v>
+      </c>
+      <c r="D227" s="2">
+        <v>0</v>
+      </c>
+      <c r="E227" s="2">
+        <v>0</v>
+      </c>
+      <c r="F227" s="2">
+        <v>0</v>
+      </c>
+      <c r="G227" s="2">
+        <v>0</v>
+      </c>
+      <c r="H227" s="2">
+        <v>0</v>
+      </c>
+      <c r="I227" s="2">
+        <v>0</v>
+      </c>
+      <c r="J227" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>500192537</t>
+        </is>
+      </c>
+      <c r="B228" s="2">
+        <v>0</v>
+      </c>
+      <c r="C228" s="2">
+        <v>0</v>
+      </c>
+      <c r="D228" s="2">
+        <v>0</v>
+      </c>
+      <c r="E228" s="2">
+        <v>0</v>
+      </c>
+      <c r="F228" s="2">
+        <v>0</v>
+      </c>
+      <c r="G228" s="2">
+        <v>0</v>
+      </c>
+      <c r="H228" s="2">
+        <v>1</v>
+      </c>
+      <c r="I228" s="2">
+        <v>0</v>
+      </c>
+      <c r="J228" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>500199878</t>
+        </is>
+      </c>
+      <c r="B229" s="2">
+        <v>0</v>
+      </c>
+      <c r="C229" s="2">
+        <v>0</v>
+      </c>
+      <c r="D229" s="2">
+        <v>0</v>
+      </c>
+      <c r="E229" s="2">
+        <v>0</v>
+      </c>
+      <c r="F229" s="2">
+        <v>1</v>
+      </c>
+      <c r="G229" s="2">
+        <v>0</v>
+      </c>
+      <c r="H229" s="2">
+        <v>0</v>
+      </c>
+      <c r="I229" s="2">
+        <v>0</v>
+      </c>
+      <c r="J229" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>500201947</t>
+        </is>
+      </c>
+      <c r="B230" s="2">
+        <v>0</v>
+      </c>
+      <c r="C230" s="2">
+        <v>0</v>
+      </c>
+      <c r="D230" s="2">
+        <v>0</v>
+      </c>
+      <c r="E230" s="2">
+        <v>0</v>
+      </c>
+      <c r="F230" s="2">
+        <v>0</v>
+      </c>
+      <c r="G230" s="2">
+        <v>0</v>
+      </c>
+      <c r="H230" s="2">
+        <v>1</v>
+      </c>
+      <c r="I230" s="2">
+        <v>0</v>
+      </c>
+      <c r="J230" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>500211718</t>
+        </is>
+      </c>
+      <c r="B231" s="2">
+        <v>0</v>
+      </c>
+      <c r="C231" s="2">
+        <v>1</v>
+      </c>
+      <c r="D231" s="2">
+        <v>2</v>
+      </c>
+      <c r="E231" s="2">
+        <v>0</v>
+      </c>
+      <c r="F231" s="2">
+        <v>0</v>
+      </c>
+      <c r="G231" s="2">
+        <v>0</v>
+      </c>
+      <c r="H231" s="2">
+        <v>0</v>
+      </c>
+      <c r="I231" s="2">
+        <v>0</v>
+      </c>
+      <c r="J231" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>500217683</t>
+        </is>
+      </c>
+      <c r="B232" s="2">
+        <v>0</v>
+      </c>
+      <c r="C232" s="2">
+        <v>1</v>
+      </c>
+      <c r="D232" s="2">
+        <v>1</v>
+      </c>
+      <c r="E232" s="2">
+        <v>0</v>
+      </c>
+      <c r="F232" s="2">
+        <v>0</v>
+      </c>
+      <c r="G232" s="2">
+        <v>1</v>
+      </c>
+      <c r="H232" s="2">
+        <v>0</v>
+      </c>
+      <c r="I232" s="2">
+        <v>0</v>
+      </c>
+      <c r="J232" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>500219602</t>
+        </is>
+      </c>
+      <c r="B233" s="2">
+        <v>0</v>
+      </c>
+      <c r="C233" s="2">
+        <v>0</v>
+      </c>
+      <c r="D233" s="2">
+        <v>0</v>
+      </c>
+      <c r="E233" s="2">
+        <v>0</v>
+      </c>
+      <c r="F233" s="2">
+        <v>0</v>
+      </c>
+      <c r="G233" s="2">
+        <v>0</v>
+      </c>
+      <c r="H233" s="2">
+        <v>1</v>
+      </c>
+      <c r="I233" s="2">
+        <v>0</v>
+      </c>
+      <c r="J233" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>500232043</t>
+        </is>
+      </c>
+      <c r="B234" s="2">
+        <v>0</v>
+      </c>
+      <c r="C234" s="2">
+        <v>0</v>
+      </c>
+      <c r="D234" s="2">
+        <v>0</v>
+      </c>
+      <c r="E234" s="2">
+        <v>0</v>
+      </c>
+      <c r="F234" s="2">
+        <v>0</v>
+      </c>
+      <c r="G234" s="2">
+        <v>0</v>
+      </c>
+      <c r="H234" s="2">
+        <v>0</v>
+      </c>
+      <c r="I234" s="2">
+        <v>0</v>
+      </c>
+      <c r="J234" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>500235468</t>
+        </is>
+      </c>
+      <c r="B235" s="2">
+        <v>0</v>
+      </c>
+      <c r="C235" s="2">
+        <v>0</v>
+      </c>
+      <c r="D235" s="2">
+        <v>0</v>
+      </c>
+      <c r="E235" s="2">
+        <v>0</v>
+      </c>
+      <c r="F235" s="2">
+        <v>0</v>
+      </c>
+      <c r="G235" s="2">
+        <v>1</v>
+      </c>
+      <c r="H235" s="2">
+        <v>0</v>
+      </c>
+      <c r="I235" s="2">
+        <v>0</v>
+      </c>
+      <c r="J235" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>500236829</t>
+        </is>
+      </c>
+      <c r="B236" s="2">
+        <v>0</v>
+      </c>
+      <c r="C236" s="2">
+        <v>1</v>
+      </c>
+      <c r="D236" s="2">
+        <v>0</v>
+      </c>
+      <c r="E236" s="2">
+        <v>0</v>
+      </c>
+      <c r="F236" s="2">
+        <v>0</v>
+      </c>
+      <c r="G236" s="2">
+        <v>0</v>
+      </c>
+      <c r="H236" s="2">
+        <v>0</v>
+      </c>
+      <c r="I236" s="2">
+        <v>0</v>
+      </c>
+      <c r="J236" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>500240447</t>
+        </is>
+      </c>
+      <c r="B237" s="2">
+        <v>1</v>
+      </c>
+      <c r="C237" s="2">
+        <v>0</v>
+      </c>
+      <c r="D237" s="2">
+        <v>0</v>
+      </c>
+      <c r="E237" s="2">
+        <v>0</v>
+      </c>
+      <c r="F237" s="2">
+        <v>0</v>
+      </c>
+      <c r="G237" s="2">
+        <v>0</v>
+      </c>
+      <c r="H237" s="2">
+        <v>1</v>
+      </c>
+      <c r="I237" s="2">
+        <v>0</v>
+      </c>
+      <c r="J237" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>500241388</t>
+        </is>
+      </c>
+      <c r="B238" s="2">
+        <v>1</v>
+      </c>
+      <c r="C238" s="2">
+        <v>1</v>
+      </c>
+      <c r="D238" s="2">
+        <v>0</v>
+      </c>
+      <c r="E238" s="2">
+        <v>0</v>
+      </c>
+      <c r="F238" s="2">
+        <v>1</v>
+      </c>
+      <c r="G238" s="2">
+        <v>0</v>
+      </c>
+      <c r="H238" s="2">
+        <v>0</v>
+      </c>
+      <c r="I238" s="2">
+        <v>0</v>
+      </c>
+      <c r="J238" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>500255345</t>
+        </is>
+      </c>
+      <c r="B239" s="2">
+        <v>1</v>
+      </c>
+      <c r="C239" s="2">
+        <v>0</v>
+      </c>
+      <c r="D239" s="2">
+        <v>0</v>
+      </c>
+      <c r="E239" s="2">
+        <v>1</v>
+      </c>
+      <c r="F239" s="2">
+        <v>0</v>
+      </c>
+      <c r="G239" s="2">
+        <v>0</v>
+      </c>
+      <c r="H239" s="2">
+        <v>0</v>
+      </c>
+      <c r="I239" s="2">
+        <v>1</v>
+      </c>
+      <c r="J239" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>500255732</t>
+        </is>
+      </c>
+      <c r="B240" s="2">
+        <v>0</v>
+      </c>
+      <c r="C240" s="2">
+        <v>0</v>
+      </c>
+      <c r="D240" s="2">
+        <v>0</v>
+      </c>
+      <c r="E240" s="2">
+        <v>0</v>
+      </c>
+      <c r="F240" s="2">
+        <v>0</v>
+      </c>
+      <c r="G240" s="2">
+        <v>0</v>
+      </c>
+      <c r="H240" s="2">
+        <v>0</v>
+      </c>
+      <c r="I240" s="2">
+        <v>1</v>
+      </c>
+      <c r="J240" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>500258101</t>
+        </is>
+      </c>
+      <c r="B241" s="2">
+        <v>0</v>
+      </c>
+      <c r="C241" s="2">
+        <v>0</v>
+      </c>
+      <c r="D241" s="2">
+        <v>0</v>
+      </c>
+      <c r="E241" s="2">
+        <v>1</v>
+      </c>
+      <c r="F241" s="2">
+        <v>0</v>
+      </c>
+      <c r="G241" s="2">
+        <v>0</v>
+      </c>
+      <c r="H241" s="2">
+        <v>0</v>
+      </c>
+      <c r="I241" s="2">
+        <v>0</v>
+      </c>
+      <c r="J241" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>500272158</t>
+        </is>
+      </c>
+      <c r="B242" s="2">
+        <v>0</v>
+      </c>
+      <c r="C242" s="2">
+        <v>0</v>
+      </c>
+      <c r="D242" s="2">
+        <v>0</v>
+      </c>
+      <c r="E242" s="2">
+        <v>1</v>
+      </c>
+      <c r="F242" s="2">
+        <v>0</v>
+      </c>
+      <c r="G242" s="2">
+        <v>0</v>
+      </c>
+      <c r="H242" s="2">
+        <v>0</v>
+      </c>
+      <c r="I242" s="2">
+        <v>0</v>
+      </c>
+      <c r="J242" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>500274670</t>
+        </is>
+      </c>
+      <c r="B243" s="2">
+        <v>0</v>
+      </c>
+      <c r="C243" s="2">
+        <v>0</v>
+      </c>
+      <c r="D243" s="2">
+        <v>0</v>
+      </c>
+      <c r="E243" s="2">
+        <v>0</v>
+      </c>
+      <c r="F243" s="2">
+        <v>0</v>
+      </c>
+      <c r="G243" s="2">
+        <v>1</v>
+      </c>
+      <c r="H243" s="2">
+        <v>0</v>
+      </c>
+      <c r="I243" s="2">
+        <v>0</v>
+      </c>
+      <c r="J243" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>500284150</t>
+        </is>
+      </c>
+      <c r="B244" s="2">
+        <v>0</v>
+      </c>
+      <c r="C244" s="2">
+        <v>0</v>
+      </c>
+      <c r="D244" s="2">
+        <v>0</v>
+      </c>
+      <c r="E244" s="2">
+        <v>0</v>
+      </c>
+      <c r="F244" s="2">
+        <v>1</v>
+      </c>
+      <c r="G244" s="2">
+        <v>0</v>
+      </c>
+      <c r="H244" s="2">
+        <v>0</v>
+      </c>
+      <c r="I244" s="2">
+        <v>0</v>
+      </c>
+      <c r="J244" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
           <t>500286107</t>
         </is>
       </c>
-      <c r="B223" s="2">
-        <v>0</v>
-      </c>
-      <c r="C223" s="2">
-        <v>0</v>
-      </c>
-      <c r="D223" s="2">
-        <v>0</v>
-      </c>
-      <c r="E223" s="2">
-        <v>0</v>
-      </c>
-      <c r="F223" s="2">
-        <v>0</v>
-      </c>
-      <c r="G223" s="2">
-        <v>0</v>
-      </c>
-      <c r="H223" s="2">
-        <v>1</v>
-      </c>
-      <c r="I223" s="2">
+      <c r="B245" s="2">
+        <v>0</v>
+      </c>
+      <c r="C245" s="2">
+        <v>0</v>
+      </c>
+      <c r="D245" s="2">
+        <v>0</v>
+      </c>
+      <c r="E245" s="2">
+        <v>0</v>
+      </c>
+      <c r="F245" s="2">
+        <v>0</v>
+      </c>
+      <c r="G245" s="2">
+        <v>0</v>
+      </c>
+      <c r="H245" s="2">
+        <v>1</v>
+      </c>
+      <c r="I245" s="2">
+        <v>0</v>
+      </c>
+      <c r="J245" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I223"/>
+  <autoFilter ref="A1:J245"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q325"/>
+  <dimension ref="A1:Q364"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -30766,7 +32186,2854 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>100136792</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>13243547720</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>[슈퍼적립] 매일두유 99.9 서리태 190ML 24팩 [+99.9 플레인 6팩 추가 증정] [포토리뷰 2,000원]</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G326" s="2">
+        <v>17900</v>
+      </c>
+      <c r="H326" s="2">
+        <v>33600</v>
+      </c>
+      <c r="I326" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13243547720</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260423_106/1776926537598lUW9R_JPEG/34409557365863491_1919931895.jpg</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N326" s="2">
+        <v>1</v>
+      </c>
+      <c r="O326" s="2">
+        <v>0</v>
+      </c>
+      <c r="P326" s="2">
+        <v>17900</v>
+      </c>
+      <c r="Q326" s="3">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>100200351</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>4072544295</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>브레드이발소X닥터바이오 1시간 라이브, ~57% OFFㅣ닥터바이오 가려움개선 고보습 로션,워시,샴푸,크림 등 모음전 특가</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>뷰티/헬스</t>
+        </is>
+      </c>
+      <c r="G327" s="2">
+        <v>16900</v>
+      </c>
+      <c r="H327" s="2">
+        <v>158000</v>
+      </c>
+      <c r="I327" s="3">
+        <v>0.89</v>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/4072544295</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260427_50/1777252291123IwSCg_JPEG/57165100990800941_448565709.jpg</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N327" s="2">
+        <v>1</v>
+      </c>
+      <c r="O327" s="2">
+        <v>0</v>
+      </c>
+      <c r="P327" s="2">
+        <v>16900</v>
+      </c>
+      <c r="Q327" s="3">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>100259128</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>10413773394</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>발란스핏 EMS 슬림 벨트 / 초강력 간편 홈트레이닝 뱃살 강력 자극 &amp; 복부 온열 찜질</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G328" s="2">
+        <v>95800</v>
+      </c>
+      <c r="H328" s="2">
+        <v>179000</v>
+      </c>
+      <c r="I328" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10413773394</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260427_99/1777255975754VaROX_JPEG/11152998761460281_1723403306.jpg</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N328" s="2">
+        <v>1</v>
+      </c>
+      <c r="O328" s="2">
+        <v>0</v>
+      </c>
+      <c r="P328" s="2">
+        <v>95800</v>
+      </c>
+      <c r="Q328" s="3">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>100368280</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>6540487975</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>26년 햇블루베리 국내산 무농약 끝달림 블루베리 생블루베리 생과 점보</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G329" s="2">
+        <v>24900</v>
+      </c>
+      <c r="H329" s="2">
+        <v>49800</v>
+      </c>
+      <c r="I329" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/6540487975</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20220428_121/16511356475725D8ES_JPEG/52271475307941281_252680570.jpg</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N329" s="2">
+        <v>1</v>
+      </c>
+      <c r="O329" s="2">
+        <v>0</v>
+      </c>
+      <c r="P329" s="2">
+        <v>24900</v>
+      </c>
+      <c r="Q329" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>스페셜 체험딜</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>100369232</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>13243679894</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>[쇼핑백 증정] 원씽 나이아신아마이드 글루타치온 미스트 100ml, 1개</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G330" s="2">
+        <v>1990</v>
+      </c>
+      <c r="H330" s="2">
+        <v>24000</v>
+      </c>
+      <c r="I330" s="3">
+        <v>0.91</v>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13243679894</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260331_73/1774944927283meChi_JPEG/20902001084669632_2095854744.jpg</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N330" s="2">
+        <v>1</v>
+      </c>
+      <c r="O330" s="2">
+        <v>0</v>
+      </c>
+      <c r="P330" s="2">
+        <v>1990</v>
+      </c>
+      <c r="Q330" s="3">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>스페셜 멤버십</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>100437155</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>8248458988</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>[4/27스페셜딜][본사직영] 이즈니 생메르 냉동 비가염 버터 컵 10g x 60개 외 6종 버터컵 가염</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G331" s="2">
+        <v>26900</v>
+      </c>
+      <c r="H331" s="2">
+        <v>49900</v>
+      </c>
+      <c r="I331" s="3">
+        <v>0.46</v>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/8248458988</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260115_95/1768443746178MOXqn_PNG/55642352985904703_978871921.png</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N331" s="2">
+        <v>1</v>
+      </c>
+      <c r="O331" s="2">
+        <v>0</v>
+      </c>
+      <c r="P331" s="2">
+        <v>26900</v>
+      </c>
+      <c r="Q331" s="3">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>100449673</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>10957313676</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>[네이버단독] 정관장 에브리타임 샷 20ml 50개입</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G332" s="2">
+        <v>119000</v>
+      </c>
+      <c r="H332" s="2">
+        <v>142000</v>
+      </c>
+      <c r="I332" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10957313676</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260427_122/1777215663432uMbuW_JPEG/49183153520315173_1986035540.jpg</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N332" s="2">
+        <v>1</v>
+      </c>
+      <c r="O332" s="2">
+        <v>0</v>
+      </c>
+      <c r="P332" s="2">
+        <v>119000</v>
+      </c>
+      <c r="Q332" s="3">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>100791832</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>5550612484</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>제스프리 썬골드 키위 1.7kg, 2.6kg</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G333" s="2">
+        <v>15900</v>
+      </c>
+      <c r="H333" s="2">
+        <v>24800</v>
+      </c>
+      <c r="I333" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5550612484</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20230518_104/1684377164311DnmkA_JPEG/3889253312542448_1144238010.jpg</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N333" s="2">
+        <v>1</v>
+      </c>
+      <c r="O333" s="2">
+        <v>0</v>
+      </c>
+      <c r="P333" s="2">
+        <v>15900</v>
+      </c>
+      <c r="Q333" s="3">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>100903790</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>5165467725</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>엔하이픈PICK 리스테린 가글 구강청결제 입냄새제거 쿨민트 1L, 3개</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G334" s="2">
+        <v>20200</v>
+      </c>
+      <c r="H334" s="2">
+        <v>35700</v>
+      </c>
+      <c r="I334" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5165467725</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260419_241/1776606142853vknWr_JPEG/110739021366709729_776767311.jpg</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N334" s="2">
+        <v>1</v>
+      </c>
+      <c r="O334" s="2">
+        <v>0</v>
+      </c>
+      <c r="P334" s="2">
+        <v>20200</v>
+      </c>
+      <c r="Q334" s="3">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>스페셜 멤버십</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>100937343</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>13030417556</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>[시크릿]트레비 무라벨 350ml 40펫 4종</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>육아/반려</t>
+        </is>
+      </c>
+      <c r="G335" s="2">
+        <v>22800</v>
+      </c>
+      <c r="H335" s="2">
+        <v>23800</v>
+      </c>
+      <c r="I335" s="3">
+        <v>0.04</v>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13030417556</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20230425_236/1682383961078K1J7H_JPEG/20464818206925391_27249905.jpg</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N335" s="2">
+        <v>1</v>
+      </c>
+      <c r="O335" s="2">
+        <v>0</v>
+      </c>
+      <c r="P335" s="2">
+        <v>22800</v>
+      </c>
+      <c r="Q335" s="3">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>100938809</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>11725805814</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>[대림시장 명물식] 감자국 거리 명물 착한 응암동 감자탕 괴물용량 5KG</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G336" s="2">
+        <v>18900</v>
+      </c>
+      <c r="H336" s="2">
+        <v>33900</v>
+      </c>
+      <c r="I336" s="3">
+        <v>0.44</v>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11725805814</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260424_299/17770044688580xWg8_PNG/111137347390789254_769806065.png</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N336" s="2">
+        <v>1</v>
+      </c>
+      <c r="O336" s="2">
+        <v>0</v>
+      </c>
+      <c r="P336" s="2">
+        <v>18900</v>
+      </c>
+      <c r="Q336" s="3">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>100945557</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>5237747764</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>더바른 카스테라인절미 호박떡 1box 떡선물</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G337" s="2">
+        <v>12900</v>
+      </c>
+      <c r="H337" s="2">
+        <v>16400</v>
+      </c>
+      <c r="I337" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5237747764</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250511_66/1746959098309jAvDT_JPEG/73542297125281804_660459752.jpg</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N337" s="2">
+        <v>1</v>
+      </c>
+      <c r="O337" s="2">
+        <v>0</v>
+      </c>
+      <c r="P337" s="2">
+        <v>12900</v>
+      </c>
+      <c r="Q337" s="3">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>100969228</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>10718647050</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>[4개월분] 락티브 미오이노시톨 앤 콜린 엽산 비타민c 비타민d 30포, 4개</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>뷰티/헬스</t>
+        </is>
+      </c>
+      <c r="G338" s="2">
+        <v>117000</v>
+      </c>
+      <c r="H338" s="2">
+        <v>196000</v>
+      </c>
+      <c r="I338" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10718647050</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250321_9/1742539352969mycAa_JPEG/90208177749712579_1089669545.jpg</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N338" s="2">
+        <v>1</v>
+      </c>
+      <c r="O338" s="2">
+        <v>0</v>
+      </c>
+      <c r="P338" s="2">
+        <v>117000</v>
+      </c>
+      <c r="Q338" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>100984156</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>7106569186</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>[3박스★NEW낮밤밤맥]하기스 2025 네이처메이드 밤부 2박스 5단계(44매x4팩)남아 팬티형+맥스드라이 1박스 2단계(76매x2팩)공용 팬티형</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G339" s="2">
+        <v>187500</v>
+      </c>
+      <c r="H339" s="2">
+        <v>332400</v>
+      </c>
+      <c r="I339" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/7106569186</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250929_129/1759075092584kxs5X_JPEG/93207931709346345_628958657.jpg</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N339" s="2">
+        <v>1</v>
+      </c>
+      <c r="O339" s="2">
+        <v>0</v>
+      </c>
+      <c r="P339" s="2">
+        <v>187500</v>
+      </c>
+      <c r="Q339" s="3">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>100997360</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>5279251727</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>좋은느낌 입는 오버나이트 8매 X 3팩 / 입는생리대</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G340" s="2">
+        <v>20000</v>
+      </c>
+      <c r="H340" s="2">
+        <v>38100</v>
+      </c>
+      <c r="I340" s="3">
+        <v>0.47</v>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5279251727</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251002_66/1759380443827WVdgz_JPEG/5337517520662830_516072966.jpg</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N340" s="2">
+        <v>1</v>
+      </c>
+      <c r="O340" s="2">
+        <v>0</v>
+      </c>
+      <c r="P340" s="2">
+        <v>20000</v>
+      </c>
+      <c r="Q340" s="3">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>101015607</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>5684175077</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>멀티비타민 오쏘몰 이뮨 비타민 7입x4개+2입 (총 30일분) 이뮨샷</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>뷰티/헬스</t>
+        </is>
+      </c>
+      <c r="G341" s="2">
+        <v>69700</v>
+      </c>
+      <c r="H341" s="2">
+        <v>129000</v>
+      </c>
+      <c r="I341" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5684175077</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260330_13/1774855850285SL8qk_JPEG/29404241553422235_505112938.jpg</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N341" s="2">
+        <v>1</v>
+      </c>
+      <c r="O341" s="2">
+        <v>0</v>
+      </c>
+      <c r="P341" s="2">
+        <v>69700</v>
+      </c>
+      <c r="Q341" s="3">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>101020603</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>11646420884</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>마지막 [대저토마토 2.5kg 2L-2S 랜덤] 맛있는 가락시장</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G342" s="2">
+        <v>9750</v>
+      </c>
+      <c r="H342" s="2">
+        <v>15000</v>
+      </c>
+      <c r="I342" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11646420884</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260321_150/1774085263327Qgpv6_JPEG/121416137738233635_1559006722.jpg</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N342" s="2">
+        <v>1</v>
+      </c>
+      <c r="O342" s="2">
+        <v>0</v>
+      </c>
+      <c r="P342" s="2">
+        <v>9750</v>
+      </c>
+      <c r="Q342" s="3">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>101058434</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>12276347067</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>[빅웨이브] 피스어게인 그래픽 후드집업 (라이트 슬레이트)</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G343" s="2">
+        <v>87200</v>
+      </c>
+      <c r="H343" s="2">
+        <v>109000</v>
+      </c>
+      <c r="I343" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12276347067</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260324_158/1774331970265yB8rW_JPEG/108464814339587323_478401484.jpg</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N343" s="2">
+        <v>1</v>
+      </c>
+      <c r="O343" s="2">
+        <v>0</v>
+      </c>
+      <c r="P343" s="2">
+        <v>87200</v>
+      </c>
+      <c r="Q343" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>101214695</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>8210575442</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>1++ 등급 투뿔한우 실속 가성비 모듬구이 세트 설로인 숙성로스 이츠홈마카세</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G344" s="2">
+        <v>49900</v>
+      </c>
+      <c r="H344" s="2">
+        <v>99000</v>
+      </c>
+      <c r="I344" s="3">
+        <v>0.49</v>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/8210575442</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260318_184/1773830450638HcGBd_PNG/29110208116378881_717908595.png</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N344" s="2">
+        <v>1</v>
+      </c>
+      <c r="O344" s="2">
+        <v>0</v>
+      </c>
+      <c r="P344" s="2">
+        <v>49900</v>
+      </c>
+      <c r="Q344" s="3">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>스페셜 멤버십</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>101336693</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>13100758373</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>[네이버 단독] 더미식 당찬진미 백미밥 200g x 24개</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G345" s="2">
+        <v>20900</v>
+      </c>
+      <c r="H345" s="2">
+        <v>33000</v>
+      </c>
+      <c r="I345" s="3">
+        <v>0.36</v>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13100758373</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260303_135/17725439920970qiA1_JPEG/101905609614156143_610879329.jpg</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N345" s="2">
+        <v>1</v>
+      </c>
+      <c r="O345" s="2">
+        <v>0</v>
+      </c>
+      <c r="P345" s="2">
+        <v>20900</v>
+      </c>
+      <c r="Q345" s="3">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>101424907</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>9560539005</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>HP 오멘 16 게이밍 노트북 LM 인텔 AI 울트라 U5 RTX5060 포토샵 챗GPT</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>디지털/가전</t>
+        </is>
+      </c>
+      <c r="G346" s="2">
+        <v>1899000</v>
+      </c>
+      <c r="H346" s="2">
+        <v>2349000</v>
+      </c>
+      <c r="I346" s="3">
+        <v>0.19</v>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/9560539005</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260205_175/17702592699563QjOB_PNG/17000674036969456_236419663.png</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N346" s="2">
+        <v>1</v>
+      </c>
+      <c r="O346" s="2">
+        <v>0</v>
+      </c>
+      <c r="P346" s="2">
+        <v>1899000</v>
+      </c>
+      <c r="Q346" s="3">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>101708491</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>10408470157</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>[풀리오본사] [선물SET] 종아리 마사지기 V3 + 파우치 + 쇼핑백M</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G347" s="2">
+        <v>159000</v>
+      </c>
+      <c r="H347" s="2">
+        <v>248000</v>
+      </c>
+      <c r="I347" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10408470157</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260310_231/1773104397465J4qz4_JPEG/91668145263835517_1384509491.jpg</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N347" s="2">
+        <v>1</v>
+      </c>
+      <c r="O347" s="2">
+        <v>0</v>
+      </c>
+      <c r="P347" s="2">
+        <v>159000</v>
+      </c>
+      <c r="Q347" s="3">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>102307203</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>12941213356</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>에코센스 올트라이탄 밀폐용기 히트락 반찬통 세트 10P</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G348" s="2">
+        <v>49800</v>
+      </c>
+      <c r="H348" s="2">
+        <v>161000</v>
+      </c>
+      <c r="I348" s="3">
+        <v>0.69</v>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/12941213356</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260316_131/17736378664387PJFG_JPEG/36619599543398032_107691599.jpg</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N348" s="2">
+        <v>1</v>
+      </c>
+      <c r="O348" s="2">
+        <v>0</v>
+      </c>
+      <c r="P348" s="2">
+        <v>49800</v>
+      </c>
+      <c r="Q348" s="3">
+        <v>0.69</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>102591998</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>13209629364</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>(가정용) 참외 성주 실속 참외 랜덤또는꼬마소과, 4kg, 1개</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G349" s="2">
+        <v>15900</v>
+      </c>
+      <c r="H349" s="2">
+        <v>19900</v>
+      </c>
+      <c r="I349" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13209629364</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260306_203/1772781853055k7E6b_JPEG/18887025283255314_612192900.jpg</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N349" s="2">
+        <v>1</v>
+      </c>
+      <c r="O349" s="2">
+        <v>0</v>
+      </c>
+      <c r="P349" s="2">
+        <v>15900</v>
+      </c>
+      <c r="Q349" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>102655931</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>13380507716</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>[2개 구매 시 20%][Sea to Table] 간편 손질 오징어링 500g (냉동)</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G350" s="2">
+        <v>8200</v>
+      </c>
+      <c r="H350" s="2">
+        <v>8200</v>
+      </c>
+      <c r="I350" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13380507716</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260410_161/1775788650409tjaMT_JPEG/161133631240718_1204083633.jpg</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N350" s="2">
+        <v>1</v>
+      </c>
+      <c r="O350" s="2">
+        <v>0</v>
+      </c>
+      <c r="P350" s="2">
+        <v>8200</v>
+      </c>
+      <c r="Q350" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>102655931</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>13446989937</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>[이연복의 목란] 인기 BEST 골라담기 6종 (택2)</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G351" s="2">
+        <v>10</v>
+      </c>
+      <c r="H351" s="2">
+        <v>10</v>
+      </c>
+      <c r="I351" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13446989937</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260421_83/1776754337313SaoHh_JPEG/108319249114658301_1877947802.jpg</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N351" s="2">
+        <v>1</v>
+      </c>
+      <c r="O351" s="2">
+        <v>0</v>
+      </c>
+      <c r="P351" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q351" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>1100075478</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>13074658352</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>1996스탠다드 남성용 무지 드라이핏 하프 삭스 10켤레 세트</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G352" s="2">
+        <v>9900</v>
+      </c>
+      <c r="H352" s="2">
+        <v>16900</v>
+      </c>
+      <c r="I352" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13074658352</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260206_51/1770350867866pfOcq_JPEG/43170922007909951_1533011159.jpg</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N352" s="2">
+        <v>1</v>
+      </c>
+      <c r="O352" s="2">
+        <v>0</v>
+      </c>
+      <c r="P352" s="2">
+        <v>9900</v>
+      </c>
+      <c r="Q352" s="3">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>500000438</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>8719636951</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>산과들에 과자 간식 42봉 심쿵 간식 선물세트+쇼핑백증정 (하루견과 다크초코볼 프레첼 에너지바 미숫가루 등 어린이날가정의달선물)</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G353" s="2">
+        <v>21900</v>
+      </c>
+      <c r="H353" s="2">
+        <v>35900</v>
+      </c>
+      <c r="I353" s="3">
+        <v>0.38</v>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/8719636951</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260427_128/1777253302437dl8oT_JPEG/31771294774479109_1935072494.jpg</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N353" s="2">
+        <v>1</v>
+      </c>
+      <c r="O353" s="2">
+        <v>0</v>
+      </c>
+      <c r="P353" s="2">
+        <v>21900</v>
+      </c>
+      <c r="Q353" s="3">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>500000823</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>13197658930</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>[네이버단독] 리벤스 엔데일리 엠보싱 아기물티슈 100매, 10개</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>생활/주방</t>
+        </is>
+      </c>
+      <c r="G354" s="2">
+        <v>8900</v>
+      </c>
+      <c r="H354" s="2">
+        <v>15900</v>
+      </c>
+      <c r="I354" s="3">
+        <v>0.44</v>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13197658930</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260304_73/17726160800414LFJ6_JPEG/2616533126839838_1746768761.jpg</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N354" s="2">
+        <v>1</v>
+      </c>
+      <c r="O354" s="2">
+        <v>0</v>
+      </c>
+      <c r="P354" s="2">
+        <v>8900</v>
+      </c>
+      <c r="Q354" s="3">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>500016197</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>10285398141</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>[N배송] 더자리 시원한 큐라론 쿨파워 냉감 밴딩형 베개커버 침대패드 세트</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>생활/주방</t>
+        </is>
+      </c>
+      <c r="G355" s="2">
+        <v>45900</v>
+      </c>
+      <c r="H355" s="2">
+        <v>65900</v>
+      </c>
+      <c r="I355" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10285398141</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260327_245/1774574659663wkbUN_JPEG/43234094538912324_1900415570.jpg</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N355" s="2">
+        <v>1</v>
+      </c>
+      <c r="O355" s="2">
+        <v>0</v>
+      </c>
+      <c r="P355" s="2">
+        <v>45900</v>
+      </c>
+      <c r="Q355" s="3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>500028485</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>11746238181</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>더 빅토리아 탄산수 에코 플레인 500mL 20개 외 1종</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G356" s="2">
+        <v>13900</v>
+      </c>
+      <c r="H356" s="2">
+        <v>13900</v>
+      </c>
+      <c r="I356" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/11746238181</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251119_137/1763528161249xfi0r_PNG/97661014397174276_1234292671.png</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N356" s="2">
+        <v>1</v>
+      </c>
+      <c r="O356" s="2">
+        <v>0</v>
+      </c>
+      <c r="P356" s="2">
+        <v>13900</v>
+      </c>
+      <c r="Q356" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>500028485</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>13325758120</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>[쯔양 PICK] 초록매실 제로 500mL 12개+티즐 제로 자몽블랙티 500mL 12개</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G357" s="2">
+        <v>20900</v>
+      </c>
+      <c r="H357" s="2">
+        <v>28900</v>
+      </c>
+      <c r="I357" s="3">
+        <v>0.27</v>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13325758120</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260420_168/1776675754268S3yaF_JPEG/124006628713104034_1494967832.jpg</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N357" s="2">
+        <v>1</v>
+      </c>
+      <c r="O357" s="2">
+        <v>0</v>
+      </c>
+      <c r="P357" s="2">
+        <v>20900</v>
+      </c>
+      <c r="Q357" s="3">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>500070063</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>10337174622</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>오아 에어리소닉 BLDC 플라즈마 헤어 드라이기 항공모터 고속 드라이어 음이온 저소음</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G358" s="2">
+        <v>64800</v>
+      </c>
+      <c r="H358" s="2">
+        <v>78000</v>
+      </c>
+      <c r="I358" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10337174622</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20241018_58/1729230938356k4QES_JPEG/63363902469715594_149269062.jpg</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N358" s="2">
+        <v>1</v>
+      </c>
+      <c r="O358" s="2">
+        <v>0</v>
+      </c>
+      <c r="P358" s="2">
+        <v>64800</v>
+      </c>
+      <c r="Q358" s="3">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>500091839</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>6876806179</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>[오늘끝딜] 다신샵 국산쌀로 만든 저당 현미 주먹밥 10종 30팩 / 현미밥 곤약밥 냉동 김치치즈</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G359" s="2">
+        <v>35900</v>
+      </c>
+      <c r="H359" s="2">
+        <v>84000</v>
+      </c>
+      <c r="I359" s="3">
+        <v>0.57</v>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/6876806179</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20251205_173/1764921890513wBpG9_PNG/19884904716514760_172853450.png</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N359" s="2">
+        <v>1</v>
+      </c>
+      <c r="O359" s="2">
+        <v>0</v>
+      </c>
+      <c r="P359" s="2">
+        <v>35900</v>
+      </c>
+      <c r="Q359" s="3">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>500120286</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>5473386730</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>25년 무농약 영암 세척 꿀고구마 3kg 5kg 베니하루카 황금호박</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G360" s="2">
+        <v>14900</v>
+      </c>
+      <c r="H360" s="2">
+        <v>24000</v>
+      </c>
+      <c r="I360" s="3">
+        <v>0.37</v>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/5473386730</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20231204_13/17016622244519OuLp_JPEG/21159903271245273_1270107573.jpg</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N360" s="2">
+        <v>1</v>
+      </c>
+      <c r="O360" s="2">
+        <v>0</v>
+      </c>
+      <c r="P360" s="2">
+        <v>14900</v>
+      </c>
+      <c r="Q360" s="3">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>500146241</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>10909517544</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>[4/27스페셜딜][슈퍼적립][1+1] 투다리 시그니처 김치우동 2인분 x 2팩 (총 4인분)</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>식품/음료</t>
+        </is>
+      </c>
+      <c r="G361" s="2">
+        <v>21900</v>
+      </c>
+      <c r="H361" s="2">
+        <v>31960</v>
+      </c>
+      <c r="I361" s="3">
+        <v>0.31</v>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/10909517544</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250910_235/17574650204522HXxJ_PNG/91597930563879788_1563086513.png</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N361" s="2">
+        <v>1</v>
+      </c>
+      <c r="O361" s="2">
+        <v>0</v>
+      </c>
+      <c r="P361" s="2">
+        <v>21900</v>
+      </c>
+      <c r="Q361" s="3">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>500146241</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>8496319934</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>[4/27스페셜딜][1+1]하코야 살얼음동동 오리지널 냉메밀소바 2인분 2팩 (총 4인분) 외 (소비기한 2026-05-26)</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G362" s="2">
+        <v>10900</v>
+      </c>
+      <c r="H362" s="2">
+        <v>21800</v>
+      </c>
+      <c r="I362" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/8496319934</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20250909_173/1757405144424Hrlo8_PNG/69094432475484976_1001629758.png</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N362" s="2">
+        <v>1</v>
+      </c>
+      <c r="O362" s="2">
+        <v>0</v>
+      </c>
+      <c r="P362" s="2">
+        <v>10900</v>
+      </c>
+      <c r="Q362" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>스페셜딜</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>500146800</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>4592947042</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>[슈퍼적립] 이클립스 페퍼민트+워터멜론+피치+스트로베리 4종 각2개 (총 8개입)</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G363" s="2">
+        <v>16500</v>
+      </c>
+      <c r="H363" s="2">
+        <v>18400</v>
+      </c>
+      <c r="I363" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/4592947042</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260331_196/1774921896984Xa0h7_JPEG/24168164706050423_115770836.jpg</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N363" s="2">
+        <v>1</v>
+      </c>
+      <c r="O363" s="2">
+        <v>0</v>
+      </c>
+      <c r="P363" s="2">
+        <v>16500</v>
+      </c>
+      <c r="Q363" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>스페셜 멤버십</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>500232043</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>13358931834</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>쿠캣메이드 상하이 버터쫀득 120g (4입) X 2팩</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="G364" s="2">
+        <v>16900</v>
+      </c>
+      <c r="H364" s="2">
+        <v>21900</v>
+      </c>
+      <c r="I364" s="3">
+        <v>0.22</v>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/main/products/13358931834</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>https://shop-phinf.pstatic.net/20260406_67/1775436413759xqlHQ_JPEG/33814510017810832_553282658.jpg</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="N364" s="2">
+        <v>1</v>
+      </c>
+      <c r="O364" s="2">
+        <v>0</v>
+      </c>
+      <c r="P364" s="2">
+        <v>16900</v>
+      </c>
+      <c r="Q364" s="3">
+        <v>0.22</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q325"/>
+  <autoFilter ref="A1:Q364"/>
 </worksheet>
 </file>